--- a/MASTER.xlsx
+++ b/MASTER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Javid Shiriyev\Documents\GitHub\sand-control-failure-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21BE2910-4F10-42D2-B061-B0CC3A5741AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B292F37D-5B0E-4B80-A980-0297D87C0E32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-2730" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterView" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="396">
   <si>
     <t>Category</t>
   </si>
@@ -77,15 +77,6 @@
     <t>Dropdown Menu</t>
   </si>
   <si>
-    <t>{"Operator", "Service Company", "Report", "SPE Paper", "Public Data"}</t>
-  </si>
-  <si>
-    <t>{"High", "Mid", "Low"}</t>
-  </si>
-  <si>
-    <t>{"Internal Use Only", "Anonymous External Use", "Aggregated Analysis Only", "Approved for Direct Disclosure", "Not Disclosed"}</t>
-  </si>
-  <si>
     <t>Text</t>
   </si>
   <si>
@@ -101,15 +92,9 @@
     <t>ft</t>
   </si>
   <si>
-    <t>{"Wet Tree", "Dry Tree"}</t>
-  </si>
-  <si>
     <t>Well TD, MD</t>
   </si>
   <si>
-    <t>{"International Major / Supermajor", "National Oil Company", "Independent Operator", "Small / Private Operator", "Joint Venture Operator", "Service Company / Integrated Project Operator", "Other / Not Disclosed"}</t>
-  </si>
-  <si>
     <t>Region</t>
   </si>
   <si>
@@ -119,12 +104,6 @@
     <t>days</t>
   </si>
   <si>
-    <t>{"Surface Solids Samples", "ASD Response", "Surface Equipment Erosion"}</t>
-  </si>
-  <si>
-    <t>{"Minor", "Major", "Catastrophic"}</t>
-  </si>
-  <si>
     <t>stb/d or mmscf/d</t>
   </si>
   <si>
@@ -170,18 +149,12 @@
     <t>psi</t>
   </si>
   <si>
-    <t>{"Same", "Increased", "Decreased", "Variable", "Unknown", "Not applicable"}</t>
-  </si>
-  <si>
     <t>Completion Details</t>
   </si>
   <si>
     <t>Reservoir Drilling Fluid Type</t>
   </si>
   <si>
-    <t>{"OBM", "WBM", "OBM Acid Soluble", "WBM Acid Soluble"}</t>
-  </si>
-  <si>
     <t>Reservoir Drilling Fluid Density</t>
   </si>
   <si>
@@ -194,15 +167,9 @@
     <t>Additional Bridging Agent</t>
   </si>
   <si>
-    <t>{"CaCO3", "None"}</t>
-  </si>
-  <si>
     <t>Mud PSD</t>
   </si>
   <si>
-    <t>D10 / D50 / D90</t>
-  </si>
-  <si>
     <t>PSD Test Volume</t>
   </si>
   <si>
@@ -218,39 +185,21 @@
     <t>Completion Type</t>
   </si>
   <si>
-    <t>{"Open Hole", "Cased Hole"}</t>
-  </si>
-  <si>
     <t>Sand Control Decision Justification</t>
   </si>
   <si>
-    <t>{"Uncertain Sand Risk / Conservative Design", "Offset Well Experience", "Core-Based Geomechanical Analysis", "Operational Constraint", "Regulatory Requirement", "Completion Type Standardization", "Unknown / Not Documented"}</t>
-  </si>
-  <si>
     <t>Remedial Acid Pumped as Productivity was Below Expectation</t>
   </si>
   <si>
-    <t>{"Yes", "No", "Unknown", "Not Applicable"}</t>
-  </si>
-  <si>
     <t>Remedial Acid Helped Productivity</t>
   </si>
   <si>
-    <t>{"Yes", "No", "Partially", "Unknown", "Not Applicable"}</t>
-  </si>
-  <si>
     <t>Remedial Acid Type</t>
   </si>
   <si>
-    <t>{"Organic", "Inorganic", "Mud acid", "Blend", "Other", "Unknown", "Not applicable"}</t>
-  </si>
-  <si>
     <t>Percentage of ideal PI or skin achieved</t>
   </si>
   <si>
-    <t>{"YYYY-MM-DD"}</t>
-  </si>
-  <si>
     <t>Reservoir Characterization</t>
   </si>
   <si>
@@ -275,9 +224,6 @@
     <t>PSD Measurement Method</t>
   </si>
   <si>
-    <t>{"LPSA", "Sieve"}</t>
-  </si>
-  <si>
     <t>microns</t>
   </si>
   <si>
@@ -311,9 +257,6 @@
     <t>Fluid Type</t>
   </si>
   <si>
-    <t>{"Oil", "Condensate", "Wet Gas", "Dry Gas"}</t>
-  </si>
-  <si>
     <t>Producing Fluid Viscosity</t>
   </si>
   <si>
@@ -347,9 +290,6 @@
     <t>Fluid Type Left in OH at end of Completion</t>
   </si>
   <si>
-    <t>{"Completion Brine", "Reservoir Drill-In Fluid", "Filter-Cake Breaker Fluid", "Produced Fluid / Hydrocarbon", "Mixed / Contaminated Fluid"}</t>
-  </si>
-  <si>
     <t>Cased Hole Details</t>
   </si>
   <si>
@@ -377,21 +317,12 @@
     <t>Perforation Charge Casing Material</t>
   </si>
   <si>
-    <t>{"Steel", "Low Debris Steel", "Zinc"}</t>
-  </si>
-  <si>
     <t>Charge Type</t>
   </si>
   <si>
-    <t>{"DP", "BH"}</t>
-  </si>
-  <si>
     <t>Perforation Strategy</t>
   </si>
   <si>
-    <t>{"OB", "UB", "OB &amp; Surge", "UB &amp; Surge"}</t>
-  </si>
-  <si>
     <t>OB / OB Magnitude</t>
   </si>
   <si>
@@ -416,33 +347,21 @@
     <t>Screen RIH Fluid Type</t>
   </si>
   <si>
-    <t>{"Brine", "OBM", "Brine in Casing &amp; Mud in OH"}</t>
-  </si>
-  <si>
     <t>If screens ran in mud, was mud removed once screens on bottom?</t>
   </si>
   <si>
     <t>Filter cake breaker placement</t>
   </si>
   <si>
-    <t>{"Spotted inside screens", "Displaced outside screens", "Not used"}</t>
-  </si>
-  <si>
     <t>Gravel Packing</t>
   </si>
   <si>
     <t>Placement Method</t>
   </si>
   <si>
-    <t>{"Shunt", "Circ Pack"}</t>
-  </si>
-  <si>
     <t>Proppant Type</t>
   </si>
   <si>
-    <t>{"Natural Sand", "Resin-Coated Sand", "Ceramic Proppant"}</t>
-  </si>
-  <si>
     <t>Proppant Size</t>
   </si>
   <si>
@@ -452,9 +371,6 @@
     <t>Carrier Fluid Type</t>
   </si>
   <si>
-    <t>{"Brine", "Crosslinked Gel", "Foam-Based Fluid", "Oil-Based Fluid", "Other / Proprietary"}</t>
-  </si>
-  <si>
     <t>Carrier Fluid Density</t>
   </si>
   <si>
@@ -512,27 +428,15 @@
     <t>Notes / comments</t>
   </si>
   <si>
-    <t>{"Oil Producer", "Gas Producer", "Gas Condensate Producer"}</t>
-  </si>
-  <si>
-    <t>{"Onshore", "Shelf Offshore (&lt; 3,000 ft)", "Deepwater Offshore (3,000 - 6,000 ft)", "Ultra-Deepwater Offshore (&gt; 6,000 ft)", "Unknown / Not Disclosed"}</t>
-  </si>
-  <si>
     <t>Well TD, TVD (RKB)</t>
   </si>
   <si>
-    <t>{"US Gulf Coast / Gulf Shelf", "US Gulf / Deepwater", "Central America", "North Sea / Northeast Atlantic", "West Africa Atlantic Margin", "Brazil / South Atlantic Margin", "Middle East / Arabian Gulf", "Caspian / Central Asia", "North Africa / Eastern Mediterranean", "South &amp; Southeast Asia", "East Asia", "Australasia", "North America Onshore / Heavy Oil", "Latin America Onshore", "Latin America Offshore / Caribbean", "Other / Not Disclosed"}</t>
-  </si>
-  <si>
     <t>Failure Confirmation</t>
   </si>
   <si>
     <t>Severity of sand production</t>
   </si>
   <si>
-    <t>{"Minor (&lt;10lb/hr)", "Major (10 to 100 lb/hr)", "Catastrophic (&gt;100lb/hr)"}</t>
-  </si>
-  <si>
     <t>Time to well shut-in due to sand</t>
   </si>
   <si>
@@ -542,9 +446,6 @@
     <t>Sand failure mechanism</t>
   </si>
   <si>
-    <t>{"Aggressive drawdown", "Screen plugging", "Water breakthrough", "Water hammer", "Hard shutdown", "Other", "Unknown"}</t>
-  </si>
-  <si>
     <t>Sand production rate at first choke back</t>
   </si>
   <si>
@@ -575,33 +476,15 @@
     <t>Deviated well skin after choke-back</t>
   </si>
   <si>
-    <t>{"Flowing Unrestricted by Sand", "Flowing Restricted by Sand", "Shut-in Due to Sand", "Shut in due to reasons other than sand", "Not Producing"}</t>
-  </si>
-  <si>
     <t>Initial reservoir pore pressure</t>
   </si>
   <si>
-    <t>{"Gradual (≤ 0.01 in/hr average increase in choke diameter)", "Aggressive (&gt; 0.01 in/hr, or a single increase ≥ 0.05 in within 1 hr)", "Mixed (Both gradual and aggressive behavior occur during the evaluated period)", "Unknown (Insufficient choke-size/time data)", "Not applicable (No meaningful choke-management period exists)"}</t>
-  </si>
-  <si>
-    <t>Production Zones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Each production interval can have several sand bodies. </t>
-  </si>
-  <si>
     <t>Tooltip</t>
   </si>
   <si>
     <t>Drilling Details</t>
   </si>
   <si>
-    <t>{"API Barite", "UFG Barite", "Calcium Carbonate", "Hematite", "None"}</t>
-  </si>
-  <si>
-    <t>Production Interval {id}</t>
-  </si>
-  <si>
     <t>Pre-production and cleanup</t>
   </si>
   <si>
@@ -635,21 +518,9 @@
     <t>Number of Completion Intervals</t>
   </si>
   <si>
-    <t>Production Zone Details</t>
-  </si>
-  <si>
-    <t>Completion Interval Details</t>
-  </si>
-  <si>
     <t>Drill Bit Size</t>
   </si>
   <si>
-    <t>{"OHGP", "SAS"}</t>
-  </si>
-  <si>
-    <t>{"CHFP", "CHGP", "Cased and Perforated"}</t>
-  </si>
-  <si>
     <t>Cased Hole Sand Control Selected Method</t>
   </si>
   <si>
@@ -674,24 +545,12 @@
     <t>Source of sand sample</t>
   </si>
   <si>
-    <t>{"cores", "bottom-hole sand sample", "surface sample", "analog well"}</t>
-  </si>
-  <si>
     <t>Particle Size Distribution D10/D25/D40/D50/D75/D90</t>
   </si>
   <si>
-    <t>{"Number / Number / Number / Number / Number / Number"}</t>
-  </si>
-  <si>
     <t>Oil Formation Volume Factor (Bo) at downhole conditions</t>
   </si>
   <si>
-    <t>{"Plain Slotted Liners", "Wire-Wrapped Screens (WWS)", "Premium Mesh Screen", "Prepacked Screens", "Metal-Fiber / Wool Screen", "Ceramic Screen", "Other Erosion Resistant Screen", "Other"}</t>
-  </si>
-  <si>
-    <t>{"Measurable", "Unable to quantify", "No sand"}</t>
-  </si>
-  <si>
     <t>User comment</t>
   </si>
   <si>
@@ -701,9 +560,6 @@
     <t>Pack Efficiency Value</t>
   </si>
   <si>
-    <t>{"Gravel Pack Evaluation Log", "Pressure / Pumping Data", "Volume Balance", "Returns / Surface Monitoring", "Post-Job Well Performance", "Combination of Methods", "Other", "Unknown / Not Disclosed"}</t>
-  </si>
-  <si>
     <t>Primary source from which the well data were obtained</t>
   </si>
   <si>
@@ -1034,9 +890,6 @@
     <t>Well performance after cleanup expressed relative to the modeled/theoretical ideal PI or skin target.</t>
   </si>
   <si>
-    <t>Number of distinct reservoir/completion intervals represented within the production interval.</t>
-  </si>
-  <si>
     <t>Original reservoir pressure before depletion or production-induced pressure decline.</t>
   </si>
   <si>
@@ -1139,36 +992,12 @@
     <t>Well identification number</t>
   </si>
   <si>
-    <t>{"Positive Integer": {"min": 1, "max": 10}}</t>
-  </si>
-  <si>
-    <t>{"Number / Number / Number"}</t>
-  </si>
-  <si>
-    <t>{"Positive Integer": {"required": True}}</t>
-  </si>
-  <si>
-    <t>{"Positive Number"}</t>
-  </si>
-  <si>
-    <t>{"Number"}</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>{"Yes", "No"}</t>
-  </si>
-  <si>
     <t>Time to first choke back</t>
   </si>
   <si>
     <t>Frac gradient</t>
   </si>
   <si>
-    <t>YYYY-MM-DD</t>
-  </si>
-  <si>
     <t>Sand failure</t>
   </si>
   <si>
@@ -1226,13 +1055,175 @@
     <t>Post-shut-in water-cut response</t>
   </si>
   <si>
-    <t>Number of production intervals</t>
-  </si>
-  <si>
     <t>{"Measurable": {"Max sand rate", "Average sand rate"}}</t>
   </si>
   <si>
     <t>Completion Interval Length</t>
+  </si>
+  <si>
+    <t>Sand Body {id}</t>
+  </si>
+  <si>
+    <t>Sand Bodies</t>
+  </si>
+  <si>
+    <t>Number of sand bodies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each completion interval can have several sand bodies. </t>
+  </si>
+  <si>
+    <t>Number of distinct reservoir/completion intervals represented within the well.</t>
+  </si>
+  <si>
+    <t>{"Any Value": {}}</t>
+  </si>
+  <si>
+    <t>{"Whole number": {"min": 1, "max": 10}}</t>
+  </si>
+  <si>
+    <t>{"List": ["Aggressive drawdown", "Screen plugging", "Water breakthrough", "Water hammer", "Hard shutdown", "Other", "Unknown"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["API Barite", "UFG Barite", "Calcium Carbonate", "Hematite", "None"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["Brine", "OBM", "Brine in Casing &amp; Mud in OH"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["Brine", "Crosslinked Gel", "Foam-Based Fluid", "Oil-Based Fluid", "Other / Proprietary"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["CaCO3", "None"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["Completion Brine", "Reservoir Drill-In Fluid", "Filter-Cake Breaker Fluid", "Produced Fluid / Hydrocarbon", "Mixed / Contaminated Fluid"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["DP", "BH"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["CHFP", "CHGP", "Cased and Perforated"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["cores", "bottom-hole sand sample", "surface sample", "analog well"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["Operator", "Service Company", "Report", "SPE Paper", "Public Data"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["High", "Mid", "Low"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["Internal Use Only", "Anonymous External Use", "Aggregated Analysis Only", "Approved for Direct Disclosure", "Not Disclosed"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["Oil Producer", "Gas Producer", "Gas Condensate Producer"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["Onshore", "Shelf Offshore (&lt; 3,000 ft)", "Deepwater Offshore (3,000 - 6,000 ft)", "Ultra-Deepwater Offshore (&gt; 6,000 ft)", "Unknown / Not Disclosed"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["Wet Tree", "Dry Tree"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["International Major / Supermajor", "National Oil Company", "Independent Operator", "Small / Private Operator", "Joint Venture Operator", "Service Company / Integrated Project Operator", "Other / Not Disclosed"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["US Gulf Coast / Gulf Shelf", "US Gulf / Deepwater", "Central America", "North Sea / Northeast Atlantic", "West Africa Atlantic Margin", "Brazil / South Atlantic Margin", "Middle East / Arabian Gulf", "Caspian / Central Asia", "North Africa / Eastern Mediterranean", "South &amp; Southeast Asia", "East Asia", "Australasia", "North America Onshore / Heavy Oil", "Latin America Onshore", "Latin America Offshore / Caribbean", "Other / Not Disclosed"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["Yes", "No"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["Minor (&lt;10lb/hr)", "Major (10 to 100 lb/hr)", "Catastrophic (&gt;100lb/hr)"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["Surface Solids Samples", "ASD Response", "Surface Equipment Erosion"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["Minor", "Major", "Catastrophic"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["Flowing Unrestricted by Sand", "Flowing Restricted by Sand", "Shut-in Due to Sand", "Shut in due to reasons other than sand", "Not Producing"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["Measurable", "Unable to quantify", "No sand"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["Gradual (≤ 0.01 in/hr average increase in choke diameter)", "Aggressive (&gt; 0.01 in/hr, or a single increase ≥ 0.05 in within 1 hr)", "Mixed (Both gradual and aggressive behavior occur during the evaluated period)", "Unknown (Insufficient choke-size/time data)", "Not applicable (No meaningful choke-management period exists)"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["Same", "Increased", "Decreased", "Variable", "Unknown", "Not applicable"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["OBM", "WBM", "OBM Acid Soluble", "WBM Acid Soluble"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["Open Hole", "Cased Hole"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["Steel", "Low Debris Steel", "Zinc"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["OB", "UB", "OB &amp; Surge", "UB &amp; Surge"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["OHGP", "SAS"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["Uncertain Sand Risk / Conservative Design", "Offset Well Experience", "Core-Based Geomechanical Analysis", "Operational Constraint", "Regulatory Requirement", "Completion Type Standardization", "Unknown / Not Documented"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["Plain Slotted Liners", "Wire-Wrapped Screens (WWS)", "Premium Mesh Screen", "Prepacked Screens", "Metal-Fiber / Wool Screen", "Ceramic Screen", "Other Erosion Resistant Screen", "Other"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["Spotted inside screens", "Displaced outside screens", "Not used"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["Shunt", "Circ Pack"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["Natural Sand", "Resin-Coated Sand", "Ceramic Proppant"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["Gravel Pack Evaluation Log", "Pressure / Pumping Data", "Volume Balance", "Returns / Surface Monitoring", "Post-Job Well Performance", "Combination of Methods", "Other", "Unknown / Not Disclosed"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["Yes", "No", "Unknown", "Not Applicable"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["Yes", "No", "Partially", "Unknown", "Not Applicable"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["Organic", "Inorganic", "Mud acid", "Blend", "Other", "Unknown", "Not applicable"]}</t>
+  </si>
+  <si>
+    <t>{"List": ["LPSA", "Sieve"]}</t>
+  </si>
+  <si>
+    <t>{"Whole number": {"required": True, "min": 0}}</t>
+  </si>
+  <si>
+    <t>{"Decimal": {"min": 0}}</t>
+  </si>
+  <si>
+    <t>{"Decimal"}</t>
+  </si>
+  <si>
+    <t>{"Short Date"}</t>
+  </si>
+  <si>
+    <t>{"Whole number"}</t>
+  </si>
+  <si>
+    <t>{"List": ["Oil", "Condensate", "Wet Gas", "Dry Gas"]}</t>
+  </si>
+  <si>
+    <t>{["Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}]}</t>
+  </si>
+  <si>
+    <t>{["Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}]}</t>
   </si>
 </sst>
 </file>
@@ -1290,7 +1281,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1319,12 +1310,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1338,6 +1323,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1355,7 +1352,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1377,15 +1374,17 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2040,10 +2039,10 @@
         <v>6</v>
       </c>
       <c r="J1" s="10" t="s">
-        <v>184</v>
+        <v>147</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>218</v>
+        <v>171</v>
       </c>
       <c r="L1" s="1"/>
     </row>
@@ -2058,7 +2057,7 @@
         <v>10</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>12</v>
@@ -2067,10 +2066,10 @@
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
       <c r="I2" s="5" t="s">
-        <v>13</v>
+        <v>357</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>222</v>
+        <v>174</v>
       </c>
       <c r="K2" s="5"/>
       <c r="L2" s="1"/>
@@ -2086,7 +2085,7 @@
         <v>10</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>147</v>
+        <v>119</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>12</v>
@@ -2095,10 +2094,10 @@
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
       <c r="I3" s="5" t="s">
-        <v>14</v>
+        <v>358</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>223</v>
+        <v>175</v>
       </c>
       <c r="K3" s="5"/>
       <c r="L3" s="1"/>
@@ -2114,7 +2113,7 @@
         <v>10</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>148</v>
+        <v>120</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>12</v>
@@ -2123,10 +2122,10 @@
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="5" t="s">
-        <v>15</v>
+        <v>359</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>224</v>
+        <v>176</v>
       </c>
       <c r="K4" s="5"/>
       <c r="L4" s="1"/>
@@ -2142,19 +2141,19 @@
         <v>10</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5" t="s">
-        <v>372</v>
+        <v>346</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>225</v>
+        <v>177</v>
       </c>
       <c r="K5" s="5"/>
       <c r="L5" s="1"/>
@@ -2164,25 +2163,25 @@
         <v>11</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
       <c r="H6" s="6"/>
       <c r="I6" s="6" t="s">
-        <v>372</v>
+        <v>346</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>226</v>
+        <v>178</v>
       </c>
       <c r="K6" s="6"/>
       <c r="L6" s="1"/>
@@ -2192,25 +2191,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>366</v>
+        <v>317</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
       <c r="I7" s="6" t="s">
-        <v>369</v>
+        <v>388</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>227</v>
+        <v>179</v>
       </c>
       <c r="K7" s="6"/>
       <c r="L7" s="1"/>
@@ -2220,13 +2219,13 @@
         <v>11</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>12</v>
@@ -2235,10 +2234,10 @@
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
       <c r="I8" s="6" t="s">
-        <v>158</v>
+        <v>360</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>228</v>
+        <v>180</v>
       </c>
       <c r="K8" s="6"/>
       <c r="L8" s="1"/>
@@ -2248,13 +2247,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>151</v>
+        <v>123</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>12</v>
@@ -2262,13 +2261,13 @@
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
       <c r="H9" s="6" t="s">
-        <v>363</v>
+        <v>314</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>159</v>
+        <v>361</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>229</v>
+        <v>181</v>
       </c>
       <c r="K9" s="6"/>
       <c r="L9" s="1"/>
@@ -2278,27 +2277,27 @@
         <v>11</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="6" t="s">
         <v>17</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>20</v>
       </c>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
       <c r="I10" s="6" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>230</v>
+        <v>182</v>
       </c>
       <c r="K10" s="6"/>
       <c r="L10" s="1"/>
@@ -2308,13 +2307,13 @@
         <v>11</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>12</v>
@@ -2323,10 +2322,10 @@
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
       <c r="I11" s="6" t="s">
-        <v>21</v>
+        <v>362</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>231</v>
+        <v>183</v>
       </c>
       <c r="K11" s="6"/>
       <c r="L11" s="1"/>
@@ -2336,27 +2335,27 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="6" t="s">
         <v>17</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>20</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
       <c r="I12" s="6" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>232</v>
+        <v>184</v>
       </c>
       <c r="K12" s="6"/>
       <c r="L12" s="1"/>
@@ -2366,27 +2365,27 @@
         <v>11</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="6" t="s">
         <v>17</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>20</v>
       </c>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
       <c r="I13" s="6" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>233</v>
+        <v>185</v>
       </c>
       <c r="K13" s="6"/>
       <c r="L13" s="1"/>
@@ -2396,25 +2395,25 @@
         <v>11</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
       <c r="I14" s="6" t="s">
-        <v>372</v>
+        <v>346</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>234</v>
+        <v>186</v>
       </c>
       <c r="K14" s="6"/>
       <c r="L14" s="1"/>
@@ -2424,25 +2423,25 @@
         <v>11</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
       <c r="I15" s="6" t="s">
-        <v>372</v>
+        <v>346</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>235</v>
+        <v>187</v>
       </c>
       <c r="K15" s="6"/>
       <c r="L15" s="1"/>
@@ -2452,13 +2451,13 @@
         <v>11</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>12</v>
@@ -2467,10 +2466,10 @@
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
       <c r="I16" s="6" t="s">
-        <v>23</v>
+        <v>363</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="K16" s="6"/>
       <c r="L16" s="1"/>
@@ -2480,13 +2479,13 @@
         <v>11</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>12</v>
@@ -2495,10 +2494,10 @@
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
       <c r="I17" s="6" t="s">
-        <v>161</v>
+        <v>364</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>237</v>
+        <v>189</v>
       </c>
       <c r="K17" s="6"/>
       <c r="L17" s="1"/>
@@ -2508,27 +2507,27 @@
         <v>11</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>377</v>
+        <v>320</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="6" t="s">
-        <v>365</v>
+        <v>316</v>
       </c>
       <c r="H18" s="6"/>
       <c r="I18" s="6" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>238</v>
+        <v>190</v>
       </c>
       <c r="K18" s="6"/>
       <c r="L18" s="1"/>
@@ -2538,13 +2537,13 @@
         <v>11</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>12</v>
@@ -2553,10 +2552,10 @@
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
       <c r="I19" s="6" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>239</v>
+        <v>191</v>
       </c>
       <c r="K19" s="6"/>
       <c r="L19" s="1"/>
@@ -2566,27 +2565,27 @@
         <v>11</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>374</v>
+        <v>318</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
       <c r="I20" s="6" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>240</v>
+        <v>192</v>
       </c>
       <c r="K20" s="6"/>
       <c r="L20" s="1"/>
@@ -2596,27 +2595,27 @@
         <v>11</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>165</v>
+        <v>133</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
       <c r="I21" s="6" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>241</v>
+        <v>193</v>
       </c>
       <c r="K21" s="6"/>
       <c r="L21" s="1"/>
@@ -2626,27 +2625,27 @@
         <v>11</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
       <c r="I22" s="6" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>242</v>
+        <v>194</v>
       </c>
       <c r="K22" s="6"/>
       <c r="L22" s="1"/>
@@ -2656,13 +2655,13 @@
         <v>11</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>12</v>
@@ -2671,10 +2670,10 @@
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
       <c r="I23" s="6" t="s">
-        <v>27</v>
+        <v>367</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>243</v>
+        <v>195</v>
       </c>
       <c r="K23" s="6"/>
       <c r="L23" s="1"/>
@@ -2684,13 +2683,13 @@
         <v>11</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>12</v>
@@ -2698,11 +2697,11 @@
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
-      <c r="I24" s="8" t="s">
-        <v>168</v>
+      <c r="I24" s="6" t="s">
+        <v>348</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>244</v>
+        <v>196</v>
       </c>
       <c r="K24" s="6"/>
       <c r="L24" s="1"/>
@@ -2712,13 +2711,13 @@
         <v>11</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>359</v>
+        <v>310</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>12</v>
@@ -2727,10 +2726,10 @@
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
       <c r="I25" s="6" t="s">
-        <v>28</v>
+        <v>368</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>358</v>
+        <v>309</v>
       </c>
       <c r="K25" s="6"/>
       <c r="L25" s="1"/>
@@ -2740,27 +2739,27 @@
         <v>11</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>169</v>
+        <v>136</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
       <c r="I26" s="6" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>245</v>
+        <v>197</v>
       </c>
       <c r="K26" s="6"/>
       <c r="L26" s="1"/>
@@ -2770,27 +2769,27 @@
         <v>11</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>170</v>
+        <v>137</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
       <c r="I27" s="6" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>246</v>
+        <v>198</v>
       </c>
       <c r="K27" s="6"/>
       <c r="L27" s="1"/>
@@ -2800,27 +2799,27 @@
         <v>11</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
       <c r="I28" s="6" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>247</v>
+        <v>199</v>
       </c>
       <c r="K28" s="6"/>
       <c r="L28" s="1"/>
@@ -2830,27 +2829,27 @@
         <v>11</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G29" s="6"/>
       <c r="H29" s="6"/>
       <c r="I29" s="6" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>248</v>
+        <v>200</v>
       </c>
       <c r="K29" s="6"/>
       <c r="L29" s="1"/>
@@ -2860,25 +2859,25 @@
         <v>11</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
       <c r="H30" s="6"/>
-      <c r="I30" s="8" t="s">
-        <v>371</v>
+      <c r="I30" s="6" t="s">
+        <v>390</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>249</v>
+        <v>201</v>
       </c>
       <c r="K30" s="6"/>
       <c r="L30" s="1"/>
@@ -2888,25 +2887,25 @@
         <v>11</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>173</v>
+        <v>140</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
       <c r="H31" s="6"/>
-      <c r="I31" s="8" t="s">
-        <v>371</v>
+      <c r="I31" s="6" t="s">
+        <v>390</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>250</v>
+        <v>202</v>
       </c>
       <c r="K31" s="6"/>
       <c r="L31" s="1"/>
@@ -2916,25 +2915,25 @@
         <v>11</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>174</v>
+        <v>141</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
-      <c r="I32" s="8" t="s">
-        <v>371</v>
+      <c r="I32" s="6" t="s">
+        <v>390</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>251</v>
+        <v>203</v>
       </c>
       <c r="K32" s="6"/>
       <c r="L32" s="1"/>
@@ -2944,27 +2943,27 @@
         <v>11</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>175</v>
+        <v>142</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
       <c r="I33" s="6" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>252</v>
+        <v>204</v>
       </c>
       <c r="K33" s="6"/>
       <c r="L33" s="1"/>
@@ -2974,25 +2973,25 @@
         <v>11</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
-      <c r="I34" s="8" t="s">
-        <v>371</v>
+      <c r="I34" s="6" t="s">
+        <v>390</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>253</v>
+        <v>205</v>
       </c>
       <c r="K34" s="6"/>
       <c r="L34" s="1"/>
@@ -3002,25 +3001,25 @@
         <v>11</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>177</v>
+        <v>144</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
       <c r="H35" s="6"/>
-      <c r="I35" s="8" t="s">
-        <v>371</v>
+      <c r="I35" s="6" t="s">
+        <v>390</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>254</v>
+        <v>206</v>
       </c>
       <c r="K35" s="6"/>
       <c r="L35" s="1"/>
@@ -3030,25 +3029,25 @@
         <v>11</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>178</v>
+        <v>145</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
-      <c r="I36" s="8" t="s">
-        <v>371</v>
+      <c r="I36" s="6" t="s">
+        <v>390</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>255</v>
+        <v>207</v>
       </c>
       <c r="K36" s="6"/>
       <c r="L36" s="1"/>
@@ -3058,25 +3057,25 @@
         <v>11</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
       <c r="I37" s="6" t="s">
-        <v>372</v>
+        <v>346</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>256</v>
+        <v>208</v>
       </c>
       <c r="K37" s="6"/>
       <c r="L37" s="1"/>
@@ -3086,13 +3085,13 @@
         <v>11</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>360</v>
+        <v>311</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>378</v>
+        <v>321</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>12</v>
@@ -3100,11 +3099,11 @@
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
       <c r="H38" s="6"/>
-      <c r="I38" s="8" t="s">
-        <v>179</v>
+      <c r="I38" s="6" t="s">
+        <v>369</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>257</v>
+        <v>209</v>
       </c>
       <c r="K38" s="6"/>
       <c r="L38" s="1"/>
@@ -3114,27 +3113,25 @@
         <v>11</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>360</v>
+        <v>311</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>379</v>
+        <v>322</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>376</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="F39" s="6"/>
       <c r="G39" s="6"/>
       <c r="H39" s="6"/>
       <c r="I39" s="6" t="s">
-        <v>70</v>
+        <v>391</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>258</v>
+        <v>210</v>
       </c>
       <c r="K39" s="6"/>
       <c r="L39" s="1"/>
@@ -3144,27 +3141,25 @@
         <v>11</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>360</v>
+        <v>311</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>380</v>
+        <v>323</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>376</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="F40" s="6"/>
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
       <c r="I40" s="6" t="s">
-        <v>70</v>
+        <v>391</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>259</v>
+        <v>211</v>
       </c>
       <c r="K40" s="6"/>
       <c r="L40" s="1"/>
@@ -3174,27 +3169,25 @@
         <v>11</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>360</v>
+        <v>311</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>381</v>
+        <v>324</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>376</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="F41" s="6"/>
       <c r="G41" s="6"/>
       <c r="H41" s="6"/>
       <c r="I41" s="6" t="s">
-        <v>70</v>
+        <v>391</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>260</v>
+        <v>212</v>
       </c>
       <c r="K41" s="6"/>
       <c r="L41" s="1"/>
@@ -3204,27 +3197,27 @@
         <v>11</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>360</v>
+        <v>311</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G42" s="6"/>
       <c r="H42" s="6"/>
       <c r="I42" s="6" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>261</v>
+        <v>213</v>
       </c>
       <c r="K42" s="6"/>
       <c r="L42" s="1"/>
@@ -3234,27 +3227,27 @@
         <v>11</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>360</v>
+        <v>311</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G43" s="6"/>
       <c r="H43" s="6"/>
       <c r="I43" s="6" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>262</v>
+        <v>214</v>
       </c>
       <c r="K43" s="6"/>
       <c r="L43" s="1"/>
@@ -3264,27 +3257,27 @@
         <v>11</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>360</v>
+        <v>311</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G44" s="6"/>
       <c r="H44" s="6"/>
       <c r="I44" s="6" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>263</v>
+        <v>215</v>
       </c>
       <c r="K44" s="6"/>
       <c r="L44" s="1"/>
@@ -3294,27 +3287,27 @@
         <v>11</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>360</v>
+        <v>311</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G45" s="6"/>
       <c r="H45" s="6"/>
       <c r="I45" s="6" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>264</v>
+        <v>216</v>
       </c>
       <c r="K45" s="6"/>
       <c r="L45" s="1"/>
@@ -3324,27 +3317,27 @@
         <v>11</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>360</v>
+        <v>311</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G46" s="6"/>
       <c r="H46" s="6"/>
       <c r="I46" s="6" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>265</v>
+        <v>217</v>
       </c>
       <c r="K46" s="6"/>
       <c r="L46" s="1"/>
@@ -3354,27 +3347,27 @@
         <v>11</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>360</v>
+        <v>311</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G47" s="6"/>
       <c r="H47" s="6"/>
       <c r="I47" s="6" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>266</v>
+        <v>218</v>
       </c>
       <c r="K47" s="6"/>
       <c r="L47" s="1"/>
@@ -3384,27 +3377,27 @@
         <v>11</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>360</v>
+        <v>311</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>382</v>
+        <v>325</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G48" s="6"/>
       <c r="H48" s="6"/>
       <c r="I48" s="6" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>267</v>
+        <v>219</v>
       </c>
       <c r="K48" s="6"/>
       <c r="L48" s="1"/>
@@ -3414,27 +3407,27 @@
         <v>11</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>360</v>
+        <v>311</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>383</v>
+        <v>326</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G49" s="6"/>
       <c r="H49" s="6"/>
       <c r="I49" s="6" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>268</v>
+        <v>220</v>
       </c>
       <c r="K49" s="6"/>
       <c r="L49" s="1"/>
@@ -3444,27 +3437,27 @@
         <v>11</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>360</v>
+        <v>311</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>384</v>
+        <v>327</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G50" s="6"/>
       <c r="H50" s="6"/>
       <c r="I50" s="6" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>269</v>
+        <v>221</v>
       </c>
       <c r="K50" s="6"/>
       <c r="L50" s="1"/>
@@ -3474,27 +3467,27 @@
         <v>11</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>360</v>
+        <v>311</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>385</v>
+        <v>328</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G51" s="6"/>
       <c r="H51" s="6"/>
       <c r="I51" s="6" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>270</v>
+        <v>222</v>
       </c>
       <c r="K51" s="6"/>
       <c r="L51" s="1"/>
@@ -3504,13 +3497,13 @@
         <v>11</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>360</v>
+        <v>311</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>386</v>
+        <v>329</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>12</v>
@@ -3518,13 +3511,13 @@
       <c r="F52" s="6"/>
       <c r="G52" s="6"/>
       <c r="H52" s="6" t="s">
-        <v>397</v>
+        <v>339</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>217</v>
+        <v>370</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>271</v>
+        <v>223</v>
       </c>
       <c r="K52" s="6"/>
       <c r="L52" s="1"/>
@@ -3534,27 +3527,27 @@
         <v>11</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>360</v>
+        <v>311</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>387</v>
+        <v>330</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G53" s="6"/>
       <c r="H53" s="6"/>
       <c r="I53" s="6" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>272</v>
+        <v>224</v>
       </c>
       <c r="K53" s="6"/>
       <c r="L53" s="1"/>
@@ -3564,27 +3557,27 @@
         <v>11</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>360</v>
+        <v>311</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>388</v>
+        <v>331</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G54" s="6"/>
       <c r="H54" s="6"/>
       <c r="I54" s="6" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>273</v>
+        <v>225</v>
       </c>
       <c r="K54" s="6"/>
       <c r="L54" s="1"/>
@@ -3594,25 +3587,25 @@
         <v>11</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>360</v>
+        <v>311</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>389</v>
+        <v>332</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F55" s="6"/>
       <c r="G55" s="6"/>
       <c r="H55" s="6"/>
       <c r="I55" s="6" t="s">
-        <v>372</v>
+        <v>346</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>274</v>
+        <v>226</v>
       </c>
       <c r="K55" s="6"/>
       <c r="L55" s="1"/>
@@ -3622,27 +3615,27 @@
         <v>11</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>360</v>
+        <v>311</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>180</v>
+        <v>146</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="G56" s="6"/>
       <c r="H56" s="6"/>
       <c r="I56" s="6" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>275</v>
+        <v>227</v>
       </c>
       <c r="K56" s="6"/>
       <c r="L56" s="1"/>
@@ -3652,27 +3645,27 @@
         <v>11</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>360</v>
+        <v>311</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>390</v>
+        <v>333</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="G57" s="6"/>
       <c r="H57" s="6"/>
       <c r="I57" s="6" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>276</v>
+        <v>228</v>
       </c>
       <c r="K57" s="6"/>
       <c r="L57" s="1"/>
@@ -3682,27 +3675,27 @@
         <v>11</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>360</v>
+        <v>311</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>391</v>
+        <v>334</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="G58" s="6"/>
       <c r="H58" s="6"/>
       <c r="I58" s="6" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>277</v>
+        <v>229</v>
       </c>
       <c r="K58" s="6"/>
       <c r="L58" s="1"/>
@@ -3712,13 +3705,13 @@
         <v>11</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>360</v>
+        <v>311</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>392</v>
+        <v>335</v>
       </c>
       <c r="E59" s="6" t="s">
         <v>12</v>
@@ -3726,11 +3719,11 @@
       <c r="F59" s="6"/>
       <c r="G59" s="6"/>
       <c r="H59" s="6"/>
-      <c r="I59" s="8" t="s">
-        <v>181</v>
+      <c r="I59" s="6" t="s">
+        <v>371</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>278</v>
+        <v>230</v>
       </c>
       <c r="K59" s="6"/>
       <c r="L59" s="1"/>
@@ -3740,13 +3733,13 @@
         <v>11</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>360</v>
+        <v>311</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>393</v>
+        <v>336</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>12</v>
@@ -3755,10 +3748,10 @@
       <c r="G60" s="6"/>
       <c r="H60" s="6"/>
       <c r="I60" s="6" t="s">
-        <v>44</v>
+        <v>372</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>279</v>
+        <v>231</v>
       </c>
       <c r="K60" s="6"/>
       <c r="L60" s="1"/>
@@ -3768,13 +3761,13 @@
         <v>11</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>360</v>
+        <v>311</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>395</v>
+        <v>338</v>
       </c>
       <c r="E61" s="6" t="s">
         <v>12</v>
@@ -3783,10 +3776,10 @@
       <c r="G61" s="6"/>
       <c r="H61" s="6"/>
       <c r="I61" s="6" t="s">
-        <v>44</v>
+        <v>372</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>280</v>
+        <v>232</v>
       </c>
       <c r="K61" s="6"/>
       <c r="L61" s="1"/>
@@ -3796,13 +3789,13 @@
         <v>11</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>360</v>
+        <v>311</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>394</v>
+        <v>337</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>12</v>
@@ -3811,196 +3804,196 @@
       <c r="G62" s="6"/>
       <c r="H62" s="6"/>
       <c r="I62" s="6" t="s">
-        <v>44</v>
+        <v>372</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>281</v>
+        <v>233</v>
       </c>
       <c r="K62" s="6"/>
       <c r="L62" s="1"/>
     </row>
-    <row r="63" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A63" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B63" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="D63" s="11" t="s">
-        <v>396</v>
-      </c>
-      <c r="E63" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F63" s="11"/>
-      <c r="G63" s="11"/>
-      <c r="H63" s="11"/>
-      <c r="I63" s="11" t="s">
-        <v>367</v>
+    <row r="63" spans="1:12" ht="14" x14ac:dyDescent="0.35">
+      <c r="A63" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B63" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="E63" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F63" s="12"/>
+      <c r="G63" s="12"/>
+      <c r="H63" s="12"/>
+      <c r="I63" s="12" t="s">
+        <v>347</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>183</v>
+        <v>345</v>
       </c>
       <c r="K63" s="11"/>
       <c r="L63" s="1"/>
     </row>
-    <row r="64" spans="1:12" ht="14" x14ac:dyDescent="0.35">
-      <c r="A64" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="B64" s="13" t="s">
-        <v>200</v>
+    <row r="64" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="A64" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>154</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="D64" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="E64" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="F64" s="13"/>
-      <c r="G64" s="13"/>
-      <c r="H64" s="13"/>
-      <c r="I64" s="13" t="s">
-        <v>367</v>
-      </c>
-      <c r="J64" s="12" t="s">
-        <v>332</v>
-      </c>
-      <c r="K64" s="12"/>
+        <v>151</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F64" s="7"/>
+      <c r="G64" s="7"/>
+      <c r="H64" s="7"/>
+      <c r="I64" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="J64" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="K64" s="7"/>
       <c r="L64" s="1"/>
     </row>
     <row r="65" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A65" s="15" t="s">
-        <v>197</v>
+      <c r="A65" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="C65" s="14" t="s">
-        <v>190</v>
+        <v>152</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>148</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>398</v>
+        <v>160</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F65" s="7"/>
       <c r="G65" s="7"/>
       <c r="H65" s="7"/>
       <c r="I65" s="7" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>282</v>
+        <v>235</v>
       </c>
       <c r="K65" s="7"/>
       <c r="L65" s="1"/>
     </row>
     <row r="66" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A66" s="15" t="s">
-        <v>197</v>
+      <c r="A66" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>185</v>
+        <v>152</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>148</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>201</v>
+        <v>38</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F66" s="7"/>
       <c r="G66" s="7"/>
       <c r="H66" s="7"/>
       <c r="I66" s="7" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="J66" s="7" t="s">
-        <v>283</v>
+        <v>236</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="1"/>
     </row>
     <row r="67" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A67" s="15" t="s">
-        <v>197</v>
+      <c r="A67" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>191</v>
+        <v>152</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>185</v>
+        <v>148</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F67" s="7"/>
+        <v>16</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="G67" s="7"/>
       <c r="H67" s="7"/>
       <c r="I67" s="7" t="s">
-        <v>47</v>
+        <v>389</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>284</v>
+        <v>237</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="1"/>
     </row>
     <row r="68" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A68" s="15" t="s">
-        <v>197</v>
+      <c r="A68" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>191</v>
+        <v>152</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>185</v>
+        <v>148</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F68" s="7" t="s">
-        <v>49</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F68" s="7"/>
       <c r="G68" s="7"/>
       <c r="H68" s="7"/>
       <c r="I68" s="7" t="s">
-        <v>370</v>
+        <v>349</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="1"/>
     </row>
     <row r="69" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A69" s="15" t="s">
-        <v>197</v>
+      <c r="A69" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>191</v>
+        <v>152</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>185</v>
+        <v>148</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E69" s="7" t="s">
         <v>12</v>
@@ -4009,444 +4002,440 @@
       <c r="G69" s="7"/>
       <c r="H69" s="7"/>
       <c r="I69" s="7" t="s">
-        <v>186</v>
+        <v>352</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>286</v>
+        <v>239</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="1"/>
     </row>
     <row r="70" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A70" s="15" t="s">
-        <v>197</v>
+      <c r="A70" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>191</v>
+        <v>152</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>185</v>
+        <v>148</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F70" s="7"/>
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
       <c r="I70" s="7" t="s">
-        <v>52</v>
+        <v>394</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>287</v>
+        <v>240</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="1"/>
     </row>
     <row r="71" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A71" s="15" t="s">
-        <v>197</v>
+      <c r="A71" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>191</v>
+        <v>152</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>185</v>
+        <v>148</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="E71" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="G71" s="7"/>
       <c r="H71" s="7"/>
       <c r="I71" s="7" t="s">
-        <v>368</v>
+        <v>389</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>288</v>
+        <v>241</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="1"/>
     </row>
     <row r="72" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A72" s="15" t="s">
-        <v>197</v>
+      <c r="A72" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="C72" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="D72" s="7" t="s">
-        <v>55</v>
+        <v>153</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>48</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F72" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G72" s="7"/>
-      <c r="H72" s="7"/>
+        <v>12</v>
+      </c>
+      <c r="F72" s="7"/>
+      <c r="G72" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="H72" s="7" t="s">
+        <v>313</v>
+      </c>
       <c r="I72" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="J72" s="7" t="s">
-        <v>289</v>
+        <v>374</v>
+      </c>
+      <c r="J72" s="9" t="s">
+        <v>242</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="1"/>
     </row>
     <row r="73" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A73" s="15" t="s">
-        <v>197</v>
+      <c r="A73" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D73" s="9" t="s">
-        <v>59</v>
+        <v>37</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F73" s="7"/>
-      <c r="G73" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="H73" s="7" t="s">
-        <v>362</v>
-      </c>
+      <c r="G73" s="7"/>
+      <c r="H73" s="7"/>
       <c r="I73" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="J73" s="9" t="s">
-        <v>290</v>
+        <v>391</v>
+      </c>
+      <c r="J73" s="7" t="s">
+        <v>243</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="1"/>
     </row>
     <row r="74" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A74" s="15" t="s">
-        <v>197</v>
+      <c r="A74" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>376</v>
+        <v>80</v>
       </c>
       <c r="G74" s="7"/>
       <c r="H74" s="7"/>
       <c r="I74" s="7" t="s">
-        <v>70</v>
+        <v>389</v>
       </c>
       <c r="J74" s="7" t="s">
-        <v>291</v>
+        <v>244</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="1"/>
     </row>
     <row r="75" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A75" s="15" t="s">
-        <v>197</v>
+      <c r="A75" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>99</v>
+        <v>17</v>
       </c>
       <c r="G75" s="7"/>
       <c r="H75" s="7"/>
       <c r="I75" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="J75" s="7" t="s">
-        <v>292</v>
+        <v>389</v>
+      </c>
+      <c r="J75" s="9" t="s">
+        <v>245</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="1"/>
     </row>
     <row r="76" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A76" s="15" t="s">
-        <v>197</v>
+      <c r="A76" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G76" s="7"/>
       <c r="H76" s="7"/>
       <c r="I76" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="J76" s="9" t="s">
-        <v>293</v>
+        <v>389</v>
+      </c>
+      <c r="J76" s="7" t="s">
+        <v>246</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="1"/>
     </row>
     <row r="77" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A77" s="15" t="s">
-        <v>197</v>
+      <c r="A77" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F77" s="7" t="s">
-        <v>20</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F77" s="7"/>
       <c r="G77" s="7"/>
       <c r="H77" s="7"/>
       <c r="I77" s="7" t="s">
-        <v>370</v>
+        <v>353</v>
       </c>
       <c r="J77" s="7" t="s">
-        <v>294</v>
+        <v>247</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="1"/>
     </row>
     <row r="78" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A78" s="15" t="s">
-        <v>197</v>
+      <c r="A78" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F78" s="7"/>
+        <v>16</v>
+      </c>
+      <c r="F78" s="7" t="s">
+        <v>80</v>
+      </c>
       <c r="G78" s="7"/>
       <c r="H78" s="7"/>
       <c r="I78" s="7" t="s">
-        <v>103</v>
+        <v>389</v>
       </c>
       <c r="J78" s="7" t="s">
-        <v>295</v>
+        <v>248</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="1"/>
     </row>
     <row r="79" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A79" s="15" t="s">
-        <v>197</v>
+      <c r="A79" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>99</v>
+        <v>17</v>
       </c>
       <c r="G79" s="7"/>
       <c r="H79" s="7"/>
       <c r="I79" s="7" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J79" s="7" t="s">
-        <v>296</v>
+        <v>249</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="1"/>
     </row>
     <row r="80" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A80" s="15" t="s">
-        <v>197</v>
+      <c r="A80" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
       <c r="I80" s="7" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J80" s="7" t="s">
-        <v>297</v>
+        <v>250</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="1"/>
     </row>
     <row r="81" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A81" s="15" t="s">
-        <v>197</v>
+      <c r="A81" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="G81" s="7"/>
       <c r="H81" s="7"/>
       <c r="I81" s="7" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J81" s="7" t="s">
-        <v>298</v>
+        <v>251</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="1"/>
     </row>
     <row r="82" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A82" s="15" t="s">
-        <v>197</v>
+      <c r="A82" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="G82" s="7"/>
       <c r="H82" s="7"/>
       <c r="I82" s="7" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J82" s="7" t="s">
-        <v>299</v>
+        <v>252</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="1"/>
     </row>
     <row r="83" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A83" s="15" t="s">
-        <v>197</v>
+      <c r="A83" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F83" s="7" t="s">
-        <v>111</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F83" s="7"/>
       <c r="G83" s="7"/>
       <c r="H83" s="7"/>
       <c r="I83" s="7" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="J83" s="7" t="s">
-        <v>300</v>
+        <v>253</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="1"/>
     </row>
     <row r="84" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A84" s="15" t="s">
-        <v>197</v>
+      <c r="A84" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="E84" s="7" t="s">
         <v>12</v>
@@ -4455,26 +4444,26 @@
       <c r="G84" s="7"/>
       <c r="H84" s="7"/>
       <c r="I84" s="7" t="s">
-        <v>113</v>
+        <v>354</v>
       </c>
       <c r="J84" s="7" t="s">
-        <v>301</v>
+        <v>254</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="1"/>
     </row>
     <row r="85" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A85" s="15" t="s">
-        <v>197</v>
+      <c r="A85" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="E85" s="7" t="s">
         <v>12</v>
@@ -4483,84 +4472,84 @@
       <c r="G85" s="7"/>
       <c r="H85" s="7"/>
       <c r="I85" s="7" t="s">
-        <v>115</v>
+        <v>376</v>
       </c>
       <c r="J85" s="7" t="s">
-        <v>302</v>
+        <v>255</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="1"/>
     </row>
     <row r="86" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A86" s="15" t="s">
-        <v>197</v>
+      <c r="A86" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F86" s="7"/>
+        <v>16</v>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="G86" s="7"/>
       <c r="H86" s="7"/>
       <c r="I86" s="7" t="s">
-        <v>117</v>
+        <v>389</v>
       </c>
       <c r="J86" s="7" t="s">
-        <v>303</v>
+        <v>256</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="1"/>
     </row>
     <row r="87" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A87" s="15" t="s">
-        <v>197</v>
+      <c r="A87" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>118</v>
+        <v>162</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F87" s="7" t="s">
-        <v>43</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F87" s="7"/>
       <c r="G87" s="7"/>
       <c r="H87" s="7"/>
       <c r="I87" s="7" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="J87" s="7" t="s">
-        <v>304</v>
+        <v>257</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="1"/>
     </row>
     <row r="88" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A88" s="15" t="s">
-        <v>197</v>
+      <c r="A88" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>189</v>
+        <v>150</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>205</v>
+        <v>161</v>
       </c>
       <c r="E88" s="7" t="s">
         <v>12</v>
@@ -4569,26 +4558,26 @@
       <c r="G88" s="7"/>
       <c r="H88" s="7"/>
       <c r="I88" s="7" t="s">
-        <v>202</v>
+        <v>355</v>
       </c>
       <c r="J88" s="7" t="s">
-        <v>305</v>
+        <v>258</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="1"/>
     </row>
     <row r="89" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A89" s="15" t="s">
-        <v>197</v>
+      <c r="A89" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>189</v>
+        <v>150</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>204</v>
+        <v>49</v>
       </c>
       <c r="E89" s="7" t="s">
         <v>12</v>
@@ -4597,26 +4586,26 @@
       <c r="G89" s="7"/>
       <c r="H89" s="7"/>
       <c r="I89" s="7" t="s">
-        <v>203</v>
+        <v>378</v>
       </c>
       <c r="J89" s="7" t="s">
-        <v>306</v>
+        <v>259</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="1"/>
     </row>
     <row r="90" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A90" s="15" t="s">
-        <v>197</v>
+      <c r="A90" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>189</v>
+        <v>96</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="E90" s="7" t="s">
         <v>12</v>
@@ -4625,198 +4614,198 @@
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
       <c r="I90" s="7" t="s">
-        <v>62</v>
+        <v>379</v>
       </c>
       <c r="J90" s="7" t="s">
-        <v>307</v>
+        <v>260</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="1"/>
     </row>
     <row r="91" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A91" s="15" t="s">
-        <v>197</v>
+      <c r="A91" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="F91" s="7"/>
       <c r="G91" s="7"/>
       <c r="H91" s="7"/>
-      <c r="I91" s="9" t="s">
-        <v>216</v>
+      <c r="I91" s="7" t="s">
+        <v>365</v>
       </c>
       <c r="J91" s="7" t="s">
-        <v>308</v>
+        <v>261</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="1"/>
     </row>
     <row r="92" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A92" s="15" t="s">
-        <v>197</v>
+      <c r="A92" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="F92" s="7"/>
+        <v>16</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>100</v>
+      </c>
       <c r="G92" s="7"/>
       <c r="H92" s="7"/>
       <c r="I92" s="7" t="s">
-        <v>373</v>
+        <v>389</v>
       </c>
       <c r="J92" s="7" t="s">
-        <v>309</v>
+        <v>262</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="1"/>
     </row>
     <row r="93" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A93" s="15" t="s">
-        <v>197</v>
+      <c r="A93" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="G93" s="7"/>
       <c r="H93" s="7"/>
       <c r="I93" s="7" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>310</v>
+        <v>263</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="1"/>
     </row>
     <row r="94" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A94" s="15" t="s">
-        <v>197</v>
+      <c r="A94" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F94" s="7" t="s">
-        <v>99</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F94" s="7"/>
       <c r="G94" s="7"/>
       <c r="H94" s="7"/>
       <c r="I94" s="7" t="s">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="J94" s="7" t="s">
-        <v>311</v>
+        <v>264</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="1"/>
     </row>
     <row r="95" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A95" s="15" t="s">
-        <v>197</v>
+      <c r="A95" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="F95" s="7"/>
       <c r="G95" s="7"/>
       <c r="H95" s="7"/>
       <c r="I95" s="7" t="s">
-        <v>126</v>
+        <v>365</v>
       </c>
       <c r="J95" s="7" t="s">
-        <v>312</v>
+        <v>265</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="1"/>
     </row>
     <row r="96" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A96" s="15" t="s">
-        <v>197</v>
+      <c r="A96" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="D96" s="7" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="E96" s="7" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="F96" s="7"/>
       <c r="G96" s="7"/>
       <c r="H96" s="7"/>
       <c r="I96" s="7" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="J96" s="7" t="s">
-        <v>313</v>
+        <v>266</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="1"/>
     </row>
     <row r="97" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A97" s="15" t="s">
-        <v>197</v>
+      <c r="A97" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="E97" s="7" t="s">
         <v>12</v>
@@ -4825,26 +4814,26 @@
       <c r="G97" s="7"/>
       <c r="H97" s="7"/>
       <c r="I97" s="7" t="s">
-        <v>129</v>
+        <v>381</v>
       </c>
       <c r="J97" s="7" t="s">
-        <v>314</v>
+        <v>267</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="1"/>
     </row>
     <row r="98" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A98" s="15" t="s">
-        <v>197</v>
+      <c r="A98" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="D98" s="7" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="E98" s="7" t="s">
         <v>12</v>
@@ -4853,1216 +4842,1216 @@
       <c r="G98" s="7"/>
       <c r="H98" s="7"/>
       <c r="I98" s="7" t="s">
-        <v>132</v>
+        <v>382</v>
       </c>
       <c r="J98" s="7" t="s">
-        <v>315</v>
+        <v>268</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="1"/>
     </row>
     <row r="99" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A99" s="15" t="s">
-        <v>197</v>
+      <c r="A99" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F99" s="7"/>
       <c r="G99" s="7"/>
       <c r="H99" s="7"/>
       <c r="I99" s="7" t="s">
-        <v>134</v>
+        <v>389</v>
       </c>
       <c r="J99" s="7" t="s">
-        <v>316</v>
+        <v>269</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="1"/>
     </row>
     <row r="100" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A100" s="15" t="s">
-        <v>197</v>
+      <c r="A100" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="E100" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F100" s="7"/>
+        <v>16</v>
+      </c>
+      <c r="F100" s="7" t="s">
+        <v>17</v>
+      </c>
       <c r="G100" s="7"/>
       <c r="H100" s="7"/>
       <c r="I100" s="7" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J100" s="7" t="s">
-        <v>317</v>
+        <v>270</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="1"/>
     </row>
     <row r="101" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A101" s="15" t="s">
-        <v>197</v>
+      <c r="A101" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F101" s="7" t="s">
-        <v>20</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F101" s="7"/>
       <c r="G101" s="7"/>
       <c r="H101" s="7"/>
       <c r="I101" s="7" t="s">
-        <v>370</v>
+        <v>351</v>
       </c>
       <c r="J101" s="7" t="s">
-        <v>318</v>
+        <v>271</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="1"/>
     </row>
     <row r="102" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A102" s="15" t="s">
-        <v>197</v>
+      <c r="A102" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F102" s="7"/>
+        <v>16</v>
+      </c>
+      <c r="F102" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="G102" s="7"/>
       <c r="H102" s="7"/>
       <c r="I102" s="7" t="s">
-        <v>138</v>
+        <v>389</v>
       </c>
       <c r="J102" s="7" t="s">
-        <v>319</v>
+        <v>272</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="1"/>
     </row>
     <row r="103" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A103" s="15" t="s">
-        <v>197</v>
+      <c r="A103" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="G103" s="7"/>
       <c r="H103" s="7"/>
       <c r="I103" s="7" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J103" s="7" t="s">
-        <v>320</v>
+        <v>273</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="1"/>
     </row>
     <row r="104" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A104" s="15" t="s">
-        <v>197</v>
+      <c r="A104" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="E104" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="G104" s="7"/>
       <c r="H104" s="7"/>
       <c r="I104" s="7" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J104" s="7" t="s">
-        <v>321</v>
+        <v>274</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="1"/>
     </row>
     <row r="105" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A105" s="15" t="s">
-        <v>197</v>
+      <c r="A105" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G105" s="7"/>
       <c r="H105" s="7"/>
       <c r="I105" s="7" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J105" s="7" t="s">
-        <v>322</v>
+        <v>275</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="1"/>
     </row>
     <row r="106" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A106" s="15" t="s">
-        <v>197</v>
+      <c r="A106" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="G106" s="7"/>
       <c r="H106" s="7"/>
       <c r="I106" s="7" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J106" s="7" t="s">
-        <v>323</v>
+        <v>276</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="1"/>
     </row>
     <row r="107" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A107" s="15" t="s">
-        <v>197</v>
+      <c r="A107" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="D107" s="7" t="s">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F107" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F107" s="7"/>
       <c r="G107" s="7"/>
-      <c r="H107" s="7"/>
+      <c r="H107" s="7" t="s">
+        <v>315</v>
+      </c>
       <c r="I107" s="7" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="J107" s="7" t="s">
-        <v>324</v>
+        <v>277</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="1"/>
     </row>
     <row r="108" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A108" s="15" t="s">
-        <v>197</v>
+      <c r="A108" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="D108" s="7" t="s">
-        <v>219</v>
+        <v>105</v>
+      </c>
+      <c r="D108" s="9" t="s">
+        <v>173</v>
       </c>
       <c r="E108" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F108" s="7"/>
+        <v>16</v>
+      </c>
+      <c r="F108" s="7" t="s">
+        <v>34</v>
+      </c>
       <c r="G108" s="7"/>
-      <c r="H108" s="7" t="s">
-        <v>364</v>
-      </c>
+      <c r="H108" s="7"/>
       <c r="I108" s="7" t="s">
-        <v>221</v>
+        <v>389</v>
       </c>
       <c r="J108" s="7" t="s">
-        <v>325</v>
+        <v>278</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="1"/>
     </row>
     <row r="109" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A109" s="15" t="s">
-        <v>197</v>
+      <c r="A109" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="D109" s="9" t="s">
-        <v>220</v>
+        <v>105</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>116</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F109" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="F109" s="7"/>
       <c r="G109" s="7"/>
       <c r="H109" s="7"/>
       <c r="I109" s="7" t="s">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="J109" s="7" t="s">
-        <v>326</v>
+        <v>279</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="1"/>
     </row>
     <row r="110" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A110" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="B110" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="C110" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="D110" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="E110" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F110" s="7"/>
-      <c r="G110" s="7"/>
-      <c r="H110" s="7"/>
-      <c r="I110" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="J110" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="K110" s="7"/>
+        <v>158</v>
+      </c>
+      <c r="B110" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="C110" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="D110" s="15" t="s">
+        <v>343</v>
+      </c>
+      <c r="E110" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="F110" s="15"/>
+      <c r="G110" s="15"/>
+      <c r="H110" s="15"/>
+      <c r="I110" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="J110" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="K110" s="15"/>
       <c r="L110" s="1"/>
     </row>
     <row r="111" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A111" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="B111" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="C111" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="D111" s="7" t="s">
+      <c r="A111" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="B111" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="C111" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="D111" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="E111" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F111" s="17"/>
+      <c r="G111" s="17"/>
+      <c r="H111" s="17"/>
+      <c r="I111" s="17" t="s">
+        <v>384</v>
+      </c>
+      <c r="J111" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="K111" s="17"/>
+      <c r="L111" s="1"/>
+    </row>
+    <row r="112" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="A112" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="B112" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="C112" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="D112" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="E112" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F112" s="17"/>
+      <c r="G112" s="17"/>
+      <c r="H112" s="17"/>
+      <c r="I112" s="17" t="s">
+        <v>385</v>
+      </c>
+      <c r="J112" s="17" t="s">
+        <v>281</v>
+      </c>
+      <c r="K112" s="17"/>
+      <c r="L112" s="1"/>
+    </row>
+    <row r="113" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="A113" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="B113" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="C113" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="D113" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="E113" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F113" s="17"/>
+      <c r="G113" s="17"/>
+      <c r="H113" s="17"/>
+      <c r="I113" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="J113" s="17" t="s">
+        <v>282</v>
+      </c>
+      <c r="K113" s="17"/>
+      <c r="L113" s="1"/>
+    </row>
+    <row r="114" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="A114" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="B114" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="C114" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="D114" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="E114" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F114" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="G114" s="17"/>
+      <c r="H114" s="17"/>
+      <c r="I114" s="17" t="s">
+        <v>392</v>
+      </c>
+      <c r="J114" s="17" t="s">
+        <v>283</v>
+      </c>
+      <c r="K114" s="17"/>
+      <c r="L114" s="1"/>
+    </row>
+    <row r="115" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="A115" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="B115" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C115" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D115" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="E115" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F115" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="G115" s="17"/>
+      <c r="H115" s="17"/>
+      <c r="I115" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="J115" s="17" t="s">
+        <v>284</v>
+      </c>
+      <c r="K115" s="17"/>
+      <c r="L115" s="1"/>
+    </row>
+    <row r="116" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="A116" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="B116" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C116" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D116" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="E116" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F116" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="G116" s="17"/>
+      <c r="H116" s="17"/>
+      <c r="I116" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="J116" s="17" t="s">
+        <v>285</v>
+      </c>
+      <c r="K116" s="17"/>
+      <c r="L116" s="1"/>
+    </row>
+    <row r="117" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="A117" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="B117" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C117" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D117" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="E117" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F117" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="G117" s="17"/>
+      <c r="H117" s="17"/>
+      <c r="I117" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="J117" s="17" t="s">
+        <v>286</v>
+      </c>
+      <c r="K117" s="17"/>
+      <c r="L117" s="1"/>
+    </row>
+    <row r="118" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="A118" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="B118" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C118" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D118" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="E118" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F118" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="G118" s="17"/>
+      <c r="H118" s="17"/>
+      <c r="I118" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="J118" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="K118" s="17"/>
+      <c r="L118" s="1"/>
+    </row>
+    <row r="119" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="A119" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="B119" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C119" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D119" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="E119" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F119" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="G119" s="17"/>
+      <c r="H119" s="17"/>
+      <c r="I119" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="J119" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="K119" s="17"/>
+      <c r="L119" s="1"/>
+    </row>
+    <row r="120" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="A120" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="B120" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C120" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D120" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="E120" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F120" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="G120" s="17"/>
+      <c r="H120" s="17"/>
+      <c r="I120" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="J120" s="17" t="s">
+        <v>289</v>
+      </c>
+      <c r="K120" s="17"/>
+      <c r="L120" s="1"/>
+    </row>
+    <row r="121" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="A121" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="B121" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C121" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D121" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="E121" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F121" s="17"/>
+      <c r="G121" s="17"/>
+      <c r="H121" s="17"/>
+      <c r="I121" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="J121" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="K121" s="17"/>
+      <c r="L121" s="1"/>
+    </row>
+    <row r="122" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="A122" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="B122" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C122" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D122" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="E122" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F122" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="G122" s="17"/>
+      <c r="H122" s="17"/>
+      <c r="I122" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="J122" s="17" t="s">
+        <v>291</v>
+      </c>
+      <c r="K122" s="17"/>
+      <c r="L122" s="1"/>
+    </row>
+    <row r="123" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="A123" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="B123" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C123" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D123" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="E123" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F123" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="G123" s="17"/>
+      <c r="H123" s="17"/>
+      <c r="I123" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="J123" s="17" t="s">
+        <v>292</v>
+      </c>
+      <c r="K123" s="17"/>
+      <c r="L123" s="1"/>
+    </row>
+    <row r="124" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="A124" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="B124" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C124" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D124" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="E124" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F124" s="17"/>
+      <c r="G124" s="17"/>
+      <c r="H124" s="17"/>
+      <c r="I124" s="17" t="s">
+        <v>356</v>
+      </c>
+      <c r="J124" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="K124" s="17"/>
+      <c r="L124" s="1"/>
+    </row>
+    <row r="125" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="A125" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="B125" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C125" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D125" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="E125" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F125" s="17"/>
+      <c r="G125" s="17"/>
+      <c r="H125" s="17"/>
+      <c r="I125" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="J125" s="17" t="s">
+        <v>294</v>
+      </c>
+      <c r="K125" s="17"/>
+      <c r="L125" s="1"/>
+    </row>
+    <row r="126" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="A126" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="B126" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C126" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D126" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="E126" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F126" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="G126" s="17"/>
+      <c r="H126" s="17"/>
+      <c r="I126" s="17" t="s">
+        <v>395</v>
+      </c>
+      <c r="J126" s="17" t="s">
+        <v>295</v>
+      </c>
+      <c r="K126" s="17"/>
+      <c r="L126" s="1"/>
+    </row>
+    <row r="127" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="A127" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="B127" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C127" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D127" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="E111" s="7" t="s">
+      <c r="E127" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F127" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="G127" s="17"/>
+      <c r="H127" s="17"/>
+      <c r="I127" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="J127" s="17" t="s">
+        <v>296</v>
+      </c>
+      <c r="K127" s="17"/>
+      <c r="L127" s="1"/>
+    </row>
+    <row r="128" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="A128" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="B128" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C128" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D128" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="E128" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F128" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="G128" s="17"/>
+      <c r="H128" s="17"/>
+      <c r="I128" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="J128" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="K128" s="17"/>
+      <c r="L128" s="1"/>
+    </row>
+    <row r="129" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="A129" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="B129" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C129" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D129" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E129" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F129" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="G129" s="17"/>
+      <c r="H129" s="17"/>
+      <c r="I129" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="J129" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="K129" s="17"/>
+      <c r="L129" s="1"/>
+    </row>
+    <row r="130" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="A130" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="B130" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C130" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D130" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="E130" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F130" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="G130" s="17"/>
+      <c r="H130" s="17"/>
+      <c r="I130" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="J130" s="17" t="s">
+        <v>299</v>
+      </c>
+      <c r="K130" s="17"/>
+      <c r="L130" s="1"/>
+    </row>
+    <row r="131" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="A131" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="B131" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C131" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D131" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="E131" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F131" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="G131" s="17"/>
+      <c r="H131" s="17"/>
+      <c r="I131" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="J131" s="17" t="s">
+        <v>300</v>
+      </c>
+      <c r="K131" s="17"/>
+      <c r="L131" s="1"/>
+    </row>
+    <row r="132" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="A132" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="B132" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C132" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D132" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="E132" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F132" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="G132" s="17"/>
+      <c r="H132" s="17"/>
+      <c r="I132" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="J132" s="17" t="s">
+        <v>301</v>
+      </c>
+      <c r="K132" s="17"/>
+      <c r="L132" s="1"/>
+    </row>
+    <row r="133" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="A133" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="B133" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C133" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D133" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="E133" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F133" s="17"/>
+      <c r="G133" s="17"/>
+      <c r="H133" s="17"/>
+      <c r="I133" s="17" t="s">
+        <v>392</v>
+      </c>
+      <c r="J133" s="17" t="s">
+        <v>302</v>
+      </c>
+      <c r="K133" s="17"/>
+      <c r="L133" s="1"/>
+    </row>
+    <row r="134" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="A134" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="B134" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C134" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D134" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="E134" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="F111" s="7"/>
-      <c r="G111" s="7"/>
-      <c r="H111" s="7"/>
-      <c r="I111" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="J111" s="7" t="s">
-        <v>328</v>
-      </c>
-      <c r="K111" s="7"/>
-      <c r="L111" s="1"/>
-    </row>
-    <row r="112" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A112" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="B112" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="C112" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="D112" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E112" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F112" s="7"/>
-      <c r="G112" s="7"/>
-      <c r="H112" s="7"/>
-      <c r="I112" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="J112" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="K112" s="7"/>
-      <c r="L112" s="1"/>
-    </row>
-    <row r="113" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A113" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="B113" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="C113" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="D113" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="E113" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F113" s="7"/>
-      <c r="G113" s="7"/>
-      <c r="H113" s="7"/>
-      <c r="I113" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="J113" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="K113" s="7"/>
-      <c r="L113" s="1"/>
-    </row>
-    <row r="114" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A114" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="B114" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="C114" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="D114" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="E114" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F114" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G114" s="7"/>
-      <c r="H114" s="7"/>
-      <c r="I114" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="J114" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="K114" s="7"/>
-      <c r="L114" s="1"/>
-    </row>
-    <row r="115" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A115" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="B115" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C115" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="D115" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E115" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F115" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="G115" s="14"/>
-      <c r="H115" s="14"/>
-      <c r="I115" s="14" t="s">
-        <v>370</v>
-      </c>
-      <c r="J115" s="14" t="s">
-        <v>333</v>
-      </c>
-      <c r="K115" s="14"/>
-      <c r="L115" s="1"/>
-    </row>
-    <row r="116" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A116" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="B116" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C116" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="D116" s="14" t="s">
+      <c r="F134" s="17"/>
+      <c r="G134" s="17"/>
+      <c r="H134" s="17"/>
+      <c r="I134" s="17" t="s">
+        <v>393</v>
+      </c>
+      <c r="J134" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="K134" s="17"/>
+      <c r="L134" s="1"/>
+    </row>
+    <row r="135" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="A135" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="B135" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C135" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D135" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="E135" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F135" s="17"/>
+      <c r="G135" s="17"/>
+      <c r="H135" s="17"/>
+      <c r="I135" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="J135" s="17" t="s">
+        <v>304</v>
+      </c>
+      <c r="K135" s="17"/>
+      <c r="L135" s="1"/>
+    </row>
+    <row r="136" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="A136" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="B136" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C136" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D136" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="E116" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F116" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="G116" s="14"/>
-      <c r="H116" s="14"/>
-      <c r="I116" s="14" t="s">
-        <v>370</v>
-      </c>
-      <c r="J116" s="14" t="s">
-        <v>334</v>
-      </c>
-      <c r="K116" s="14"/>
-      <c r="L116" s="1"/>
-    </row>
-    <row r="117" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A117" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="B117" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C117" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="D117" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="E117" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F117" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="G117" s="14"/>
-      <c r="H117" s="14"/>
-      <c r="I117" s="14" t="s">
-        <v>370</v>
-      </c>
-      <c r="J117" s="14" t="s">
-        <v>335</v>
-      </c>
-      <c r="K117" s="14"/>
-      <c r="L117" s="1"/>
-    </row>
-    <row r="118" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A118" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="B118" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C118" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="D118" s="14" t="s">
+      <c r="E136" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F136" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="E118" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F118" s="14" t="s">
+      <c r="G136" s="17"/>
+      <c r="H136" s="17"/>
+      <c r="I136" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="J136" s="17" t="s">
+        <v>305</v>
+      </c>
+      <c r="K136" s="17"/>
+      <c r="L136" s="1"/>
+    </row>
+    <row r="137" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="A137" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="B137" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C137" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D137" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="G118" s="14"/>
-      <c r="H118" s="14"/>
-      <c r="I118" s="14" t="s">
-        <v>370</v>
-      </c>
-      <c r="J118" s="14" t="s">
-        <v>336</v>
-      </c>
-      <c r="K118" s="14"/>
-      <c r="L118" s="1"/>
-    </row>
-    <row r="119" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A119" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="B119" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C119" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="D119" s="14" t="s">
-        <v>206</v>
-      </c>
-      <c r="E119" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F119" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="G119" s="14"/>
-      <c r="H119" s="14"/>
-      <c r="I119" s="14" t="s">
-        <v>370</v>
-      </c>
-      <c r="J119" s="14" t="s">
-        <v>337</v>
-      </c>
-      <c r="K119" s="14"/>
-      <c r="L119" s="1"/>
-    </row>
-    <row r="120" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A120" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="B120" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C120" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="D120" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="E120" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F120" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="G120" s="14"/>
-      <c r="H120" s="14"/>
-      <c r="I120" s="14" t="s">
-        <v>370</v>
-      </c>
-      <c r="J120" s="14" t="s">
-        <v>338</v>
-      </c>
-      <c r="K120" s="14"/>
-      <c r="L120" s="1"/>
-    </row>
-    <row r="121" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A121" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="B121" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C121" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="D121" s="14" t="s">
+      <c r="E137" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F137" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="G137" s="17"/>
+      <c r="H137" s="17"/>
+      <c r="I137" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="J137" s="17" t="s">
+        <v>306</v>
+      </c>
+      <c r="K137" s="17"/>
+      <c r="L137" s="1"/>
+    </row>
+    <row r="138" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="A138" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="B138" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C138" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D138" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="E121" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F121" s="14"/>
-      <c r="G121" s="14"/>
-      <c r="H121" s="14"/>
-      <c r="I121" s="14" t="s">
-        <v>370</v>
-      </c>
-      <c r="J121" s="14" t="s">
-        <v>339</v>
-      </c>
-      <c r="K121" s="14"/>
-      <c r="L121" s="1"/>
-    </row>
-    <row r="122" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A122" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="B122" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C122" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="D122" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="E122" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F122" s="14" t="s">
+      <c r="E138" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F138" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="G122" s="14"/>
-      <c r="H122" s="14"/>
-      <c r="I122" s="14" t="s">
-        <v>370</v>
-      </c>
-      <c r="J122" s="14" t="s">
-        <v>340</v>
-      </c>
-      <c r="K122" s="14"/>
-      <c r="L122" s="1"/>
-    </row>
-    <row r="123" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A123" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="B123" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C123" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="D123" s="14" t="s">
-        <v>210</v>
-      </c>
-      <c r="E123" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F123" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="G123" s="14"/>
-      <c r="H123" s="14"/>
-      <c r="I123" s="14" t="s">
-        <v>370</v>
-      </c>
-      <c r="J123" s="14" t="s">
+      <c r="G138" s="17"/>
+      <c r="H138" s="17"/>
+      <c r="I138" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="J138" s="17" t="s">
+        <v>307</v>
+      </c>
+      <c r="K138" s="17"/>
+      <c r="L138" s="1"/>
+    </row>
+    <row r="139" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="A139" s="17" t="s">
         <v>341</v>
       </c>
-      <c r="K123" s="14"/>
-      <c r="L123" s="1"/>
-    </row>
-    <row r="124" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A124" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="B124" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C124" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="D124" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="E124" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F124" s="14"/>
-      <c r="G124" s="14"/>
-      <c r="H124" s="14"/>
-      <c r="I124" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="J124" s="14" t="s">
-        <v>342</v>
-      </c>
-      <c r="K124" s="14"/>
-      <c r="L124" s="1"/>
-    </row>
-    <row r="125" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A125" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="B125" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C125" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="D125" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="E125" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F125" s="14"/>
-      <c r="G125" s="14"/>
-      <c r="H125" s="14"/>
-      <c r="I125" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="J125" s="14" t="s">
-        <v>343</v>
-      </c>
-      <c r="K125" s="14"/>
-      <c r="L125" s="1"/>
-    </row>
-    <row r="126" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A126" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="B126" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C126" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="D126" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="E126" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="F126" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="G126" s="14"/>
-      <c r="H126" s="14"/>
-      <c r="I126" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="J126" s="14" t="s">
-        <v>344</v>
-      </c>
-      <c r="K126" s="14"/>
-      <c r="L126" s="1"/>
-    </row>
-    <row r="127" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A127" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="B127" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C127" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="D127" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="E127" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F127" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="G127" s="14"/>
-      <c r="H127" s="14"/>
-      <c r="I127" s="14" t="s">
-        <v>370</v>
-      </c>
-      <c r="J127" s="14" t="s">
-        <v>345</v>
-      </c>
-      <c r="K127" s="14"/>
-      <c r="L127" s="1"/>
-    </row>
-    <row r="128" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A128" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="B128" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C128" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="D128" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="E128" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F128" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="G128" s="14"/>
-      <c r="H128" s="14"/>
-      <c r="I128" s="14" t="s">
-        <v>370</v>
-      </c>
-      <c r="J128" s="14" t="s">
-        <v>346</v>
-      </c>
-      <c r="K128" s="14"/>
-      <c r="L128" s="1"/>
-    </row>
-    <row r="129" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A129" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="B129" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C129" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="D129" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="E129" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F129" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="G129" s="14"/>
-      <c r="H129" s="14"/>
-      <c r="I129" s="14" t="s">
-        <v>370</v>
-      </c>
-      <c r="J129" s="14" t="s">
-        <v>347</v>
-      </c>
-      <c r="K129" s="14"/>
-      <c r="L129" s="1"/>
-    </row>
-    <row r="130" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A130" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="B130" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C130" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="D130" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="E130" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F130" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="G130" s="14"/>
-      <c r="H130" s="14"/>
-      <c r="I130" s="14" t="s">
-        <v>370</v>
-      </c>
-      <c r="J130" s="14" t="s">
-        <v>348</v>
-      </c>
-      <c r="K130" s="14"/>
-      <c r="L130" s="1"/>
-    </row>
-    <row r="131" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A131" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="B131" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C131" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="D131" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="E131" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F131" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="G131" s="14"/>
-      <c r="H131" s="14"/>
-      <c r="I131" s="14" t="s">
-        <v>370</v>
-      </c>
-      <c r="J131" s="14" t="s">
-        <v>349</v>
-      </c>
-      <c r="K131" s="14"/>
-      <c r="L131" s="1"/>
-    </row>
-    <row r="132" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A132" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="B132" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C132" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="D132" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="E132" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F132" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="G132" s="14"/>
-      <c r="H132" s="14"/>
-      <c r="I132" s="14" t="s">
-        <v>370</v>
-      </c>
-      <c r="J132" s="14" t="s">
-        <v>350</v>
-      </c>
-      <c r="K132" s="14"/>
-      <c r="L132" s="1"/>
-    </row>
-    <row r="133" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A133" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="B133" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C133" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="D133" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="E133" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F133" s="14"/>
-      <c r="G133" s="14"/>
-      <c r="H133" s="14"/>
-      <c r="I133" s="14" t="s">
-        <v>371</v>
-      </c>
-      <c r="J133" s="14" t="s">
-        <v>351</v>
-      </c>
-      <c r="K133" s="14"/>
-      <c r="L133" s="1"/>
-    </row>
-    <row r="134" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A134" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="B134" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C134" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="D134" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="E134" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F134" s="14"/>
-      <c r="G134" s="14"/>
-      <c r="H134" s="14"/>
-      <c r="I134" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="J134" s="14" t="s">
-        <v>352</v>
-      </c>
-      <c r="K134" s="14"/>
-      <c r="L134" s="1"/>
-    </row>
-    <row r="135" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A135" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="B135" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C135" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="D135" s="14" t="s">
-        <v>215</v>
-      </c>
-      <c r="E135" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F135" s="14"/>
-      <c r="G135" s="14"/>
-      <c r="H135" s="14"/>
-      <c r="I135" s="14" t="s">
-        <v>370</v>
-      </c>
-      <c r="J135" s="14" t="s">
-        <v>353</v>
-      </c>
-      <c r="K135" s="14"/>
-      <c r="L135" s="1"/>
-    </row>
-    <row r="136" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A136" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="B136" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C136" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="D136" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="E136" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F136" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="G136" s="14"/>
-      <c r="H136" s="14"/>
-      <c r="I136" s="14" t="s">
-        <v>370</v>
-      </c>
-      <c r="J136" s="14" t="s">
-        <v>354</v>
-      </c>
-      <c r="K136" s="14"/>
-      <c r="L136" s="1"/>
-    </row>
-    <row r="137" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A137" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="B137" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C137" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="D137" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="E137" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F137" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="G137" s="14"/>
-      <c r="H137" s="14"/>
-      <c r="I137" s="14" t="s">
-        <v>370</v>
-      </c>
-      <c r="J137" s="14" t="s">
-        <v>355</v>
-      </c>
-      <c r="K137" s="14"/>
-      <c r="L137" s="1"/>
-    </row>
-    <row r="138" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A138" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="B138" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C138" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="D138" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="E138" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F138" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="G138" s="14"/>
-      <c r="H138" s="14"/>
-      <c r="I138" s="14" t="s">
-        <v>370</v>
-      </c>
-      <c r="J138" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="K138" s="14"/>
-      <c r="L138" s="1"/>
-    </row>
-    <row r="139" spans="1:12" ht="14" x14ac:dyDescent="0.3">
-      <c r="A139" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="B139" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C139" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="D139" s="14" t="s">
-        <v>375</v>
-      </c>
-      <c r="E139" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F139" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="G139" s="14"/>
-      <c r="H139" s="14"/>
-      <c r="I139" s="14" t="s">
-        <v>370</v>
-      </c>
-      <c r="J139" s="14" t="s">
-        <v>357</v>
-      </c>
-      <c r="K139" s="14"/>
+      <c r="B139" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C139" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D139" s="17" t="s">
+        <v>319</v>
+      </c>
+      <c r="E139" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F139" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="G139" s="17"/>
+      <c r="H139" s="17"/>
+      <c r="I139" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="J139" s="17" t="s">
+        <v>308</v>
+      </c>
+      <c r="K139" s="17"/>
       <c r="L139" s="1"/>
     </row>
   </sheetData>

--- a/MASTER.xlsx
+++ b/MASTER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Javid Shiriyev\Documents\GitHub\sand-control-failure-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B292F37D-5B0E-4B80-A980-0297D87C0E32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD12FE5-5B6C-484D-BC41-C4107A12EB9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38510" yWindow="-2730" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="395">
   <si>
     <t>Category</t>
   </si>
@@ -167,9 +167,6 @@
     <t>Additional Bridging Agent</t>
   </si>
   <si>
-    <t>Mud PSD</t>
-  </si>
-  <si>
     <t>PSD Test Volume</t>
   </si>
   <si>
@@ -545,9 +542,6 @@
     <t>Source of sand sample</t>
   </si>
   <si>
-    <t>Particle Size Distribution D10/D25/D40/D50/D75/D90</t>
-  </si>
-  <si>
     <t>Oil Formation Volume Factor (Bo) at downhole conditions</t>
   </si>
   <si>
@@ -1220,10 +1214,13 @@
     <t>{"List": ["Oil", "Condensate", "Wet Gas", "Dry Gas"]}</t>
   </si>
   <si>
-    <t>{["Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}]}</t>
-  </si>
-  <si>
-    <t>{["Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}]}</t>
+    <t>{["Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}]}</t>
+  </si>
+  <si>
+    <t>PSD D10/D25/D40/D50/D75/D90</t>
+  </si>
+  <si>
+    <t>Mud PSD D10/D25/D40/D50/D75/D90</t>
   </si>
 </sst>
 </file>
@@ -2039,10 +2036,10 @@
         <v>6</v>
       </c>
       <c r="J1" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="L1" s="1"/>
     </row>
@@ -2057,7 +2054,7 @@
         <v>10</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>12</v>
@@ -2066,10 +2063,10 @@
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
       <c r="I2" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="K2" s="5"/>
       <c r="L2" s="1"/>
@@ -2085,7 +2082,7 @@
         <v>10</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>12</v>
@@ -2094,10 +2091,10 @@
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
       <c r="I3" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="K3" s="5"/>
       <c r="L3" s="1"/>
@@ -2113,7 +2110,7 @@
         <v>10</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>12</v>
@@ -2122,10 +2119,10 @@
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="5" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="K4" s="5"/>
       <c r="L4" s="1"/>
@@ -2141,7 +2138,7 @@
         <v>10</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>13</v>
@@ -2150,10 +2147,10 @@
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="K5" s="5"/>
       <c r="L5" s="1"/>
@@ -2169,7 +2166,7 @@
         <v>15</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>13</v>
@@ -2178,10 +2175,10 @@
       <c r="G6" s="6"/>
       <c r="H6" s="6"/>
       <c r="I6" s="6" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="K6" s="6"/>
       <c r="L6" s="1"/>
@@ -2197,7 +2194,7 @@
         <v>15</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>16</v>
@@ -2206,10 +2203,10 @@
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
       <c r="I7" s="6" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="K7" s="6"/>
       <c r="L7" s="1"/>
@@ -2225,7 +2222,7 @@
         <v>15</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>12</v>
@@ -2234,10 +2231,10 @@
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
       <c r="I8" s="6" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="K8" s="6"/>
       <c r="L8" s="1"/>
@@ -2253,7 +2250,7 @@
         <v>15</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>12</v>
@@ -2261,13 +2258,13 @@
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
       <c r="H9" s="6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="K9" s="6"/>
       <c r="L9" s="1"/>
@@ -2283,7 +2280,7 @@
         <v>15</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>16</v>
@@ -2294,10 +2291,10 @@
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
       <c r="I10" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K10" s="6"/>
       <c r="L10" s="1"/>
@@ -2313,7 +2310,7 @@
         <v>15</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>12</v>
@@ -2322,10 +2319,10 @@
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
       <c r="I11" s="6" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K11" s="6"/>
       <c r="L11" s="1"/>
@@ -2352,10 +2349,10 @@
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
       <c r="I12" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="K12" s="6"/>
       <c r="L12" s="1"/>
@@ -2371,7 +2368,7 @@
         <v>15</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>16</v>
@@ -2382,10 +2379,10 @@
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
       <c r="I13" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="K13" s="6"/>
       <c r="L13" s="1"/>
@@ -2401,7 +2398,7 @@
         <v>15</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>13</v>
@@ -2410,10 +2407,10 @@
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
       <c r="I14" s="6" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K14" s="6"/>
       <c r="L14" s="1"/>
@@ -2429,7 +2426,7 @@
         <v>15</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>13</v>
@@ -2438,10 +2435,10 @@
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
       <c r="I15" s="6" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K15" s="6"/>
       <c r="L15" s="1"/>
@@ -2457,7 +2454,7 @@
         <v>15</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>12</v>
@@ -2466,10 +2463,10 @@
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
       <c r="I16" s="6" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="K16" s="6"/>
       <c r="L16" s="1"/>
@@ -2494,10 +2491,10 @@
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
       <c r="I17" s="6" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="K17" s="6"/>
       <c r="L17" s="1"/>
@@ -2510,24 +2507,24 @@
         <v>14</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="6" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H18" s="6"/>
       <c r="I18" s="6" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K18" s="6"/>
       <c r="L18" s="1"/>
@@ -2543,7 +2540,7 @@
         <v>20</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>12</v>
@@ -2552,10 +2549,10 @@
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
       <c r="I19" s="6" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="K19" s="6"/>
       <c r="L19" s="1"/>
@@ -2571,7 +2568,7 @@
         <v>20</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>16</v>
@@ -2582,10 +2579,10 @@
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
       <c r="I20" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="K20" s="6"/>
       <c r="L20" s="1"/>
@@ -2601,7 +2598,7 @@
         <v>20</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>16</v>
@@ -2612,10 +2609,10 @@
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
       <c r="I21" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K21" s="6"/>
       <c r="L21" s="1"/>
@@ -2631,7 +2628,7 @@
         <v>20</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>16</v>
@@ -2642,10 +2639,10 @@
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
       <c r="I22" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="K22" s="6"/>
       <c r="L22" s="1"/>
@@ -2661,7 +2658,7 @@
         <v>20</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>12</v>
@@ -2670,10 +2667,10 @@
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
       <c r="I23" s="6" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="K23" s="6"/>
       <c r="L23" s="1"/>
@@ -2689,7 +2686,7 @@
         <v>20</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>12</v>
@@ -2698,10 +2695,10 @@
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
       <c r="I24" s="6" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="K24" s="6"/>
       <c r="L24" s="1"/>
@@ -2717,7 +2714,7 @@
         <v>20</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>12</v>
@@ -2726,10 +2723,10 @@
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
       <c r="I25" s="6" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="K25" s="6"/>
       <c r="L25" s="1"/>
@@ -2745,7 +2742,7 @@
         <v>20</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>16</v>
@@ -2756,10 +2753,10 @@
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
       <c r="I26" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K26" s="6"/>
       <c r="L26" s="1"/>
@@ -2775,7 +2772,7 @@
         <v>20</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>16</v>
@@ -2786,10 +2783,10 @@
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
       <c r="I27" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="K27" s="6"/>
       <c r="L27" s="1"/>
@@ -2805,7 +2802,7 @@
         <v>20</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>16</v>
@@ -2816,10 +2813,10 @@
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
       <c r="I28" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="K28" s="6"/>
       <c r="L28" s="1"/>
@@ -2835,7 +2832,7 @@
         <v>20</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>16</v>
@@ -2846,10 +2843,10 @@
       <c r="G29" s="6"/>
       <c r="H29" s="6"/>
       <c r="I29" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="K29" s="6"/>
       <c r="L29" s="1"/>
@@ -2865,7 +2862,7 @@
         <v>20</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>16</v>
@@ -2874,10 +2871,10 @@
       <c r="G30" s="6"/>
       <c r="H30" s="6"/>
       <c r="I30" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="K30" s="6"/>
       <c r="L30" s="1"/>
@@ -2893,7 +2890,7 @@
         <v>20</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>16</v>
@@ -2902,10 +2899,10 @@
       <c r="G31" s="6"/>
       <c r="H31" s="6"/>
       <c r="I31" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="K31" s="6"/>
       <c r="L31" s="1"/>
@@ -2921,7 +2918,7 @@
         <v>20</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>16</v>
@@ -2930,10 +2927,10 @@
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
       <c r="I32" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="K32" s="6"/>
       <c r="L32" s="1"/>
@@ -2949,7 +2946,7 @@
         <v>20</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>16</v>
@@ -2960,10 +2957,10 @@
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
       <c r="I33" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K33" s="6"/>
       <c r="L33" s="1"/>
@@ -2979,7 +2976,7 @@
         <v>20</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>16</v>
@@ -2988,10 +2985,10 @@
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
       <c r="I34" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="K34" s="6"/>
       <c r="L34" s="1"/>
@@ -3007,7 +3004,7 @@
         <v>20</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>16</v>
@@ -3016,10 +3013,10 @@
       <c r="G35" s="6"/>
       <c r="H35" s="6"/>
       <c r="I35" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="K35" s="6"/>
       <c r="L35" s="1"/>
@@ -3035,7 +3032,7 @@
         <v>20</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>16</v>
@@ -3044,10 +3041,10 @@
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
       <c r="I36" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="K36" s="6"/>
       <c r="L36" s="1"/>
@@ -3072,10 +3069,10 @@
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
       <c r="I37" s="6" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K37" s="6"/>
       <c r="L37" s="1"/>
@@ -3088,10 +3085,10 @@
         <v>14</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>12</v>
@@ -3100,10 +3097,10 @@
       <c r="G38" s="6"/>
       <c r="H38" s="6"/>
       <c r="I38" s="6" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="K38" s="6"/>
       <c r="L38" s="1"/>
@@ -3116,10 +3113,10 @@
         <v>14</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>25</v>
@@ -3128,10 +3125,10 @@
       <c r="G39" s="6"/>
       <c r="H39" s="6"/>
       <c r="I39" s="6" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K39" s="6"/>
       <c r="L39" s="1"/>
@@ -3144,10 +3141,10 @@
         <v>14</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>25</v>
@@ -3156,10 +3153,10 @@
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
       <c r="I40" s="6" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K40" s="6"/>
       <c r="L40" s="1"/>
@@ -3172,10 +3169,10 @@
         <v>14</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>25</v>
@@ -3184,10 +3181,10 @@
       <c r="G41" s="6"/>
       <c r="H41" s="6"/>
       <c r="I41" s="6" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="K41" s="6"/>
       <c r="L41" s="1"/>
@@ -3200,7 +3197,7 @@
         <v>14</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>26</v>
@@ -3214,10 +3211,10 @@
       <c r="G42" s="6"/>
       <c r="H42" s="6"/>
       <c r="I42" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="K42" s="6"/>
       <c r="L42" s="1"/>
@@ -3230,7 +3227,7 @@
         <v>14</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>28</v>
@@ -3244,10 +3241,10 @@
       <c r="G43" s="6"/>
       <c r="H43" s="6"/>
       <c r="I43" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="K43" s="6"/>
       <c r="L43" s="1"/>
@@ -3260,7 +3257,7 @@
         <v>14</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>29</v>
@@ -3274,10 +3271,10 @@
       <c r="G44" s="6"/>
       <c r="H44" s="6"/>
       <c r="I44" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="K44" s="6"/>
       <c r="L44" s="1"/>
@@ -3290,7 +3287,7 @@
         <v>14</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>31</v>
@@ -3304,10 +3301,10 @@
       <c r="G45" s="6"/>
       <c r="H45" s="6"/>
       <c r="I45" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="K45" s="6"/>
       <c r="L45" s="1"/>
@@ -3320,7 +3317,7 @@
         <v>14</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>32</v>
@@ -3334,10 +3331,10 @@
       <c r="G46" s="6"/>
       <c r="H46" s="6"/>
       <c r="I46" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K46" s="6"/>
       <c r="L46" s="1"/>
@@ -3350,7 +3347,7 @@
         <v>14</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>33</v>
@@ -3364,10 +3361,10 @@
       <c r="G47" s="6"/>
       <c r="H47" s="6"/>
       <c r="I47" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="K47" s="6"/>
       <c r="L47" s="1"/>
@@ -3380,10 +3377,10 @@
         <v>14</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>16</v>
@@ -3394,10 +3391,10 @@
       <c r="G48" s="6"/>
       <c r="H48" s="6"/>
       <c r="I48" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="K48" s="6"/>
       <c r="L48" s="1"/>
@@ -3410,10 +3407,10 @@
         <v>14</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E49" s="6" t="s">
         <v>16</v>
@@ -3424,10 +3421,10 @@
       <c r="G49" s="6"/>
       <c r="H49" s="6"/>
       <c r="I49" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K49" s="6"/>
       <c r="L49" s="1"/>
@@ -3440,10 +3437,10 @@
         <v>14</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>16</v>
@@ -3454,10 +3451,10 @@
       <c r="G50" s="6"/>
       <c r="H50" s="6"/>
       <c r="I50" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="K50" s="6"/>
       <c r="L50" s="1"/>
@@ -3470,10 +3467,10 @@
         <v>14</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>16</v>
@@ -3484,10 +3481,10 @@
       <c r="G51" s="6"/>
       <c r="H51" s="6"/>
       <c r="I51" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K51" s="6"/>
       <c r="L51" s="1"/>
@@ -3500,10 +3497,10 @@
         <v>14</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>12</v>
@@ -3511,13 +3508,13 @@
       <c r="F52" s="6"/>
       <c r="G52" s="6"/>
       <c r="H52" s="6" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K52" s="6"/>
       <c r="L52" s="1"/>
@@ -3530,10 +3527,10 @@
         <v>14</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E53" s="6" t="s">
         <v>16</v>
@@ -3544,10 +3541,10 @@
       <c r="G53" s="6"/>
       <c r="H53" s="6"/>
       <c r="I53" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="K53" s="6"/>
       <c r="L53" s="1"/>
@@ -3560,10 +3557,10 @@
         <v>14</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>16</v>
@@ -3574,10 +3571,10 @@
       <c r="G54" s="6"/>
       <c r="H54" s="6"/>
       <c r="I54" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="K54" s="6"/>
       <c r="L54" s="1"/>
@@ -3590,10 +3587,10 @@
         <v>14</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E55" s="6" t="s">
         <v>13</v>
@@ -3602,10 +3599,10 @@
       <c r="G55" s="6"/>
       <c r="H55" s="6"/>
       <c r="I55" s="6" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="K55" s="6"/>
       <c r="L55" s="1"/>
@@ -3618,10 +3615,10 @@
         <v>14</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>16</v>
@@ -3632,10 +3629,10 @@
       <c r="G56" s="6"/>
       <c r="H56" s="6"/>
       <c r="I56" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K56" s="6"/>
       <c r="L56" s="1"/>
@@ -3648,10 +3645,10 @@
         <v>14</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E57" s="6" t="s">
         <v>16</v>
@@ -3662,10 +3659,10 @@
       <c r="G57" s="6"/>
       <c r="H57" s="6"/>
       <c r="I57" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K57" s="6"/>
       <c r="L57" s="1"/>
@@ -3678,10 +3675,10 @@
         <v>14</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>16</v>
@@ -3692,10 +3689,10 @@
       <c r="G58" s="6"/>
       <c r="H58" s="6"/>
       <c r="I58" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="K58" s="6"/>
       <c r="L58" s="1"/>
@@ -3708,10 +3705,10 @@
         <v>14</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E59" s="6" t="s">
         <v>12</v>
@@ -3720,10 +3717,10 @@
       <c r="G59" s="6"/>
       <c r="H59" s="6"/>
       <c r="I59" s="6" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K59" s="6"/>
       <c r="L59" s="1"/>
@@ -3736,10 +3733,10 @@
         <v>14</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>12</v>
@@ -3748,10 +3745,10 @@
       <c r="G60" s="6"/>
       <c r="H60" s="6"/>
       <c r="I60" s="6" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K60" s="6"/>
       <c r="L60" s="1"/>
@@ -3764,10 +3761,10 @@
         <v>14</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E61" s="6" t="s">
         <v>12</v>
@@ -3776,10 +3773,10 @@
       <c r="G61" s="6"/>
       <c r="H61" s="6"/>
       <c r="I61" s="6" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="K61" s="6"/>
       <c r="L61" s="1"/>
@@ -3792,10 +3789,10 @@
         <v>14</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>12</v>
@@ -3804,10 +3801,10 @@
       <c r="G62" s="6"/>
       <c r="H62" s="6"/>
       <c r="I62" s="6" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K62" s="6"/>
       <c r="L62" s="1"/>
@@ -3817,13 +3814,13 @@
         <v>11</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E63" s="12" t="s">
         <v>16</v>
@@ -3832,26 +3829,26 @@
       <c r="G63" s="12"/>
       <c r="H63" s="12"/>
       <c r="I63" s="12" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="K63" s="11"/>
       <c r="L63" s="1"/>
     </row>
     <row r="64" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A64" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>16</v>
@@ -3860,26 +3857,26 @@
       <c r="G64" s="7"/>
       <c r="H64" s="7"/>
       <c r="I64" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="K64" s="7"/>
       <c r="L64" s="1"/>
     </row>
     <row r="65" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A65" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E65" s="7" t="s">
         <v>16</v>
@@ -3888,23 +3885,23 @@
       <c r="G65" s="7"/>
       <c r="H65" s="7"/>
       <c r="I65" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K65" s="7"/>
       <c r="L65" s="1"/>
     </row>
     <row r="66" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A66" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D66" s="7" t="s">
         <v>38</v>
@@ -3916,23 +3913,23 @@
       <c r="G66" s="7"/>
       <c r="H66" s="7"/>
       <c r="I66" s="7" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="J66" s="7" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="1"/>
     </row>
     <row r="67" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A67" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D67" s="7" t="s">
         <v>39</v>
@@ -3946,23 +3943,23 @@
       <c r="G67" s="7"/>
       <c r="H67" s="7"/>
       <c r="I67" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="1"/>
     </row>
     <row r="68" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A68" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D68" s="7" t="s">
         <v>41</v>
@@ -3974,23 +3971,23 @@
       <c r="G68" s="7"/>
       <c r="H68" s="7"/>
       <c r="I68" s="7" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="1"/>
     </row>
     <row r="69" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A69" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D69" s="7" t="s">
         <v>42</v>
@@ -4002,26 +3999,26 @@
       <c r="G69" s="7"/>
       <c r="H69" s="7"/>
       <c r="I69" s="7" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="1"/>
     </row>
     <row r="70" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A70" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>43</v>
+        <v>394</v>
       </c>
       <c r="E70" s="7" t="s">
         <v>13</v>
@@ -4030,88 +4027,88 @@
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
       <c r="I70" s="7" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="1"/>
     </row>
     <row r="71" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A71" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D71" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F71" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="E71" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F71" s="7" t="s">
-        <v>45</v>
       </c>
       <c r="G71" s="7"/>
       <c r="H71" s="7"/>
       <c r="I71" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="1"/>
     </row>
     <row r="72" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A72" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C72" s="7" t="s">
         <v>37</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E72" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F72" s="7"/>
       <c r="G72" s="7" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H72" s="7" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="I72" s="7" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="J72" s="9" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="1"/>
     </row>
     <row r="73" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A73" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C73" s="7" t="s">
         <v>37</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E73" s="7" t="s">
         <v>25</v>
@@ -4120,56 +4117,56 @@
       <c r="G73" s="7"/>
       <c r="H73" s="7"/>
       <c r="I73" s="7" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="J73" s="7" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="1"/>
     </row>
     <row r="74" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A74" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C74" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D74" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="D74" s="7" t="s">
+      <c r="E74" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F74" s="7" t="s">
         <v>79</v>
-      </c>
-      <c r="E74" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F74" s="7" t="s">
-        <v>80</v>
       </c>
       <c r="G74" s="7"/>
       <c r="H74" s="7"/>
       <c r="I74" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J74" s="7" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="1"/>
     </row>
     <row r="75" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A75" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E75" s="7" t="s">
         <v>16</v>
@@ -4180,26 +4177,26 @@
       <c r="G75" s="7"/>
       <c r="H75" s="7"/>
       <c r="I75" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J75" s="9" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="1"/>
     </row>
     <row r="76" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A76" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E76" s="7" t="s">
         <v>16</v>
@@ -4210,26 +4207,26 @@
       <c r="G76" s="7"/>
       <c r="H76" s="7"/>
       <c r="I76" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J76" s="7" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="1"/>
     </row>
     <row r="77" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A77" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E77" s="7" t="s">
         <v>12</v>
@@ -4238,56 +4235,56 @@
       <c r="G77" s="7"/>
       <c r="H77" s="7"/>
       <c r="I77" s="7" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="J77" s="7" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="1"/>
     </row>
     <row r="78" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A78" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C78" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D78" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="7" t="s">
-        <v>85</v>
-      </c>
       <c r="E78" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G78" s="7"/>
       <c r="H78" s="7"/>
       <c r="I78" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J78" s="7" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="1"/>
     </row>
     <row r="79" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A79" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E79" s="7" t="s">
         <v>16</v>
@@ -4298,26 +4295,26 @@
       <c r="G79" s="7"/>
       <c r="H79" s="7"/>
       <c r="I79" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J79" s="7" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="1"/>
     </row>
     <row r="80" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A80" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E80" s="7" t="s">
         <v>16</v>
@@ -4328,86 +4325,86 @@
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
       <c r="I80" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J80" s="7" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="1"/>
     </row>
     <row r="81" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A81" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D81" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F81" s="7" t="s">
         <v>88</v>
-      </c>
-      <c r="E81" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F81" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="G81" s="7"/>
       <c r="H81" s="7"/>
       <c r="I81" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J81" s="7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="1"/>
     </row>
     <row r="82" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A82" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D82" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E82" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F82" s="7" t="s">
         <v>90</v>
-      </c>
-      <c r="E82" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F82" s="7" t="s">
-        <v>91</v>
       </c>
       <c r="G82" s="7"/>
       <c r="H82" s="7"/>
       <c r="I82" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J82" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="1"/>
     </row>
     <row r="83" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A83" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E83" s="7" t="s">
         <v>12</v>
@@ -4416,26 +4413,26 @@
       <c r="G83" s="7"/>
       <c r="H83" s="7"/>
       <c r="I83" s="7" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="J83" s="7" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="1"/>
     </row>
     <row r="84" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A84" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E84" s="7" t="s">
         <v>12</v>
@@ -4444,26 +4441,26 @@
       <c r="G84" s="7"/>
       <c r="H84" s="7"/>
       <c r="I84" s="7" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="J84" s="7" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="1"/>
     </row>
     <row r="85" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A85" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E85" s="7" t="s">
         <v>12</v>
@@ -4472,26 +4469,26 @@
       <c r="G85" s="7"/>
       <c r="H85" s="7"/>
       <c r="I85" s="7" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J85" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="1"/>
     </row>
     <row r="86" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A86" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E86" s="7" t="s">
         <v>16</v>
@@ -4502,26 +4499,26 @@
       <c r="G86" s="7"/>
       <c r="H86" s="7"/>
       <c r="I86" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J86" s="7" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="1"/>
     </row>
     <row r="87" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A87" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E87" s="7" t="s">
         <v>12</v>
@@ -4530,26 +4527,26 @@
       <c r="G87" s="7"/>
       <c r="H87" s="7"/>
       <c r="I87" s="7" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="J87" s="7" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="1"/>
     </row>
     <row r="88" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A88" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E88" s="7" t="s">
         <v>12</v>
@@ -4558,26 +4555,26 @@
       <c r="G88" s="7"/>
       <c r="H88" s="7"/>
       <c r="I88" s="7" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="J88" s="7" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="1"/>
     </row>
     <row r="89" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A89" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E89" s="7" t="s">
         <v>12</v>
@@ -4586,26 +4583,26 @@
       <c r="G89" s="7"/>
       <c r="H89" s="7"/>
       <c r="I89" s="7" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="J89" s="7" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="1"/>
     </row>
     <row r="90" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A90" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C90" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D90" s="7" t="s">
         <v>96</v>
-      </c>
-      <c r="D90" s="7" t="s">
-        <v>97</v>
       </c>
       <c r="E90" s="7" t="s">
         <v>12</v>
@@ -4614,114 +4611,114 @@
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
       <c r="I90" s="7" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="J90" s="7" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="1"/>
     </row>
     <row r="91" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A91" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F91" s="7"/>
       <c r="G91" s="7"/>
       <c r="H91" s="7"/>
       <c r="I91" s="7" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="J91" s="7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="1"/>
     </row>
     <row r="92" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A92" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D92" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E92" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F92" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="E92" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F92" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="G92" s="7"/>
       <c r="H92" s="7"/>
       <c r="I92" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J92" s="7" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="1"/>
     </row>
     <row r="93" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A93" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E93" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G93" s="7"/>
       <c r="H93" s="7"/>
       <c r="I93" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="1"/>
     </row>
     <row r="94" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A94" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E94" s="7" t="s">
         <v>12</v>
@@ -4730,54 +4727,54 @@
       <c r="G94" s="7"/>
       <c r="H94" s="7"/>
       <c r="I94" s="7" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="J94" s="7" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="1"/>
     </row>
     <row r="95" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A95" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F95" s="7"/>
       <c r="G95" s="7"/>
       <c r="H95" s="7"/>
       <c r="I95" s="7" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="J95" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="1"/>
     </row>
     <row r="96" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A96" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D96" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E96" s="7" t="s">
         <v>12</v>
@@ -4786,26 +4783,26 @@
       <c r="G96" s="7"/>
       <c r="H96" s="7"/>
       <c r="I96" s="7" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="J96" s="7" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="1"/>
     </row>
     <row r="97" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A97" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C97" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D97" s="7" t="s">
         <v>105</v>
-      </c>
-      <c r="D97" s="7" t="s">
-        <v>106</v>
       </c>
       <c r="E97" s="7" t="s">
         <v>12</v>
@@ -4814,26 +4811,26 @@
       <c r="G97" s="7"/>
       <c r="H97" s="7"/>
       <c r="I97" s="7" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J97" s="7" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="1"/>
     </row>
     <row r="98" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A98" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D98" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E98" s="7" t="s">
         <v>12</v>
@@ -4842,26 +4839,26 @@
       <c r="G98" s="7"/>
       <c r="H98" s="7"/>
       <c r="I98" s="7" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="J98" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="1"/>
     </row>
     <row r="99" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A99" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E99" s="7" t="s">
         <v>16</v>
@@ -4870,26 +4867,26 @@
       <c r="G99" s="7"/>
       <c r="H99" s="7"/>
       <c r="I99" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J99" s="7" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="1"/>
     </row>
     <row r="100" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A100" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E100" s="7" t="s">
         <v>16</v>
@@ -4900,26 +4897,26 @@
       <c r="G100" s="7"/>
       <c r="H100" s="7"/>
       <c r="I100" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J100" s="7" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="1"/>
     </row>
     <row r="101" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A101" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E101" s="7" t="s">
         <v>12</v>
@@ -4928,26 +4925,26 @@
       <c r="G101" s="7"/>
       <c r="H101" s="7"/>
       <c r="I101" s="7" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="J101" s="7" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="1"/>
     </row>
     <row r="102" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A102" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E102" s="7" t="s">
         <v>16</v>
@@ -4958,26 +4955,26 @@
       <c r="G102" s="7"/>
       <c r="H102" s="7"/>
       <c r="I102" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J102" s="7" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="1"/>
     </row>
     <row r="103" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A103" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E103" s="7" t="s">
         <v>16</v>
@@ -4988,26 +4985,26 @@
       <c r="G103" s="7"/>
       <c r="H103" s="7"/>
       <c r="I103" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J103" s="7" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="1"/>
     </row>
     <row r="104" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A104" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E104" s="7" t="s">
         <v>16</v>
@@ -5018,26 +5015,26 @@
       <c r="G104" s="7"/>
       <c r="H104" s="7"/>
       <c r="I104" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J104" s="7" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="1"/>
     </row>
     <row r="105" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A105" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E105" s="7" t="s">
         <v>16</v>
@@ -5048,26 +5045,26 @@
       <c r="G105" s="7"/>
       <c r="H105" s="7"/>
       <c r="I105" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J105" s="7" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="1"/>
     </row>
     <row r="106" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A106" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E106" s="7" t="s">
         <v>16</v>
@@ -5078,26 +5075,26 @@
       <c r="G106" s="7"/>
       <c r="H106" s="7"/>
       <c r="I106" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J106" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="1"/>
     </row>
     <row r="107" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A107" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D107" s="7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E107" s="7" t="s">
         <v>12</v>
@@ -5105,29 +5102,29 @@
       <c r="F107" s="7"/>
       <c r="G107" s="7"/>
       <c r="H107" s="7" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="I107" s="7" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="J107" s="7" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="1"/>
     </row>
     <row r="108" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A108" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E108" s="7" t="s">
         <v>16</v>
@@ -5138,26 +5135,26 @@
       <c r="G108" s="7"/>
       <c r="H108" s="7"/>
       <c r="I108" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J108" s="7" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="1"/>
     </row>
     <row r="109" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A109" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E109" s="7" t="s">
         <v>13</v>
@@ -5166,26 +5163,26 @@
       <c r="G109" s="7"/>
       <c r="H109" s="7"/>
       <c r="I109" s="7" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="J109" s="7" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="1"/>
     </row>
     <row r="110" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A110" s="15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B110" s="15" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C110" s="15" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D110" s="15" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E110" s="15" t="s">
         <v>16</v>
@@ -5194,26 +5191,26 @@
       <c r="G110" s="15"/>
       <c r="H110" s="15"/>
       <c r="I110" s="15" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="J110" s="15" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="K110" s="15"/>
       <c r="L110" s="1"/>
     </row>
     <row r="111" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A111" s="17" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B111" s="16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C111" s="16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D111" s="17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E111" s="17" t="s">
         <v>12</v>
@@ -5222,26 +5219,26 @@
       <c r="G111" s="17"/>
       <c r="H111" s="17"/>
       <c r="I111" s="17" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="J111" s="17" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="K111" s="17"/>
       <c r="L111" s="1"/>
     </row>
     <row r="112" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A112" s="17" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B112" s="16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C112" s="16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D112" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E112" s="17" t="s">
         <v>12</v>
@@ -5250,26 +5247,26 @@
       <c r="G112" s="17"/>
       <c r="H112" s="17"/>
       <c r="I112" s="17" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="J112" s="17" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="K112" s="17"/>
       <c r="L112" s="1"/>
     </row>
     <row r="113" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A113" s="17" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B113" s="16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C113" s="16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D113" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E113" s="17" t="s">
         <v>12</v>
@@ -5278,26 +5275,26 @@
       <c r="G113" s="17"/>
       <c r="H113" s="17"/>
       <c r="I113" s="17" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="J113" s="17" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="K113" s="17"/>
       <c r="L113" s="1"/>
     </row>
     <row r="114" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A114" s="17" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B114" s="16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C114" s="16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D114" s="17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E114" s="17" t="s">
         <v>16</v>
@@ -5308,26 +5305,26 @@
       <c r="G114" s="17"/>
       <c r="H114" s="17"/>
       <c r="I114" s="17" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="J114" s="17" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="K114" s="17"/>
       <c r="L114" s="1"/>
     </row>
     <row r="115" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A115" s="17" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B115" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C115" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="D115" s="17" t="s">
         <v>54</v>
-      </c>
-      <c r="C115" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="D115" s="17" t="s">
-        <v>55</v>
       </c>
       <c r="E115" s="17" t="s">
         <v>16</v>
@@ -5338,26 +5335,26 @@
       <c r="G115" s="17"/>
       <c r="H115" s="17"/>
       <c r="I115" s="17" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J115" s="17" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K115" s="17"/>
       <c r="L115" s="1"/>
     </row>
     <row r="116" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A116" s="17" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B116" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C116" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D116" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E116" s="17" t="s">
         <v>16</v>
@@ -5368,26 +5365,26 @@
       <c r="G116" s="17"/>
       <c r="H116" s="17"/>
       <c r="I116" s="17" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J116" s="17" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="K116" s="17"/>
       <c r="L116" s="1"/>
     </row>
     <row r="117" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A117" s="17" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B117" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C117" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D117" s="17" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E117" s="17" t="s">
         <v>16</v>
@@ -5398,56 +5395,56 @@
       <c r="G117" s="17"/>
       <c r="H117" s="17"/>
       <c r="I117" s="17" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J117" s="17" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="K117" s="17"/>
       <c r="L117" s="1"/>
     </row>
     <row r="118" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A118" s="17" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B118" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C118" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D118" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="E118" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F118" s="17" t="s">
         <v>57</v>
-      </c>
-      <c r="E118" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="F118" s="17" t="s">
-        <v>58</v>
       </c>
       <c r="G118" s="17"/>
       <c r="H118" s="17"/>
       <c r="I118" s="17" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J118" s="17" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="K118" s="17"/>
       <c r="L118" s="1"/>
     </row>
     <row r="119" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A119" s="17" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B119" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C119" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D119" s="17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E119" s="17" t="s">
         <v>16</v>
@@ -5458,26 +5455,26 @@
       <c r="G119" s="17"/>
       <c r="H119" s="17"/>
       <c r="I119" s="17" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J119" s="17" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="K119" s="17"/>
       <c r="L119" s="1"/>
     </row>
     <row r="120" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A120" s="17" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B120" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C120" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D120" s="17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E120" s="17" t="s">
         <v>16</v>
@@ -5488,26 +5485,26 @@
       <c r="G120" s="17"/>
       <c r="H120" s="17"/>
       <c r="I120" s="17" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J120" s="17" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="K120" s="17"/>
       <c r="L120" s="1"/>
     </row>
     <row r="121" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A121" s="17" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B121" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C121" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D121" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E121" s="17" t="s">
         <v>16</v>
@@ -5516,86 +5513,86 @@
       <c r="G121" s="17"/>
       <c r="H121" s="17"/>
       <c r="I121" s="17" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J121" s="17" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K121" s="17"/>
       <c r="L121" s="1"/>
     </row>
     <row r="122" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A122" s="17" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B122" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C122" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D122" s="17" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E122" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F122" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G122" s="17"/>
       <c r="H122" s="17"/>
       <c r="I122" s="17" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J122" s="17" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="K122" s="17"/>
       <c r="L122" s="1"/>
     </row>
     <row r="123" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A123" s="17" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B123" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C123" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D123" s="17" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E123" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F123" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G123" s="17"/>
       <c r="H123" s="17"/>
       <c r="I123" s="17" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J123" s="17" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="K123" s="17"/>
       <c r="L123" s="1"/>
     </row>
     <row r="124" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A124" s="17" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B124" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C124" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D124" s="17" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E124" s="17" t="s">
         <v>12</v>
@@ -5604,26 +5601,26 @@
       <c r="G124" s="17"/>
       <c r="H124" s="17"/>
       <c r="I124" s="17" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="J124" s="17" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="K124" s="17"/>
       <c r="L124" s="1"/>
     </row>
     <row r="125" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A125" s="17" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B125" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C125" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D125" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E125" s="17" t="s">
         <v>12</v>
@@ -5632,56 +5629,56 @@
       <c r="G125" s="17"/>
       <c r="H125" s="17"/>
       <c r="I125" s="17" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J125" s="17" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="K125" s="17"/>
       <c r="L125" s="1"/>
     </row>
     <row r="126" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A126" s="17" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B126" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C126" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D126" s="17" t="s">
-        <v>169</v>
+        <v>393</v>
       </c>
       <c r="E126" s="17" t="s">
         <v>13</v>
       </c>
       <c r="F126" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G126" s="17"/>
       <c r="H126" s="17"/>
       <c r="I126" s="17" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="J126" s="17" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="K126" s="17"/>
       <c r="L126" s="1"/>
     </row>
     <row r="127" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A127" s="17" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B127" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C127" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D127" s="17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E127" s="17" t="s">
         <v>16</v>
@@ -5692,26 +5689,26 @@
       <c r="G127" s="17"/>
       <c r="H127" s="17"/>
       <c r="I127" s="17" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J127" s="17" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="K127" s="17"/>
       <c r="L127" s="1"/>
     </row>
     <row r="128" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A128" s="17" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B128" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C128" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D128" s="17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E128" s="17" t="s">
         <v>16</v>
@@ -5722,26 +5719,26 @@
       <c r="G128" s="17"/>
       <c r="H128" s="17"/>
       <c r="I128" s="17" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J128" s="17" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K128" s="17"/>
       <c r="L128" s="1"/>
     </row>
     <row r="129" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A129" s="17" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B129" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C129" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D129" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E129" s="17" t="s">
         <v>16</v>
@@ -5752,116 +5749,116 @@
       <c r="G129" s="17"/>
       <c r="H129" s="17"/>
       <c r="I129" s="17" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J129" s="17" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="K129" s="17"/>
       <c r="L129" s="1"/>
     </row>
     <row r="130" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A130" s="17" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B130" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C130" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D130" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E130" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F130" s="17" t="s">
         <v>66</v>
-      </c>
-      <c r="E130" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="F130" s="17" t="s">
-        <v>67</v>
       </c>
       <c r="G130" s="17"/>
       <c r="H130" s="17"/>
       <c r="I130" s="17" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J130" s="17" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="K130" s="17"/>
       <c r="L130" s="1"/>
     </row>
     <row r="131" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A131" s="17" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B131" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C131" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D131" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="E131" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F131" s="17" t="s">
         <v>68</v>
-      </c>
-      <c r="E131" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="F131" s="17" t="s">
-        <v>69</v>
       </c>
       <c r="G131" s="17"/>
       <c r="H131" s="17"/>
       <c r="I131" s="17" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J131" s="17" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="K131" s="17"/>
       <c r="L131" s="1"/>
     </row>
     <row r="132" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A132" s="17" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B132" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C132" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D132" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E132" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F132" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G132" s="17"/>
       <c r="H132" s="17"/>
       <c r="I132" s="17" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J132" s="17" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="K132" s="17"/>
       <c r="L132" s="1"/>
     </row>
     <row r="133" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A133" s="17" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B133" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C133" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D133" s="17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E133" s="17" t="s">
         <v>16</v>
@@ -5870,26 +5867,26 @@
       <c r="G133" s="17"/>
       <c r="H133" s="17"/>
       <c r="I133" s="17" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="J133" s="17" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="K133" s="17"/>
       <c r="L133" s="1"/>
     </row>
     <row r="134" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A134" s="17" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B134" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C134" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D134" s="17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E134" s="17" t="s">
         <v>12</v>
@@ -5898,26 +5895,26 @@
       <c r="G134" s="17"/>
       <c r="H134" s="17"/>
       <c r="I134" s="17" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="J134" s="17" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="K134" s="17"/>
       <c r="L134" s="1"/>
     </row>
     <row r="135" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A135" s="17" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B135" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C135" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D135" s="17" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E135" s="17" t="s">
         <v>16</v>
@@ -5926,56 +5923,56 @@
       <c r="G135" s="17"/>
       <c r="H135" s="17"/>
       <c r="I135" s="17" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J135" s="17" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="K135" s="17"/>
       <c r="L135" s="1"/>
     </row>
     <row r="136" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A136" s="17" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B136" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C136" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D136" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="E136" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F136" s="17" t="s">
         <v>73</v>
-      </c>
-      <c r="E136" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="F136" s="17" t="s">
-        <v>74</v>
       </c>
       <c r="G136" s="17"/>
       <c r="H136" s="17"/>
       <c r="I136" s="17" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J136" s="17" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="K136" s="17"/>
       <c r="L136" s="1"/>
     </row>
     <row r="137" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A137" s="17" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B137" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C137" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D137" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E137" s="17" t="s">
         <v>16</v>
@@ -5986,56 +5983,56 @@
       <c r="G137" s="17"/>
       <c r="H137" s="17"/>
       <c r="I137" s="17" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J137" s="17" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="K137" s="17"/>
       <c r="L137" s="1"/>
     </row>
     <row r="138" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A138" s="17" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B138" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C138" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D138" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="E138" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F138" s="17" t="s">
         <v>76</v>
-      </c>
-      <c r="E138" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="F138" s="17" t="s">
-        <v>77</v>
       </c>
       <c r="G138" s="17"/>
       <c r="H138" s="17"/>
       <c r="I138" s="17" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J138" s="17" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="K138" s="17"/>
       <c r="L138" s="1"/>
     </row>
     <row r="139" spans="1:12" ht="14" x14ac:dyDescent="0.3">
       <c r="A139" s="17" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B139" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C139" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D139" s="17" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E139" s="17" t="s">
         <v>16</v>
@@ -6046,10 +6043,10 @@
       <c r="G139" s="17"/>
       <c r="H139" s="17"/>
       <c r="I139" s="17" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J139" s="17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K139" s="17"/>
       <c r="L139" s="1"/>

--- a/MASTER.xlsx
+++ b/MASTER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Javid Shiriyev\Documents\GitHub\sand-control-failure-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{086EEF7A-3267-436D-85F1-0191B958F2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8EB2284-67C5-423E-99C3-4528B8C90A8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-2730" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterView" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1105" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1106" uniqueCount="413">
   <si>
     <t>Category</t>
   </si>
@@ -164,9 +164,6 @@
     <t>Additional Bridging Agent</t>
   </si>
   <si>
-    <t>PSD Test Volume</t>
-  </si>
-  <si>
     <t>L</t>
   </si>
   <si>
@@ -698,9 +695,6 @@
     <t>Particle-size distribution of solids/bridging material in the reservoir drilling fluid.</t>
   </si>
   <si>
-    <t>Fluid or sample volume used to determine the reported drilling-fluid particle-size distribution.</t>
-  </si>
-  <si>
     <t>Primary completion configuration used across the production interval</t>
   </si>
   <si>
@@ -1151,9 +1145,6 @@
     <t>{"List": {"options": ["16/20", "16/30", "20/40", "30/50", "40/60", "40/70", "35 Monomesh", "25 Monomesh", "40 Monomesh", "45 Monomesh"]}}</t>
   </si>
   <si>
-    <t>{"List": {"options": ["Brine", "Xanthan", "VES", "HES", "Oil Based"]}}</t>
-  </si>
-  <si>
     <t>{"List": {"options": ["Xlink Gel", "VES", "HEC"]}}</t>
   </si>
   <si>
@@ -1202,9 +1193,6 @@
     <t>{"List": {"required": True, "options": ["Surface Solids Samples", "ASD Response", "Surface Equipment Erosion"]}}</t>
   </si>
   <si>
-    <t>{"List": {"required": True, "options": ["Aggressive drawdown", "Screen plugging", "Water breakthrough", "Water hammer", "Hard shutdown", "Other", "Unknown"]}}</t>
-  </si>
-  <si>
     <t>{"List": {"required": True, "options": ["Flowing Unrestricted by Sand", "Flowing Restricted by Sand", "Shut-in Due to Sand", "Shut in due to reasons other than sand", "Not Producing"]}}</t>
   </si>
   <si>
@@ -1265,13 +1253,28 @@
     <t>{"SAS": {"Gravel Packing": False}, "Cased and Perforated": {"Liners and Screens": False, "Gravel Packing": False}}</t>
   </si>
   <si>
-    <t>{"OHGP": {"Placement Method", "% Pack through Shunts", "Carrier Fluid Type - OHGP", "Pack Efficiency Source", "Pack Efficiency Percentage", "ICD / AICD", "Did screens get to Target Setting Depth", "Return Percentage", "If screens ran in mud, was mud removed once screens on bottom?"}, "SAS": {"Fluid Type Left in OH at end of Completion", "ICD / AICD", "Did screens get to Target Setting Depth", "If screens ran in mud, was mud removed once screens on bottom?", "Blank pipe run across non-pay sections instead of screens?"}, "CHFP": {"Carrier Fluid Type - CHFP", "Full Pack from Log"}, "CHGP": {"Carrier Fluid Type - CHGP", "Perf Packing", "Return Percentage", "Pack Efficiency Source", "Pack Efficiency Percentage"}}</t>
-  </si>
-  <si>
     <t>{"Measurable": {"Sand production rate at first choke back", "Sand production rate at well shut-in due to sand", "Sand production rate at complete well failure"}}</t>
   </si>
   <si>
     <t>At least 7 alphanumeric characters (letters/numbers only). Do not use the actual API/UWI number.</t>
+  </si>
+  <si>
+    <t>PST Test Volume</t>
+  </si>
+  <si>
+    <t>Volume of wellbore fluid sample passed through the screen coupon to ensure no plugging</t>
+  </si>
+  <si>
+    <t>{"List": {"options": ["Brine", "Xanthan", "VES", "HEC", "Oil Based"]}}</t>
+  </si>
+  <si>
+    <t>{"Shunt": {"% Pack through Shunts", "Shunt Tubes"}, "Circ Pack": {"% Pack through Shunts": False, "Shunt Tubes": False}}</t>
+  </si>
+  <si>
+    <t>{"OHGP": {"Placement Method", "Carrier Fluid Type - OHGP", "Pack Efficiency Source", "Pack Efficiency Percentage", "ICD / AICD", "Did screens get to Target Setting Depth", "Return Percentage", "If screens ran in mud, was mud removed once screens on bottom?"}, "SAS": {"Fluid Type Left in OH at end of Completion", "ICD / AICD", "Did screens get to Target Setting Depth", "If screens ran in mud, was mud removed once screens on bottom?", "Blank pipe run across non-pay sections instead of screens?"}, "CHFP": {"Carrier Fluid Type - CHFP", "Full Pack from Log"}, "CHGP": {"Carrier Fluid Type - CHGP", "Perf Packing", "Return Percentage", "Pack Efficiency Source", "Pack Efficiency Percentage"}}</t>
+  </si>
+  <si>
+    <t>{"List": {"required": True, "options": ["Aggressive Drawdown", "Screen Plugging", "Water Breakthrough", "Hard Shutdown", "Flux", "Incomplete Gravel Pack", "Compaction", "Excessive Drawdown", "Rapid Beanup", "Hard Shut-in", "Well Slugging", "Intervention Induced Damage", "Wrongly Sized Sand Control", "No Sand Control Installed", "Other", "Unknown"]}}</t>
   </si>
 </sst>
 </file>
@@ -2086,7 +2089,7 @@
     <col min="1" max="1" width="6.08984375" style="1" customWidth="1"/>
     <col min="2" max="2" width="6.90625" style="2" customWidth="1"/>
     <col min="3" max="3" width="9.81640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.7265625" customWidth="1"/>
+    <col min="4" max="4" width="34" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="62.54296875" style="3" customWidth="1"/>
     <col min="7" max="7" width="14" style="2" customWidth="1"/>
     <col min="8" max="8" width="26.7265625" style="1" customWidth="1"/>
@@ -2100,7 +2103,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="28" x14ac:dyDescent="0.35">
       <c r="A1" s="21" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>3</v>
@@ -2130,10 +2133,10 @@
         <v>6</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L1" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M1" s="1"/>
     </row>
@@ -2151,7 +2154,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>12</v>
@@ -2160,10 +2163,10 @@
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
       <c r="J2" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L2" s="5"/>
       <c r="M2" s="1"/>
@@ -2182,7 +2185,7 @@
         <v>10</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>12</v>
@@ -2191,10 +2194,10 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L3" s="5"/>
       <c r="M3" s="1"/>
@@ -2213,7 +2216,7 @@
         <v>10</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>13</v>
@@ -2222,10 +2225,10 @@
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
       <c r="J4" s="5" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L4" s="5"/>
       <c r="M4" s="1"/>
@@ -2244,7 +2247,7 @@
         <v>15</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>13</v>
@@ -2253,10 +2256,10 @@
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L5" s="6"/>
       <c r="M5" s="1"/>
@@ -2275,7 +2278,7 @@
         <v>15</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>13</v>
@@ -2284,10 +2287,10 @@
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
       <c r="J6" s="6" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="L6" s="6"/>
       <c r="M6" s="1"/>
@@ -2306,7 +2309,7 @@
         <v>15</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>12</v>
@@ -2314,13 +2317,13 @@
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
       <c r="I7" s="6" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L7" s="6"/>
       <c r="M7" s="1"/>
@@ -2339,7 +2342,7 @@
         <v>15</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>12</v>
@@ -2347,13 +2350,13 @@
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
       <c r="I8" s="6" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L8" s="6"/>
       <c r="M8" s="1"/>
@@ -2372,7 +2375,7 @@
         <v>15</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>16</v>
@@ -2383,10 +2386,10 @@
       <c r="H9" s="6"/>
       <c r="I9" s="6"/>
       <c r="J9" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L9" s="6"/>
       <c r="M9" s="1"/>
@@ -2405,7 +2408,7 @@
         <v>15</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>12</v>
@@ -2414,10 +2417,10 @@
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
       <c r="J10" s="6" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L10" s="6"/>
       <c r="M10" s="1"/>
@@ -2447,10 +2450,10 @@
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
       <c r="J11" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L11" s="6"/>
       <c r="M11" s="1"/>
@@ -2469,7 +2472,7 @@
         <v>15</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>16</v>
@@ -2480,10 +2483,10 @@
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L12" s="6"/>
       <c r="M12" s="1"/>
@@ -2502,7 +2505,7 @@
         <v>15</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>13</v>
@@ -2511,10 +2514,10 @@
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
       <c r="J13" s="6" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L13" s="6"/>
       <c r="M13" s="1"/>
@@ -2533,7 +2536,7 @@
         <v>15</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>13</v>
@@ -2542,10 +2545,10 @@
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
       <c r="J14" s="6" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L14" s="6"/>
       <c r="M14" s="1"/>
@@ -2564,7 +2567,7 @@
         <v>15</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>12</v>
@@ -2573,10 +2576,10 @@
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
       <c r="J15" s="6" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L15" s="6"/>
       <c r="M15" s="1"/>
@@ -2604,10 +2607,10 @@
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
       <c r="J16" s="6" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L16" s="6"/>
       <c r="M16" s="1"/>
@@ -2623,24 +2626,24 @@
         <v>14</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="I17" s="6"/>
       <c r="J17" s="6" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L17" s="6"/>
       <c r="M17" s="1"/>
@@ -2659,7 +2662,7 @@
         <v>20</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>12</v>
@@ -2668,10 +2671,10 @@
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
       <c r="J18" s="6" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L18" s="6"/>
       <c r="M18" s="1"/>
@@ -2690,7 +2693,7 @@
         <v>20</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>12</v>
@@ -2699,10 +2702,10 @@
       <c r="H19" s="6"/>
       <c r="I19" s="6"/>
       <c r="J19" s="6" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L19" s="6"/>
       <c r="M19" s="1"/>
@@ -2721,7 +2724,7 @@
         <v>20</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>16</v>
@@ -2732,10 +2735,10 @@
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
       <c r="J20" s="6" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L20" s="6"/>
       <c r="M20" s="1"/>
@@ -2754,7 +2757,7 @@
         <v>20</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>16</v>
@@ -2765,10 +2768,10 @@
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
       <c r="J21" s="6" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L21" s="6"/>
       <c r="M21" s="1"/>
@@ -2787,7 +2790,7 @@
         <v>20</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>16</v>
@@ -2798,10 +2801,10 @@
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
       <c r="J22" s="6" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L22" s="6"/>
       <c r="M22" s="1"/>
@@ -2820,7 +2823,7 @@
         <v>20</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>12</v>
@@ -2829,10 +2832,10 @@
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
       <c r="J23" s="6" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L23" s="6"/>
       <c r="M23" s="1"/>
@@ -2851,7 +2854,7 @@
         <v>20</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>12</v>
@@ -2860,10 +2863,10 @@
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
       <c r="J24" s="6" t="s">
-        <v>388</v>
+        <v>412</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L24" s="6"/>
       <c r="M24" s="1"/>
@@ -2882,7 +2885,7 @@
         <v>20</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>12</v>
@@ -2890,13 +2893,13 @@
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
       <c r="I25" s="6" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L25" s="6"/>
       <c r="M25" s="1"/>
@@ -2915,7 +2918,7 @@
         <v>20</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>16</v>
@@ -2926,10 +2929,10 @@
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
       <c r="J26" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L26" s="6"/>
       <c r="M26" s="1"/>
@@ -2948,7 +2951,7 @@
         <v>20</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>16</v>
@@ -2959,10 +2962,10 @@
       <c r="H27" s="6"/>
       <c r="I27" s="6"/>
       <c r="J27" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L27" s="6"/>
       <c r="M27" s="1"/>
@@ -2981,7 +2984,7 @@
         <v>20</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>16</v>
@@ -2992,10 +2995,10 @@
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
       <c r="J28" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L28" s="6"/>
       <c r="M28" s="1"/>
@@ -3014,7 +3017,7 @@
         <v>20</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>16</v>
@@ -3025,10 +3028,10 @@
       <c r="H29" s="6"/>
       <c r="I29" s="6"/>
       <c r="J29" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L29" s="6"/>
       <c r="M29" s="1"/>
@@ -3047,7 +3050,7 @@
         <v>20</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>16</v>
@@ -3056,10 +3059,10 @@
       <c r="H30" s="6"/>
       <c r="I30" s="6"/>
       <c r="J30" s="6" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L30" s="6"/>
       <c r="M30" s="1"/>
@@ -3078,7 +3081,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F31" s="6" t="s">
         <v>16</v>
@@ -3087,10 +3090,10 @@
       <c r="H31" s="6"/>
       <c r="I31" s="6"/>
       <c r="J31" s="6" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L31" s="6"/>
       <c r="M31" s="1"/>
@@ -3109,7 +3112,7 @@
         <v>20</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>16</v>
@@ -3118,10 +3121,10 @@
       <c r="H32" s="6"/>
       <c r="I32" s="6"/>
       <c r="J32" s="6" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L32" s="6"/>
       <c r="M32" s="1"/>
@@ -3140,7 +3143,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F33" s="6" t="s">
         <v>16</v>
@@ -3151,10 +3154,10 @@
       <c r="H33" s="6"/>
       <c r="I33" s="6"/>
       <c r="J33" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="L33" s="6"/>
       <c r="M33" s="1"/>
@@ -3173,7 +3176,7 @@
         <v>20</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>16</v>
@@ -3182,10 +3185,10 @@
       <c r="H34" s="6"/>
       <c r="I34" s="6"/>
       <c r="J34" s="6" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L34" s="6"/>
       <c r="M34" s="1"/>
@@ -3204,7 +3207,7 @@
         <v>20</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F35" s="6" t="s">
         <v>16</v>
@@ -3213,10 +3216,10 @@
       <c r="H35" s="6"/>
       <c r="I35" s="6"/>
       <c r="J35" s="6" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L35" s="6"/>
       <c r="M35" s="1"/>
@@ -3235,7 +3238,7 @@
         <v>20</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>16</v>
@@ -3244,10 +3247,10 @@
       <c r="H36" s="6"/>
       <c r="I36" s="6"/>
       <c r="J36" s="6" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L36" s="6"/>
       <c r="M36" s="1"/>
@@ -3275,10 +3278,10 @@
       <c r="H37" s="6"/>
       <c r="I37" s="6"/>
       <c r="J37" s="6" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="K37" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L37" s="6"/>
       <c r="M37" s="1"/>
@@ -3294,10 +3297,10 @@
         <v>14</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>12</v>
@@ -3306,10 +3309,10 @@
       <c r="H38" s="6"/>
       <c r="I38" s="6"/>
       <c r="J38" s="6" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L38" s="6"/>
       <c r="M38" s="1"/>
@@ -3325,10 +3328,10 @@
         <v>14</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F39" s="6" t="s">
         <v>24</v>
@@ -3337,10 +3340,10 @@
       <c r="H39" s="6"/>
       <c r="I39" s="6"/>
       <c r="J39" s="6" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L39" s="6"/>
       <c r="M39" s="1"/>
@@ -3356,10 +3359,10 @@
         <v>14</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>24</v>
@@ -3368,10 +3371,10 @@
       <c r="H40" s="6"/>
       <c r="I40" s="6"/>
       <c r="J40" s="6" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="K40" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L40" s="6"/>
       <c r="M40" s="1"/>
@@ -3387,10 +3390,10 @@
         <v>14</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F41" s="6" t="s">
         <v>24</v>
@@ -3399,10 +3402,10 @@
       <c r="H41" s="6"/>
       <c r="I41" s="6"/>
       <c r="J41" s="6" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="K41" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L41" s="6"/>
       <c r="M41" s="1"/>
@@ -3418,7 +3421,7 @@
         <v>14</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>25</v>
@@ -3432,10 +3435,10 @@
       <c r="H42" s="6"/>
       <c r="I42" s="6"/>
       <c r="J42" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="K42" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L42" s="6"/>
       <c r="M42" s="1"/>
@@ -3451,7 +3454,7 @@
         <v>14</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>27</v>
@@ -3465,10 +3468,10 @@
       <c r="H43" s="6"/>
       <c r="I43" s="6"/>
       <c r="J43" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="K43" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L43" s="6"/>
       <c r="M43" s="1"/>
@@ -3484,7 +3487,7 @@
         <v>14</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>28</v>
@@ -3498,10 +3501,10 @@
       <c r="H44" s="6"/>
       <c r="I44" s="6"/>
       <c r="J44" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="K44" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L44" s="6"/>
       <c r="M44" s="1"/>
@@ -3517,7 +3520,7 @@
         <v>14</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>30</v>
@@ -3531,10 +3534,10 @@
       <c r="H45" s="6"/>
       <c r="I45" s="6"/>
       <c r="J45" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="K45" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L45" s="6"/>
       <c r="M45" s="1"/>
@@ -3550,7 +3553,7 @@
         <v>14</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>31</v>
@@ -3564,10 +3567,10 @@
       <c r="H46" s="6"/>
       <c r="I46" s="6"/>
       <c r="J46" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="K46" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L46" s="6"/>
       <c r="M46" s="1"/>
@@ -3583,7 +3586,7 @@
         <v>14</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>32</v>
@@ -3597,10 +3600,10 @@
       <c r="H47" s="6"/>
       <c r="I47" s="6"/>
       <c r="J47" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="K47" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L47" s="6"/>
       <c r="M47" s="1"/>
@@ -3616,10 +3619,10 @@
         <v>14</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>16</v>
@@ -3630,10 +3633,10 @@
       <c r="H48" s="6"/>
       <c r="I48" s="6"/>
       <c r="J48" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="K48" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L48" s="6"/>
       <c r="M48" s="1"/>
@@ -3649,10 +3652,10 @@
         <v>14</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F49" s="6" t="s">
         <v>16</v>
@@ -3663,10 +3666,10 @@
       <c r="H49" s="6"/>
       <c r="I49" s="6"/>
       <c r="J49" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="K49" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L49" s="6"/>
       <c r="M49" s="1"/>
@@ -3682,10 +3685,10 @@
         <v>14</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>16</v>
@@ -3696,10 +3699,10 @@
       <c r="H50" s="6"/>
       <c r="I50" s="6"/>
       <c r="J50" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="K50" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L50" s="6"/>
       <c r="M50" s="1"/>
@@ -3715,10 +3718,10 @@
         <v>14</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F51" s="6" t="s">
         <v>16</v>
@@ -3729,10 +3732,10 @@
       <c r="H51" s="6"/>
       <c r="I51" s="6"/>
       <c r="J51" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="K51" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L51" s="6"/>
       <c r="M51" s="1"/>
@@ -3748,10 +3751,10 @@
         <v>14</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>13</v>
@@ -3760,10 +3763,10 @@
       <c r="H52" s="6"/>
       <c r="I52" s="6"/>
       <c r="J52" s="6" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="K52" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L52" s="6"/>
       <c r="M52" s="1"/>
@@ -3779,10 +3782,10 @@
         <v>14</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F53" s="6" t="s">
         <v>16</v>
@@ -3793,10 +3796,10 @@
       <c r="H53" s="6"/>
       <c r="I53" s="6"/>
       <c r="J53" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="K53" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L53" s="6"/>
       <c r="M53" s="1"/>
@@ -3812,10 +3815,10 @@
         <v>14</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>16</v>
@@ -3826,10 +3829,10 @@
       <c r="H54" s="6"/>
       <c r="I54" s="6"/>
       <c r="J54" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="K54" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L54" s="6"/>
       <c r="M54" s="1"/>
@@ -3845,10 +3848,10 @@
         <v>14</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F55" s="6" t="s">
         <v>12</v>
@@ -3857,10 +3860,10 @@
       <c r="H55" s="6"/>
       <c r="I55" s="6"/>
       <c r="J55" s="6" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="K55" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L55" s="6"/>
       <c r="M55" s="1"/>
@@ -3876,10 +3879,10 @@
         <v>14</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>12</v>
@@ -3888,10 +3891,10 @@
       <c r="H56" s="6"/>
       <c r="I56" s="6"/>
       <c r="J56" s="6" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="K56" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="L56" s="6"/>
       <c r="M56" s="1"/>
@@ -3907,10 +3910,10 @@
         <v>14</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F57" s="6" t="s">
         <v>12</v>
@@ -3919,10 +3922,10 @@
       <c r="H57" s="6"/>
       <c r="I57" s="6"/>
       <c r="J57" s="6" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="K57" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L57" s="6"/>
       <c r="M57" s="1"/>
@@ -3938,10 +3941,10 @@
         <v>14</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>12</v>
@@ -3950,10 +3953,10 @@
       <c r="H58" s="6"/>
       <c r="I58" s="6"/>
       <c r="J58" s="6" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="K58" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L58" s="6"/>
       <c r="M58" s="1"/>
@@ -3966,13 +3969,13 @@
         <v>11</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F59" s="12" t="s">
         <v>16</v>
@@ -3981,10 +3984,10 @@
       <c r="H59" s="12"/>
       <c r="I59" s="12"/>
       <c r="J59" s="12" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="K59" s="11" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="L59" s="11"/>
       <c r="M59" s="1"/>
@@ -3994,16 +3997,16 @@
         <v>59</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F60" s="7" t="s">
         <v>16</v>
@@ -4012,10 +4015,10 @@
       <c r="H60" s="7"/>
       <c r="I60" s="7"/>
       <c r="J60" s="7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K60" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="L60" s="7"/>
       <c r="M60" s="1"/>
@@ -4025,32 +4028,32 @@
         <v>60</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D61" s="7" t="s">
         <v>36</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F61" s="7" t="s">
         <v>12</v>
       </c>
       <c r="G61" s="7"/>
       <c r="H61" s="7" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="I61" s="7" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="K61" s="9" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="L61" s="7"/>
       <c r="M61" s="1"/>
@@ -4060,16 +4063,16 @@
         <v>61</v>
       </c>
       <c r="B62" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D62" s="7" t="s">
         <v>36</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F62" s="7" t="s">
         <v>24</v>
@@ -4078,10 +4081,10 @@
       <c r="H62" s="7"/>
       <c r="I62" s="7"/>
       <c r="J62" s="7" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="K62" s="7" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="L62" s="7"/>
       <c r="M62" s="1"/>
@@ -4091,30 +4094,30 @@
         <v>62</v>
       </c>
       <c r="B63" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="F63" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H63" s="7"/>
       <c r="I63" s="7"/>
       <c r="J63" s="7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K63" s="7" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="L63" s="7"/>
       <c r="M63" s="1"/>
@@ -4124,30 +4127,30 @@
         <v>63</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D64" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E64" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E64" s="7" t="s">
+      <c r="F64" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G64" s="7" t="s">
         <v>76</v>
-      </c>
-      <c r="F64" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G64" s="7" t="s">
-        <v>77</v>
       </c>
       <c r="H64" s="7"/>
       <c r="I64" s="7"/>
       <c r="J64" s="7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K64" s="7" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L64" s="7"/>
       <c r="M64" s="1"/>
@@ -4157,16 +4160,16 @@
         <v>64</v>
       </c>
       <c r="B65" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F65" s="7" t="s">
         <v>16</v>
@@ -4177,10 +4180,10 @@
       <c r="H65" s="7"/>
       <c r="I65" s="7"/>
       <c r="J65" s="7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K65" s="9" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L65" s="7"/>
       <c r="M65" s="1"/>
@@ -4190,16 +4193,16 @@
         <v>65</v>
       </c>
       <c r="B66" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F66" s="7" t="s">
         <v>16</v>
@@ -4210,10 +4213,10 @@
       <c r="H66" s="7"/>
       <c r="I66" s="7"/>
       <c r="J66" s="7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K66" s="7" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="L66" s="7"/>
       <c r="M66" s="1"/>
@@ -4223,28 +4226,28 @@
         <v>66</v>
       </c>
       <c r="B67" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G67" s="7"/>
       <c r="H67" s="7"/>
       <c r="I67" s="7"/>
       <c r="J67" s="7" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K67" s="7" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="L67" s="7"/>
       <c r="M67" s="1"/>
@@ -4254,25 +4257,25 @@
         <v>67</v>
       </c>
       <c r="B68" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G68" s="7"/>
       <c r="H68" s="7"/>
       <c r="I68" s="7"/>
       <c r="J68" s="7" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
@@ -4283,16 +4286,16 @@
         <v>68</v>
       </c>
       <c r="B69" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F69" s="7" t="s">
         <v>16</v>
@@ -4301,10 +4304,10 @@
       <c r="H69" s="7"/>
       <c r="I69" s="7"/>
       <c r="J69" s="7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K69" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L69" s="7"/>
       <c r="M69" s="1"/>
@@ -4314,13 +4317,13 @@
         <v>69</v>
       </c>
       <c r="B70" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="E70" s="7" t="s">
         <v>37</v>
@@ -4332,10 +4335,10 @@
       <c r="H70" s="7"/>
       <c r="I70" s="7"/>
       <c r="J70" s="7" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="K70" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="L70" s="7"/>
       <c r="M70" s="1"/>
@@ -4345,13 +4348,13 @@
         <v>70</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="E71" s="7" t="s">
         <v>38</v>
@@ -4365,10 +4368,10 @@
       <c r="H71" s="7"/>
       <c r="I71" s="7"/>
       <c r="J71" s="7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K71" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="L71" s="7"/>
       <c r="M71" s="1"/>
@@ -4378,13 +4381,13 @@
         <v>71</v>
       </c>
       <c r="B72" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="E72" s="7" t="s">
         <v>40</v>
@@ -4396,10 +4399,10 @@
       <c r="H72" s="7"/>
       <c r="I72" s="7"/>
       <c r="J72" s="7" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="K72" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L72" s="7"/>
       <c r="M72" s="1"/>
@@ -4409,13 +4412,13 @@
         <v>72</v>
       </c>
       <c r="B73" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="E73" s="7" t="s">
         <v>41</v>
@@ -4427,10 +4430,10 @@
       <c r="H73" s="7"/>
       <c r="I73" s="7"/>
       <c r="J73" s="7" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="K73" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="L73" s="7"/>
       <c r="M73" s="1"/>
@@ -4440,16 +4443,16 @@
         <v>73</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F74" s="7" t="s">
         <v>13</v>
@@ -4458,10 +4461,10 @@
       <c r="H74" s="7"/>
       <c r="I74" s="7"/>
       <c r="J74" s="7" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="K74" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L74" s="7"/>
       <c r="M74" s="1"/>
@@ -4471,30 +4474,30 @@
         <v>74</v>
       </c>
       <c r="B75" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="E75" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="F75" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G75" s="7" t="s">
         <v>42</v>
-      </c>
-      <c r="F75" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G75" s="7" t="s">
-        <v>43</v>
       </c>
       <c r="H75" s="7"/>
       <c r="I75" s="7"/>
       <c r="J75" s="7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K75" s="7" t="s">
-        <v>220</v>
+        <v>408</v>
       </c>
       <c r="L75" s="7"/>
       <c r="M75" s="1"/>
@@ -4504,30 +4507,30 @@
         <v>75</v>
       </c>
       <c r="B76" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D76" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E76" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E76" s="7" t="s">
-        <v>82</v>
-      </c>
       <c r="F76" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H76" s="7"/>
       <c r="I76" s="7"/>
       <c r="J76" s="7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K76" s="7" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L76" s="7"/>
       <c r="M76" s="1"/>
@@ -4537,16 +4540,16 @@
         <v>76</v>
       </c>
       <c r="B77" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F77" s="7" t="s">
         <v>16</v>
@@ -4557,10 +4560,10 @@
       <c r="H77" s="7"/>
       <c r="I77" s="7"/>
       <c r="J77" s="7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K77" s="7" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L77" s="7"/>
       <c r="M77" s="1"/>
@@ -4570,16 +4573,16 @@
         <v>77</v>
       </c>
       <c r="B78" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F78" s="7" t="s">
         <v>16</v>
@@ -4590,10 +4593,10 @@
       <c r="H78" s="7"/>
       <c r="I78" s="7"/>
       <c r="J78" s="7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K78" s="7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L78" s="7"/>
       <c r="M78" s="1"/>
@@ -4603,30 +4606,30 @@
         <v>78</v>
       </c>
       <c r="B79" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F79" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H79" s="7"/>
       <c r="I79" s="7"/>
       <c r="J79" s="7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K79" s="7" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="L79" s="7"/>
       <c r="M79" s="1"/>
@@ -4636,30 +4639,30 @@
         <v>79</v>
       </c>
       <c r="B80" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E80" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F80" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G80" s="7" t="s">
         <v>86</v>
-      </c>
-      <c r="F80" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G80" s="7" t="s">
-        <v>87</v>
       </c>
       <c r="H80" s="7"/>
       <c r="I80" s="7"/>
       <c r="J80" s="7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K80" s="7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L80" s="7"/>
       <c r="M80" s="1"/>
@@ -4669,16 +4672,16 @@
         <v>80</v>
       </c>
       <c r="B81" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F81" s="7" t="s">
         <v>12</v>
@@ -4687,10 +4690,10 @@
       <c r="H81" s="7"/>
       <c r="I81" s="7"/>
       <c r="J81" s="7" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="K81" s="7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L81" s="7"/>
       <c r="M81" s="1"/>
@@ -4700,16 +4703,16 @@
         <v>81</v>
       </c>
       <c r="B82" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F82" s="7" t="s">
         <v>12</v>
@@ -4718,10 +4721,10 @@
       <c r="H82" s="7"/>
       <c r="I82" s="7"/>
       <c r="J82" s="7" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="K82" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="L82" s="7"/>
       <c r="M82" s="1"/>
@@ -4731,16 +4734,16 @@
         <v>82</v>
       </c>
       <c r="B83" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F83" s="7" t="s">
         <v>12</v>
@@ -4749,10 +4752,10 @@
       <c r="H83" s="7"/>
       <c r="I83" s="7"/>
       <c r="J83" s="7" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="K83" s="7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L83" s="7"/>
       <c r="M83" s="1"/>
@@ -4762,16 +4765,16 @@
         <v>83</v>
       </c>
       <c r="B84" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F84" s="7" t="s">
         <v>16</v>
@@ -4782,10 +4785,10 @@
       <c r="H84" s="7"/>
       <c r="I84" s="7"/>
       <c r="J84" s="7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K84" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="L84" s="7"/>
       <c r="M84" s="1"/>
@@ -4795,32 +4798,32 @@
         <v>84</v>
       </c>
       <c r="B85" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="F85" s="7" t="s">
         <v>12</v>
       </c>
       <c r="G85" s="7"/>
       <c r="H85" s="7" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="I85" s="7" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J85" s="7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="K85" s="7" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L85" s="7"/>
       <c r="M85" s="1"/>
@@ -4830,32 +4833,32 @@
         <v>85</v>
       </c>
       <c r="B86" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F86" s="7" t="s">
         <v>12</v>
       </c>
       <c r="G86" s="7"/>
       <c r="H86" s="7" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="I86" s="7" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J86" s="7" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="K86" s="7" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L86" s="7"/>
       <c r="M86" s="1"/>
@@ -4865,16 +4868,16 @@
         <v>86</v>
       </c>
       <c r="B87" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F87" s="7" t="s">
         <v>12</v>
@@ -4883,10 +4886,10 @@
       <c r="H87" s="7"/>
       <c r="I87" s="7"/>
       <c r="J87" s="7" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="K87" s="7" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="L87" s="7"/>
       <c r="M87" s="1"/>
@@ -4896,16 +4899,16 @@
         <v>87</v>
       </c>
       <c r="B88" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D88" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E88" s="7" t="s">
         <v>92</v>
-      </c>
-      <c r="E88" s="7" t="s">
-        <v>93</v>
       </c>
       <c r="F88" s="7" t="s">
         <v>12</v>
@@ -4914,10 +4917,10 @@
       <c r="H88" s="7"/>
       <c r="I88" s="7"/>
       <c r="J88" s="7" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="K88" s="7" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L88" s="7"/>
       <c r="M88" s="1"/>
@@ -4927,28 +4930,28 @@
         <v>88</v>
       </c>
       <c r="B89" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G89" s="7"/>
       <c r="H89" s="7"/>
       <c r="I89" s="7"/>
       <c r="J89" s="7" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="K89" s="7" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L89" s="7"/>
       <c r="M89" s="1"/>
@@ -4958,30 +4961,30 @@
         <v>89</v>
       </c>
       <c r="B90" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E90" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G90" s="7" t="s">
         <v>95</v>
-      </c>
-      <c r="F90" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G90" s="7" t="s">
-        <v>96</v>
       </c>
       <c r="H90" s="7"/>
       <c r="I90" s="7"/>
       <c r="J90" s="7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K90" s="7" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="L90" s="7"/>
       <c r="M90" s="1"/>
@@ -4991,30 +4994,30 @@
         <v>90</v>
       </c>
       <c r="B91" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="F91" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="H91" s="7"/>
       <c r="I91" s="7"/>
       <c r="J91" s="7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K91" s="7" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="L91" s="7"/>
       <c r="M91" s="1"/>
@@ -5024,30 +5027,30 @@
         <v>91</v>
       </c>
       <c r="B92" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F92" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H92" s="7"/>
       <c r="I92" s="7"/>
       <c r="J92" s="7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K92" s="7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L92" s="7"/>
       <c r="M92" s="1"/>
@@ -5057,16 +5060,16 @@
         <v>92</v>
       </c>
       <c r="B93" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F93" s="7" t="s">
         <v>12</v>
@@ -5075,10 +5078,10 @@
       <c r="H93" s="7"/>
       <c r="I93" s="7"/>
       <c r="J93" s="7" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="K93" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L93" s="7"/>
       <c r="M93" s="1"/>
@@ -5088,16 +5091,16 @@
         <v>93</v>
       </c>
       <c r="B94" s="18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="F94" s="7" t="s">
         <v>12</v>
@@ -5106,10 +5109,10 @@
       <c r="H94" s="19"/>
       <c r="I94" s="19"/>
       <c r="J94" s="7" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="K94" s="7" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="L94" s="7"/>
       <c r="M94" s="1"/>
@@ -5119,16 +5122,16 @@
         <v>94</v>
       </c>
       <c r="B95" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F95" s="7" t="s">
         <v>12</v>
@@ -5137,10 +5140,10 @@
       <c r="H95" s="7"/>
       <c r="I95" s="7"/>
       <c r="J95" s="7" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="K95" s="7" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="L95" s="7"/>
       <c r="M95" s="1"/>
@@ -5150,28 +5153,28 @@
         <v>95</v>
       </c>
       <c r="B96" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D96" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E96" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G96" s="7"/>
       <c r="H96" s="7"/>
       <c r="I96" s="7"/>
       <c r="J96" s="7" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="K96" s="7" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="L96" s="7"/>
       <c r="M96" s="1"/>
@@ -5181,25 +5184,25 @@
         <v>96</v>
       </c>
       <c r="B97" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G97" s="7"/>
       <c r="H97" s="7"/>
       <c r="I97" s="7"/>
       <c r="J97" s="7" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -5210,25 +5213,25 @@
         <v>97</v>
       </c>
       <c r="B98" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D98" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G98" s="7"/>
       <c r="H98" s="7"/>
       <c r="I98" s="7"/>
       <c r="J98" s="7" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -5239,28 +5242,30 @@
         <v>98</v>
       </c>
       <c r="B99" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D99" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E99" s="7" t="s">
         <v>100</v>
-      </c>
-      <c r="E99" s="7" t="s">
-        <v>101</v>
       </c>
       <c r="F99" s="7" t="s">
         <v>12</v>
       </c>
       <c r="G99" s="7"/>
       <c r="H99" s="7"/>
-      <c r="I99" s="7"/>
+      <c r="I99" s="7" t="s">
+        <v>410</v>
+      </c>
       <c r="J99" s="7" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="K99" s="7" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="L99" s="7"/>
       <c r="M99" s="1"/>
@@ -5270,16 +5275,16 @@
         <v>99</v>
       </c>
       <c r="B100" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E100" s="7" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F100" s="7" t="s">
         <v>16</v>
@@ -5290,7 +5295,7 @@
       <c r="H100" s="20"/>
       <c r="I100" s="20"/>
       <c r="J100" s="7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -5301,25 +5306,25 @@
         <v>100</v>
       </c>
       <c r="B101" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G101" s="7"/>
       <c r="H101" s="7"/>
       <c r="I101" s="7"/>
       <c r="J101" s="7" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
@@ -5330,16 +5335,16 @@
         <v>101</v>
       </c>
       <c r="B102" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F102" s="7" t="s">
         <v>12</v>
@@ -5348,10 +5353,10 @@
       <c r="H102" s="7"/>
       <c r="I102" s="7"/>
       <c r="J102" s="7" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="K102" s="7" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="L102" s="7"/>
       <c r="M102" s="1"/>
@@ -5361,16 +5366,16 @@
         <v>102</v>
       </c>
       <c r="B103" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F103" s="7" t="s">
         <v>12</v>
@@ -5379,10 +5384,10 @@
       <c r="H103" s="7"/>
       <c r="I103" s="7"/>
       <c r="J103" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="K103" s="7" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="L103" s="7"/>
       <c r="M103" s="1"/>
@@ -5392,30 +5397,30 @@
         <v>103</v>
       </c>
       <c r="B104" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E104" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F104" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G104" s="7" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H104" s="7"/>
       <c r="I104" s="7"/>
       <c r="J104" s="7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K104" s="7" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L104" s="7"/>
       <c r="M104" s="1"/>
@@ -5425,16 +5430,16 @@
         <v>104</v>
       </c>
       <c r="B105" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F105" s="7" t="s">
         <v>12</v>
@@ -5443,10 +5448,10 @@
       <c r="H105" s="7"/>
       <c r="I105" s="7"/>
       <c r="J105" s="7" t="s">
-        <v>371</v>
+        <v>409</v>
       </c>
       <c r="K105" s="7" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="L105" s="7"/>
       <c r="M105" s="1"/>
@@ -5456,16 +5461,16 @@
         <v>105</v>
       </c>
       <c r="B106" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F106" s="7" t="s">
         <v>12</v>
@@ -5474,10 +5479,10 @@
       <c r="H106" s="7"/>
       <c r="I106" s="7"/>
       <c r="J106" s="7" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="K106" s="7" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="L106" s="7"/>
       <c r="M106" s="1"/>
@@ -5487,16 +5492,16 @@
         <v>106</v>
       </c>
       <c r="B107" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D107" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F107" s="7" t="s">
         <v>12</v>
@@ -5505,10 +5510,10 @@
       <c r="H107" s="7"/>
       <c r="I107" s="7"/>
       <c r="J107" s="7" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="K107" s="7" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="L107" s="7"/>
       <c r="M107" s="1"/>
@@ -5518,16 +5523,16 @@
         <v>107</v>
       </c>
       <c r="B108" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D108" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E108" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F108" s="7" t="s">
         <v>16</v>
@@ -5538,10 +5543,10 @@
       <c r="H108" s="7"/>
       <c r="I108" s="7"/>
       <c r="J108" s="7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K108" s="7" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="L108" s="7"/>
       <c r="M108" s="1"/>
@@ -5551,27 +5556,27 @@
         <v>108</v>
       </c>
       <c r="B109" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E109" s="13" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F109" s="14" t="s">
         <v>16</v>
       </c>
       <c r="G109" s="14" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H109" s="20"/>
       <c r="I109" s="20"/>
       <c r="J109" s="14" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K109" s="14"/>
       <c r="L109" s="14"/>
@@ -5582,30 +5587,30 @@
         <v>109</v>
       </c>
       <c r="B110" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E110" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F110" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G110" s="7" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="H110" s="7"/>
       <c r="I110" s="7"/>
       <c r="J110" s="7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K110" s="7" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L110" s="7"/>
       <c r="M110" s="1"/>
@@ -5615,30 +5620,30 @@
         <v>110</v>
       </c>
       <c r="B111" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F111" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G111" s="7" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="H111" s="7"/>
       <c r="I111" s="7"/>
       <c r="J111" s="7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K111" s="7" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="L111" s="7"/>
       <c r="M111" s="1"/>
@@ -5648,16 +5653,16 @@
         <v>111</v>
       </c>
       <c r="B112" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D112" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F112" s="7" t="s">
         <v>16</v>
@@ -5668,10 +5673,10 @@
       <c r="H112" s="7"/>
       <c r="I112" s="7"/>
       <c r="J112" s="7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K112" s="7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="L112" s="7"/>
       <c r="M112" s="1"/>
@@ -5681,16 +5686,16 @@
         <v>112</v>
       </c>
       <c r="B113" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F113" s="7" t="s">
         <v>16</v>
@@ -5701,10 +5706,10 @@
       <c r="H113" s="7"/>
       <c r="I113" s="7"/>
       <c r="J113" s="7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K113" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="L113" s="7"/>
       <c r="M113" s="1"/>
@@ -5714,25 +5719,25 @@
         <v>113</v>
       </c>
       <c r="B114" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F114" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G114" s="7"/>
       <c r="H114" s="7"/>
       <c r="I114" s="7"/>
       <c r="J114" s="7" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -5743,16 +5748,16 @@
         <v>114</v>
       </c>
       <c r="B115" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E115" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F115" s="7" t="s">
         <v>12</v>
@@ -5760,13 +5765,13 @@
       <c r="G115" s="7"/>
       <c r="H115" s="7"/>
       <c r="I115" s="7" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="J115" s="7" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="K115" s="7" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="L115" s="7"/>
       <c r="M115" s="1"/>
@@ -5776,16 +5781,16 @@
         <v>115</v>
       </c>
       <c r="B116" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D116" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E116" s="7" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F116" s="7" t="s">
         <v>16</v>
@@ -5796,10 +5801,10 @@
       <c r="H116" s="7"/>
       <c r="I116" s="7"/>
       <c r="J116" s="7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K116" s="7" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="L116" s="7"/>
       <c r="M116" s="1"/>
@@ -5809,28 +5814,28 @@
         <v>116</v>
       </c>
       <c r="B117" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D117" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E117" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G117" s="7"/>
       <c r="H117" s="7"/>
       <c r="I117" s="7"/>
       <c r="J117" s="7" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="K117" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="L117" s="7"/>
       <c r="M117" s="1"/>
@@ -5840,16 +5845,16 @@
         <v>117</v>
       </c>
       <c r="B118" s="15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D118" s="15" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E118" s="15" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F118" s="15" t="s">
         <v>16</v>
@@ -5858,10 +5863,10 @@
       <c r="H118" s="15"/>
       <c r="I118" s="15"/>
       <c r="J118" s="15" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="K118" s="15" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="L118" s="15"/>
       <c r="M118" s="1"/>
@@ -5871,16 +5876,16 @@
         <v>118</v>
       </c>
       <c r="B119" s="17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C119" s="16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D119" s="16" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E119" s="17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F119" s="17" t="s">
         <v>12</v>
@@ -5889,10 +5894,10 @@
       <c r="H119" s="17"/>
       <c r="I119" s="17"/>
       <c r="J119" s="17" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="K119" s="17" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="L119" s="17"/>
       <c r="M119" s="1"/>
@@ -5902,16 +5907,16 @@
         <v>119</v>
       </c>
       <c r="B120" s="17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C120" s="16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D120" s="16" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E120" s="17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F120" s="17" t="s">
         <v>12</v>
@@ -5920,10 +5925,10 @@
       <c r="H120" s="17"/>
       <c r="I120" s="17"/>
       <c r="J120" s="17" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="K120" s="17" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="L120" s="17"/>
       <c r="M120" s="1"/>
@@ -5933,16 +5938,16 @@
         <v>120</v>
       </c>
       <c r="B121" s="17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C121" s="16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D121" s="16" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E121" s="17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F121" s="17" t="s">
         <v>12</v>
@@ -5951,10 +5956,10 @@
       <c r="H121" s="17"/>
       <c r="I121" s="17"/>
       <c r="J121" s="17" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="K121" s="17" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L121" s="17"/>
       <c r="M121" s="1"/>
@@ -5964,16 +5969,16 @@
         <v>121</v>
       </c>
       <c r="B122" s="17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C122" s="16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D122" s="16" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E122" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F122" s="17" t="s">
         <v>16</v>
@@ -5984,10 +5989,10 @@
       <c r="H122" s="17"/>
       <c r="I122" s="17"/>
       <c r="J122" s="17" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="K122" s="17" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="L122" s="17"/>
       <c r="M122" s="1"/>
@@ -5997,16 +6002,16 @@
         <v>122</v>
       </c>
       <c r="B123" s="17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C123" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D123" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="E123" s="17" t="s">
         <v>52</v>
-      </c>
-      <c r="D123" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="E123" s="17" t="s">
-        <v>53</v>
       </c>
       <c r="F123" s="17" t="s">
         <v>16</v>
@@ -6017,10 +6022,10 @@
       <c r="H123" s="17"/>
       <c r="I123" s="17"/>
       <c r="J123" s="17" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K123" s="17" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="L123" s="17"/>
       <c r="M123" s="1"/>
@@ -6030,16 +6035,16 @@
         <v>123</v>
       </c>
       <c r="B124" s="17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C124" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D124" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E124" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F124" s="17" t="s">
         <v>16</v>
@@ -6050,10 +6055,10 @@
       <c r="H124" s="17"/>
       <c r="I124" s="17"/>
       <c r="J124" s="17" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K124" s="17" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="L124" s="17"/>
       <c r="M124" s="1"/>
@@ -6063,16 +6068,16 @@
         <v>124</v>
       </c>
       <c r="B125" s="17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C125" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D125" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E125" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F125" s="17" t="s">
         <v>16</v>
@@ -6083,10 +6088,10 @@
       <c r="H125" s="17"/>
       <c r="I125" s="17"/>
       <c r="J125" s="17" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K125" s="17" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="L125" s="17"/>
       <c r="M125" s="1"/>
@@ -6096,30 +6101,30 @@
         <v>125</v>
       </c>
       <c r="B126" s="17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C126" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D126" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E126" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="F126" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G126" s="17" t="s">
         <v>55</v>
-      </c>
-      <c r="F126" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="G126" s="17" t="s">
-        <v>56</v>
       </c>
       <c r="H126" s="17"/>
       <c r="I126" s="17"/>
       <c r="J126" s="17" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K126" s="17" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="L126" s="17"/>
       <c r="M126" s="1"/>
@@ -6129,16 +6134,16 @@
         <v>126</v>
       </c>
       <c r="B127" s="17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C127" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D127" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E127" s="17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F127" s="17" t="s">
         <v>16</v>
@@ -6149,10 +6154,10 @@
       <c r="H127" s="17"/>
       <c r="I127" s="17"/>
       <c r="J127" s="17" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K127" s="17" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L127" s="17"/>
       <c r="M127" s="1"/>
@@ -6162,16 +6167,16 @@
         <v>127</v>
       </c>
       <c r="B128" s="17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C128" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D128" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E128" s="17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F128" s="17" t="s">
         <v>16</v>
@@ -6182,10 +6187,10 @@
       <c r="H128" s="17"/>
       <c r="I128" s="17"/>
       <c r="J128" s="17" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K128" s="17" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="L128" s="17"/>
       <c r="M128" s="1"/>
@@ -6195,16 +6200,16 @@
         <v>128</v>
       </c>
       <c r="B129" s="17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C129" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D129" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E129" s="17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F129" s="17" t="s">
         <v>16</v>
@@ -6213,10 +6218,10 @@
       <c r="H129" s="17"/>
       <c r="I129" s="17"/>
       <c r="J129" s="17" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K129" s="17" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="L129" s="17"/>
       <c r="M129" s="1"/>
@@ -6226,30 +6231,30 @@
         <v>129</v>
       </c>
       <c r="B130" s="17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C130" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D130" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E130" s="17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F130" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G130" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H130" s="17"/>
       <c r="I130" s="17"/>
       <c r="J130" s="17" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K130" s="17" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="L130" s="17"/>
       <c r="M130" s="1"/>
@@ -6259,30 +6264,30 @@
         <v>130</v>
       </c>
       <c r="B131" s="17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C131" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D131" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E131" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F131" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G131" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H131" s="17"/>
       <c r="I131" s="17"/>
       <c r="J131" s="17" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K131" s="17" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="L131" s="17"/>
       <c r="M131" s="1"/>
@@ -6292,16 +6297,16 @@
         <v>131</v>
       </c>
       <c r="B132" s="17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C132" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D132" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E132" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F132" s="17" t="s">
         <v>12</v>
@@ -6310,10 +6315,10 @@
       <c r="H132" s="17"/>
       <c r="I132" s="17"/>
       <c r="J132" s="17" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="K132" s="17" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="L132" s="17"/>
       <c r="M132" s="1"/>
@@ -6323,16 +6328,16 @@
         <v>132</v>
       </c>
       <c r="B133" s="17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C133" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D133" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E133" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F133" s="17" t="s">
         <v>12</v>
@@ -6341,10 +6346,10 @@
       <c r="H133" s="17"/>
       <c r="I133" s="17"/>
       <c r="J133" s="17" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="K133" s="17" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="L133" s="17"/>
       <c r="M133" s="1"/>
@@ -6354,30 +6359,30 @@
         <v>133</v>
       </c>
       <c r="B134" s="17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C134" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D134" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E134" s="17" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F134" s="17" t="s">
         <v>13</v>
       </c>
       <c r="G134" s="17" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="H134" s="17"/>
       <c r="I134" s="17"/>
       <c r="J134" s="17" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="K134" s="17" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="L134" s="17"/>
       <c r="M134" s="1"/>
@@ -6387,16 +6392,16 @@
         <v>134</v>
       </c>
       <c r="B135" s="17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C135" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D135" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E135" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F135" s="17" t="s">
         <v>16</v>
@@ -6407,10 +6412,10 @@
       <c r="H135" s="17"/>
       <c r="I135" s="17"/>
       <c r="J135" s="17" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K135" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L135" s="17"/>
       <c r="M135" s="1"/>
@@ -6420,16 +6425,16 @@
         <v>135</v>
       </c>
       <c r="B136" s="17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C136" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D136" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E136" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F136" s="17" t="s">
         <v>16</v>
@@ -6440,10 +6445,10 @@
       <c r="H136" s="17"/>
       <c r="I136" s="17"/>
       <c r="J136" s="17" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K136" s="17" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L136" s="17"/>
       <c r="M136" s="1"/>
@@ -6453,16 +6458,16 @@
         <v>136</v>
       </c>
       <c r="B137" s="17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C137" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D137" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E137" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F137" s="17" t="s">
         <v>16</v>
@@ -6473,10 +6478,10 @@
       <c r="H137" s="17"/>
       <c r="I137" s="17"/>
       <c r="J137" s="17" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K137" s="17" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="L137" s="17"/>
       <c r="M137" s="1"/>
@@ -6486,30 +6491,30 @@
         <v>137</v>
       </c>
       <c r="B138" s="17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C138" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D138" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E138" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="F138" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G138" s="17" t="s">
         <v>63</v>
-      </c>
-      <c r="F138" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="G138" s="17" t="s">
-        <v>64</v>
       </c>
       <c r="H138" s="17"/>
       <c r="I138" s="17"/>
       <c r="J138" s="17" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K138" s="17" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="L138" s="17"/>
       <c r="M138" s="1"/>
@@ -6519,30 +6524,30 @@
         <v>138</v>
       </c>
       <c r="B139" s="17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C139" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D139" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E139" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="F139" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G139" s="17" t="s">
         <v>65</v>
-      </c>
-      <c r="F139" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="G139" s="17" t="s">
-        <v>66</v>
       </c>
       <c r="H139" s="17"/>
       <c r="I139" s="17"/>
       <c r="J139" s="17" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K139" s="17" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="L139" s="17"/>
       <c r="M139" s="1"/>
@@ -6552,30 +6557,30 @@
         <v>139</v>
       </c>
       <c r="B140" s="17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C140" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D140" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E140" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F140" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G140" s="17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H140" s="17"/>
       <c r="I140" s="17"/>
       <c r="J140" s="17" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K140" s="17" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="L140" s="17"/>
       <c r="M140" s="1"/>
@@ -6585,16 +6590,16 @@
         <v>140</v>
       </c>
       <c r="B141" s="17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C141" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D141" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E141" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F141" s="17" t="s">
         <v>16</v>
@@ -6603,10 +6608,10 @@
       <c r="H141" s="17"/>
       <c r="I141" s="17"/>
       <c r="J141" s="17" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="K141" s="17" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="L141" s="17"/>
       <c r="M141" s="1"/>
@@ -6616,16 +6621,16 @@
         <v>141</v>
       </c>
       <c r="B142" s="17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C142" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D142" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E142" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F142" s="17" t="s">
         <v>12</v>
@@ -6634,10 +6639,10 @@
       <c r="H142" s="17"/>
       <c r="I142" s="17"/>
       <c r="J142" s="17" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="K142" s="17" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="L142" s="17"/>
       <c r="M142" s="1"/>
@@ -6647,16 +6652,16 @@
         <v>142</v>
       </c>
       <c r="B143" s="17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C143" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D143" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E143" s="17" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F143" s="17" t="s">
         <v>16</v>
@@ -6665,10 +6670,10 @@
       <c r="H143" s="17"/>
       <c r="I143" s="17"/>
       <c r="J143" s="17" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K143" s="17" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="L143" s="17"/>
       <c r="M143" s="1"/>
@@ -6678,30 +6683,30 @@
         <v>143</v>
       </c>
       <c r="B144" s="17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C144" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D144" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E144" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="F144" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G144" s="17" t="s">
         <v>70</v>
-      </c>
-      <c r="F144" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="G144" s="17" t="s">
-        <v>71</v>
       </c>
       <c r="H144" s="17"/>
       <c r="I144" s="17"/>
       <c r="J144" s="17" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K144" s="17" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="L144" s="17"/>
       <c r="M144" s="1"/>
@@ -6711,16 +6716,16 @@
         <v>144</v>
       </c>
       <c r="B145" s="17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C145" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D145" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E145" s="17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F145" s="17" t="s">
         <v>16</v>
@@ -6731,10 +6736,10 @@
       <c r="H145" s="17"/>
       <c r="I145" s="17"/>
       <c r="J145" s="17" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K145" s="17" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="L145" s="17"/>
       <c r="M145" s="1"/>
@@ -6744,30 +6749,30 @@
         <v>145</v>
       </c>
       <c r="B146" s="17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C146" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D146" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E146" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="F146" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G146" s="17" t="s">
         <v>73</v>
-      </c>
-      <c r="F146" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="G146" s="17" t="s">
-        <v>74</v>
       </c>
       <c r="H146" s="17"/>
       <c r="I146" s="17"/>
       <c r="J146" s="17" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K146" s="17" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="L146" s="17"/>
       <c r="M146" s="1"/>
@@ -6777,16 +6782,16 @@
         <v>146</v>
       </c>
       <c r="B147" s="17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C147" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D147" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E147" s="17" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="F147" s="17" t="s">
         <v>16</v>
@@ -6797,10 +6802,10 @@
       <c r="H147" s="17"/>
       <c r="I147" s="17"/>
       <c r="J147" s="17" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K147" s="17" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="L147" s="17"/>
       <c r="M147" s="1"/>

--- a/MASTER.xlsx
+++ b/MASTER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Javid Shiriyev\Documents\GitHub\sand-control-failure-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8EB2284-67C5-423E-99C3-4528B8C90A8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A0C3F0B-9AA7-4B32-88B0-CC45FCCAB736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38510" yWindow="-2730" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1106" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="417">
   <si>
     <t>Category</t>
   </si>
@@ -140,9 +140,6 @@
     <t>%</t>
   </si>
   <si>
-    <t>pptb / lbs perf mmscf</t>
-  </si>
-  <si>
     <t>psi</t>
   </si>
   <si>
@@ -431,9 +428,6 @@
     <t>Initial non-Darcy skin</t>
   </si>
   <si>
-    <t>Initial deviated well skin</t>
-  </si>
-  <si>
     <t>Well PI after choke-back</t>
   </si>
   <si>
@@ -443,9 +437,6 @@
     <t>Non-Darcy skin after choke-back</t>
   </si>
   <si>
-    <t>Deviated well skin after choke-back</t>
-  </si>
-  <si>
     <t>Tooltip</t>
   </si>
   <si>
@@ -1079,12 +1070,6 @@
     <t>{"required": True, "Decimal": {"min": 0}}</t>
   </si>
   <si>
-    <t>{"Decimal": {"required": True}}</t>
-  </si>
-  <si>
-    <t>{"Short Date": {"required": True}}</t>
-  </si>
-  <si>
     <t>{"List": {"options": ["Operator", "Service Company", "Report", "SPE Paper", "Public Data"]}}</t>
   </si>
   <si>
@@ -1193,18 +1178,9 @@
     <t>{"List": {"required": True, "options": ["Surface Solids Samples", "ASD Response", "Surface Equipment Erosion"]}}</t>
   </si>
   <si>
-    <t>{"List": {"required": True, "options": ["Flowing Unrestricted by Sand", "Flowing Restricted by Sand", "Shut-in Due to Sand", "Shut in due to reasons other than sand", "Not Producing"]}}</t>
-  </si>
-  <si>
     <t>{"List": {"required": True, "options": ["Measurable", "Unable to quantify", "No sand"]}}</t>
   </si>
   <si>
-    <t>{"List": {"required": True, "options": ["Gradual (≤ 0.01 in/hr average increase in choke diameter)", "Aggressive (&gt; 0.01 in/hr, or a single increase ≥ 0.05 in within 1 hr)", "Mixed (Both gradual and aggressive behavior occur during the evaluated period)", "Unknown (Insufficient choke-size/time data)", "Not applicable (No meaningful choke-management period exists)"]}}</t>
-  </si>
-  <si>
-    <t>{"List": {"required": True, "options": ["Same", "Increased", "Decreased", "Variable", "Unknown", "Not applicable"]}}</t>
-  </si>
-  <si>
     <t>Severity of sand production - Oil Well</t>
   </si>
   <si>
@@ -1274,7 +1250,43 @@
     <t>{"OHGP": {"Placement Method", "Carrier Fluid Type - OHGP", "Pack Efficiency Source", "Pack Efficiency Percentage", "ICD / AICD", "Did screens get to Target Setting Depth", "Return Percentage", "If screens ran in mud, was mud removed once screens on bottom?"}, "SAS": {"Fluid Type Left in OH at end of Completion", "ICD / AICD", "Did screens get to Target Setting Depth", "If screens ran in mud, was mud removed once screens on bottom?", "Blank pipe run across non-pay sections instead of screens?"}, "CHFP": {"Carrier Fluid Type - CHFP", "Full Pack from Log"}, "CHGP": {"Carrier Fluid Type - CHGP", "Perf Packing", "Return Percentage", "Pack Efficiency Source", "Pack Efficiency Percentage"}}</t>
   </si>
   <si>
-    <t>{"List": {"required": True, "options": ["Aggressive Drawdown", "Screen Plugging", "Water Breakthrough", "Hard Shutdown", "Flux", "Incomplete Gravel Pack", "Compaction", "Excessive Drawdown", "Rapid Beanup", "Hard Shut-in", "Well Slugging", "Intervention Induced Damage", "Wrongly Sized Sand Control", "No Sand Control Installed", "Other", "Unknown"]}}</t>
+    <t>pptb or lb/mmscf</t>
+  </si>
+  <si>
+    <t>{"List": {"required": True, "options": ["Screen Plugging", "Water Breakthrough", "Flux (excessive perf fluid velocity)", "Incomplete Gravel Pack", "Compaction", "Excessive Drawdown", "Rapid Beanup", "Hard Shut-in", "Well Slugging", "Intervention Induced Damage", "Wrongly Sized Sand Control", "No Sand Control Installed", "Corrosion", "Geomechanical / Compaction", "Geomechanical / Other", "Annular Convergent Flow (for stand alone screens)", "Other", "Unknown"]}}</t>
+  </si>
+  <si>
+    <t>Did sanding start immediately after water breakthrough</t>
+  </si>
+  <si>
+    <t>{"Text": {"required": False}}</t>
+  </si>
+  <si>
+    <t>{"Decimal": {"required": False, "min": 0}}</t>
+  </si>
+  <si>
+    <t>{"Decimal": {"required": False}}</t>
+  </si>
+  <si>
+    <t>{"List": {"required": False, "options": ["Flowing Unrestricted by Sand", "Flowing Restricted by Sand", "Shut-in Due to Sand", "Shut in due to reasons other than sand", "Not Producing"]}}</t>
+  </si>
+  <si>
+    <t>{"Short Date": {"required": False}}</t>
+  </si>
+  <si>
+    <t>{"List": {"required": False, "options": ["Gradual (≤ 0.01 in/hr average increase in choke diameter)", "Aggressive (&gt; 0.01 in/hr, or a single increase ≥ 0.05 in within 1 hr)", "Mixed (Both gradual and aggressive behavior occur during the evaluated period)", "Unknown (Insufficient choke-size/time data)", "Not applicable (No meaningful choke-management period exists)"]}}</t>
+  </si>
+  <si>
+    <t>{"List": {"required": False, "options": ["Same", "Increased", "Decreased", "Variable", "Unknown", "Not applicable"]}}</t>
+  </si>
+  <si>
+    <t>Initial Mechanical / Completion skin</t>
+  </si>
+  <si>
+    <t>Mechanical / Completion skin after choke-back</t>
+  </si>
+  <si>
+    <t>{"List": {"required": False, "options": ["Yes", "No"]}}</t>
   </si>
 </sst>
 </file>
@@ -1767,8 +1779,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table22" displayName="Table22" ref="B1:L147" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="B1:L147" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table22" displayName="Table22" ref="B1:L148" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="B1:L148" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="11">
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Scope" dataDxfId="10"/>
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Category" dataDxfId="9"/>
@@ -2083,7 +2095,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M147"/>
+  <dimension ref="A1:M148"/>
   <sheetFormatPr defaultColWidth="30" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.08984375" style="1" customWidth="1"/>
@@ -2091,7 +2103,7 @@
     <col min="3" max="3" width="9.81640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="34" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="62.54296875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="14" style="2" customWidth="1"/>
+    <col min="7" max="7" width="22" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="26.7265625" style="1" customWidth="1"/>
     <col min="9" max="9" width="25" style="1" customWidth="1"/>
     <col min="10" max="10" width="40.26953125" style="1" customWidth="1"/>
@@ -2103,7 +2115,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="28" x14ac:dyDescent="0.35">
       <c r="A1" s="21" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>3</v>
@@ -2133,10 +2145,10 @@
         <v>6</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="L1" s="10" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="M1" s="1"/>
     </row>
@@ -2154,7 +2166,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>12</v>
@@ -2163,10 +2175,10 @@
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
       <c r="J2" s="5" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="L2" s="5"/>
       <c r="M2" s="1"/>
@@ -2185,7 +2197,7 @@
         <v>10</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>12</v>
@@ -2194,10 +2206,10 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="L3" s="5"/>
       <c r="M3" s="1"/>
@@ -2216,7 +2228,7 @@
         <v>10</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>13</v>
@@ -2225,10 +2237,10 @@
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
       <c r="J4" s="5" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="L4" s="5"/>
       <c r="M4" s="1"/>
@@ -2247,7 +2259,7 @@
         <v>15</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>13</v>
@@ -2256,10 +2268,10 @@
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="L5" s="6"/>
       <c r="M5" s="1"/>
@@ -2278,7 +2290,7 @@
         <v>15</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>13</v>
@@ -2287,10 +2299,10 @@
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
       <c r="J6" s="6" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="L6" s="6"/>
       <c r="M6" s="1"/>
@@ -2309,7 +2321,7 @@
         <v>15</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>12</v>
@@ -2317,13 +2329,13 @@
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
       <c r="I7" s="6" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="L7" s="6"/>
       <c r="M7" s="1"/>
@@ -2342,7 +2354,7 @@
         <v>15</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>12</v>
@@ -2350,13 +2362,13 @@
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
       <c r="I8" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="L8" s="6"/>
       <c r="M8" s="1"/>
@@ -2375,7 +2387,7 @@
         <v>15</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>16</v>
@@ -2386,10 +2398,10 @@
       <c r="H9" s="6"/>
       <c r="I9" s="6"/>
       <c r="J9" s="6" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="L9" s="6"/>
       <c r="M9" s="1"/>
@@ -2408,7 +2420,7 @@
         <v>15</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>12</v>
@@ -2417,10 +2429,10 @@
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
       <c r="J10" s="6" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="L10" s="6"/>
       <c r="M10" s="1"/>
@@ -2450,10 +2462,10 @@
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
       <c r="J11" s="6" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="L11" s="6"/>
       <c r="M11" s="1"/>
@@ -2472,7 +2484,7 @@
         <v>15</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>16</v>
@@ -2483,10 +2495,10 @@
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="L12" s="6"/>
       <c r="M12" s="1"/>
@@ -2505,7 +2517,7 @@
         <v>15</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>13</v>
@@ -2514,10 +2526,10 @@
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
       <c r="J13" s="6" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="L13" s="6"/>
       <c r="M13" s="1"/>
@@ -2536,7 +2548,7 @@
         <v>15</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>13</v>
@@ -2545,10 +2557,10 @@
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
       <c r="J14" s="6" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="L14" s="6"/>
       <c r="M14" s="1"/>
@@ -2567,7 +2579,7 @@
         <v>15</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>12</v>
@@ -2576,10 +2588,10 @@
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
       <c r="J15" s="6" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="L15" s="6"/>
       <c r="M15" s="1"/>
@@ -2607,10 +2619,10 @@
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
       <c r="J16" s="6" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L16" s="6"/>
       <c r="M16" s="1"/>
@@ -2626,24 +2638,24 @@
         <v>14</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="I17" s="6"/>
       <c r="J17" s="6" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L17" s="6"/>
       <c r="M17" s="1"/>
@@ -2662,7 +2674,7 @@
         <v>20</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>12</v>
@@ -2671,10 +2683,10 @@
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
       <c r="J18" s="6" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L18" s="6"/>
       <c r="M18" s="1"/>
@@ -2693,7 +2705,7 @@
         <v>20</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>12</v>
@@ -2702,10 +2714,10 @@
       <c r="H19" s="6"/>
       <c r="I19" s="6"/>
       <c r="J19" s="6" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L19" s="6"/>
       <c r="M19" s="1"/>
@@ -2724,7 +2736,7 @@
         <v>20</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>16</v>
@@ -2735,10 +2747,10 @@
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
       <c r="J20" s="6" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="L20" s="6"/>
       <c r="M20" s="1"/>
@@ -2757,7 +2769,7 @@
         <v>20</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>16</v>
@@ -2768,10 +2780,10 @@
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
       <c r="J21" s="6" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="L21" s="6"/>
       <c r="M21" s="1"/>
@@ -2790,7 +2802,7 @@
         <v>20</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>16</v>
@@ -2801,10 +2813,10 @@
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
       <c r="J22" s="6" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="L22" s="6"/>
       <c r="M22" s="1"/>
@@ -2823,7 +2835,7 @@
         <v>20</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>12</v>
@@ -2832,10 +2844,10 @@
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
       <c r="J23" s="6" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L23" s="6"/>
       <c r="M23" s="1"/>
@@ -2854,7 +2866,7 @@
         <v>20</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>12</v>
@@ -2863,10 +2875,10 @@
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
       <c r="J24" s="6" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L24" s="6"/>
       <c r="M24" s="1"/>
@@ -2884,24 +2896,20 @@
       <c r="D25" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E25" s="6" t="s">
-        <v>297</v>
+      <c r="E25" s="8" t="s">
+        <v>406</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6" t="s">
-        <v>405</v>
-      </c>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
       <c r="J25" s="6" t="s">
-        <v>386</v>
-      </c>
-      <c r="K25" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="L25" s="6"/>
+        <v>416</v>
+      </c>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
       <c r="M25" s="1"/>
     </row>
     <row r="26" spans="1:13" ht="14" x14ac:dyDescent="0.3">
@@ -2918,21 +2926,21 @@
         <v>20</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>126</v>
+        <v>294</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>34</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="G26" s="6"/>
       <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
+      <c r="I26" s="6" t="s">
+        <v>397</v>
+      </c>
       <c r="J26" s="6" t="s">
-        <v>345</v>
+        <v>380</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="L26" s="6"/>
       <c r="M26" s="1"/>
@@ -2951,21 +2959,21 @@
         <v>20</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>34</v>
+        <v>404</v>
       </c>
       <c r="H27" s="6"/>
       <c r="I27" s="6"/>
       <c r="J27" s="6" t="s">
-        <v>345</v>
+        <v>408</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L27" s="6"/>
       <c r="M27" s="1"/>
@@ -2984,21 +2992,21 @@
         <v>20</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>34</v>
+        <v>404</v>
       </c>
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
       <c r="J28" s="6" t="s">
-        <v>345</v>
+        <v>408</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="L28" s="6"/>
       <c r="M28" s="1"/>
@@ -3017,21 +3025,21 @@
         <v>20</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>60</v>
+        <v>127</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>22</v>
+        <v>404</v>
       </c>
       <c r="H29" s="6"/>
       <c r="I29" s="6"/>
       <c r="J29" s="6" t="s">
-        <v>345</v>
+        <v>408</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="L29" s="6"/>
       <c r="M29" s="1"/>
@@ -3050,19 +3058,21 @@
         <v>20</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>129</v>
+        <v>59</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G30" s="6"/>
+      <c r="G30" s="6" t="s">
+        <v>22</v>
+      </c>
       <c r="H30" s="6"/>
       <c r="I30" s="6"/>
       <c r="J30" s="6" t="s">
-        <v>347</v>
+        <v>408</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="L30" s="6"/>
       <c r="M30" s="1"/>
@@ -3081,7 +3091,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F31" s="6" t="s">
         <v>16</v>
@@ -3090,10 +3100,10 @@
       <c r="H31" s="6"/>
       <c r="I31" s="6"/>
       <c r="J31" s="6" t="s">
-        <v>347</v>
+        <v>409</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="L31" s="6"/>
       <c r="M31" s="1"/>
@@ -3112,7 +3122,7 @@
         <v>20</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>16</v>
@@ -3121,10 +3131,10 @@
       <c r="H32" s="6"/>
       <c r="I32" s="6"/>
       <c r="J32" s="6" t="s">
-        <v>347</v>
+        <v>409</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="L32" s="6"/>
       <c r="M32" s="1"/>
@@ -3143,21 +3153,19 @@
         <v>20</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>132</v>
+        <v>414</v>
       </c>
       <c r="F33" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G33" s="6" t="s">
-        <v>22</v>
-      </c>
+      <c r="G33" s="6"/>
       <c r="H33" s="6"/>
       <c r="I33" s="6"/>
       <c r="J33" s="6" t="s">
-        <v>345</v>
+        <v>409</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="L33" s="6"/>
       <c r="M33" s="1"/>
@@ -3176,19 +3184,21 @@
         <v>20</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G34" s="6"/>
+      <c r="G34" s="6" t="s">
+        <v>22</v>
+      </c>
       <c r="H34" s="6"/>
       <c r="I34" s="6"/>
       <c r="J34" s="6" t="s">
-        <v>347</v>
+        <v>408</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="L34" s="6"/>
       <c r="M34" s="1"/>
@@ -3207,7 +3217,7 @@
         <v>20</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F35" s="6" t="s">
         <v>16</v>
@@ -3216,10 +3226,10 @@
       <c r="H35" s="6"/>
       <c r="I35" s="6"/>
       <c r="J35" s="6" t="s">
-        <v>347</v>
+        <v>409</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="L35" s="6"/>
       <c r="M35" s="1"/>
@@ -3238,7 +3248,7 @@
         <v>20</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>16</v>
@@ -3247,10 +3257,10 @@
       <c r="H36" s="6"/>
       <c r="I36" s="6"/>
       <c r="J36" s="6" t="s">
-        <v>347</v>
+        <v>409</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="L36" s="6"/>
       <c r="M36" s="1"/>
@@ -3269,19 +3279,19 @@
         <v>20</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>23</v>
+        <v>415</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
       <c r="I37" s="6"/>
       <c r="J37" s="6" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="K37" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="L37" s="6"/>
       <c r="M37" s="1"/>
@@ -3296,23 +3306,23 @@
       <c r="C38" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D38" s="8" t="s">
-        <v>283</v>
+      <c r="D38" s="6" t="s">
+        <v>20</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>289</v>
+        <v>23</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G38" s="6"/>
       <c r="H38" s="6"/>
       <c r="I38" s="6"/>
       <c r="J38" s="6" t="s">
-        <v>385</v>
+        <v>407</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="L38" s="6"/>
       <c r="M38" s="1"/>
@@ -3328,22 +3338,22 @@
         <v>14</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G39" s="6"/>
       <c r="H39" s="6"/>
       <c r="I39" s="6"/>
       <c r="J39" s="6" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="L39" s="6"/>
       <c r="M39" s="1"/>
@@ -3359,10 +3369,10 @@
         <v>14</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>24</v>
@@ -3371,10 +3381,10 @@
       <c r="H40" s="6"/>
       <c r="I40" s="6"/>
       <c r="J40" s="6" t="s">
-        <v>348</v>
+        <v>411</v>
       </c>
       <c r="K40" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="L40" s="6"/>
       <c r="M40" s="1"/>
@@ -3390,10 +3400,10 @@
         <v>14</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="F41" s="6" t="s">
         <v>24</v>
@@ -3402,10 +3412,10 @@
       <c r="H41" s="6"/>
       <c r="I41" s="6"/>
       <c r="J41" s="6" t="s">
-        <v>348</v>
+        <v>411</v>
       </c>
       <c r="K41" s="6" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="L41" s="6"/>
       <c r="M41" s="1"/>
@@ -3421,24 +3431,22 @@
         <v>14</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>25</v>
+        <v>289</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>26</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="G42" s="6"/>
       <c r="H42" s="6"/>
       <c r="I42" s="6"/>
       <c r="J42" s="6" t="s">
-        <v>345</v>
+        <v>411</v>
       </c>
       <c r="K42" s="6" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="L42" s="6"/>
       <c r="M42" s="1"/>
@@ -3454,10 +3462,10 @@
         <v>14</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F43" s="6" t="s">
         <v>16</v>
@@ -3468,10 +3476,10 @@
       <c r="H43" s="6"/>
       <c r="I43" s="6"/>
       <c r="J43" s="6" t="s">
-        <v>345</v>
+        <v>408</v>
       </c>
       <c r="K43" s="6" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L43" s="6"/>
       <c r="M43" s="1"/>
@@ -3487,24 +3495,24 @@
         <v>14</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H44" s="6"/>
       <c r="I44" s="6"/>
       <c r="J44" s="6" t="s">
-        <v>345</v>
+        <v>408</v>
       </c>
       <c r="K44" s="6" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L44" s="6"/>
       <c r="M44" s="1"/>
@@ -3520,10 +3528,10 @@
         <v>14</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F45" s="6" t="s">
         <v>16</v>
@@ -3534,10 +3542,10 @@
       <c r="H45" s="6"/>
       <c r="I45" s="6"/>
       <c r="J45" s="6" t="s">
-        <v>345</v>
+        <v>408</v>
       </c>
       <c r="K45" s="6" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="L45" s="6"/>
       <c r="M45" s="1"/>
@@ -3553,24 +3561,24 @@
         <v>14</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H46" s="6"/>
       <c r="I46" s="6"/>
       <c r="J46" s="6" t="s">
-        <v>345</v>
+        <v>408</v>
       </c>
       <c r="K46" s="6" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="L46" s="6"/>
       <c r="M46" s="1"/>
@@ -3586,10 +3594,10 @@
         <v>14</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F47" s="6" t="s">
         <v>16</v>
@@ -3600,10 +3608,10 @@
       <c r="H47" s="6"/>
       <c r="I47" s="6"/>
       <c r="J47" s="6" t="s">
-        <v>345</v>
+        <v>408</v>
       </c>
       <c r="K47" s="6" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="L47" s="6"/>
       <c r="M47" s="1"/>
@@ -3619,10 +3627,10 @@
         <v>14</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>293</v>
+        <v>32</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>16</v>
@@ -3633,10 +3641,10 @@
       <c r="H48" s="6"/>
       <c r="I48" s="6"/>
       <c r="J48" s="6" t="s">
-        <v>345</v>
+        <v>408</v>
       </c>
       <c r="K48" s="6" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="L48" s="6"/>
       <c r="M48" s="1"/>
@@ -3652,24 +3660,24 @@
         <v>14</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="F49" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H49" s="6"/>
       <c r="I49" s="6"/>
       <c r="J49" s="6" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="K49" s="6" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="L49" s="6"/>
       <c r="M49" s="1"/>
@@ -3685,24 +3693,24 @@
         <v>14</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H50" s="6"/>
       <c r="I50" s="6"/>
       <c r="J50" s="6" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="K50" s="6" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="L50" s="6"/>
       <c r="M50" s="1"/>
@@ -3718,24 +3726,24 @@
         <v>14</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="F51" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="H51" s="6"/>
       <c r="I51" s="6"/>
       <c r="J51" s="6" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="K51" s="6" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="L51" s="6"/>
       <c r="M51" s="1"/>
@@ -3751,22 +3759,24 @@
         <v>14</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G52" s="6"/>
+        <v>16</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>33</v>
+      </c>
       <c r="H52" s="6"/>
       <c r="I52" s="6"/>
       <c r="J52" s="6" t="s">
-        <v>402</v>
+        <v>342</v>
       </c>
       <c r="K52" s="6" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="L52" s="6"/>
       <c r="M52" s="1"/>
@@ -3782,24 +3792,22 @@
         <v>14</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G53" s="6" t="s">
-        <v>35</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G53" s="6"/>
       <c r="H53" s="6"/>
       <c r="I53" s="6"/>
       <c r="J53" s="6" t="s">
-        <v>345</v>
+        <v>407</v>
       </c>
       <c r="K53" s="6" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="L53" s="6"/>
       <c r="M53" s="1"/>
@@ -3815,24 +3823,24 @@
         <v>14</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H54" s="6"/>
       <c r="I54" s="6"/>
       <c r="J54" s="6" t="s">
-        <v>345</v>
+        <v>408</v>
       </c>
       <c r="K54" s="6" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L54" s="6"/>
       <c r="M54" s="1"/>
@@ -3848,22 +3856,24 @@
         <v>14</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G55" s="6"/>
+        <v>16</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="H55" s="6"/>
       <c r="I55" s="6"/>
       <c r="J55" s="6" t="s">
-        <v>387</v>
+        <v>408</v>
       </c>
       <c r="K55" s="6" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="L55" s="6"/>
       <c r="M55" s="1"/>
@@ -3879,10 +3889,10 @@
         <v>14</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>12</v>
@@ -3891,10 +3901,10 @@
       <c r="H56" s="6"/>
       <c r="I56" s="6"/>
       <c r="J56" s="6" t="s">
-        <v>388</v>
+        <v>412</v>
       </c>
       <c r="K56" s="6" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="L56" s="6"/>
       <c r="M56" s="1"/>
@@ -3910,10 +3920,10 @@
         <v>14</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="F57" s="6" t="s">
         <v>12</v>
@@ -3922,10 +3932,10 @@
       <c r="H57" s="6"/>
       <c r="I57" s="6"/>
       <c r="J57" s="6" t="s">
-        <v>388</v>
+        <v>413</v>
       </c>
       <c r="K57" s="6" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="L57" s="6"/>
       <c r="M57" s="1"/>
@@ -3941,10 +3951,10 @@
         <v>14</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>12</v>
@@ -3953,74 +3963,74 @@
       <c r="H58" s="6"/>
       <c r="I58" s="6"/>
       <c r="J58" s="6" t="s">
-        <v>388</v>
+        <v>413</v>
       </c>
       <c r="K58" s="6" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="L58" s="6"/>
       <c r="M58" s="1"/>
     </row>
-    <row r="59" spans="1:13" ht="14" x14ac:dyDescent="0.35">
-      <c r="A59" s="27">
+    <row r="59" spans="1:13" ht="14" x14ac:dyDescent="0.3">
+      <c r="A59" s="25">
         <v>58</v>
       </c>
-      <c r="B59" s="12" t="s">
+      <c r="B59" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C59" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="D59" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="E59" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="F59" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="G59" s="12"/>
-      <c r="H59" s="12"/>
-      <c r="I59" s="12"/>
-      <c r="J59" s="12" t="s">
-        <v>311</v>
-      </c>
-      <c r="K59" s="11" t="s">
-        <v>310</v>
-      </c>
-      <c r="L59" s="11"/>
+      <c r="C59" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G59" s="6"/>
+      <c r="H59" s="6"/>
+      <c r="I59" s="6"/>
+      <c r="J59" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="K59" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="L59" s="6"/>
       <c r="M59" s="1"/>
     </row>
-    <row r="60" spans="1:13" ht="14" x14ac:dyDescent="0.3">
-      <c r="A60" s="26">
+    <row r="60" spans="1:13" ht="14" x14ac:dyDescent="0.35">
+      <c r="A60" s="27">
         <v>59</v>
       </c>
-      <c r="B60" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="C60" s="7" t="s">
+      <c r="B60" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C60" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="D60" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="E60" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G60" s="7"/>
-      <c r="H60" s="7"/>
-      <c r="I60" s="7"/>
-      <c r="J60" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="K60" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="L60" s="7"/>
+      <c r="D60" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="E60" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="F60" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G60" s="12"/>
+      <c r="H60" s="12"/>
+      <c r="I60" s="12"/>
+      <c r="J60" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="K60" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="L60" s="11"/>
       <c r="M60" s="1"/>
     </row>
     <row r="61" spans="1:13" ht="14" x14ac:dyDescent="0.3">
@@ -4028,32 +4038,28 @@
         <v>60</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E61" s="9" t="s">
-        <v>45</v>
+        <v>138</v>
+      </c>
+      <c r="D61" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>302</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G61" s="7"/>
-      <c r="H61" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="I61" s="7" t="s">
-        <v>396</v>
-      </c>
+      <c r="H61" s="7"/>
+      <c r="I61" s="7"/>
       <c r="J61" s="7" t="s">
-        <v>355</v>
-      </c>
-      <c r="K61" s="9" t="s">
-        <v>219</v>
+        <v>309</v>
+      </c>
+      <c r="K61" s="7" t="s">
+        <v>209</v>
       </c>
       <c r="L61" s="7"/>
       <c r="M61" s="1"/>
@@ -4063,28 +4069,32 @@
         <v>61</v>
       </c>
       <c r="B62" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E62" s="7" t="s">
-        <v>43</v>
+        <v>35</v>
+      </c>
+      <c r="E62" s="9" t="s">
+        <v>44</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G62" s="7"/>
-      <c r="H62" s="7"/>
-      <c r="I62" s="7"/>
+      <c r="H62" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="I62" s="7" t="s">
+        <v>388</v>
+      </c>
       <c r="J62" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="K62" s="7" t="s">
-        <v>220</v>
+        <v>350</v>
+      </c>
+      <c r="K62" s="9" t="s">
+        <v>216</v>
       </c>
       <c r="L62" s="7"/>
       <c r="M62" s="1"/>
@@ -4094,30 +4104,28 @@
         <v>62</v>
       </c>
       <c r="B63" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>403</v>
+        <v>42</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G63" s="7" t="s">
-        <v>76</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="G63" s="7"/>
       <c r="H63" s="7"/>
       <c r="I63" s="7"/>
       <c r="J63" s="7" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="K63" s="7" t="s">
-        <v>323</v>
+        <v>217</v>
       </c>
       <c r="L63" s="7"/>
       <c r="M63" s="1"/>
@@ -4127,30 +4135,30 @@
         <v>63</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E64" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G64" s="7" t="s">
         <v>75</v>
-      </c>
-      <c r="F64" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G64" s="7" t="s">
-        <v>76</v>
       </c>
       <c r="H64" s="7"/>
       <c r="I64" s="7"/>
       <c r="J64" s="7" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K64" s="7" t="s">
-        <v>221</v>
+        <v>320</v>
       </c>
       <c r="L64" s="7"/>
       <c r="M64" s="1"/>
@@ -4160,30 +4168,30 @@
         <v>64</v>
       </c>
       <c r="B65" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D65" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E65" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E65" s="7" t="s">
-        <v>77</v>
-      </c>
       <c r="F65" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="H65" s="7"/>
       <c r="I65" s="7"/>
       <c r="J65" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="K65" s="9" t="s">
-        <v>222</v>
+        <v>309</v>
+      </c>
+      <c r="K65" s="7" t="s">
+        <v>218</v>
       </c>
       <c r="L65" s="7"/>
       <c r="M65" s="1"/>
@@ -4193,16 +4201,16 @@
         <v>65</v>
       </c>
       <c r="B66" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F66" s="7" t="s">
         <v>16</v>
@@ -4213,10 +4221,10 @@
       <c r="H66" s="7"/>
       <c r="I66" s="7"/>
       <c r="J66" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="K66" s="7" t="s">
-        <v>223</v>
+        <v>309</v>
+      </c>
+      <c r="K66" s="9" t="s">
+        <v>219</v>
       </c>
       <c r="L66" s="7"/>
       <c r="M66" s="1"/>
@@ -4226,28 +4234,30 @@
         <v>66</v>
       </c>
       <c r="B67" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G67" s="7"/>
+        <v>16</v>
+      </c>
+      <c r="G67" s="7" t="s">
+        <v>17</v>
+      </c>
       <c r="H67" s="7"/>
       <c r="I67" s="7"/>
       <c r="J67" s="7" t="s">
-        <v>356</v>
+        <v>309</v>
       </c>
       <c r="K67" s="7" t="s">
-        <v>324</v>
+        <v>220</v>
       </c>
       <c r="L67" s="7"/>
       <c r="M67" s="1"/>
@@ -4257,19 +4267,19 @@
         <v>67</v>
       </c>
       <c r="B68" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>330</v>
+        <v>97</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G68" s="7"/>
       <c r="H68" s="7"/>
@@ -4277,7 +4287,9 @@
       <c r="J68" s="7" t="s">
         <v>351</v>
       </c>
-      <c r="K68" s="7"/>
+      <c r="K68" s="7" t="s">
+        <v>321</v>
+      </c>
       <c r="L68" s="7"/>
       <c r="M68" s="1"/>
     </row>
@@ -4286,29 +4298,27 @@
         <v>68</v>
       </c>
       <c r="B69" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>394</v>
+        <v>73</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>147</v>
+        <v>327</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="G69" s="7"/>
       <c r="H69" s="7"/>
       <c r="I69" s="7"/>
       <c r="J69" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="K69" s="7" t="s">
-        <v>213</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="K69" s="7"/>
       <c r="L69" s="7"/>
       <c r="M69" s="1"/>
     </row>
@@ -4317,28 +4327,28 @@
         <v>69</v>
       </c>
       <c r="B70" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="D70" s="9" t="s">
-        <v>394</v>
+        <v>137</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>386</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>37</v>
+        <v>144</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
       <c r="I70" s="7"/>
       <c r="J70" s="7" t="s">
-        <v>352</v>
+        <v>309</v>
       </c>
       <c r="K70" s="7" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="L70" s="7"/>
       <c r="M70" s="1"/>
@@ -4348,30 +4358,28 @@
         <v>70</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G71" s="7" t="s">
-        <v>39</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="G71" s="7"/>
       <c r="H71" s="7"/>
       <c r="I71" s="7"/>
       <c r="J71" s="7" t="s">
-        <v>312</v>
+        <v>347</v>
       </c>
       <c r="K71" s="7" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="L71" s="7"/>
       <c r="M71" s="1"/>
@@ -4381,28 +4389,30 @@
         <v>71</v>
       </c>
       <c r="B72" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G72" s="7"/>
+        <v>16</v>
+      </c>
+      <c r="G72" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="H72" s="7"/>
       <c r="I72" s="7"/>
       <c r="J72" s="7" t="s">
-        <v>353</v>
+        <v>309</v>
       </c>
       <c r="K72" s="7" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="L72" s="7"/>
       <c r="M72" s="1"/>
@@ -4412,16 +4422,16 @@
         <v>72</v>
       </c>
       <c r="B73" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F73" s="7" t="s">
         <v>12</v>
@@ -4430,10 +4440,10 @@
       <c r="H73" s="7"/>
       <c r="I73" s="7"/>
       <c r="J73" s="7" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="K73" s="7" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="L73" s="7"/>
       <c r="M73" s="1"/>
@@ -4443,28 +4453,28 @@
         <v>73</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>317</v>
+        <v>40</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G74" s="7"/>
       <c r="H74" s="7"/>
       <c r="I74" s="7"/>
       <c r="J74" s="7" t="s">
-        <v>315</v>
+        <v>349</v>
       </c>
       <c r="K74" s="7" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="L74" s="7"/>
       <c r="M74" s="1"/>
@@ -4474,30 +4484,28 @@
         <v>74</v>
       </c>
       <c r="B75" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>407</v>
+        <v>314</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G75" s="7" t="s">
-        <v>42</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G75" s="7"/>
       <c r="H75" s="7"/>
       <c r="I75" s="7"/>
       <c r="J75" s="7" t="s">
         <v>312</v>
       </c>
       <c r="K75" s="7" t="s">
-        <v>408</v>
+        <v>215</v>
       </c>
       <c r="L75" s="7"/>
       <c r="M75" s="1"/>
@@ -4507,30 +4515,30 @@
         <v>75</v>
       </c>
       <c r="B76" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="D76" s="7" t="s">
-        <v>80</v>
+        <v>137</v>
+      </c>
+      <c r="D76" s="9" t="s">
+        <v>386</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>81</v>
+        <v>399</v>
       </c>
       <c r="F76" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="H76" s="7"/>
       <c r="I76" s="7"/>
       <c r="J76" s="7" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K76" s="7" t="s">
-        <v>225</v>
+        <v>400</v>
       </c>
       <c r="L76" s="7"/>
       <c r="M76" s="1"/>
@@ -4540,30 +4548,30 @@
         <v>76</v>
       </c>
       <c r="B77" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D77" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E77" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="E77" s="7" t="s">
-        <v>82</v>
-      </c>
       <c r="F77" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="H77" s="7"/>
       <c r="I77" s="7"/>
       <c r="J77" s="7" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K77" s="7" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="L77" s="7"/>
       <c r="M77" s="1"/>
@@ -4573,16 +4581,16 @@
         <v>77</v>
       </c>
       <c r="B78" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F78" s="7" t="s">
         <v>16</v>
@@ -4593,10 +4601,10 @@
       <c r="H78" s="7"/>
       <c r="I78" s="7"/>
       <c r="J78" s="7" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K78" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="L78" s="7"/>
       <c r="M78" s="1"/>
@@ -4606,30 +4614,30 @@
         <v>78</v>
       </c>
       <c r="B79" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F79" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="H79" s="7"/>
       <c r="I79" s="7"/>
       <c r="J79" s="7" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K79" s="7" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="L79" s="7"/>
       <c r="M79" s="1"/>
@@ -4639,30 +4647,30 @@
         <v>79</v>
       </c>
       <c r="B80" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F80" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="H80" s="7"/>
       <c r="I80" s="7"/>
       <c r="J80" s="7" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K80" s="7" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="L80" s="7"/>
       <c r="M80" s="1"/>
@@ -4672,28 +4680,30 @@
         <v>80</v>
       </c>
       <c r="B81" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G81" s="7"/>
+        <v>16</v>
+      </c>
+      <c r="G81" s="7" t="s">
+        <v>85</v>
+      </c>
       <c r="H81" s="7"/>
       <c r="I81" s="7"/>
       <c r="J81" s="7" t="s">
-        <v>357</v>
+        <v>309</v>
       </c>
       <c r="K81" s="7" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="L81" s="7"/>
       <c r="M81" s="1"/>
@@ -4703,16 +4713,16 @@
         <v>81</v>
       </c>
       <c r="B82" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F82" s="7" t="s">
         <v>12</v>
@@ -4721,10 +4731,10 @@
       <c r="H82" s="7"/>
       <c r="I82" s="7"/>
       <c r="J82" s="7" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="K82" s="7" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="L82" s="7"/>
       <c r="M82" s="1"/>
@@ -4734,16 +4744,16 @@
         <v>82</v>
       </c>
       <c r="B83" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F83" s="7" t="s">
         <v>12</v>
@@ -4752,10 +4762,10 @@
       <c r="H83" s="7"/>
       <c r="I83" s="7"/>
       <c r="J83" s="7" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="K83" s="7" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="L83" s="7"/>
       <c r="M83" s="1"/>
@@ -4765,30 +4775,28 @@
         <v>83</v>
       </c>
       <c r="B84" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G84" s="7" t="s">
-        <v>35</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="G84" s="7"/>
       <c r="H84" s="7"/>
       <c r="I84" s="7"/>
       <c r="J84" s="7" t="s">
-        <v>312</v>
+        <v>354</v>
       </c>
       <c r="K84" s="7" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L84" s="7"/>
       <c r="M84" s="1"/>
@@ -4798,32 +4806,30 @@
         <v>84</v>
       </c>
       <c r="B85" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>395</v>
+        <v>89</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G85" s="7"/>
-      <c r="H85" s="7" t="s">
-        <v>404</v>
-      </c>
-      <c r="I85" s="7" t="s">
-        <v>411</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G85" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H85" s="7"/>
+      <c r="I85" s="7"/>
       <c r="J85" s="7" t="s">
-        <v>360</v>
+        <v>309</v>
       </c>
       <c r="K85" s="7" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="L85" s="7"/>
       <c r="M85" s="1"/>
@@ -4833,32 +4839,32 @@
         <v>85</v>
       </c>
       <c r="B86" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="F86" s="7" t="s">
         <v>12</v>
       </c>
       <c r="G86" s="7"/>
       <c r="H86" s="7" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="I86" s="7" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="J86" s="7" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="K86" s="7" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="L86" s="7"/>
       <c r="M86" s="1"/>
@@ -4868,28 +4874,32 @@
         <v>86</v>
       </c>
       <c r="B87" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>46</v>
+        <v>389</v>
       </c>
       <c r="F87" s="7" t="s">
         <v>12</v>
       </c>
       <c r="G87" s="7"/>
-      <c r="H87" s="7"/>
-      <c r="I87" s="7"/>
+      <c r="H87" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="I87" s="7" t="s">
+        <v>403</v>
+      </c>
       <c r="J87" s="7" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="K87" s="7" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="L87" s="7"/>
       <c r="M87" s="1"/>
@@ -4899,16 +4909,16 @@
         <v>87</v>
       </c>
       <c r="B88" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="F88" s="7" t="s">
         <v>12</v>
@@ -4917,10 +4927,10 @@
       <c r="H88" s="7"/>
       <c r="I88" s="7"/>
       <c r="J88" s="7" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="K88" s="7" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="L88" s="7"/>
       <c r="M88" s="1"/>
@@ -4930,28 +4940,28 @@
         <v>88</v>
       </c>
       <c r="B89" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D89" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E89" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E89" s="7" t="s">
-        <v>93</v>
-      </c>
       <c r="F89" s="7" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="G89" s="7"/>
       <c r="H89" s="7"/>
       <c r="I89" s="7"/>
       <c r="J89" s="7" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="K89" s="7" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="L89" s="7"/>
       <c r="M89" s="1"/>
@@ -4961,30 +4971,28 @@
         <v>89</v>
       </c>
       <c r="B90" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G90" s="7" t="s">
-        <v>95</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="G90" s="7"/>
       <c r="H90" s="7"/>
       <c r="I90" s="7"/>
       <c r="J90" s="7" t="s">
-        <v>312</v>
+        <v>346</v>
       </c>
       <c r="K90" s="7" t="s">
-        <v>328</v>
+        <v>235</v>
       </c>
       <c r="L90" s="7"/>
       <c r="M90" s="1"/>
@@ -4994,30 +5002,30 @@
         <v>90</v>
       </c>
       <c r="B91" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>325</v>
+        <v>93</v>
       </c>
       <c r="F91" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>326</v>
+        <v>94</v>
       </c>
       <c r="H91" s="7"/>
       <c r="I91" s="7"/>
       <c r="J91" s="7" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K91" s="7" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="L91" s="7"/>
       <c r="M91" s="1"/>
@@ -5027,30 +5035,30 @@
         <v>91</v>
       </c>
       <c r="B92" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>96</v>
+        <v>322</v>
       </c>
       <c r="F92" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>76</v>
+        <v>323</v>
       </c>
       <c r="H92" s="7"/>
       <c r="I92" s="7"/>
       <c r="J92" s="7" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K92" s="7" t="s">
-        <v>239</v>
+        <v>324</v>
       </c>
       <c r="L92" s="7"/>
       <c r="M92" s="1"/>
@@ -5060,28 +5068,30 @@
         <v>92</v>
       </c>
       <c r="B93" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G93" s="7"/>
+        <v>16</v>
+      </c>
+      <c r="G93" s="7" t="s">
+        <v>75</v>
+      </c>
       <c r="H93" s="7"/>
       <c r="I93" s="7"/>
       <c r="J93" s="7" t="s">
-        <v>364</v>
+        <v>309</v>
       </c>
       <c r="K93" s="7" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="L93" s="7"/>
       <c r="M93" s="1"/>
@@ -5090,29 +5100,29 @@
       <c r="A94" s="26">
         <v>93</v>
       </c>
-      <c r="B94" s="18" t="s">
-        <v>145</v>
+      <c r="B94" s="14" t="s">
+        <v>142</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>318</v>
+        <v>78</v>
       </c>
       <c r="F94" s="7" t="s">
         <v>12</v>
       </c>
       <c r="G94" s="7"/>
-      <c r="H94" s="19"/>
-      <c r="I94" s="19"/>
+      <c r="H94" s="7"/>
+      <c r="I94" s="7"/>
       <c r="J94" s="7" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="K94" s="7" t="s">
-        <v>319</v>
+        <v>221</v>
       </c>
       <c r="L94" s="7"/>
       <c r="M94" s="1"/>
@@ -5121,29 +5131,29 @@
       <c r="A95" s="26">
         <v>94</v>
       </c>
-      <c r="B95" s="14" t="s">
-        <v>145</v>
+      <c r="B95" s="18" t="s">
+        <v>142</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>331</v>
+        <v>315</v>
       </c>
       <c r="F95" s="7" t="s">
         <v>12</v>
       </c>
       <c r="G95" s="7"/>
-      <c r="H95" s="7"/>
-      <c r="I95" s="7"/>
+      <c r="H95" s="19"/>
+      <c r="I95" s="19"/>
       <c r="J95" s="7" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="K95" s="7" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="L95" s="7"/>
       <c r="M95" s="1"/>
@@ -5153,28 +5163,28 @@
         <v>95</v>
       </c>
       <c r="B96" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D96" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E96" s="7" t="s">
-        <v>97</v>
+        <v>328</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="G96" s="7"/>
       <c r="H96" s="7"/>
       <c r="I96" s="7"/>
       <c r="J96" s="7" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="K96" s="7" t="s">
-        <v>240</v>
+        <v>317</v>
       </c>
       <c r="L96" s="7"/>
       <c r="M96" s="1"/>
@@ -5184,27 +5194,29 @@
         <v>96</v>
       </c>
       <c r="B97" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>334</v>
+        <v>96</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G97" s="7"/>
       <c r="H97" s="7"/>
       <c r="I97" s="7"/>
       <c r="J97" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="K97" s="7"/>
+        <v>346</v>
+      </c>
+      <c r="K97" s="7" t="s">
+        <v>237</v>
+      </c>
       <c r="L97" s="7"/>
       <c r="M97" s="1"/>
     </row>
@@ -5213,25 +5225,25 @@
         <v>97</v>
       </c>
       <c r="B98" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D98" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G98" s="7"/>
       <c r="H98" s="7"/>
       <c r="I98" s="7"/>
       <c r="J98" s="7" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -5242,31 +5254,27 @@
         <v>98</v>
       </c>
       <c r="B99" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>100</v>
+        <v>332</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="G99" s="7"/>
       <c r="H99" s="7"/>
-      <c r="I99" s="7" t="s">
-        <v>410</v>
-      </c>
+      <c r="I99" s="7"/>
       <c r="J99" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="K99" s="7" t="s">
-        <v>241</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="K99" s="7"/>
       <c r="L99" s="7"/>
       <c r="M99" s="1"/>
     </row>
@@ -5275,29 +5283,31 @@
         <v>99</v>
       </c>
       <c r="B100" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D100" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E100" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="E100" s="7" t="s">
-        <v>339</v>
-      </c>
       <c r="F100" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G100" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H100" s="20"/>
-      <c r="I100" s="20"/>
+        <v>12</v>
+      </c>
+      <c r="G100" s="7"/>
+      <c r="H100" s="7"/>
+      <c r="I100" s="7" t="s">
+        <v>402</v>
+      </c>
       <c r="J100" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="K100" s="7"/>
+        <v>361</v>
+      </c>
+      <c r="K100" s="7" t="s">
+        <v>238</v>
+      </c>
       <c r="L100" s="7"/>
       <c r="M100" s="1"/>
     </row>
@@ -5306,25 +5316,27 @@
         <v>100</v>
       </c>
       <c r="B101" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G101" s="7"/>
-      <c r="H101" s="7"/>
-      <c r="I101" s="7"/>
+        <v>16</v>
+      </c>
+      <c r="G101" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H101" s="20"/>
+      <c r="I101" s="20"/>
       <c r="J101" s="7" t="s">
-        <v>351</v>
+        <v>309</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
@@ -5335,29 +5347,27 @@
         <v>101</v>
       </c>
       <c r="B102" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>101</v>
+        <v>326</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="G102" s="7"/>
       <c r="H102" s="7"/>
       <c r="I102" s="7"/>
       <c r="J102" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="K102" s="7" t="s">
-        <v>242</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="K102" s="7"/>
       <c r="L102" s="7"/>
       <c r="M102" s="1"/>
     </row>
@@ -5366,16 +5376,16 @@
         <v>102</v>
       </c>
       <c r="B103" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F103" s="7" t="s">
         <v>12</v>
@@ -5384,10 +5394,10 @@
       <c r="H103" s="7"/>
       <c r="I103" s="7"/>
       <c r="J103" s="7" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="K103" s="7" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="L103" s="7"/>
       <c r="M103" s="1"/>
@@ -5397,30 +5407,28 @@
         <v>103</v>
       </c>
       <c r="B104" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E104" s="7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G104" s="7" t="s">
-        <v>332</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="G104" s="7"/>
       <c r="H104" s="7"/>
       <c r="I104" s="7"/>
       <c r="J104" s="7" t="s">
-        <v>312</v>
+        <v>363</v>
       </c>
       <c r="K104" s="7" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="L104" s="7"/>
       <c r="M104" s="1"/>
@@ -5430,28 +5438,30 @@
         <v>104</v>
       </c>
       <c r="B105" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>336</v>
+        <v>102</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G105" s="7"/>
+        <v>16</v>
+      </c>
+      <c r="G105" s="7" t="s">
+        <v>329</v>
+      </c>
       <c r="H105" s="7"/>
       <c r="I105" s="7"/>
       <c r="J105" s="7" t="s">
-        <v>409</v>
+        <v>309</v>
       </c>
       <c r="K105" s="7" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="L105" s="7"/>
       <c r="M105" s="1"/>
@@ -5461,16 +5471,16 @@
         <v>105</v>
       </c>
       <c r="B106" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="F106" s="7" t="s">
         <v>12</v>
@@ -5479,10 +5489,10 @@
       <c r="H106" s="7"/>
       <c r="I106" s="7"/>
       <c r="J106" s="7" t="s">
-        <v>369</v>
+        <v>401</v>
       </c>
       <c r="K106" s="7" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="L106" s="7"/>
       <c r="M106" s="1"/>
@@ -5492,16 +5502,16 @@
         <v>106</v>
       </c>
       <c r="B107" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D107" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="F107" s="7" t="s">
         <v>12</v>
@@ -5510,10 +5520,10 @@
       <c r="H107" s="7"/>
       <c r="I107" s="7"/>
       <c r="J107" s="7" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="K107" s="7" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="L107" s="7"/>
       <c r="M107" s="1"/>
@@ -5523,30 +5533,28 @@
         <v>107</v>
       </c>
       <c r="B108" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D108" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E108" s="7" t="s">
-        <v>104</v>
+        <v>335</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G108" s="7" t="s">
-        <v>39</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="G108" s="7"/>
       <c r="H108" s="7"/>
       <c r="I108" s="7"/>
       <c r="J108" s="7" t="s">
-        <v>312</v>
+        <v>365</v>
       </c>
       <c r="K108" s="7" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="L108" s="7"/>
       <c r="M108" s="1"/>
@@ -5556,30 +5564,32 @@
         <v>108</v>
       </c>
       <c r="B109" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="E109" s="13" t="s">
-        <v>341</v>
-      </c>
-      <c r="F109" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="G109" s="14" t="s">
-        <v>332</v>
-      </c>
-      <c r="H109" s="20"/>
-      <c r="I109" s="20"/>
-      <c r="J109" s="14" t="s">
-        <v>312</v>
-      </c>
-      <c r="K109" s="14"/>
-      <c r="L109" s="14"/>
+        <v>98</v>
+      </c>
+      <c r="E109" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="F109" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G109" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H109" s="7"/>
+      <c r="I109" s="7"/>
+      <c r="J109" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="K109" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="L109" s="7"/>
       <c r="M109" s="1"/>
     </row>
     <row r="110" spans="1:13" ht="14" x14ac:dyDescent="0.3">
@@ -5587,32 +5597,30 @@
         <v>109</v>
       </c>
       <c r="B110" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="E110" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="F110" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G110" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="H110" s="7"/>
-      <c r="I110" s="7"/>
-      <c r="J110" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="K110" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="L110" s="7"/>
+        <v>98</v>
+      </c>
+      <c r="E110" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="F110" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G110" s="14" t="s">
+        <v>329</v>
+      </c>
+      <c r="H110" s="20"/>
+      <c r="I110" s="20"/>
+      <c r="J110" s="14" t="s">
+        <v>309</v>
+      </c>
+      <c r="K110" s="14"/>
+      <c r="L110" s="14"/>
       <c r="M110" s="1"/>
     </row>
     <row r="111" spans="1:13" ht="14" x14ac:dyDescent="0.3">
@@ -5620,30 +5628,30 @@
         <v>110</v>
       </c>
       <c r="B111" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F111" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G111" s="7" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="H111" s="7"/>
       <c r="I111" s="7"/>
       <c r="J111" s="7" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K111" s="7" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="L111" s="7"/>
       <c r="M111" s="1"/>
@@ -5653,30 +5661,30 @@
         <v>111</v>
       </c>
       <c r="B112" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D112" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F112" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G112" s="7" t="s">
-        <v>35</v>
+        <v>319</v>
       </c>
       <c r="H112" s="7"/>
       <c r="I112" s="7"/>
       <c r="J112" s="7" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K112" s="7" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="L112" s="7"/>
       <c r="M112" s="1"/>
@@ -5686,30 +5694,30 @@
         <v>112</v>
       </c>
       <c r="B113" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F113" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G113" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H113" s="7"/>
       <c r="I113" s="7"/>
       <c r="J113" s="7" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K113" s="7" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="L113" s="7"/>
       <c r="M113" s="1"/>
@@ -5719,27 +5727,31 @@
         <v>113</v>
       </c>
       <c r="B114" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>340</v>
+        <v>107</v>
       </c>
       <c r="F114" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G114" s="7"/>
+        <v>16</v>
+      </c>
+      <c r="G114" s="7" t="s">
+        <v>33</v>
+      </c>
       <c r="H114" s="7"/>
       <c r="I114" s="7"/>
       <c r="J114" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="K114" s="7"/>
+        <v>309</v>
+      </c>
+      <c r="K114" s="7" t="s">
+        <v>247</v>
+      </c>
       <c r="L114" s="7"/>
       <c r="M114" s="1"/>
     </row>
@@ -5748,31 +5760,27 @@
         <v>114</v>
       </c>
       <c r="B115" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E115" s="7" t="s">
-        <v>156</v>
+        <v>337</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="G115" s="7"/>
       <c r="H115" s="7"/>
-      <c r="I115" s="7" t="s">
-        <v>398</v>
-      </c>
+      <c r="I115" s="7"/>
       <c r="J115" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="K115" s="7" t="s">
-        <v>251</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="K115" s="7"/>
       <c r="L115" s="7"/>
       <c r="M115" s="1"/>
     </row>
@@ -5781,30 +5789,30 @@
         <v>115</v>
       </c>
       <c r="B116" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D116" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E116" s="7" t="s">
-        <v>333</v>
+        <v>153</v>
       </c>
       <c r="F116" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G116" s="7" t="s">
-        <v>33</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="G116" s="7"/>
       <c r="H116" s="7"/>
-      <c r="I116" s="7"/>
+      <c r="I116" s="7" t="s">
+        <v>390</v>
+      </c>
       <c r="J116" s="7" t="s">
-        <v>312</v>
+        <v>366</v>
       </c>
       <c r="K116" s="7" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="L116" s="7"/>
       <c r="M116" s="1"/>
@@ -5814,92 +5822,94 @@
         <v>116</v>
       </c>
       <c r="B117" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D117" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E117" s="7" t="s">
-        <v>109</v>
+        <v>330</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G117" s="7"/>
+        <v>16</v>
+      </c>
+      <c r="G117" s="7" t="s">
+        <v>33</v>
+      </c>
       <c r="H117" s="7"/>
       <c r="I117" s="7"/>
       <c r="J117" s="7" t="s">
-        <v>351</v>
+        <v>309</v>
       </c>
       <c r="K117" s="7" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="L117" s="7"/>
       <c r="M117" s="1"/>
     </row>
     <row r="118" spans="1:13" ht="14" x14ac:dyDescent="0.3">
-      <c r="A118" s="23">
+      <c r="A118" s="26">
         <v>117</v>
       </c>
-      <c r="B118" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="C118" s="15" t="s">
-        <v>307</v>
-      </c>
-      <c r="D118" s="15" t="s">
-        <v>307</v>
-      </c>
-      <c r="E118" s="15" t="s">
+      <c r="B118" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="C118" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="D118" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E118" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="F118" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G118" s="7"/>
+      <c r="H118" s="7"/>
+      <c r="I118" s="7"/>
+      <c r="J118" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="K118" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="L118" s="7"/>
+      <c r="M118" s="1"/>
+    </row>
+    <row r="119" spans="1:13" ht="14" x14ac:dyDescent="0.3">
+      <c r="A119" s="23">
+        <v>118</v>
+      </c>
+      <c r="B119" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="C119" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="D119" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="E119" s="15" t="s">
+        <v>305</v>
+      </c>
+      <c r="F119" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G119" s="15"/>
+      <c r="H119" s="15"/>
+      <c r="I119" s="15"/>
+      <c r="J119" s="15" t="s">
         <v>308</v>
       </c>
-      <c r="F118" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G118" s="15"/>
-      <c r="H118" s="15"/>
-      <c r="I118" s="15"/>
-      <c r="J118" s="15" t="s">
-        <v>311</v>
-      </c>
-      <c r="K118" s="15" t="s">
-        <v>309</v>
-      </c>
-      <c r="L118" s="15"/>
-      <c r="M118" s="1"/>
-    </row>
-    <row r="119" spans="1:13" ht="14" x14ac:dyDescent="0.3">
-      <c r="A119" s="24">
-        <v>118</v>
-      </c>
-      <c r="B119" s="17" t="s">
+      <c r="K119" s="15" t="s">
         <v>306</v>
       </c>
-      <c r="C119" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="D119" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="E119" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="F119" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G119" s="17"/>
-      <c r="H119" s="17"/>
-      <c r="I119" s="17"/>
-      <c r="J119" s="17" t="s">
-        <v>372</v>
-      </c>
-      <c r="K119" s="17" t="s">
-        <v>254</v>
-      </c>
-      <c r="L119" s="17"/>
+      <c r="L119" s="15"/>
       <c r="M119" s="1"/>
     </row>
     <row r="120" spans="1:13" ht="14" x14ac:dyDescent="0.3">
@@ -5907,16 +5917,16 @@
         <v>119</v>
       </c>
       <c r="B120" s="17" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C120" s="16" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D120" s="16" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E120" s="17" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F120" s="17" t="s">
         <v>12</v>
@@ -5925,10 +5935,10 @@
       <c r="H120" s="17"/>
       <c r="I120" s="17"/>
       <c r="J120" s="17" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="K120" s="17" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="L120" s="17"/>
       <c r="M120" s="1"/>
@@ -5938,16 +5948,16 @@
         <v>120</v>
       </c>
       <c r="B121" s="17" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C121" s="16" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D121" s="16" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E121" s="17" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F121" s="17" t="s">
         <v>12</v>
@@ -5956,10 +5966,10 @@
       <c r="H121" s="17"/>
       <c r="I121" s="17"/>
       <c r="J121" s="17" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="K121" s="17" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="L121" s="17"/>
       <c r="M121" s="1"/>
@@ -5969,30 +5979,28 @@
         <v>121</v>
       </c>
       <c r="B122" s="17" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C122" s="16" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D122" s="16" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E122" s="17" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F122" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="G122" s="17" t="s">
-        <v>33</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="G122" s="17"/>
       <c r="H122" s="17"/>
       <c r="I122" s="17"/>
       <c r="J122" s="17" t="s">
-        <v>314</v>
+        <v>369</v>
       </c>
       <c r="K122" s="17" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="L122" s="17"/>
       <c r="M122" s="1"/>
@@ -6002,30 +6010,30 @@
         <v>122</v>
       </c>
       <c r="B123" s="17" t="s">
-        <v>306</v>
-      </c>
-      <c r="C123" s="17" t="s">
-        <v>51</v>
+        <v>303</v>
+      </c>
+      <c r="C123" s="16" t="s">
+        <v>134</v>
       </c>
       <c r="D123" s="16" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E123" s="17" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F123" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G123" s="17" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H123" s="17"/>
       <c r="I123" s="17"/>
       <c r="J123" s="17" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K123" s="17" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="L123" s="17"/>
       <c r="M123" s="1"/>
@@ -6035,30 +6043,30 @@
         <v>123</v>
       </c>
       <c r="B124" s="17" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C124" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D124" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="E124" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D124" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="E124" s="17" t="s">
-        <v>53</v>
-      </c>
       <c r="F124" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G124" s="17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H124" s="17"/>
       <c r="I124" s="17"/>
       <c r="J124" s="17" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K124" s="17" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="L124" s="17"/>
       <c r="M124" s="1"/>
@@ -6068,30 +6076,30 @@
         <v>124</v>
       </c>
       <c r="B125" s="17" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C125" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D125" s="16" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E125" s="17" t="s">
-        <v>151</v>
+        <v>52</v>
       </c>
       <c r="F125" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G125" s="17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H125" s="17"/>
       <c r="I125" s="17"/>
       <c r="J125" s="17" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K125" s="17" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="L125" s="17"/>
       <c r="M125" s="1"/>
@@ -6101,30 +6109,30 @@
         <v>125</v>
       </c>
       <c r="B126" s="17" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C126" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D126" s="16" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E126" s="17" t="s">
-        <v>54</v>
+        <v>148</v>
       </c>
       <c r="F126" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G126" s="17" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="H126" s="17"/>
       <c r="I126" s="17"/>
       <c r="J126" s="17" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K126" s="17" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="L126" s="17"/>
       <c r="M126" s="1"/>
@@ -6134,30 +6142,30 @@
         <v>126</v>
       </c>
       <c r="B127" s="17" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C127" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D127" s="16" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E127" s="17" t="s">
-        <v>148</v>
+        <v>53</v>
       </c>
       <c r="F127" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G127" s="17" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="H127" s="17"/>
       <c r="I127" s="17"/>
       <c r="J127" s="17" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K127" s="17" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="L127" s="17"/>
       <c r="M127" s="1"/>
@@ -6167,30 +6175,30 @@
         <v>127</v>
       </c>
       <c r="B128" s="17" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C128" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D128" s="16" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E128" s="17" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="F128" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G128" s="17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H128" s="17"/>
       <c r="I128" s="17"/>
       <c r="J128" s="17" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K128" s="17" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="L128" s="17"/>
       <c r="M128" s="1"/>
@@ -6200,28 +6208,30 @@
         <v>128</v>
       </c>
       <c r="B129" s="17" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C129" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D129" s="16" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E129" s="17" t="s">
-        <v>56</v>
+        <v>146</v>
       </c>
       <c r="F129" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="G129" s="17"/>
+      <c r="G129" s="17" t="s">
+        <v>34</v>
+      </c>
       <c r="H129" s="17"/>
       <c r="I129" s="17"/>
       <c r="J129" s="17" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K129" s="17" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="L129" s="17"/>
       <c r="M129" s="1"/>
@@ -6231,30 +6241,28 @@
         <v>129</v>
       </c>
       <c r="B130" s="17" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C130" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D130" s="16" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E130" s="17" t="s">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="F130" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="G130" s="17" t="s">
-        <v>57</v>
-      </c>
+      <c r="G130" s="17"/>
       <c r="H130" s="17"/>
       <c r="I130" s="17"/>
       <c r="J130" s="17" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K130" s="17" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="L130" s="17"/>
       <c r="M130" s="1"/>
@@ -6264,30 +6272,30 @@
         <v>130</v>
       </c>
       <c r="B131" s="17" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C131" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D131" s="16" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E131" s="17" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="F131" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G131" s="17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H131" s="17"/>
       <c r="I131" s="17"/>
       <c r="J131" s="17" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K131" s="17" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="L131" s="17"/>
       <c r="M131" s="1"/>
@@ -6297,28 +6305,30 @@
         <v>131</v>
       </c>
       <c r="B132" s="17" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C132" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D132" s="16" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E132" s="17" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F132" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G132" s="17"/>
+        <v>16</v>
+      </c>
+      <c r="G132" s="17" t="s">
+        <v>56</v>
+      </c>
       <c r="H132" s="17"/>
       <c r="I132" s="17"/>
       <c r="J132" s="17" t="s">
-        <v>375</v>
+        <v>309</v>
       </c>
       <c r="K132" s="17" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="L132" s="17"/>
       <c r="M132" s="1"/>
@@ -6328,16 +6338,16 @@
         <v>132</v>
       </c>
       <c r="B133" s="17" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C133" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D133" s="16" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E133" s="17" t="s">
-        <v>58</v>
+        <v>150</v>
       </c>
       <c r="F133" s="17" t="s">
         <v>12</v>
@@ -6346,10 +6356,10 @@
       <c r="H133" s="17"/>
       <c r="I133" s="17"/>
       <c r="J133" s="17" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="K133" s="17" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="L133" s="17"/>
       <c r="M133" s="1"/>
@@ -6359,30 +6369,28 @@
         <v>133</v>
       </c>
       <c r="B134" s="17" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C134" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D134" s="16" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E134" s="17" t="s">
-        <v>316</v>
+        <v>57</v>
       </c>
       <c r="F134" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="G134" s="17" t="s">
-        <v>326</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="G134" s="17"/>
       <c r="H134" s="17"/>
       <c r="I134" s="17"/>
       <c r="J134" s="17" t="s">
-        <v>315</v>
+        <v>371</v>
       </c>
       <c r="K134" s="17" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="L134" s="17"/>
       <c r="M134" s="1"/>
@@ -6392,22 +6400,22 @@
         <v>134</v>
       </c>
       <c r="B135" s="17" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C135" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D135" s="16" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E135" s="17" t="s">
-        <v>59</v>
+        <v>313</v>
       </c>
       <c r="F135" s="17" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G135" s="17" t="s">
-        <v>33</v>
+        <v>323</v>
       </c>
       <c r="H135" s="17"/>
       <c r="I135" s="17"/>
@@ -6415,7 +6423,7 @@
         <v>312</v>
       </c>
       <c r="K135" s="17" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="L135" s="17"/>
       <c r="M135" s="1"/>
@@ -6425,30 +6433,30 @@
         <v>135</v>
       </c>
       <c r="B136" s="17" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C136" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D136" s="16" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E136" s="17" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F136" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G136" s="17" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="H136" s="17"/>
       <c r="I136" s="17"/>
       <c r="J136" s="17" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K136" s="17" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L136" s="17"/>
       <c r="M136" s="1"/>
@@ -6458,30 +6466,30 @@
         <v>136</v>
       </c>
       <c r="B137" s="17" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C137" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D137" s="16" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E137" s="17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F137" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G137" s="17" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H137" s="17"/>
       <c r="I137" s="17"/>
       <c r="J137" s="17" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K137" s="17" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="L137" s="17"/>
       <c r="M137" s="1"/>
@@ -6491,30 +6499,30 @@
         <v>137</v>
       </c>
       <c r="B138" s="17" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C138" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D138" s="16" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E138" s="17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F138" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G138" s="17" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="H138" s="17"/>
       <c r="I138" s="17"/>
       <c r="J138" s="17" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K138" s="17" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="L138" s="17"/>
       <c r="M138" s="1"/>
@@ -6524,30 +6532,30 @@
         <v>138</v>
       </c>
       <c r="B139" s="17" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C139" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D139" s="16" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E139" s="17" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F139" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G139" s="17" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H139" s="17"/>
       <c r="I139" s="17"/>
       <c r="J139" s="17" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K139" s="17" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="L139" s="17"/>
       <c r="M139" s="1"/>
@@ -6557,30 +6565,30 @@
         <v>139</v>
       </c>
       <c r="B140" s="17" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C140" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D140" s="16" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E140" s="17" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F140" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G140" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H140" s="17"/>
       <c r="I140" s="17"/>
       <c r="J140" s="17" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K140" s="17" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="L140" s="17"/>
       <c r="M140" s="1"/>
@@ -6590,28 +6598,30 @@
         <v>140</v>
       </c>
       <c r="B141" s="17" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C141" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D141" s="16" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E141" s="17" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F141" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="G141" s="17"/>
+      <c r="G141" s="17" t="s">
+        <v>64</v>
+      </c>
       <c r="H141" s="17"/>
       <c r="I141" s="17"/>
       <c r="J141" s="17" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="K141" s="17" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="L141" s="17"/>
       <c r="M141" s="1"/>
@@ -6621,28 +6631,28 @@
         <v>141</v>
       </c>
       <c r="B142" s="17" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C142" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D142" s="16" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E142" s="17" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F142" s="17" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G142" s="17"/>
       <c r="H142" s="17"/>
       <c r="I142" s="17"/>
       <c r="J142" s="17" t="s">
-        <v>377</v>
+        <v>311</v>
       </c>
       <c r="K142" s="17" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="L142" s="17"/>
       <c r="M142" s="1"/>
@@ -6652,28 +6662,28 @@
         <v>142</v>
       </c>
       <c r="B143" s="17" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C143" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D143" s="16" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E143" s="17" t="s">
-        <v>154</v>
+        <v>67</v>
       </c>
       <c r="F143" s="17" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G143" s="17"/>
       <c r="H143" s="17"/>
       <c r="I143" s="17"/>
       <c r="J143" s="17" t="s">
-        <v>312</v>
+        <v>372</v>
       </c>
       <c r="K143" s="17" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="L143" s="17"/>
       <c r="M143" s="1"/>
@@ -6683,30 +6693,28 @@
         <v>143</v>
       </c>
       <c r="B144" s="17" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C144" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D144" s="16" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E144" s="17" t="s">
-        <v>69</v>
+        <v>151</v>
       </c>
       <c r="F144" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="G144" s="17" t="s">
-        <v>70</v>
-      </c>
+      <c r="G144" s="17"/>
       <c r="H144" s="17"/>
       <c r="I144" s="17"/>
       <c r="J144" s="17" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K144" s="17" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="L144" s="17"/>
       <c r="M144" s="1"/>
@@ -6716,30 +6724,30 @@
         <v>144</v>
       </c>
       <c r="B145" s="17" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C145" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D145" s="16" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E145" s="17" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F145" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G145" s="17" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="H145" s="17"/>
       <c r="I145" s="17"/>
       <c r="J145" s="17" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K145" s="17" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="L145" s="17"/>
       <c r="M145" s="1"/>
@@ -6749,30 +6757,30 @@
         <v>145</v>
       </c>
       <c r="B146" s="17" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C146" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D146" s="16" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E146" s="17" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F146" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G146" s="17" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="H146" s="17"/>
       <c r="I146" s="17"/>
       <c r="J146" s="17" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K146" s="17" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="L146" s="17"/>
       <c r="M146" s="1"/>
@@ -6782,33 +6790,66 @@
         <v>146</v>
       </c>
       <c r="B147" s="17" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C147" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D147" s="16" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E147" s="17" t="s">
-        <v>287</v>
+        <v>71</v>
       </c>
       <c r="F147" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G147" s="17" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="H147" s="17"/>
       <c r="I147" s="17"/>
       <c r="J147" s="17" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K147" s="17" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="L147" s="17"/>
       <c r="M147" s="1"/>
+    </row>
+    <row r="148" spans="1:13" ht="14" x14ac:dyDescent="0.3">
+      <c r="A148" s="24">
+        <v>147</v>
+      </c>
+      <c r="B148" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="C148" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D148" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="E148" s="17" t="s">
+        <v>284</v>
+      </c>
+      <c r="F148" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G148" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="H148" s="17"/>
+      <c r="I148" s="17"/>
+      <c r="J148" s="17" t="s">
+        <v>309</v>
+      </c>
+      <c r="K148" s="17" t="s">
+        <v>279</v>
+      </c>
+      <c r="L148" s="17"/>
+      <c r="M148" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/MASTER.xlsx
+++ b/MASTER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Javid Shiriyev\Documents\GitHub\sand-control-failure-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A0C3F0B-9AA7-4B32-88B0-CC45FCCAB736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38AC3A4E-4E68-4DC8-8824-36053B9C0CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38510" yWindow="-2730" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -509,9 +509,6 @@
     <t>Additional context, assumptions, uncertainties, qualifications, or observations relevant to the well record.</t>
   </si>
   <si>
-    <t>Official or reported name of the well.</t>
-  </si>
-  <si>
     <t>Produced fluid type</t>
   </si>
   <si>
@@ -1287,6 +1284,9 @@
   </si>
   <si>
     <t>{"List": {"required": False, "options": ["Yes", "No"]}}</t>
+  </si>
+  <si>
+    <t>An anonymized label you assign, not the well's real name. Reuse the same label for later submissions of this well. It also names the exported file.</t>
   </si>
 </sst>
 </file>
@@ -2115,7 +2115,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="28" x14ac:dyDescent="0.35">
       <c r="A1" s="21" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>3</v>
@@ -2175,7 +2175,7 @@
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
       <c r="J2" s="5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>154</v>
@@ -2206,7 +2206,7 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="K3" s="5" t="s">
         <v>155</v>
@@ -2237,7 +2237,7 @@
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
       <c r="J4" s="5" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="K4" s="5" t="s">
         <v>156</v>
@@ -2259,7 +2259,7 @@
         <v>15</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>13</v>
@@ -2268,10 +2268,10 @@
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>157</v>
+        <v>416</v>
       </c>
       <c r="L5" s="6"/>
       <c r="M5" s="1"/>
@@ -2290,7 +2290,7 @@
         <v>15</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>13</v>
@@ -2299,10 +2299,10 @@
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
       <c r="J6" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="L6" s="6"/>
       <c r="M6" s="1"/>
@@ -2329,13 +2329,13 @@
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
       <c r="I7" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L7" s="6"/>
       <c r="M7" s="1"/>
@@ -2362,13 +2362,13 @@
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
       <c r="I8" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L8" s="6"/>
       <c r="M8" s="1"/>
@@ -2398,10 +2398,10 @@
       <c r="H9" s="6"/>
       <c r="I9" s="6"/>
       <c r="J9" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L9" s="6"/>
       <c r="M9" s="1"/>
@@ -2429,10 +2429,10 @@
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
       <c r="J10" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L10" s="6"/>
       <c r="M10" s="1"/>
@@ -2462,10 +2462,10 @@
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
       <c r="J11" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L11" s="6"/>
       <c r="M11" s="1"/>
@@ -2495,10 +2495,10 @@
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L12" s="6"/>
       <c r="M12" s="1"/>
@@ -2526,10 +2526,10 @@
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
       <c r="J13" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L13" s="6"/>
       <c r="M13" s="1"/>
@@ -2557,10 +2557,10 @@
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
       <c r="J14" s="6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L14" s="6"/>
       <c r="M14" s="1"/>
@@ -2588,10 +2588,10 @@
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
       <c r="J15" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L15" s="6"/>
       <c r="M15" s="1"/>
@@ -2619,10 +2619,10 @@
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
       <c r="J16" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L16" s="6"/>
       <c r="M16" s="1"/>
@@ -2641,21 +2641,21 @@
         <v>121</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>43</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I17" s="6"/>
       <c r="J17" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L17" s="6"/>
       <c r="M17" s="1"/>
@@ -2674,7 +2674,7 @@
         <v>20</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>12</v>
@@ -2683,10 +2683,10 @@
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
       <c r="J18" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L18" s="6"/>
       <c r="M18" s="1"/>
@@ -2705,7 +2705,7 @@
         <v>20</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>12</v>
@@ -2714,10 +2714,10 @@
       <c r="H19" s="6"/>
       <c r="I19" s="6"/>
       <c r="J19" s="6" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L19" s="6"/>
       <c r="M19" s="1"/>
@@ -2736,7 +2736,7 @@
         <v>20</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>16</v>
@@ -2747,10 +2747,10 @@
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
       <c r="J20" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L20" s="6"/>
       <c r="M20" s="1"/>
@@ -2780,10 +2780,10 @@
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
       <c r="J21" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L21" s="6"/>
       <c r="M21" s="1"/>
@@ -2813,10 +2813,10 @@
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
       <c r="J22" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L22" s="6"/>
       <c r="M22" s="1"/>
@@ -2844,10 +2844,10 @@
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
       <c r="J23" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L23" s="6"/>
       <c r="M23" s="1"/>
@@ -2875,10 +2875,10 @@
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
       <c r="J24" s="6" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L24" s="6"/>
       <c r="M24" s="1"/>
@@ -2897,7 +2897,7 @@
         <v>20</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>12</v>
@@ -2906,7 +2906,7 @@
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
       <c r="J25" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="K25" s="8"/>
       <c r="L25" s="8"/>
@@ -2926,7 +2926,7 @@
         <v>20</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>12</v>
@@ -2934,13 +2934,13 @@
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
       <c r="I26" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L26" s="6"/>
       <c r="M26" s="1"/>
@@ -2965,15 +2965,15 @@
         <v>16</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H27" s="6"/>
       <c r="I27" s="6"/>
       <c r="J27" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L27" s="6"/>
       <c r="M27" s="1"/>
@@ -2998,15 +2998,15 @@
         <v>16</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
       <c r="J28" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L28" s="6"/>
       <c r="M28" s="1"/>
@@ -3031,15 +3031,15 @@
         <v>16</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H29" s="6"/>
       <c r="I29" s="6"/>
       <c r="J29" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L29" s="6"/>
       <c r="M29" s="1"/>
@@ -3069,10 +3069,10 @@
       <c r="H30" s="6"/>
       <c r="I30" s="6"/>
       <c r="J30" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L30" s="6"/>
       <c r="M30" s="1"/>
@@ -3100,10 +3100,10 @@
       <c r="H31" s="6"/>
       <c r="I31" s="6"/>
       <c r="J31" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L31" s="6"/>
       <c r="M31" s="1"/>
@@ -3131,10 +3131,10 @@
       <c r="H32" s="6"/>
       <c r="I32" s="6"/>
       <c r="J32" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L32" s="6"/>
       <c r="M32" s="1"/>
@@ -3153,7 +3153,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F33" s="6" t="s">
         <v>16</v>
@@ -3162,10 +3162,10 @@
       <c r="H33" s="6"/>
       <c r="I33" s="6"/>
       <c r="J33" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L33" s="6"/>
       <c r="M33" s="1"/>
@@ -3195,10 +3195,10 @@
       <c r="H34" s="6"/>
       <c r="I34" s="6"/>
       <c r="J34" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L34" s="6"/>
       <c r="M34" s="1"/>
@@ -3226,10 +3226,10 @@
       <c r="H35" s="6"/>
       <c r="I35" s="6"/>
       <c r="J35" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L35" s="6"/>
       <c r="M35" s="1"/>
@@ -3257,10 +3257,10 @@
       <c r="H36" s="6"/>
       <c r="I36" s="6"/>
       <c r="J36" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L36" s="6"/>
       <c r="M36" s="1"/>
@@ -3279,7 +3279,7 @@
         <v>20</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F37" s="6" t="s">
         <v>16</v>
@@ -3288,10 +3288,10 @@
       <c r="H37" s="6"/>
       <c r="I37" s="6"/>
       <c r="J37" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="K37" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L37" s="6"/>
       <c r="M37" s="1"/>
@@ -3319,10 +3319,10 @@
       <c r="H38" s="6"/>
       <c r="I38" s="6"/>
       <c r="J38" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="L38" s="6"/>
       <c r="M38" s="1"/>
@@ -3338,10 +3338,10 @@
         <v>14</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F39" s="6" t="s">
         <v>12</v>
@@ -3350,10 +3350,10 @@
       <c r="H39" s="6"/>
       <c r="I39" s="6"/>
       <c r="J39" s="6" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L39" s="6"/>
       <c r="M39" s="1"/>
@@ -3369,10 +3369,10 @@
         <v>14</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>24</v>
@@ -3381,10 +3381,10 @@
       <c r="H40" s="6"/>
       <c r="I40" s="6"/>
       <c r="J40" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="K40" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L40" s="6"/>
       <c r="M40" s="1"/>
@@ -3400,10 +3400,10 @@
         <v>14</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F41" s="6" t="s">
         <v>24</v>
@@ -3412,10 +3412,10 @@
       <c r="H41" s="6"/>
       <c r="I41" s="6"/>
       <c r="J41" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="K41" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L41" s="6"/>
       <c r="M41" s="1"/>
@@ -3431,10 +3431,10 @@
         <v>14</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>24</v>
@@ -3443,10 +3443,10 @@
       <c r="H42" s="6"/>
       <c r="I42" s="6"/>
       <c r="J42" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="K42" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L42" s="6"/>
       <c r="M42" s="1"/>
@@ -3462,7 +3462,7 @@
         <v>14</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>25</v>
@@ -3476,10 +3476,10 @@
       <c r="H43" s="6"/>
       <c r="I43" s="6"/>
       <c r="J43" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K43" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L43" s="6"/>
       <c r="M43" s="1"/>
@@ -3495,7 +3495,7 @@
         <v>14</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>27</v>
@@ -3509,10 +3509,10 @@
       <c r="H44" s="6"/>
       <c r="I44" s="6"/>
       <c r="J44" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K44" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L44" s="6"/>
       <c r="M44" s="1"/>
@@ -3528,7 +3528,7 @@
         <v>14</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>28</v>
@@ -3542,10 +3542,10 @@
       <c r="H45" s="6"/>
       <c r="I45" s="6"/>
       <c r="J45" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K45" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L45" s="6"/>
       <c r="M45" s="1"/>
@@ -3561,7 +3561,7 @@
         <v>14</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>30</v>
@@ -3575,10 +3575,10 @@
       <c r="H46" s="6"/>
       <c r="I46" s="6"/>
       <c r="J46" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K46" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L46" s="6"/>
       <c r="M46" s="1"/>
@@ -3594,7 +3594,7 @@
         <v>14</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>31</v>
@@ -3608,10 +3608,10 @@
       <c r="H47" s="6"/>
       <c r="I47" s="6"/>
       <c r="J47" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K47" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L47" s="6"/>
       <c r="M47" s="1"/>
@@ -3627,7 +3627,7 @@
         <v>14</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>32</v>
@@ -3641,10 +3641,10 @@
       <c r="H48" s="6"/>
       <c r="I48" s="6"/>
       <c r="J48" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K48" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L48" s="6"/>
       <c r="M48" s="1"/>
@@ -3660,10 +3660,10 @@
         <v>14</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F49" s="6" t="s">
         <v>16</v>
@@ -3674,10 +3674,10 @@
       <c r="H49" s="6"/>
       <c r="I49" s="6"/>
       <c r="J49" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="K49" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L49" s="6"/>
       <c r="M49" s="1"/>
@@ -3693,10 +3693,10 @@
         <v>14</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>16</v>
@@ -3707,10 +3707,10 @@
       <c r="H50" s="6"/>
       <c r="I50" s="6"/>
       <c r="J50" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="K50" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L50" s="6"/>
       <c r="M50" s="1"/>
@@ -3726,10 +3726,10 @@
         <v>14</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F51" s="6" t="s">
         <v>16</v>
@@ -3740,10 +3740,10 @@
       <c r="H51" s="6"/>
       <c r="I51" s="6"/>
       <c r="J51" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="K51" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L51" s="6"/>
       <c r="M51" s="1"/>
@@ -3759,10 +3759,10 @@
         <v>14</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>16</v>
@@ -3773,10 +3773,10 @@
       <c r="H52" s="6"/>
       <c r="I52" s="6"/>
       <c r="J52" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="K52" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L52" s="6"/>
       <c r="M52" s="1"/>
@@ -3792,10 +3792,10 @@
         <v>14</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F53" s="6" t="s">
         <v>13</v>
@@ -3804,10 +3804,10 @@
       <c r="H53" s="6"/>
       <c r="I53" s="6"/>
       <c r="J53" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="K53" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L53" s="6"/>
       <c r="M53" s="1"/>
@@ -3823,10 +3823,10 @@
         <v>14</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>16</v>
@@ -3837,10 +3837,10 @@
       <c r="H54" s="6"/>
       <c r="I54" s="6"/>
       <c r="J54" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K54" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L54" s="6"/>
       <c r="M54" s="1"/>
@@ -3856,10 +3856,10 @@
         <v>14</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F55" s="6" t="s">
         <v>16</v>
@@ -3870,10 +3870,10 @@
       <c r="H55" s="6"/>
       <c r="I55" s="6"/>
       <c r="J55" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K55" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L55" s="6"/>
       <c r="M55" s="1"/>
@@ -3889,10 +3889,10 @@
         <v>14</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>12</v>
@@ -3901,10 +3901,10 @@
       <c r="H56" s="6"/>
       <c r="I56" s="6"/>
       <c r="J56" s="6" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="K56" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L56" s="6"/>
       <c r="M56" s="1"/>
@@ -3920,10 +3920,10 @@
         <v>14</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F57" s="6" t="s">
         <v>12</v>
@@ -3932,10 +3932,10 @@
       <c r="H57" s="6"/>
       <c r="I57" s="6"/>
       <c r="J57" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="K57" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L57" s="6"/>
       <c r="M57" s="1"/>
@@ -3951,10 +3951,10 @@
         <v>14</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>12</v>
@@ -3963,10 +3963,10 @@
       <c r="H58" s="6"/>
       <c r="I58" s="6"/>
       <c r="J58" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="K58" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L58" s="6"/>
       <c r="M58" s="1"/>
@@ -3982,10 +3982,10 @@
         <v>14</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F59" s="6" t="s">
         <v>12</v>
@@ -3994,10 +3994,10 @@
       <c r="H59" s="6"/>
       <c r="I59" s="6"/>
       <c r="J59" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="K59" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L59" s="6"/>
       <c r="M59" s="1"/>
@@ -4025,10 +4025,10 @@
       <c r="H60" s="12"/>
       <c r="I60" s="12"/>
       <c r="J60" s="12" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="K60" s="11" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L60" s="11"/>
       <c r="M60" s="1"/>
@@ -4047,7 +4047,7 @@
         <v>136</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F61" s="7" t="s">
         <v>16</v>
@@ -4056,10 +4056,10 @@
       <c r="H61" s="7"/>
       <c r="I61" s="7"/>
       <c r="J61" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K61" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L61" s="7"/>
       <c r="M61" s="1"/>
@@ -4085,16 +4085,16 @@
       </c>
       <c r="G62" s="7"/>
       <c r="H62" s="7" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I62" s="7" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="K62" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="L62" s="7"/>
       <c r="M62" s="1"/>
@@ -4122,10 +4122,10 @@
       <c r="H63" s="7"/>
       <c r="I63" s="7"/>
       <c r="J63" s="7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="K63" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L63" s="7"/>
       <c r="M63" s="1"/>
@@ -4144,7 +4144,7 @@
         <v>73</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F64" s="7" t="s">
         <v>16</v>
@@ -4155,10 +4155,10 @@
       <c r="H64" s="7"/>
       <c r="I64" s="7"/>
       <c r="J64" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K64" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L64" s="7"/>
       <c r="M64" s="1"/>
@@ -4188,10 +4188,10 @@
       <c r="H65" s="7"/>
       <c r="I65" s="7"/>
       <c r="J65" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K65" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="L65" s="7"/>
       <c r="M65" s="1"/>
@@ -4221,10 +4221,10 @@
       <c r="H66" s="7"/>
       <c r="I66" s="7"/>
       <c r="J66" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K66" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L66" s="7"/>
       <c r="M66" s="1"/>
@@ -4254,10 +4254,10 @@
       <c r="H67" s="7"/>
       <c r="I67" s="7"/>
       <c r="J67" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K67" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="L67" s="7"/>
       <c r="M67" s="1"/>
@@ -4285,10 +4285,10 @@
       <c r="H68" s="7"/>
       <c r="I68" s="7"/>
       <c r="J68" s="7" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="K68" s="7" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="L68" s="7"/>
       <c r="M68" s="1"/>
@@ -4307,7 +4307,7 @@
         <v>73</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F69" s="7" t="s">
         <v>43</v>
@@ -4316,7 +4316,7 @@
       <c r="H69" s="7"/>
       <c r="I69" s="7"/>
       <c r="J69" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
@@ -4333,7 +4333,7 @@
         <v>137</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E70" s="7" t="s">
         <v>144</v>
@@ -4345,10 +4345,10 @@
       <c r="H70" s="7"/>
       <c r="I70" s="7"/>
       <c r="J70" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K70" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="L70" s="7"/>
       <c r="M70" s="1"/>
@@ -4364,7 +4364,7 @@
         <v>137</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E71" s="7" t="s">
         <v>36</v>
@@ -4376,10 +4376,10 @@
       <c r="H71" s="7"/>
       <c r="I71" s="7"/>
       <c r="J71" s="7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="K71" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L71" s="7"/>
       <c r="M71" s="1"/>
@@ -4395,7 +4395,7 @@
         <v>137</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E72" s="7" t="s">
         <v>37</v>
@@ -4409,10 +4409,10 @@
       <c r="H72" s="7"/>
       <c r="I72" s="7"/>
       <c r="J72" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K72" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L72" s="7"/>
       <c r="M72" s="1"/>
@@ -4428,7 +4428,7 @@
         <v>137</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E73" s="7" t="s">
         <v>39</v>
@@ -4440,10 +4440,10 @@
       <c r="H73" s="7"/>
       <c r="I73" s="7"/>
       <c r="J73" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K73" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="L73" s="7"/>
       <c r="M73" s="1"/>
@@ -4459,7 +4459,7 @@
         <v>137</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E74" s="7" t="s">
         <v>40</v>
@@ -4471,10 +4471,10 @@
       <c r="H74" s="7"/>
       <c r="I74" s="7"/>
       <c r="J74" s="7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="K74" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L74" s="7"/>
       <c r="M74" s="1"/>
@@ -4490,10 +4490,10 @@
         <v>137</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F75" s="7" t="s">
         <v>13</v>
@@ -4502,10 +4502,10 @@
       <c r="H75" s="7"/>
       <c r="I75" s="7"/>
       <c r="J75" s="7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K75" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="L75" s="7"/>
       <c r="M75" s="1"/>
@@ -4521,10 +4521,10 @@
         <v>137</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F76" s="7" t="s">
         <v>16</v>
@@ -4535,10 +4535,10 @@
       <c r="H76" s="7"/>
       <c r="I76" s="7"/>
       <c r="J76" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K76" s="7" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="L76" s="7"/>
       <c r="M76" s="1"/>
@@ -4568,10 +4568,10 @@
       <c r="H77" s="7"/>
       <c r="I77" s="7"/>
       <c r="J77" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K77" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L77" s="7"/>
       <c r="M77" s="1"/>
@@ -4601,10 +4601,10 @@
       <c r="H78" s="7"/>
       <c r="I78" s="7"/>
       <c r="J78" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K78" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L78" s="7"/>
       <c r="M78" s="1"/>
@@ -4634,10 +4634,10 @@
       <c r="H79" s="7"/>
       <c r="I79" s="7"/>
       <c r="J79" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K79" s="7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L79" s="7"/>
       <c r="M79" s="1"/>
@@ -4667,10 +4667,10 @@
       <c r="H80" s="7"/>
       <c r="I80" s="7"/>
       <c r="J80" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K80" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L80" s="7"/>
       <c r="M80" s="1"/>
@@ -4700,10 +4700,10 @@
       <c r="H81" s="7"/>
       <c r="I81" s="7"/>
       <c r="J81" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K81" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L81" s="7"/>
       <c r="M81" s="1"/>
@@ -4731,10 +4731,10 @@
       <c r="H82" s="7"/>
       <c r="I82" s="7"/>
       <c r="J82" s="7" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="K82" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L82" s="7"/>
       <c r="M82" s="1"/>
@@ -4762,10 +4762,10 @@
       <c r="H83" s="7"/>
       <c r="I83" s="7"/>
       <c r="J83" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="K83" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L83" s="7"/>
       <c r="M83" s="1"/>
@@ -4793,10 +4793,10 @@
       <c r="H84" s="7"/>
       <c r="I84" s="7"/>
       <c r="J84" s="7" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="K84" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L84" s="7"/>
       <c r="M84" s="1"/>
@@ -4826,10 +4826,10 @@
       <c r="H85" s="7"/>
       <c r="I85" s="7"/>
       <c r="J85" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K85" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L85" s="7"/>
       <c r="M85" s="1"/>
@@ -4848,23 +4848,23 @@
         <v>135</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F86" s="7" t="s">
         <v>12</v>
       </c>
       <c r="G86" s="7"/>
       <c r="H86" s="7" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I86" s="7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="J86" s="7" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="K86" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L86" s="7"/>
       <c r="M86" s="1"/>
@@ -4883,23 +4883,23 @@
         <v>135</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F87" s="7" t="s">
         <v>12</v>
       </c>
       <c r="G87" s="7"/>
       <c r="H87" s="7" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I87" s="7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="J87" s="7" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="K87" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L87" s="7"/>
       <c r="M87" s="1"/>
@@ -4927,10 +4927,10 @@
       <c r="H88" s="7"/>
       <c r="I88" s="7"/>
       <c r="J88" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="K88" s="7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="L88" s="7"/>
       <c r="M88" s="1"/>
@@ -4958,10 +4958,10 @@
       <c r="H89" s="7"/>
       <c r="I89" s="7"/>
       <c r="J89" s="7" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="K89" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L89" s="7"/>
       <c r="M89" s="1"/>
@@ -4989,10 +4989,10 @@
       <c r="H90" s="7"/>
       <c r="I90" s="7"/>
       <c r="J90" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="K90" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L90" s="7"/>
       <c r="M90" s="1"/>
@@ -5022,10 +5022,10 @@
       <c r="H91" s="7"/>
       <c r="I91" s="7"/>
       <c r="J91" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K91" s="7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L91" s="7"/>
       <c r="M91" s="1"/>
@@ -5044,21 +5044,21 @@
         <v>90</v>
       </c>
       <c r="E92" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G92" s="7" t="s">
         <v>322</v>
-      </c>
-      <c r="F92" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G92" s="7" t="s">
-        <v>323</v>
       </c>
       <c r="H92" s="7"/>
       <c r="I92" s="7"/>
       <c r="J92" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K92" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L92" s="7"/>
       <c r="M92" s="1"/>
@@ -5088,10 +5088,10 @@
       <c r="H93" s="7"/>
       <c r="I93" s="7"/>
       <c r="J93" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K93" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="L93" s="7"/>
       <c r="M93" s="1"/>
@@ -5119,10 +5119,10 @@
       <c r="H94" s="7"/>
       <c r="I94" s="7"/>
       <c r="J94" s="7" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="K94" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="L94" s="7"/>
       <c r="M94" s="1"/>
@@ -5141,7 +5141,7 @@
         <v>90</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F95" s="7" t="s">
         <v>12</v>
@@ -5150,10 +5150,10 @@
       <c r="H95" s="19"/>
       <c r="I95" s="19"/>
       <c r="J95" s="7" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="K95" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="L95" s="7"/>
       <c r="M95" s="1"/>
@@ -5172,7 +5172,7 @@
         <v>90</v>
       </c>
       <c r="E96" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F96" s="7" t="s">
         <v>12</v>
@@ -5181,10 +5181,10 @@
       <c r="H96" s="7"/>
       <c r="I96" s="7"/>
       <c r="J96" s="7" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="K96" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="L96" s="7"/>
       <c r="M96" s="1"/>
@@ -5212,10 +5212,10 @@
       <c r="H97" s="7"/>
       <c r="I97" s="7"/>
       <c r="J97" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="K97" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="L97" s="7"/>
       <c r="M97" s="1"/>
@@ -5234,7 +5234,7 @@
         <v>90</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F98" s="7" t="s">
         <v>43</v>
@@ -5243,7 +5243,7 @@
       <c r="H98" s="7"/>
       <c r="I98" s="7"/>
       <c r="J98" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -5263,7 +5263,7 @@
         <v>90</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F99" s="7" t="s">
         <v>43</v>
@@ -5272,7 +5272,7 @@
       <c r="H99" s="7"/>
       <c r="I99" s="7"/>
       <c r="J99" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -5300,13 +5300,13 @@
       <c r="G100" s="7"/>
       <c r="H100" s="7"/>
       <c r="I100" s="7" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="J100" s="7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K100" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L100" s="7"/>
       <c r="M100" s="1"/>
@@ -5325,7 +5325,7 @@
         <v>98</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F101" s="7" t="s">
         <v>16</v>
@@ -5336,7 +5336,7 @@
       <c r="H101" s="20"/>
       <c r="I101" s="20"/>
       <c r="J101" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
@@ -5356,7 +5356,7 @@
         <v>98</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F102" s="7" t="s">
         <v>43</v>
@@ -5365,7 +5365,7 @@
       <c r="H102" s="7"/>
       <c r="I102" s="7"/>
       <c r="J102" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -5394,10 +5394,10 @@
       <c r="H103" s="7"/>
       <c r="I103" s="7"/>
       <c r="J103" s="7" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="K103" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L103" s="7"/>
       <c r="M103" s="1"/>
@@ -5425,10 +5425,10 @@
       <c r="H104" s="7"/>
       <c r="I104" s="7"/>
       <c r="J104" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="K104" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="L104" s="7"/>
       <c r="M104" s="1"/>
@@ -5453,15 +5453,15 @@
         <v>16</v>
       </c>
       <c r="G105" s="7" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H105" s="7"/>
       <c r="I105" s="7"/>
       <c r="J105" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K105" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L105" s="7"/>
       <c r="M105" s="1"/>
@@ -5480,7 +5480,7 @@
         <v>98</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F106" s="7" t="s">
         <v>12</v>
@@ -5489,10 +5489,10 @@
       <c r="H106" s="7"/>
       <c r="I106" s="7"/>
       <c r="J106" s="7" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="K106" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L106" s="7"/>
       <c r="M106" s="1"/>
@@ -5511,7 +5511,7 @@
         <v>98</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F107" s="7" t="s">
         <v>12</v>
@@ -5520,10 +5520,10 @@
       <c r="H107" s="7"/>
       <c r="I107" s="7"/>
       <c r="J107" s="7" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="K107" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L107" s="7"/>
       <c r="M107" s="1"/>
@@ -5542,7 +5542,7 @@
         <v>98</v>
       </c>
       <c r="E108" s="7" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F108" s="7" t="s">
         <v>12</v>
@@ -5551,10 +5551,10 @@
       <c r="H108" s="7"/>
       <c r="I108" s="7"/>
       <c r="J108" s="7" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="K108" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L108" s="7"/>
       <c r="M108" s="1"/>
@@ -5584,10 +5584,10 @@
       <c r="H109" s="7"/>
       <c r="I109" s="7"/>
       <c r="J109" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K109" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L109" s="7"/>
       <c r="M109" s="1"/>
@@ -5606,18 +5606,18 @@
         <v>98</v>
       </c>
       <c r="E110" s="13" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F110" s="14" t="s">
         <v>16</v>
       </c>
       <c r="G110" s="14" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H110" s="20"/>
       <c r="I110" s="20"/>
       <c r="J110" s="14" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K110" s="14"/>
       <c r="L110" s="14"/>
@@ -5643,15 +5643,15 @@
         <v>16</v>
       </c>
       <c r="G111" s="7" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H111" s="7"/>
       <c r="I111" s="7"/>
       <c r="J111" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K111" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L111" s="7"/>
       <c r="M111" s="1"/>
@@ -5676,15 +5676,15 @@
         <v>16</v>
       </c>
       <c r="G112" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H112" s="7"/>
       <c r="I112" s="7"/>
       <c r="J112" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K112" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L112" s="7"/>
       <c r="M112" s="1"/>
@@ -5714,10 +5714,10 @@
       <c r="H113" s="7"/>
       <c r="I113" s="7"/>
       <c r="J113" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K113" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L113" s="7"/>
       <c r="M113" s="1"/>
@@ -5747,10 +5747,10 @@
       <c r="H114" s="7"/>
       <c r="I114" s="7"/>
       <c r="J114" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K114" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L114" s="7"/>
       <c r="M114" s="1"/>
@@ -5769,7 +5769,7 @@
         <v>98</v>
       </c>
       <c r="E115" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F115" s="7" t="s">
         <v>43</v>
@@ -5778,7 +5778,7 @@
       <c r="H115" s="7"/>
       <c r="I115" s="7"/>
       <c r="J115" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5806,13 +5806,13 @@
       <c r="G116" s="7"/>
       <c r="H116" s="7"/>
       <c r="I116" s="7" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="J116" s="7" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="K116" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="L116" s="7"/>
       <c r="M116" s="1"/>
@@ -5831,7 +5831,7 @@
         <v>98</v>
       </c>
       <c r="E117" s="7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F117" s="7" t="s">
         <v>16</v>
@@ -5842,10 +5842,10 @@
       <c r="H117" s="7"/>
       <c r="I117" s="7"/>
       <c r="J117" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K117" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="L117" s="7"/>
       <c r="M117" s="1"/>
@@ -5873,10 +5873,10 @@
       <c r="H118" s="7"/>
       <c r="I118" s="7"/>
       <c r="J118" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="K118" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="L118" s="7"/>
       <c r="M118" s="1"/>
@@ -5889,13 +5889,13 @@
         <v>142</v>
       </c>
       <c r="C119" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="D119" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="E119" s="15" t="s">
         <v>304</v>
-      </c>
-      <c r="D119" s="15" t="s">
-        <v>304</v>
-      </c>
-      <c r="E119" s="15" t="s">
-        <v>305</v>
       </c>
       <c r="F119" s="15" t="s">
         <v>16</v>
@@ -5904,10 +5904,10 @@
       <c r="H119" s="15"/>
       <c r="I119" s="15"/>
       <c r="J119" s="15" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="K119" s="15" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L119" s="15"/>
       <c r="M119" s="1"/>
@@ -5917,7 +5917,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C120" s="16" t="s">
         <v>134</v>
@@ -5935,10 +5935,10 @@
       <c r="H120" s="17"/>
       <c r="I120" s="17"/>
       <c r="J120" s="17" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="K120" s="17" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L120" s="17"/>
       <c r="M120" s="1"/>
@@ -5948,7 +5948,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C121" s="16" t="s">
         <v>134</v>
@@ -5966,10 +5966,10 @@
       <c r="H121" s="17"/>
       <c r="I121" s="17"/>
       <c r="J121" s="17" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="K121" s="17" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L121" s="17"/>
       <c r="M121" s="1"/>
@@ -5979,7 +5979,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C122" s="16" t="s">
         <v>134</v>
@@ -5997,10 +5997,10 @@
       <c r="H122" s="17"/>
       <c r="I122" s="17"/>
       <c r="J122" s="17" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="K122" s="17" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L122" s="17"/>
       <c r="M122" s="1"/>
@@ -6010,7 +6010,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C123" s="16" t="s">
         <v>134</v>
@@ -6030,10 +6030,10 @@
       <c r="H123" s="17"/>
       <c r="I123" s="17"/>
       <c r="J123" s="17" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="K123" s="17" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L123" s="17"/>
       <c r="M123" s="1"/>
@@ -6043,7 +6043,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C124" s="17" t="s">
         <v>50</v>
@@ -6063,10 +6063,10 @@
       <c r="H124" s="17"/>
       <c r="I124" s="17"/>
       <c r="J124" s="17" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K124" s="17" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L124" s="17"/>
       <c r="M124" s="1"/>
@@ -6076,7 +6076,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C125" s="17" t="s">
         <v>50</v>
@@ -6096,10 +6096,10 @@
       <c r="H125" s="17"/>
       <c r="I125" s="17"/>
       <c r="J125" s="17" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K125" s="17" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="L125" s="17"/>
       <c r="M125" s="1"/>
@@ -6109,7 +6109,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C126" s="17" t="s">
         <v>50</v>
@@ -6129,10 +6129,10 @@
       <c r="H126" s="17"/>
       <c r="I126" s="17"/>
       <c r="J126" s="17" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K126" s="17" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L126" s="17"/>
       <c r="M126" s="1"/>
@@ -6142,7 +6142,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C127" s="17" t="s">
         <v>50</v>
@@ -6162,10 +6162,10 @@
       <c r="H127" s="17"/>
       <c r="I127" s="17"/>
       <c r="J127" s="17" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K127" s="17" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L127" s="17"/>
       <c r="M127" s="1"/>
@@ -6175,7 +6175,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C128" s="17" t="s">
         <v>50</v>
@@ -6195,10 +6195,10 @@
       <c r="H128" s="17"/>
       <c r="I128" s="17"/>
       <c r="J128" s="17" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K128" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L128" s="17"/>
       <c r="M128" s="1"/>
@@ -6208,7 +6208,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C129" s="17" t="s">
         <v>50</v>
@@ -6228,10 +6228,10 @@
       <c r="H129" s="17"/>
       <c r="I129" s="17"/>
       <c r="J129" s="17" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K129" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L129" s="17"/>
       <c r="M129" s="1"/>
@@ -6241,7 +6241,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C130" s="17" t="s">
         <v>50</v>
@@ -6259,10 +6259,10 @@
       <c r="H130" s="17"/>
       <c r="I130" s="17"/>
       <c r="J130" s="17" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K130" s="17" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L130" s="17"/>
       <c r="M130" s="1"/>
@@ -6272,7 +6272,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C131" s="17" t="s">
         <v>50</v>
@@ -6292,10 +6292,10 @@
       <c r="H131" s="17"/>
       <c r="I131" s="17"/>
       <c r="J131" s="17" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K131" s="17" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="L131" s="17"/>
       <c r="M131" s="1"/>
@@ -6305,7 +6305,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C132" s="17" t="s">
         <v>50</v>
@@ -6325,10 +6325,10 @@
       <c r="H132" s="17"/>
       <c r="I132" s="17"/>
       <c r="J132" s="17" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K132" s="17" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L132" s="17"/>
       <c r="M132" s="1"/>
@@ -6338,7 +6338,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C133" s="17" t="s">
         <v>50</v>
@@ -6356,10 +6356,10 @@
       <c r="H133" s="17"/>
       <c r="I133" s="17"/>
       <c r="J133" s="17" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="K133" s="17" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L133" s="17"/>
       <c r="M133" s="1"/>
@@ -6369,7 +6369,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C134" s="17" t="s">
         <v>50</v>
@@ -6387,10 +6387,10 @@
       <c r="H134" s="17"/>
       <c r="I134" s="17"/>
       <c r="J134" s="17" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="K134" s="17" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L134" s="17"/>
       <c r="M134" s="1"/>
@@ -6400,7 +6400,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C135" s="17" t="s">
         <v>50</v>
@@ -6409,21 +6409,21 @@
         <v>140</v>
       </c>
       <c r="E135" s="17" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F135" s="17" t="s">
         <v>13</v>
       </c>
       <c r="G135" s="17" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H135" s="17"/>
       <c r="I135" s="17"/>
       <c r="J135" s="17" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K135" s="17" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L135" s="17"/>
       <c r="M135" s="1"/>
@@ -6433,7 +6433,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C136" s="17" t="s">
         <v>50</v>
@@ -6453,10 +6453,10 @@
       <c r="H136" s="17"/>
       <c r="I136" s="17"/>
       <c r="J136" s="17" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K136" s="17" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L136" s="17"/>
       <c r="M136" s="1"/>
@@ -6466,7 +6466,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C137" s="17" t="s">
         <v>50</v>
@@ -6486,10 +6486,10 @@
       <c r="H137" s="17"/>
       <c r="I137" s="17"/>
       <c r="J137" s="17" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K137" s="17" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L137" s="17"/>
       <c r="M137" s="1"/>
@@ -6499,7 +6499,7 @@
         <v>137</v>
       </c>
       <c r="B138" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C138" s="17" t="s">
         <v>50</v>
@@ -6519,10 +6519,10 @@
       <c r="H138" s="17"/>
       <c r="I138" s="17"/>
       <c r="J138" s="17" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K138" s="17" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="L138" s="17"/>
       <c r="M138" s="1"/>
@@ -6532,7 +6532,7 @@
         <v>138</v>
       </c>
       <c r="B139" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C139" s="17" t="s">
         <v>50</v>
@@ -6552,10 +6552,10 @@
       <c r="H139" s="17"/>
       <c r="I139" s="17"/>
       <c r="J139" s="17" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K139" s="17" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L139" s="17"/>
       <c r="M139" s="1"/>
@@ -6565,7 +6565,7 @@
         <v>139</v>
       </c>
       <c r="B140" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C140" s="17" t="s">
         <v>50</v>
@@ -6585,10 +6585,10 @@
       <c r="H140" s="17"/>
       <c r="I140" s="17"/>
       <c r="J140" s="17" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K140" s="17" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L140" s="17"/>
       <c r="M140" s="1"/>
@@ -6598,7 +6598,7 @@
         <v>140</v>
       </c>
       <c r="B141" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C141" s="17" t="s">
         <v>50</v>
@@ -6618,10 +6618,10 @@
       <c r="H141" s="17"/>
       <c r="I141" s="17"/>
       <c r="J141" s="17" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K141" s="17" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L141" s="17"/>
       <c r="M141" s="1"/>
@@ -6631,7 +6631,7 @@
         <v>141</v>
       </c>
       <c r="B142" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C142" s="17" t="s">
         <v>50</v>
@@ -6649,10 +6649,10 @@
       <c r="H142" s="17"/>
       <c r="I142" s="17"/>
       <c r="J142" s="17" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="K142" s="17" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="L142" s="17"/>
       <c r="M142" s="1"/>
@@ -6662,7 +6662,7 @@
         <v>142</v>
       </c>
       <c r="B143" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C143" s="17" t="s">
         <v>50</v>
@@ -6680,10 +6680,10 @@
       <c r="H143" s="17"/>
       <c r="I143" s="17"/>
       <c r="J143" s="17" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="K143" s="17" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L143" s="17"/>
       <c r="M143" s="1"/>
@@ -6693,7 +6693,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C144" s="17" t="s">
         <v>50</v>
@@ -6711,10 +6711,10 @@
       <c r="H144" s="17"/>
       <c r="I144" s="17"/>
       <c r="J144" s="17" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K144" s="17" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L144" s="17"/>
       <c r="M144" s="1"/>
@@ -6724,7 +6724,7 @@
         <v>144</v>
       </c>
       <c r="B145" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C145" s="17" t="s">
         <v>50</v>
@@ -6744,10 +6744,10 @@
       <c r="H145" s="17"/>
       <c r="I145" s="17"/>
       <c r="J145" s="17" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K145" s="17" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L145" s="17"/>
       <c r="M145" s="1"/>
@@ -6757,7 +6757,7 @@
         <v>145</v>
       </c>
       <c r="B146" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C146" s="17" t="s">
         <v>50</v>
@@ -6777,10 +6777,10 @@
       <c r="H146" s="17"/>
       <c r="I146" s="17"/>
       <c r="J146" s="17" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K146" s="17" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L146" s="17"/>
       <c r="M146" s="1"/>
@@ -6790,7 +6790,7 @@
         <v>146</v>
       </c>
       <c r="B147" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C147" s="17" t="s">
         <v>50</v>
@@ -6810,10 +6810,10 @@
       <c r="H147" s="17"/>
       <c r="I147" s="17"/>
       <c r="J147" s="17" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K147" s="17" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="L147" s="17"/>
       <c r="M147" s="1"/>
@@ -6823,7 +6823,7 @@
         <v>147</v>
       </c>
       <c r="B148" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C148" s="17" t="s">
         <v>50</v>
@@ -6832,7 +6832,7 @@
         <v>140</v>
       </c>
       <c r="E148" s="17" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F148" s="17" t="s">
         <v>16</v>
@@ -6843,10 +6843,10 @@
       <c r="H148" s="17"/>
       <c r="I148" s="17"/>
       <c r="J148" s="17" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K148" s="17" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="L148" s="17"/>
       <c r="M148" s="1"/>

--- a/MASTER.xlsx
+++ b/MASTER.xlsx
@@ -555,8 +555,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table22" displayName="Table22" ref="B1:L149" headerRowCount="1" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="B1:L149"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table22" displayName="Table22" ref="B1:L151" headerRowCount="1" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="B1:L151"/>
   <tableColumns count="11">
     <tableColumn id="4" name="Scope" dataDxfId="10"/>
     <tableColumn id="1" name="Category" dataDxfId="9"/>
@@ -875,7 +875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M149"/>
+  <dimension ref="A1:M151"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="30" defaultRowHeight="14.5"/>
   <cols>
     <col width="6.08984375" customWidth="1" style="1" min="1" max="1"/>
@@ -4394,25 +4394,29 @@
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>Mud PSD D10/D25/D40/D50/D75/D90</t>
+          <t>Weighting Agent Loading</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="G75" s="7" t="n"/>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>lb/bbl</t>
+        </is>
+      </c>
       <c r="H75" s="7" t="n"/>
       <c r="I75" s="7" t="n"/>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>{["Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}]}</t>
+          <t>{"Decimal": {"min": 0}}</t>
         </is>
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>Particle-size distribution of solids/bridging material in the reservoir drilling fluid.</t>
+          <t>Concentration of weighting agent added to the reservoir drilling fluid.</t>
         </is>
       </c>
       <c r="L75" s="7" t="n"/>
@@ -4439,7 +4443,7 @@
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>PST Test Volume</t>
+          <t>Bridging Agent Loading</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
@@ -4449,7 +4453,7 @@
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>lb/bbl</t>
         </is>
       </c>
       <c r="H76" s="7" t="n"/>
@@ -4461,7 +4465,7 @@
       </c>
       <c r="K76" s="7" t="inlineStr">
         <is>
-          <t>Volume of wellbore fluid sample passed through the screen coupon to ensure no plugging</t>
+          <t>Concentration of bridging agent added to the reservoir drilling fluid.</t>
         </is>
       </c>
       <c r="L76" s="7" t="n"/>
@@ -4481,36 +4485,32 @@
           <t>Completion</t>
         </is>
       </c>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>Cased Hole Details</t>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>OH Drilling Details</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>Casing Size</t>
+          <t>Mud PSD D10/D25/D40/D50/D75/D90</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="G77" s="7" t="inlineStr">
-        <is>
-          <t>inch</t>
-        </is>
-      </c>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="n"/>
       <c r="H77" s="7" t="n"/>
       <c r="I77" s="7" t="n"/>
       <c r="J77" s="7" t="inlineStr">
         <is>
-          <t>{"Decimal": {"min": 0}}</t>
+          <t>{["Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}]}</t>
         </is>
       </c>
       <c r="K77" s="7" t="inlineStr">
         <is>
-          <t>Nominal casing or liner diameter across the production interval.</t>
+          <t>Particle-size distribution of solids/bridging material in the reservoir drilling fluid.</t>
         </is>
       </c>
       <c r="L77" s="7" t="n"/>
@@ -4530,14 +4530,14 @@
           <t>Completion</t>
         </is>
       </c>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>Cased Hole Details</t>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>OH Drilling Details</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>Gross Perf Length</t>
+          <t>PST Test Volume</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H78" s="7" t="n"/>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="K78" s="7" t="inlineStr">
         <is>
-          <t>Total interval from the uppermost to lowermost perforation, including unperforated gaps.</t>
+          <t>Volume of wellbore fluid sample passed through the screen coupon to ensure no plugging</t>
         </is>
       </c>
       <c r="L78" s="7" t="n"/>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>Net Perf Length</t>
+          <t>Casing Size</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>inch</t>
         </is>
       </c>
       <c r="H79" s="7" t="n"/>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="K79" s="7" t="inlineStr">
         <is>
-          <t>Cumulative length actually perforated and open to formation flow.</t>
+          <t>Nominal casing or liner diameter across the production interval.</t>
         </is>
       </c>
       <c r="L79" s="7" t="n"/>
@@ -4635,7 +4635,7 @@
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>Perforation Gun Size</t>
+          <t>Gross Perf Length</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>inch</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="H80" s="7" t="n"/>
@@ -4657,7 +4657,7 @@
       </c>
       <c r="K80" s="7" t="inlineStr">
         <is>
-          <t>Nominal outside diameter of the perforating gun used across the interval.</t>
+          <t>Total interval from the uppermost to lowermost perforation, including unperforated gaps.</t>
         </is>
       </c>
       <c r="L80" s="7" t="n"/>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>Perforation SPF</t>
+          <t>Net Perf Length</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>shots/ft</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="H81" s="7" t="n"/>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
-          <t>Perforation shot density expressed as shots per foot (SPF).</t>
+          <t>Cumulative length actually perforated and open to formation flow.</t>
         </is>
       </c>
       <c r="L81" s="7" t="n"/>
@@ -4733,25 +4733,29 @@
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>Perforation Charge Casing Material</t>
+          <t>Perforation Gun Size</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>Dropdown Menu</t>
-        </is>
-      </c>
-      <c r="G82" s="7" t="n"/>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>inch</t>
+        </is>
+      </c>
       <c r="H82" s="7" t="n"/>
       <c r="I82" s="7" t="n"/>
       <c r="J82" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Steel", "Low Debris Steel", "Zinc"]}}</t>
+          <t>{"Decimal": {"min": 0}}</t>
         </is>
       </c>
       <c r="K82" s="7" t="inlineStr">
         <is>
-          <t>Material of the shaped-charge case, e.g., steel, low-debris steel, or zinc.</t>
+          <t>Nominal outside diameter of the perforating gun used across the interval.</t>
         </is>
       </c>
       <c r="L82" s="7" t="n"/>
@@ -4778,25 +4782,29 @@
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>Charge Type</t>
+          <t>Perforation SPF</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>Dropdown Menu</t>
-        </is>
-      </c>
-      <c r="G83" s="7" t="n"/>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>shots/ft</t>
+        </is>
+      </c>
       <c r="H83" s="7" t="n"/>
       <c r="I83" s="7" t="n"/>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["BH", "DP"]}}</t>
+          <t>{"Decimal": {"min": 0}}</t>
         </is>
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>Type/design of shaped charge used, such as deep-penetrating or big-hole charge.</t>
+          <t>Perforation shot density expressed as shots per foot (SPF).</t>
         </is>
       </c>
       <c r="L83" s="7" t="n"/>
@@ -4823,7 +4831,7 @@
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>Perforation Strategy</t>
+          <t>Perforation Charge Casing Material</t>
         </is>
       </c>
       <c r="F84" s="7" t="inlineStr">
@@ -4836,12 +4844,12 @@
       <c r="I84" s="7" t="n"/>
       <c r="J84" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["OB", "UB", "OB &amp; Surge", "UB &amp; Surge"]}}</t>
+          <t>{"List": {"options": ["Steel", "Low Debris Steel", "Zinc"]}}</t>
         </is>
       </c>
       <c r="K84" s="7" t="inlineStr">
         <is>
-          <t>Overall perforating approach, including phasing, shot density, orientation, and pressure condition where available.</t>
+          <t>Material of the shaped-charge case, e.g., steel, low-debris steel, or zinc.</t>
         </is>
       </c>
       <c r="L84" s="7" t="n"/>
@@ -4868,29 +4876,25 @@
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>OB / OB Magnitude</t>
+          <t>Charge Type</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="G85" s="7" t="inlineStr">
-        <is>
-          <t>psi</t>
-        </is>
-      </c>
+          <t>Dropdown Menu</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="n"/>
       <c r="H85" s="7" t="n"/>
       <c r="I85" s="7" t="n"/>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>{"Decimal": {"min": 0}}</t>
+          <t>{"List": {"options": ["BH", "DP"]}}</t>
         </is>
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>Perforating pressure condition and magnitude of overbalance relative to formation pressure at the time of perforation.</t>
+          <t>Type/design of shaped charge used, such as deep-penetrating or big-hole charge.</t>
         </is>
       </c>
       <c r="L85" s="7" t="n"/>
@@ -4912,12 +4916,12 @@
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>Sand Control Details</t>
+          <t>Cased Hole Details</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>OH Sand Control Selected Method</t>
+          <t>Perforation Strategy</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
@@ -4926,24 +4930,16 @@
         </is>
       </c>
       <c r="G86" s="7" t="n"/>
-      <c r="H86" s="7" t="inlineStr">
-        <is>
-          <t>{"SAS": {"Gravel Packing": False}, "Cased and Perforated": {"Liners and Screens": False, "Gravel Packing": False}}</t>
-        </is>
-      </c>
-      <c r="I86" s="7" t="inlineStr">
-        <is>
-          <t>{"OHGP": {"Placement Method", "Carrier Fluid Type - OHGP", "Pack Efficiency Source", "Pack Efficiency Percentage", "ICD / AICD", "Did screens get to Target Setting Depth", "Return Percentage", "If screens ran in mud, was mud removed once screens on bottom?"}, "SAS": {"Fluid Type Left in OH at end of Completion", "ICD / AICD", "Did screens get to Target Setting Depth", "If screens ran in mud, was mud removed once screens on bottom?", "Blank pipe run across non-pay sections instead of screens?"}, "CHFP": {"Carrier Fluid Type - CHFP", "Full Pack from Log"}, "CHGP": {"Carrier Fluid Type - CHGP", "Perf Packing", "Return Percentage", "Pack Efficiency Source", "Pack Efficiency Percentage"}}</t>
-        </is>
-      </c>
+      <c r="H86" s="7" t="n"/>
+      <c r="I86" s="7" t="n"/>
       <c r="J86" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["OHGP", "SAS"]}}</t>
+          <t>{"List": {"options": ["OB", "UB", "OB &amp; Surge", "UB &amp; Surge"]}}</t>
         </is>
       </c>
       <c r="K86" s="7" t="inlineStr">
         <is>
-          <t>Sand-control method installed in an open-hole interval, e.g., standalone screen or open-hole gravel pack.</t>
+          <t>Overall perforating approach, including phasing, shot density, orientation, and pressure condition where available.</t>
         </is>
       </c>
       <c r="L86" s="7" t="n"/>
@@ -4965,38 +4961,34 @@
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Sand Control Details</t>
+          <t>Cased Hole Details</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>CH Sand Control Selected Method</t>
+          <t>OB / OB Magnitude</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>Dropdown Menu</t>
-        </is>
-      </c>
-      <c r="G87" s="7" t="n"/>
-      <c r="H87" s="7" t="inlineStr">
-        <is>
-          <t>{"SAS": {"Gravel Packing": False}, "Cased and Perforated": {"Liners and Screens": False, "Gravel Packing": False}}</t>
-        </is>
-      </c>
-      <c r="I87" s="7" t="inlineStr">
-        <is>
-          <t>{"OHGP": {"Placement Method", "Carrier Fluid Type - OHGP", "Pack Efficiency Source", "Pack Efficiency Percentage", "ICD / AICD", "Did screens get to Target Setting Depth", "Return Percentage", "If screens ran in mud, was mud removed once screens on bottom?"}, "SAS": {"Fluid Type Left in OH at end of Completion", "ICD / AICD", "Did screens get to Target Setting Depth", "If screens ran in mud, was mud removed once screens on bottom?", "Blank pipe run across non-pay sections instead of screens?"}, "CHFP": {"Carrier Fluid Type - CHFP", "Full Pack from Log"}, "CHGP": {"Carrier Fluid Type - CHGP", "Perf Packing", "Return Percentage", "Pack Efficiency Source", "Pack Efficiency Percentage"}}</t>
-        </is>
-      </c>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>psi</t>
+        </is>
+      </c>
+      <c r="H87" s="7" t="n"/>
+      <c r="I87" s="7" t="n"/>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["CHFP", "CHGP", "Cased and Perforated"]}}</t>
+          <t>{"Decimal": {"min": 0}}</t>
         </is>
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>Sand-control method installed in a cased/perforated interval, e.g., cased-hole gravel pack or frac pack.</t>
+          <t>Perforating pressure condition and magnitude of overbalance relative to formation pressure at the time of perforation.</t>
         </is>
       </c>
       <c r="L87" s="7" t="n"/>
@@ -5023,7 +5015,7 @@
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>Sand Control Decision Justification</t>
+          <t>OH Sand Control Selected Method</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
@@ -5032,16 +5024,24 @@
         </is>
       </c>
       <c r="G88" s="7" t="n"/>
-      <c r="H88" s="7" t="n"/>
-      <c r="I88" s="7" t="n"/>
+      <c r="H88" s="7" t="inlineStr">
+        <is>
+          <t>{"SAS": {"Gravel Packing": False}, "Cased and Perforated": {"Liners and Screens": False, "Gravel Packing": False}}</t>
+        </is>
+      </c>
+      <c r="I88" s="7" t="inlineStr">
+        <is>
+          <t>{"OHGP": {"Placement Method", "Carrier Fluid Type - OHGP", "Pack Efficiency Source", "Pack Efficiency Percentage", "ICD / AICD", "Did screens get to Target Setting Depth", "Return Percentage", "If screens ran in mud, was mud removed once screens on bottom?"}, "SAS": {"Fluid Type Left in OH at end of Completion", "ICD / AICD", "Did screens get to Target Setting Depth", "If screens ran in mud, was mud removed once screens on bottom?", "Blank pipe run across non-pay sections instead of screens?"}, "CHFP": {"Carrier Fluid Type - CHFP", "Full Pack from Log"}, "CHGP": {"Carrier Fluid Type - CHGP", "Perf Packing", "Return Percentage", "Pack Efficiency Source", "Pack Efficiency Percentage"}}</t>
+        </is>
+      </c>
       <c r="J88" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Uncertain Sand Risk / Conservative Design", "Offset Well Experience", "Core-Based Geomechanical Analysis", "Operational Constraint", "Regulatory Requirement", "Completion Type Standardization", "Unknown / Not Documented"]}}</t>
+          <t>{"List": {"options": ["OHGP", "SAS"]}}</t>
         </is>
       </c>
       <c r="K88" s="7" t="inlineStr">
         <is>
-          <t>Documented technical rationale for selecting the installed sand-control method.</t>
+          <t>Sand-control method installed in an open-hole interval, e.g., standalone screen or open-hole gravel pack.</t>
         </is>
       </c>
       <c r="L88" s="7" t="n"/>
@@ -5063,12 +5063,12 @@
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Liners and Screens</t>
+          <t>Sand Control Details</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>Screen Type</t>
+          <t>CH Sand Control Selected Method</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
@@ -5077,16 +5077,24 @@
         </is>
       </c>
       <c r="G89" s="7" t="n"/>
-      <c r="H89" s="7" t="n"/>
-      <c r="I89" s="7" t="n"/>
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t>{"SAS": {"Gravel Packing": False}, "Cased and Perforated": {"Liners and Screens": False, "Gravel Packing": False}}</t>
+        </is>
+      </c>
+      <c r="I89" s="7" t="inlineStr">
+        <is>
+          <t>{"OHGP": {"Placement Method", "Carrier Fluid Type - OHGP", "Pack Efficiency Source", "Pack Efficiency Percentage", "ICD / AICD", "Did screens get to Target Setting Depth", "Return Percentage", "If screens ran in mud, was mud removed once screens on bottom?"}, "SAS": {"Fluid Type Left in OH at end of Completion", "ICD / AICD", "Did screens get to Target Setting Depth", "If screens ran in mud, was mud removed once screens on bottom?", "Blank pipe run across non-pay sections instead of screens?"}, "CHFP": {"Carrier Fluid Type - CHFP", "Full Pack from Log"}, "CHGP": {"Carrier Fluid Type - CHGP", "Perf Packing", "Return Percentage", "Pack Efficiency Source", "Pack Efficiency Percentage"}}</t>
+        </is>
+      </c>
       <c r="J89" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Plain Slotted Liners", "Wire-Wrapped Screens (WWS)", "Premium Mesh Screen", "Prepacked Screens", "Metal-Fiber / Wool Screen", "Ceramic Screen", "Other Erosion Resistant Screen", "Other"]}}</t>
+          <t>{"List": {"options": ["CHFP", "CHGP", "Cased and Perforated"]}}</t>
         </is>
       </c>
       <c r="K89" s="7" t="inlineStr">
         <is>
-          <t>Type/design of sand-control screen installed across the production interval.</t>
+          <t>Sand-control method installed in a cased/perforated interval, e.g., cased-hole gravel pack or frac pack.</t>
         </is>
       </c>
       <c r="L89" s="7" t="n"/>
@@ -5108,17 +5116,17 @@
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>Liners and Screens</t>
+          <t>Sand Control Details</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>ICD / AICD</t>
+          <t>Sand Control Decision Justification</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Dropdown Menu</t>
         </is>
       </c>
       <c r="G90" s="7" t="n"/>
@@ -5126,12 +5134,12 @@
       <c r="I90" s="7" t="n"/>
       <c r="J90" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Yes", "No"]}}</t>
+          <t>{"List": {"options": ["Uncertain Sand Risk / Conservative Design", "Offset Well Experience", "Core-Based Geomechanical Analysis", "Operational Constraint", "Regulatory Requirement", "Completion Type Standardization", "Unknown / Not Documented"]}}</t>
         </is>
       </c>
       <c r="K90" s="7" t="inlineStr">
         <is>
-          <t>Indicates whether an inflow control device (ICD) or autonomous inflow control device (AICD) is incorporated in the completion.</t>
+          <t>Documented technical rationale for selecting the installed sand-control method.</t>
         </is>
       </c>
       <c r="L90" s="7" t="n"/>
@@ -5158,29 +5166,25 @@
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>Screen Gauge</t>
+          <t>Screen Type</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="G91" s="7" t="inlineStr">
-        <is>
-          <t>gauge or micron</t>
-        </is>
-      </c>
+          <t>Dropdown Menu</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="n"/>
       <c r="H91" s="7" t="n"/>
       <c r="I91" s="7" t="n"/>
       <c r="J91" s="7" t="inlineStr">
         <is>
-          <t>{"Decimal": {"min": 0}}</t>
+          <t>{"List": {"options": ["Plain Slotted Liners", "Wire-Wrapped Screens (WWS)", "Premium Mesh Screen", "Prepacked Screens", "Metal-Fiber / Wool Screen", "Ceramic Screen", "Other Erosion Resistant Screen", "Other"]}}</t>
         </is>
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
-          <t>Nominal slot or screen-opening width. Primarily applicable to slotted liners and wire-wrapped screens.</t>
+          <t>Type/design of sand-control screen installed across the production interval.</t>
         </is>
       </c>
       <c r="L91" s="7" t="n"/>
@@ -5207,29 +5211,25 @@
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>Filter Media Size</t>
+          <t>ICD / AICD</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="G92" s="7" t="inlineStr">
-        <is>
-          <t>micron</t>
-        </is>
-      </c>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="G92" s="7" t="n"/>
       <c r="H92" s="7" t="n"/>
       <c r="I92" s="7" t="n"/>
       <c r="J92" s="7" t="inlineStr">
         <is>
-          <t>{"Decimal": {"min": 0}}</t>
+          <t>{"List": {"options": ["Yes", "No"]}}</t>
         </is>
       </c>
       <c r="K92" s="7" t="inlineStr">
         <is>
-          <t>Nominal pore or particle-retention rating of the screen’s filtering medium. Applicable to premium mesh, metal-fiber/wool, ceramic, and similar media-based screens.</t>
+          <t>Indicates whether an inflow control device (ICD) or autonomous inflow control device (AICD) is incorporated in the completion.</t>
         </is>
       </c>
       <c r="L92" s="7" t="n"/>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>Screen Base Pipe Size</t>
+          <t>Screen Gauge</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
-          <t>inch</t>
+          <t>gauge or micron</t>
         </is>
       </c>
       <c r="H93" s="7" t="n"/>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="K93" s="7" t="inlineStr">
         <is>
-          <t>Nominal outside diameter of the screen base pipe.</t>
+          <t>Nominal slot or screen-opening width. Primarily applicable to slotted liners and wire-wrapped screens.</t>
         </is>
       </c>
       <c r="L93" s="7" t="n"/>
@@ -5305,25 +5305,29 @@
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>Fluid Type Left in OH at end of Completion</t>
+          <t>Filter Media Size</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>Dropdown Menu</t>
-        </is>
-      </c>
-      <c r="G94" s="7" t="n"/>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>micron</t>
+        </is>
+      </c>
       <c r="H94" s="7" t="n"/>
       <c r="I94" s="7" t="n"/>
       <c r="J94" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Completion Brine", "Reservoir Drill-In Fluid", "Filter-Cake Breaker Fluid", "Produced Fluid / Hydrocarbon", "Mixed / Contaminated Fluid"]}}</t>
+          <t>{"Decimal": {"min": 0}}</t>
         </is>
       </c>
       <c r="K94" s="7" t="inlineStr">
         <is>
-          <t>Fluid occupying the open-hole interval at the end of completion operations before cleanup/startup.</t>
+          <t>Nominal pore or particle-retention rating of the screen’s filtering medium. Applicable to premium mesh, metal-fiber/wool, ceramic, and similar media-based screens.</t>
         </is>
       </c>
       <c r="L94" s="7" t="n"/>
@@ -5333,7 +5337,7 @@
       <c r="A95" s="26" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="18" t="inlineStr">
+      <c r="B95" s="14" t="inlineStr">
         <is>
           <t>Completion Interval {id}</t>
         </is>
@@ -5350,25 +5354,29 @@
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>Screen RIH Fluid Type in Casing</t>
+          <t>Screen Base Pipe Size</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
         <is>
-          <t>Dropdown Menu</t>
-        </is>
-      </c>
-      <c r="G95" s="7" t="n"/>
-      <c r="H95" s="19" t="n"/>
-      <c r="I95" s="19" t="n"/>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr">
+        <is>
+          <t>inch</t>
+        </is>
+      </c>
+      <c r="H95" s="7" t="n"/>
+      <c r="I95" s="7" t="n"/>
       <c r="J95" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Brine", "OBM", "WBM", "Low/No Solids WBM", "Low/No Solids OBM"]}}</t>
+          <t>{"Decimal": {"min": 0}}</t>
         </is>
       </c>
       <c r="K95" s="7" t="inlineStr">
         <is>
-          <t>Fluid present in the casing while the screen assembly was run in hole (RIH).</t>
+          <t>Nominal outside diameter of the screen base pipe.</t>
         </is>
       </c>
       <c r="L95" s="7" t="n"/>
@@ -5395,7 +5403,7 @@
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>Screen RIH Fluid Type in Open-Hole</t>
+          <t>Fluid Type Left in OH at end of Completion</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
@@ -5408,12 +5416,12 @@
       <c r="I96" s="7" t="n"/>
       <c r="J96" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Brine", "OBM", "WBM", "Low/No Solids WBM", "Low/No Solids OBM"]}}</t>
+          <t>{"List": {"options": ["Completion Brine", "Reservoir Drill-In Fluid", "Filter-Cake Breaker Fluid", "Produced Fluid / Hydrocarbon", "Mixed / Contaminated Fluid"]}}</t>
         </is>
       </c>
       <c r="K96" s="7" t="inlineStr">
         <is>
-          <t>Fluid present in the open-hole while the screen assembly was run in hole (RIH).</t>
+          <t>Fluid occupying the open-hole interval at the end of completion operations before cleanup/startup.</t>
         </is>
       </c>
       <c r="L96" s="7" t="n"/>
@@ -5423,7 +5431,7 @@
       <c r="A97" s="26" t="n">
         <v>96</v>
       </c>
-      <c r="B97" s="14" t="inlineStr">
+      <c r="B97" s="18" t="inlineStr">
         <is>
           <t>Completion Interval {id}</t>
         </is>
@@ -5440,25 +5448,25 @@
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>If screens ran in mud, was mud removed once screens on bottom?</t>
+          <t>Screen RIH Fluid Type in Casing</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Dropdown Menu</t>
         </is>
       </c>
       <c r="G97" s="7" t="n"/>
-      <c r="H97" s="7" t="n"/>
-      <c r="I97" s="7" t="n"/>
+      <c r="H97" s="19" t="n"/>
+      <c r="I97" s="19" t="n"/>
       <c r="J97" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Yes", "No"]}}</t>
+          <t>{"List": {"options": ["Brine", "OBM", "WBM", "Low/No Solids WBM", "Low/No Solids OBM"]}}</t>
         </is>
       </c>
       <c r="K97" s="7" t="inlineStr">
         <is>
-          <t>Indicates whether drilling mud was displaced/removed after the screens reached final setting depth.</t>
+          <t>Fluid present in the casing while the screen assembly was run in hole (RIH).</t>
         </is>
       </c>
       <c r="L97" s="7" t="n"/>
@@ -5485,12 +5493,12 @@
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>Did screens get to Target Setting Depth</t>
+          <t>Screen RIH Fluid Type in Open-Hole</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Dropdown Menu</t>
         </is>
       </c>
       <c r="G98" s="7" t="n"/>
@@ -5498,10 +5506,14 @@
       <c r="I98" s="7" t="n"/>
       <c r="J98" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Yes", "No"]}}</t>
-        </is>
-      </c>
-      <c r="K98" s="7" t="n"/>
+          <t>{"List": {"options": ["Brine", "OBM", "WBM", "Low/No Solids WBM", "Low/No Solids OBM"]}}</t>
+        </is>
+      </c>
+      <c r="K98" s="7" t="inlineStr">
+        <is>
+          <t>Fluid present in the open-hole while the screen assembly was run in hole (RIH).</t>
+        </is>
+      </c>
       <c r="L98" s="7" t="n"/>
       <c r="M98" s="1" t="n"/>
     </row>
@@ -5526,7 +5538,7 @@
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>Blank pipe run across non-pay sections instead of screens?</t>
+          <t>If screens ran in mud, was mud removed once screens on bottom?</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr">
@@ -5542,7 +5554,11 @@
           <t>{"List": {"options": ["Yes", "No"]}}</t>
         </is>
       </c>
-      <c r="K99" s="7" t="n"/>
+      <c r="K99" s="7" t="inlineStr">
+        <is>
+          <t>Indicates whether drilling mud was displaced/removed after the screens reached final setting depth.</t>
+        </is>
+      </c>
       <c r="L99" s="7" t="n"/>
       <c r="M99" s="1" t="n"/>
     </row>
@@ -5567,12 +5583,12 @@
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>Screen Size Selection</t>
+          <t>Did screens get to Target Setting Depth</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>Dropdown Menu</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="G100" s="7" t="n"/>
@@ -5580,14 +5596,10 @@
       <c r="I100" s="7" t="n"/>
       <c r="J100" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Screen retention test", "Rule of thumb", "Company standard"]}}</t>
-        </is>
-      </c>
-      <c r="K100" s="7" t="inlineStr">
-        <is>
-          <t>Basis used to select the screen size.</t>
-        </is>
-      </c>
+          <t>{"List": {"options": ["Yes", "No"]}}</t>
+        </is>
+      </c>
+      <c r="K100" s="7" t="n"/>
       <c r="L100" s="7" t="n"/>
       <c r="M100" s="1" t="n"/>
     </row>
@@ -5607,36 +5619,28 @@
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Gravel Packing</t>
+          <t>Liners and Screens</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>Placement Method</t>
+          <t>Blank pipe run across non-pay sections instead of screens?</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>Dropdown Menu</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="G101" s="7" t="n"/>
       <c r="H101" s="7" t="n"/>
-      <c r="I101" s="7" t="inlineStr">
-        <is>
-          <t>{"Shunt": {"% Pack through Shunts", "Shunt Tubes"}, "Circ Pack": {"% Pack through Shunts": False, "Shunt Tubes": False}}</t>
-        </is>
-      </c>
+      <c r="I101" s="7" t="n"/>
       <c r="J101" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Shunt", "Circ Pack"]}}</t>
-        </is>
-      </c>
-      <c r="K101" s="7" t="inlineStr">
-        <is>
-          <t>Technique used to place gravel/proppant around the screen and across the production interval.</t>
-        </is>
-      </c>
+          <t>{"List": {"options": ["Yes", "No"]}}</t>
+        </is>
+      </c>
+      <c r="K101" s="7" t="n"/>
       <c r="L101" s="7" t="n"/>
       <c r="M101" s="1" t="n"/>
     </row>
@@ -5656,32 +5660,32 @@
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>Gravel Packing</t>
+          <t>Liners and Screens</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>% Pack through Shunts</t>
+          <t>Screen Size Selection</t>
         </is>
       </c>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="G102" s="7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H102" s="20" t="n"/>
-      <c r="I102" s="20" t="n"/>
+          <t>Dropdown Menu</t>
+        </is>
+      </c>
+      <c r="G102" s="7" t="n"/>
+      <c r="H102" s="7" t="n"/>
+      <c r="I102" s="7" t="n"/>
       <c r="J102" s="7" t="inlineStr">
         <is>
-          <t>{"Decimal": {"min": 0}}</t>
-        </is>
-      </c>
-      <c r="K102" s="7" t="n"/>
+          <t>{"List": {"options": ["Screen retention test", "Rule of thumb", "Company standard"]}}</t>
+        </is>
+      </c>
+      <c r="K102" s="7" t="inlineStr">
+        <is>
+          <t>Basis used to select the screen size.</t>
+        </is>
+      </c>
       <c r="L102" s="7" t="n"/>
       <c r="M102" s="1" t="n"/>
     </row>
@@ -5706,23 +5710,31 @@
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>Shunt Tubes</t>
+          <t>Placement Method</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Dropdown Menu</t>
         </is>
       </c>
       <c r="G103" s="7" t="n"/>
       <c r="H103" s="7" t="n"/>
-      <c r="I103" s="7" t="n"/>
+      <c r="I103" s="7" t="inlineStr">
+        <is>
+          <t>{"Shunt": {"% Pack through Shunts", "Shunt Tubes"}, "Circ Pack": {"% Pack through Shunts": False, "Shunt Tubes": False}}</t>
+        </is>
+      </c>
       <c r="J103" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Yes", "No"]}}</t>
-        </is>
-      </c>
-      <c r="K103" s="7" t="n"/>
+          <t>{"List": {"options": ["Shunt", "Circ Pack"]}}</t>
+        </is>
+      </c>
+      <c r="K103" s="7" t="inlineStr">
+        <is>
+          <t>Technique used to place gravel/proppant around the screen and across the production interval.</t>
+        </is>
+      </c>
       <c r="L103" s="7" t="n"/>
       <c r="M103" s="1" t="n"/>
     </row>
@@ -5747,27 +5759,27 @@
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>Proppant Type</t>
+          <t>% Pack through Shunts</t>
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>Dropdown Menu</t>
-        </is>
-      </c>
-      <c r="G104" s="7" t="n"/>
-      <c r="H104" s="7" t="n"/>
-      <c r="I104" s="7" t="n"/>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G104" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H104" s="20" t="n"/>
+      <c r="I104" s="20" t="n"/>
       <c r="J104" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Natural Sand", "Ceramic Proppant"]}}</t>
-        </is>
-      </c>
-      <c r="K104" s="7" t="inlineStr">
-        <is>
-          <t>Material used as gravel-pack/proppant media, including material composition or commercial type where known.</t>
-        </is>
-      </c>
+          <t>{"Decimal": {"min": 0}}</t>
+        </is>
+      </c>
+      <c r="K104" s="7" t="n"/>
       <c r="L104" s="7" t="n"/>
       <c r="M104" s="1" t="n"/>
     </row>
@@ -5792,12 +5804,12 @@
       </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
-          <t>Proppant Size</t>
+          <t>Shunt Tubes</t>
         </is>
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>Dropdown Menu</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="G105" s="7" t="n"/>
@@ -5805,14 +5817,10 @@
       <c r="I105" s="7" t="n"/>
       <c r="J105" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["16/20", "16/30", "20/40", "30/50", "40/60", "40/70", "35 Monomesh", "25 Monomesh", "40 Monomesh", "45 Monomesh"]}}</t>
-        </is>
-      </c>
-      <c r="K105" s="7" t="inlineStr">
-        <is>
-          <t>Nominal gravel/proppant mesh-size range used in the sand-control treatment.</t>
-        </is>
-      </c>
+          <t>{"List": {"options": ["Yes", "No"]}}</t>
+        </is>
+      </c>
+      <c r="K105" s="7" t="n"/>
       <c r="L105" s="7" t="n"/>
       <c r="M105" s="1" t="n"/>
     </row>
@@ -5837,29 +5845,25 @@
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>Proppant / Unit Length</t>
+          <t>Proppant Type</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="G106" s="7" t="inlineStr">
-        <is>
-          <t>lbs/ft</t>
-        </is>
-      </c>
+          <t>Dropdown Menu</t>
+        </is>
+      </c>
+      <c r="G106" s="7" t="n"/>
       <c r="H106" s="7" t="n"/>
       <c r="I106" s="7" t="n"/>
       <c r="J106" s="7" t="inlineStr">
         <is>
-          <t>{"Decimal": {"min": 0}}</t>
+          <t>{"List": {"options": ["Natural Sand", "Ceramic Proppant"]}}</t>
         </is>
       </c>
       <c r="K106" s="7" t="inlineStr">
         <is>
-          <t>Total quantity of gravel/proppant placed normalized by completed interval length.</t>
+          <t>Material used as gravel-pack/proppant media, including material composition or commercial type where known.</t>
         </is>
       </c>
       <c r="L106" s="7" t="n"/>
@@ -5886,7 +5890,7 @@
       </c>
       <c r="E107" s="7" t="inlineStr">
         <is>
-          <t>Carrier Fluid Type - OHGP</t>
+          <t>Proppant Size</t>
         </is>
       </c>
       <c r="F107" s="7" t="inlineStr">
@@ -5899,12 +5903,12 @@
       <c r="I107" s="7" t="n"/>
       <c r="J107" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Brine", "Xanthan", "VES", "HEC", "Oil Based"]}}</t>
+          <t>{"List": {"options": ["16/20", "16/30", "20/40", "30/50", "40/60", "40/70", "35 Monomesh", "25 Monomesh", "40 Monomesh", "45 Monomesh"]}}</t>
         </is>
       </c>
       <c r="K107" s="7" t="inlineStr">
         <is>
-          <t>Base fluid/system used to transport gravel or proppant during placement.</t>
+          <t>Nominal gravel/proppant mesh-size range used in the sand-control treatment.</t>
         </is>
       </c>
       <c r="L107" s="7" t="n"/>
@@ -5931,25 +5935,29 @@
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
-          <t>Carrier Fluid Type - CHFP</t>
+          <t>Proppant / Unit Length</t>
         </is>
       </c>
       <c r="F108" s="7" t="inlineStr">
         <is>
-          <t>Dropdown Menu</t>
-        </is>
-      </c>
-      <c r="G108" s="7" t="n"/>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>lbs/ft</t>
+        </is>
+      </c>
       <c r="H108" s="7" t="n"/>
       <c r="I108" s="7" t="n"/>
       <c r="J108" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Xlink Gel", "VES", "HEC"]}}</t>
+          <t>{"Decimal": {"min": 0}}</t>
         </is>
       </c>
       <c r="K108" s="7" t="inlineStr">
         <is>
-          <t>Base fluid/system used to transport gravel or proppant during placement.</t>
+          <t>Total quantity of gravel/proppant placed normalized by completed interval length.</t>
         </is>
       </c>
       <c r="L108" s="7" t="n"/>
@@ -5976,7 +5984,7 @@
       </c>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>Carrier Fluid Type - CHGP</t>
+          <t>Carrier Fluid Type - OHGP</t>
         </is>
       </c>
       <c r="F109" s="7" t="inlineStr">
@@ -5989,7 +5997,7 @@
       <c r="I109" s="7" t="n"/>
       <c r="J109" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Brine", "Linear Gel", "HEC", "Xlinked Gel", "VES", "Xanthan"]}}</t>
+          <t>{"List": {"options": ["Brine", "Xanthan", "VES", "HEC", "Oil Based"]}}</t>
         </is>
       </c>
       <c r="K109" s="7" t="inlineStr">
@@ -6021,29 +6029,25 @@
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t>Carrier Fluid Density</t>
+          <t>Carrier Fluid Type - CHFP</t>
         </is>
       </c>
       <c r="F110" s="7" t="inlineStr">
         <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="G110" s="7" t="inlineStr">
-        <is>
-          <t>ppg</t>
-        </is>
-      </c>
+          <t>Dropdown Menu</t>
+        </is>
+      </c>
+      <c r="G110" s="7" t="n"/>
       <c r="H110" s="7" t="n"/>
       <c r="I110" s="7" t="n"/>
       <c r="J110" s="7" t="inlineStr">
         <is>
-          <t>{"Decimal": {"min": 0}}</t>
+          <t>{"List": {"options": ["Xlink Gel", "VES", "HEC"]}}</t>
         </is>
       </c>
       <c r="K110" s="7" t="inlineStr">
         <is>
-          <t>Density of the carrier/slurry fluid used during gravel-pack placement.</t>
+          <t>Base fluid/system used to transport gravel or proppant during placement.</t>
         </is>
       </c>
       <c r="L110" s="7" t="n"/>
@@ -6068,30 +6072,30 @@
           <t>Gravel Packing</t>
         </is>
       </c>
-      <c r="E111" s="13" t="inlineStr">
-        <is>
-          <t>Perf Packing</t>
-        </is>
-      </c>
-      <c r="F111" s="14" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="G111" s="14" t="inlineStr">
-        <is>
-          <t>lbs/ft</t>
-        </is>
-      </c>
-      <c r="H111" s="20" t="n"/>
-      <c r="I111" s="20" t="n"/>
-      <c r="J111" s="14" t="inlineStr">
-        <is>
-          <t>{"Decimal": {"min": 0}}</t>
-        </is>
-      </c>
-      <c r="K111" s="14" t="n"/>
-      <c r="L111" s="14" t="n"/>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
+          <t>Carrier Fluid Type - CHGP</t>
+        </is>
+      </c>
+      <c r="F111" s="7" t="inlineStr">
+        <is>
+          <t>Dropdown Menu</t>
+        </is>
+      </c>
+      <c r="G111" s="7" t="n"/>
+      <c r="H111" s="7" t="n"/>
+      <c r="I111" s="7" t="n"/>
+      <c r="J111" s="7" t="inlineStr">
+        <is>
+          <t>{"List": {"options": ["Brine", "Linear Gel", "HEC", "Xlinked Gel", "VES", "Xanthan"]}}</t>
+        </is>
+      </c>
+      <c r="K111" s="7" t="inlineStr">
+        <is>
+          <t>Base fluid/system used to transport gravel or proppant during placement.</t>
+        </is>
+      </c>
+      <c r="L111" s="7" t="n"/>
       <c r="M111" s="1" t="n"/>
     </row>
     <row r="112" ht="14" customHeight="1">
@@ -6115,7 +6119,7 @@
       </c>
       <c r="E112" s="7" t="inlineStr">
         <is>
-          <t>Max Proppant Concentration</t>
+          <t>Carrier Fluid Density</t>
         </is>
       </c>
       <c r="F112" s="7" t="inlineStr">
@@ -6125,7 +6129,7 @@
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
-          <t>ppa</t>
+          <t>ppg</t>
         </is>
       </c>
       <c r="H112" s="7" t="n"/>
@@ -6137,7 +6141,7 @@
       </c>
       <c r="K112" s="7" t="inlineStr">
         <is>
-          <t>Maximum proppant concentration reached during the placement treatment.</t>
+          <t>Density of the carrier/slurry fluid used during gravel-pack placement.</t>
         </is>
       </c>
       <c r="L112" s="7" t="n"/>
@@ -6162,34 +6166,30 @@
           <t>Gravel Packing</t>
         </is>
       </c>
-      <c r="E113" s="7" t="inlineStr">
-        <is>
-          <t>Max Pump Rate</t>
-        </is>
-      </c>
-      <c r="F113" s="7" t="inlineStr">
+      <c r="E113" s="13" t="inlineStr">
+        <is>
+          <t>Perf Packing</t>
+        </is>
+      </c>
+      <c r="F113" s="14" t="inlineStr">
         <is>
           <t>Number</t>
         </is>
       </c>
-      <c r="G113" s="7" t="inlineStr">
-        <is>
-          <t>bpm</t>
-        </is>
-      </c>
-      <c r="H113" s="7" t="n"/>
-      <c r="I113" s="7" t="n"/>
-      <c r="J113" s="7" t="inlineStr">
+      <c r="G113" s="14" t="inlineStr">
+        <is>
+          <t>lbs/ft</t>
+        </is>
+      </c>
+      <c r="H113" s="20" t="n"/>
+      <c r="I113" s="20" t="n"/>
+      <c r="J113" s="14" t="inlineStr">
         <is>
           <t>{"Decimal": {"min": 0}}</t>
         </is>
       </c>
-      <c r="K113" s="7" t="inlineStr">
-        <is>
-          <t>Maximum pumping rate reached during gravel-pack placement.</t>
-        </is>
-      </c>
-      <c r="L113" s="7" t="n"/>
+      <c r="K113" s="14" t="n"/>
+      <c r="L113" s="14" t="n"/>
       <c r="M113" s="1" t="n"/>
     </row>
     <row r="114" ht="14" customHeight="1">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>Net Pressure Gain</t>
+          <t>Max Proppant Concentration</t>
         </is>
       </c>
       <c r="F114" s="7" t="inlineStr">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>psi</t>
+          <t>ppa</t>
         </is>
       </c>
       <c r="H114" s="7" t="n"/>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="K114" s="7" t="inlineStr">
         <is>
-          <t>Increase in net treatment pressure observed during gravel/proppant placement.</t>
+          <t>Maximum proppant concentration reached during the placement treatment.</t>
         </is>
       </c>
       <c r="L114" s="7" t="n"/>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>Return Percentage</t>
+          <t>Max Pump Rate</t>
         </is>
       </c>
       <c r="F115" s="7" t="inlineStr">
@@ -6272,7 +6272,7 @@
       </c>
       <c r="G115" s="7" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>bpm</t>
         </is>
       </c>
       <c r="H115" s="7" t="n"/>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="K115" s="7" t="inlineStr">
         <is>
-          <t>Percentage of pumped carrier fluid or slurry returns observed/recovered during the gravel-pack operation, as defined by the source.</t>
+          <t>Maximum pumping rate reached during gravel-pack placement.</t>
         </is>
       </c>
       <c r="L115" s="7" t="n"/>
@@ -6311,23 +6311,31 @@
       </c>
       <c r="E116" s="7" t="inlineStr">
         <is>
-          <t>Full Pack from Log</t>
+          <t>Net Pressure Gain</t>
         </is>
       </c>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>Boolean</t>
-        </is>
-      </c>
-      <c r="G116" s="7" t="n"/>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G116" s="7" t="inlineStr">
+        <is>
+          <t>psi</t>
+        </is>
+      </c>
       <c r="H116" s="7" t="n"/>
       <c r="I116" s="7" t="n"/>
       <c r="J116" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Yes", "No"]}}</t>
-        </is>
-      </c>
-      <c r="K116" s="7" t="n"/>
+          <t>{"Decimal": {"min": 0}}</t>
+        </is>
+      </c>
+      <c r="K116" s="7" t="inlineStr">
+        <is>
+          <t>Increase in net treatment pressure observed during gravel/proppant placement.</t>
+        </is>
+      </c>
       <c r="L116" s="7" t="n"/>
       <c r="M116" s="1" t="n"/>
     </row>
@@ -6352,29 +6360,29 @@
       </c>
       <c r="E117" s="7" t="inlineStr">
         <is>
-          <t>Pack Efficiency Source</t>
+          <t>Return Percentage</t>
         </is>
       </c>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>Dropdown Menu</t>
-        </is>
-      </c>
-      <c r="G117" s="7" t="n"/>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G117" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
       <c r="H117" s="7" t="n"/>
-      <c r="I117" s="7" t="inlineStr">
-        <is>
-          <t>{"None": {"Pack Efficiency Percentage": False}}</t>
-        </is>
-      </c>
+      <c r="I117" s="7" t="n"/>
       <c r="J117" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Gravel Pack Log", "Gauge Analysis", "Volumetrics", "None"]}}</t>
+          <t>{"Decimal": {"min": 0}}</t>
         </is>
       </c>
       <c r="K117" s="7" t="inlineStr">
         <is>
-          <t>Method used to determine gravel-pack placement efficiency, e.g., evaluation log, volume balance, pumping data, or returns.</t>
+          <t>Percentage of pumped carrier fluid or slurry returns observed/recovered during the gravel-pack operation, as defined by the source.</t>
         </is>
       </c>
       <c r="L117" s="7" t="n"/>
@@ -6401,31 +6409,23 @@
       </c>
       <c r="E118" s="7" t="inlineStr">
         <is>
-          <t>Pack Efficiency Percentage</t>
+          <t>Full Pack from Log</t>
         </is>
       </c>
       <c r="F118" s="7" t="inlineStr">
         <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="G118" s="7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="G118" s="7" t="n"/>
       <c r="H118" s="7" t="n"/>
       <c r="I118" s="7" t="n"/>
       <c r="J118" s="7" t="inlineStr">
         <is>
-          <t>{"Decimal": {"min": 0}}</t>
-        </is>
-      </c>
-      <c r="K118" s="7" t="inlineStr">
-        <is>
-          <t>Reported or calculated percentage of the target interval/annular volume successfully packed with gravel.</t>
-        </is>
-      </c>
+          <t>{"List": {"options": ["Yes", "No"]}}</t>
+        </is>
+      </c>
+      <c r="K118" s="7" t="n"/>
       <c r="L118" s="7" t="n"/>
       <c r="M118" s="1" t="n"/>
     </row>
@@ -6450,163 +6450,171 @@
       </c>
       <c r="E119" s="7" t="inlineStr">
         <is>
-          <t>Placement Issues</t>
+          <t>Pack Efficiency Source</t>
         </is>
       </c>
       <c r="F119" s="7" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Dropdown Menu</t>
         </is>
       </c>
       <c r="G119" s="7" t="n"/>
       <c r="H119" s="7" t="n"/>
-      <c r="I119" s="7" t="n"/>
+      <c r="I119" s="7" t="inlineStr">
+        <is>
+          <t>{"None": {"Pack Efficiency Percentage": False}}</t>
+        </is>
+      </c>
       <c r="J119" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Yes", "No"]}}</t>
+          <t>{"List": {"options": ["Gravel Pack Log", "Gauge Analysis", "Volumetrics", "None"]}}</t>
         </is>
       </c>
       <c r="K119" s="7" t="inlineStr">
         <is>
-          <t>Problems encountered during gravel placement, such as premature screenout, losses, bridging, incomplete packing, or poor returns.</t>
+          <t>Method used to determine gravel-pack placement efficiency, e.g., evaluation log, volume balance, pumping data, or returns.</t>
         </is>
       </c>
       <c r="L119" s="7" t="n"/>
       <c r="M119" s="1" t="n"/>
     </row>
     <row r="120" ht="14" customHeight="1">
-      <c r="A120" s="23" t="n">
+      <c r="A120" s="26" t="n">
         <v>119</v>
       </c>
-      <c r="B120" s="15" t="inlineStr">
+      <c r="B120" s="14" t="inlineStr">
         <is>
           <t>Completion Interval {id}</t>
         </is>
       </c>
-      <c r="C120" s="15" t="inlineStr">
+      <c r="C120" s="7" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="D120" s="7" t="inlineStr">
+        <is>
+          <t>Gravel Packing</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t>Pack Efficiency Percentage</t>
+        </is>
+      </c>
+      <c r="F120" s="7" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G120" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H120" s="7" t="n"/>
+      <c r="I120" s="7" t="n"/>
+      <c r="J120" s="7" t="inlineStr">
+        <is>
+          <t>{"Decimal": {"min": 0}}</t>
+        </is>
+      </c>
+      <c r="K120" s="7" t="inlineStr">
+        <is>
+          <t>Reported or calculated percentage of the target interval/annular volume successfully packed with gravel.</t>
+        </is>
+      </c>
+      <c r="L120" s="7" t="n"/>
+      <c r="M120" s="1" t="n"/>
+    </row>
+    <row r="121" ht="14" customHeight="1">
+      <c r="A121" s="26" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="14" t="inlineStr">
+        <is>
+          <t>Completion Interval {id}</t>
+        </is>
+      </c>
+      <c r="C121" s="7" t="inlineStr">
+        <is>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="D121" s="7" t="inlineStr">
+        <is>
+          <t>Gravel Packing</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="inlineStr">
+        <is>
+          <t>Placement Issues</t>
+        </is>
+      </c>
+      <c r="F121" s="7" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="G121" s="7" t="n"/>
+      <c r="H121" s="7" t="n"/>
+      <c r="I121" s="7" t="n"/>
+      <c r="J121" s="7" t="inlineStr">
+        <is>
+          <t>{"List": {"options": ["Yes", "No"]}}</t>
+        </is>
+      </c>
+      <c r="K121" s="7" t="inlineStr">
+        <is>
+          <t>Problems encountered during gravel placement, such as premature screenout, losses, bridging, incomplete packing, or poor returns.</t>
+        </is>
+      </c>
+      <c r="L121" s="7" t="n"/>
+      <c r="M121" s="1" t="n"/>
+    </row>
+    <row r="122" ht="14" customHeight="1">
+      <c r="A122" s="23" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="15" t="inlineStr">
+        <is>
+          <t>Completion Interval {id}</t>
+        </is>
+      </c>
+      <c r="C122" s="15" t="inlineStr">
         <is>
           <t>Sand Bodies</t>
         </is>
       </c>
-      <c r="D120" s="15" t="inlineStr">
+      <c r="D122" s="15" t="inlineStr">
         <is>
           <t>Sand Bodies</t>
         </is>
       </c>
-      <c r="E120" s="15" t="inlineStr">
+      <c r="E122" s="15" t="inlineStr">
         <is>
           <t>Number of sand bodies</t>
         </is>
       </c>
-      <c r="F120" s="15" t="inlineStr">
+      <c r="F122" s="15" t="inlineStr">
         <is>
           <t>Number</t>
         </is>
       </c>
-      <c r="G120" s="15" t="n"/>
-      <c r="H120" s="15" t="n"/>
-      <c r="I120" s="15" t="n"/>
-      <c r="J120" s="15" t="inlineStr">
+      <c r="G122" s="15" t="n"/>
+      <c r="H122" s="15" t="n"/>
+      <c r="I122" s="15" t="n"/>
+      <c r="J122" s="15" t="inlineStr">
         <is>
           <t>{"Whole number": {"min": 1, "max": 10}}</t>
         </is>
       </c>
-      <c r="K120" s="15" t="inlineStr">
+      <c r="K122" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Each completion interval can have several sand bodies. </t>
         </is>
       </c>
-      <c r="L120" s="15" t="n"/>
-      <c r="M120" s="1" t="n"/>
-    </row>
-    <row r="121" ht="14" customHeight="1">
-      <c r="A121" s="24" t="n">
-        <v>120</v>
-      </c>
-      <c r="B121" s="17" t="inlineStr">
-        <is>
-          <t>Sand Body {id}</t>
-        </is>
-      </c>
-      <c r="C121" s="16" t="inlineStr">
-        <is>
-          <t>Pre-production and cleanup</t>
-        </is>
-      </c>
-      <c r="D121" s="16" t="inlineStr">
-        <is>
-          <t>Pre-production and cleanup details</t>
-        </is>
-      </c>
-      <c r="E121" s="17" t="inlineStr">
-        <is>
-          <t>Remedial Acid Pumped as Productivity was Below Expectation</t>
-        </is>
-      </c>
-      <c r="F121" s="17" t="inlineStr">
-        <is>
-          <t>Dropdown Menu</t>
-        </is>
-      </c>
-      <c r="G121" s="17" t="n"/>
-      <c r="H121" s="17" t="n"/>
-      <c r="I121" s="17" t="n"/>
-      <c r="J121" s="17" t="inlineStr">
-        <is>
-          <t>{"List": {"options": ["Yes", "No", "Unknown", "Not Applicable"]}}</t>
-        </is>
-      </c>
-      <c r="K121" s="17" t="inlineStr">
-        <is>
-          <t>Indicates whether remedial acid treatment was performed because initial well productivity was below the expected level.</t>
-        </is>
-      </c>
-      <c r="L121" s="17" t="n"/>
-      <c r="M121" s="1" t="n"/>
-    </row>
-    <row r="122" ht="14" customHeight="1">
-      <c r="A122" s="24" t="n">
-        <v>121</v>
-      </c>
-      <c r="B122" s="17" t="inlineStr">
-        <is>
-          <t>Sand Body {id}</t>
-        </is>
-      </c>
-      <c r="C122" s="16" t="inlineStr">
-        <is>
-          <t>Pre-production and cleanup</t>
-        </is>
-      </c>
-      <c r="D122" s="16" t="inlineStr">
-        <is>
-          <t>Pre-production and cleanup details</t>
-        </is>
-      </c>
-      <c r="E122" s="17" t="inlineStr">
-        <is>
-          <t>Remedial Acid Helped Productivity</t>
-        </is>
-      </c>
-      <c r="F122" s="17" t="inlineStr">
-        <is>
-          <t>Dropdown Menu</t>
-        </is>
-      </c>
-      <c r="G122" s="17" t="n"/>
-      <c r="H122" s="17" t="n"/>
-      <c r="I122" s="17" t="n"/>
-      <c r="J122" s="17" t="inlineStr">
-        <is>
-          <t>{"List": {"options": ["Yes", "No", "Partially", "Unknown", "Not Applicable"]}}</t>
-        </is>
-      </c>
-      <c r="K122" s="17" t="inlineStr">
-        <is>
-          <t>Indicates whether the remedial acid treatment produced a measurable or documented improvement in well productivity.</t>
-        </is>
-      </c>
-      <c r="L122" s="17" t="n"/>
+      <c r="L122" s="15" t="n"/>
       <c r="M122" s="1" t="n"/>
     </row>
     <row r="123" ht="14" customHeight="1">
@@ -6630,7 +6638,7 @@
       </c>
       <c r="E123" s="17" t="inlineStr">
         <is>
-          <t>Remedial Acid Type</t>
+          <t>Remedial Acid Pumped as Productivity was Below Expectation</t>
         </is>
       </c>
       <c r="F123" s="17" t="inlineStr">
@@ -6643,12 +6651,12 @@
       <c r="I123" s="17" t="n"/>
       <c r="J123" s="17" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Organic", "Inorganic", "Mud acid", "Blend", "Other", "Unknown", "Not applicable"]}}</t>
+          <t>{"List": {"options": ["Yes", "No", "Unknown", "Not Applicable"]}}</t>
         </is>
       </c>
       <c r="K123" s="17" t="inlineStr">
         <is>
-          <t>Type or formulation of acid system used for the remedial treatment, e.g., HCl, mud acid, or organic acid.</t>
+          <t>Indicates whether remedial acid treatment was performed because initial well productivity was below the expected level.</t>
         </is>
       </c>
       <c r="L123" s="17" t="n"/>
@@ -6675,29 +6683,25 @@
       </c>
       <c r="E124" s="17" t="inlineStr">
         <is>
-          <t>Percentage of ideal PI or skin achieved</t>
+          <t>Remedial Acid Helped Productivity</t>
         </is>
       </c>
       <c r="F124" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="G124" s="17" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
+          <t>Dropdown Menu</t>
+        </is>
+      </c>
+      <c r="G124" s="17" t="n"/>
       <c r="H124" s="17" t="n"/>
       <c r="I124" s="17" t="n"/>
       <c r="J124" s="17" t="inlineStr">
         <is>
-          <t>{"Whole number"}</t>
+          <t>{"List": {"options": ["Yes", "No", "Partially", "Unknown", "Not Applicable"]}}</t>
         </is>
       </c>
       <c r="K124" s="17" t="inlineStr">
         <is>
-          <t>Well performance after cleanup expressed relative to the modeled/theoretical ideal PI or skin target.</t>
+          <t>Indicates whether the remedial acid treatment produced a measurable or documented improvement in well productivity.</t>
         </is>
       </c>
       <c r="L124" s="17" t="n"/>
@@ -6712,41 +6716,37 @@
           <t>Sand Body {id}</t>
         </is>
       </c>
-      <c r="C125" s="17" t="inlineStr">
-        <is>
-          <t>Reservoir Characterization</t>
+      <c r="C125" s="16" t="inlineStr">
+        <is>
+          <t>Pre-production and cleanup</t>
         </is>
       </c>
       <c r="D125" s="16" t="inlineStr">
         <is>
-          <t>Reservoir Rock and Fluid Properties</t>
+          <t>Pre-production and cleanup details</t>
         </is>
       </c>
       <c r="E125" s="17" t="inlineStr">
         <is>
-          <t>Virgin Reservoir Pressure</t>
+          <t>Remedial Acid Type</t>
         </is>
       </c>
       <c r="F125" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="G125" s="17" t="inlineStr">
-        <is>
-          <t>psi</t>
-        </is>
-      </c>
+          <t>Dropdown Menu</t>
+        </is>
+      </c>
+      <c r="G125" s="17" t="n"/>
       <c r="H125" s="17" t="n"/>
       <c r="I125" s="17" t="n"/>
       <c r="J125" s="17" t="inlineStr">
         <is>
-          <t>{"Decimal": {"min": 0}}</t>
+          <t>{"List": {"options": ["Organic", "Inorganic", "Mud acid", "Blend", "Other", "Unknown", "Not applicable"]}}</t>
         </is>
       </c>
       <c r="K125" s="17" t="inlineStr">
         <is>
-          <t>Original reservoir pressure before depletion or production-induced pressure decline.</t>
+          <t>Type or formulation of acid system used for the remedial treatment, e.g., HCl, mud acid, or organic acid.</t>
         </is>
       </c>
       <c r="L125" s="17" t="n"/>
@@ -6761,19 +6761,19 @@
           <t>Sand Body {id}</t>
         </is>
       </c>
-      <c r="C126" s="17" t="inlineStr">
-        <is>
-          <t>Reservoir Characterization</t>
+      <c r="C126" s="16" t="inlineStr">
+        <is>
+          <t>Pre-production and cleanup</t>
         </is>
       </c>
       <c r="D126" s="16" t="inlineStr">
         <is>
-          <t>Reservoir Rock and Fluid Properties</t>
+          <t>Pre-production and cleanup details</t>
         </is>
       </c>
       <c r="E126" s="17" t="inlineStr">
         <is>
-          <t>Reservoir Pressure at Time of Completion</t>
+          <t>Percentage of ideal PI or skin achieved</t>
         </is>
       </c>
       <c r="F126" s="17" t="inlineStr">
@@ -6783,19 +6783,19 @@
       </c>
       <c r="G126" s="17" t="inlineStr">
         <is>
-          <t>psi</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H126" s="17" t="n"/>
       <c r="I126" s="17" t="n"/>
       <c r="J126" s="17" t="inlineStr">
         <is>
-          <t>{"Decimal": {"min": 0}}</t>
+          <t>{"Whole number"}</t>
         </is>
       </c>
       <c r="K126" s="17" t="inlineStr">
         <is>
-          <t>Estimated or measured reservoir pressure when the completion was installed.</t>
+          <t>Well performance after cleanup expressed relative to the modeled/theoretical ideal PI or skin target.</t>
         </is>
       </c>
       <c r="L126" s="17" t="n"/>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="E127" s="17" t="inlineStr">
         <is>
-          <t>Reservoir pressure at first sand production</t>
+          <t>Virgin Reservoir Pressure</t>
         </is>
       </c>
       <c r="F127" s="17" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="K127" s="17" t="inlineStr">
         <is>
-          <t>Estimated or measured reservoir pressure when sand production was first observed.</t>
+          <t>Original reservoir pressure before depletion or production-induced pressure decline.</t>
         </is>
       </c>
       <c r="L127" s="17" t="n"/>
@@ -6871,7 +6871,7 @@
       </c>
       <c r="E128" s="17" t="inlineStr">
         <is>
-          <t>Reservoir Temperature</t>
+          <t>Reservoir Pressure at Time of Completion</t>
         </is>
       </c>
       <c r="F128" s="17" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="G128" s="17" t="inlineStr">
         <is>
-          <t>degF</t>
+          <t>psi</t>
         </is>
       </c>
       <c r="H128" s="17" t="n"/>
@@ -6893,7 +6893,7 @@
       </c>
       <c r="K128" s="17" t="inlineStr">
         <is>
-          <t>Representative in-situ reservoir temperature for the completion interval.</t>
+          <t>Estimated or measured reservoir pressure when the completion was installed.</t>
         </is>
       </c>
       <c r="L128" s="17" t="n"/>
@@ -6920,7 +6920,7 @@
       </c>
       <c r="E129" s="17" t="inlineStr">
         <is>
-          <t>Core Derived Min Rock UCS</t>
+          <t>Reservoir pressure at first sand production</t>
         </is>
       </c>
       <c r="F129" s="17" t="inlineStr">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="K129" s="17" t="inlineStr">
         <is>
-          <t>Minimum laboratory-measured unconfined compressive strength (UCS) from representative core samples.</t>
+          <t>Estimated or measured reservoir pressure when sand production was first observed.</t>
         </is>
       </c>
       <c r="L129" s="17" t="n"/>
@@ -6969,7 +6969,7 @@
       </c>
       <c r="E130" s="17" t="inlineStr">
         <is>
-          <t>Core Derived P50 Rock UCS</t>
+          <t>Reservoir Temperature</t>
         </is>
       </c>
       <c r="F130" s="17" t="inlineStr">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="G130" s="17" t="inlineStr">
         <is>
-          <t>psi</t>
+          <t>degF</t>
         </is>
       </c>
       <c r="H130" s="17" t="n"/>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="K130" s="17" t="inlineStr">
         <is>
-          <t>Median (50th percentile) laboratory-measured UCS of representative core samples.</t>
+          <t>Representative in-situ reservoir temperature for the completion interval.</t>
         </is>
       </c>
       <c r="L130" s="17" t="n"/>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="E131" s="17" t="inlineStr">
         <is>
-          <t>Shale Reactivity CEC</t>
+          <t>Core Derived Min Rock UCS</t>
         </is>
       </c>
       <c r="F131" s="17" t="inlineStr">
@@ -7026,7 +7026,11 @@
           <t>Number</t>
         </is>
       </c>
-      <c r="G131" s="17" t="n"/>
+      <c r="G131" s="17" t="inlineStr">
+        <is>
+          <t>psi</t>
+        </is>
+      </c>
       <c r="H131" s="17" t="n"/>
       <c r="I131" s="17" t="n"/>
       <c r="J131" s="17" t="inlineStr">
@@ -7036,7 +7040,7 @@
       </c>
       <c r="K131" s="17" t="inlineStr">
         <is>
-          <t>Cation exchange capacity (CEC) used as an indicator of clay/shale reactivity, typically reported in meq/100 g.</t>
+          <t>Minimum laboratory-measured unconfined compressive strength (UCS) from representative core samples.</t>
         </is>
       </c>
       <c r="L131" s="17" t="n"/>
@@ -7063,7 +7067,7 @@
       </c>
       <c r="E132" s="17" t="inlineStr">
         <is>
-          <t>Rock compressibility at initial reservoir pressure</t>
+          <t>Core Derived P50 Rock UCS</t>
         </is>
       </c>
       <c r="F132" s="17" t="inlineStr">
@@ -7073,7 +7077,7 @@
       </c>
       <c r="G132" s="17" t="inlineStr">
         <is>
-          <t>microsips</t>
+          <t>psi</t>
         </is>
       </c>
       <c r="H132" s="17" t="n"/>
@@ -7085,7 +7089,7 @@
       </c>
       <c r="K132" s="17" t="inlineStr">
         <is>
-          <t>Rock/pore-volume compressibility evaluated at initial reservoir pressure.</t>
+          <t>Median (50th percentile) laboratory-measured UCS of representative core samples.</t>
         </is>
       </c>
       <c r="L132" s="17" t="n"/>
@@ -7112,7 +7116,7 @@
       </c>
       <c r="E133" s="17" t="inlineStr">
         <is>
-          <t>Rock compressibility at first sand production</t>
+          <t>Shale Reactivity CEC</t>
         </is>
       </c>
       <c r="F133" s="17" t="inlineStr">
@@ -7120,11 +7124,7 @@
           <t>Number</t>
         </is>
       </c>
-      <c r="G133" s="17" t="inlineStr">
-        <is>
-          <t>microsips</t>
-        </is>
-      </c>
+      <c r="G133" s="17" t="n"/>
       <c r="H133" s="17" t="n"/>
       <c r="I133" s="17" t="n"/>
       <c r="J133" s="17" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="K133" s="17" t="inlineStr">
         <is>
-          <t>Rock/pore-volume compressibility evaluated at reservoir pressure corresponding to first observed sand production.</t>
+          <t>Cation exchange capacity (CEC) used as an indicator of clay/shale reactivity, typically reported in meq/100 g.</t>
         </is>
       </c>
       <c r="L133" s="17" t="n"/>
@@ -7161,25 +7161,29 @@
       </c>
       <c r="E134" s="17" t="inlineStr">
         <is>
-          <t>Source of sand sample</t>
+          <t>Rock compressibility at initial reservoir pressure</t>
         </is>
       </c>
       <c r="F134" s="17" t="inlineStr">
         <is>
-          <t>Dropdown Menu</t>
-        </is>
-      </c>
-      <c r="G134" s="17" t="n"/>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G134" s="17" t="inlineStr">
+        <is>
+          <t>microsips</t>
+        </is>
+      </c>
       <c r="H134" s="17" t="n"/>
       <c r="I134" s="17" t="n"/>
       <c r="J134" s="17" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["cores", "bottom-hole sand sample", "surface sample", "analog well"]}}</t>
+          <t>{"Decimal": {"min": 0}}</t>
         </is>
       </c>
       <c r="K134" s="17" t="inlineStr">
         <is>
-          <t>Origin of the sample used for formation-sand characterization, e.g., core, produced sand, sidewall core, or cuttings.</t>
+          <t>Rock/pore-volume compressibility evaluated at initial reservoir pressure.</t>
         </is>
       </c>
       <c r="L134" s="17" t="n"/>
@@ -7206,25 +7210,29 @@
       </c>
       <c r="E135" s="17" t="inlineStr">
         <is>
-          <t>PSD Measurement Method</t>
+          <t>Rock compressibility at first sand production</t>
         </is>
       </c>
       <c r="F135" s="17" t="inlineStr">
         <is>
-          <t>Dropdown Menu</t>
-        </is>
-      </c>
-      <c r="G135" s="17" t="n"/>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G135" s="17" t="inlineStr">
+        <is>
+          <t>microsips</t>
+        </is>
+      </c>
       <c r="H135" s="17" t="n"/>
       <c r="I135" s="17" t="n"/>
       <c r="J135" s="17" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["LPSA", "Sieve"]}}</t>
+          <t>{"Decimal": {"min": 0}}</t>
         </is>
       </c>
       <c r="K135" s="17" t="inlineStr">
         <is>
-          <t>Laboratory or analytical technique used to determine formation-sand particle-size distribution.</t>
+          <t>Rock/pore-volume compressibility evaluated at reservoir pressure corresponding to first observed sand production.</t>
         </is>
       </c>
       <c r="L135" s="17" t="n"/>
@@ -7251,29 +7259,25 @@
       </c>
       <c r="E136" s="17" t="inlineStr">
         <is>
-          <t>PSD D10/D25/D40/D50/D75/D90</t>
+          <t>Source of sand sample</t>
         </is>
       </c>
       <c r="F136" s="17" t="inlineStr">
         <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="G136" s="17" t="inlineStr">
-        <is>
-          <t>micron</t>
-        </is>
-      </c>
+          <t>Dropdown Menu</t>
+        </is>
+      </c>
+      <c r="G136" s="17" t="n"/>
       <c r="H136" s="17" t="n"/>
       <c r="I136" s="17" t="n"/>
       <c r="J136" s="17" t="inlineStr">
         <is>
-          <t>{["Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}]}</t>
+          <t>{"List": {"options": ["cores", "bottom-hole sand sample", "surface sample", "analog well"]}}</t>
         </is>
       </c>
       <c r="K136" s="17" t="inlineStr">
         <is>
-          <t>Particle diameters corresponding to specified cumulative percentiles of the formation-sand size distribution.</t>
+          <t>Origin of the sample used for formation-sand characterization, e.g., core, produced sand, sidewall core, or cuttings.</t>
         </is>
       </c>
       <c r="L136" s="17" t="n"/>
@@ -7300,29 +7304,25 @@
       </c>
       <c r="E137" s="17" t="inlineStr">
         <is>
-          <t>Fines Content (Sub 44 microns)</t>
+          <t>PSD Measurement Method</t>
         </is>
       </c>
       <c r="F137" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="G137" s="17" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
+          <t>Dropdown Menu</t>
+        </is>
+      </c>
+      <c r="G137" s="17" t="n"/>
       <c r="H137" s="17" t="n"/>
       <c r="I137" s="17" t="n"/>
       <c r="J137" s="17" t="inlineStr">
         <is>
-          <t>{"Decimal": {"min": 0}}</t>
+          <t>{"List": {"options": ["LPSA", "Sieve"]}}</t>
         </is>
       </c>
       <c r="K137" s="17" t="inlineStr">
         <is>
-          <t>Fraction of formation particles below the defined fines-size threshold; record the threshold/method where available.</t>
+          <t>Laboratory or analytical technique used to determine formation-sand particle-size distribution.</t>
         </is>
       </c>
       <c r="L137" s="17" t="n"/>
@@ -7349,29 +7349,29 @@
       </c>
       <c r="E138" s="17" t="inlineStr">
         <is>
-          <t>Initial PI</t>
+          <t>PSD D10/D25/D40/D50/D75/D90</t>
         </is>
       </c>
       <c r="F138" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="G138" s="17" t="inlineStr">
         <is>
-          <t>stb/d/psi or mmscf/d/psi</t>
+          <t>micron</t>
         </is>
       </c>
       <c r="H138" s="17" t="n"/>
       <c r="I138" s="17" t="n"/>
       <c r="J138" s="17" t="inlineStr">
         <is>
-          <t>{"Decimal": {"min": 0}}</t>
+          <t>{["Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}]}</t>
         </is>
       </c>
       <c r="K138" s="17" t="inlineStr">
         <is>
-          <t>Initial productivity index attributed to this completion/reservoir interval.</t>
+          <t>Particle diameters corresponding to specified cumulative percentiles of the formation-sand size distribution.</t>
         </is>
       </c>
       <c r="L138" s="17" t="n"/>
@@ -7398,7 +7398,7 @@
       </c>
       <c r="E139" s="17" t="inlineStr">
         <is>
-          <t>Porosity</t>
+          <t>Fines Content (Sub 44 microns)</t>
         </is>
       </c>
       <c r="F139" s="17" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="K139" s="17" t="inlineStr">
         <is>
-          <t>Representative effective or total porosity of the reservoir interval, as specified by the source.</t>
+          <t>Fraction of formation particles below the defined fines-size threshold; record the threshold/method where available.</t>
         </is>
       </c>
       <c r="L139" s="17" t="n"/>
@@ -7447,7 +7447,7 @@
       </c>
       <c r="E140" s="17" t="inlineStr">
         <is>
-          <t>Permeability</t>
+          <t>Initial PI</t>
         </is>
       </c>
       <c r="F140" s="17" t="inlineStr">
@@ -7457,7 +7457,7 @@
       </c>
       <c r="G140" s="17" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>stb/d/psi or mmscf/d/psi</t>
         </is>
       </c>
       <c r="H140" s="17" t="n"/>
@@ -7469,7 +7469,7 @@
       </c>
       <c r="K140" s="17" t="inlineStr">
         <is>
-          <t>Representative formation permeability of the reservoir interval.</t>
+          <t>Initial productivity index attributed to this completion/reservoir interval.</t>
         </is>
       </c>
       <c r="L140" s="17" t="n"/>
@@ -7496,7 +7496,7 @@
       </c>
       <c r="E141" s="17" t="inlineStr">
         <is>
-          <t>k.h from PTA</t>
+          <t>Porosity</t>
         </is>
       </c>
       <c r="F141" s="17" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="G141" s="17" t="inlineStr">
         <is>
-          <t>md-ft</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H141" s="17" t="n"/>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="K141" s="17" t="inlineStr">
         <is>
-          <t>Permeability-thickness product derived from pressure transient analysis (PTA).</t>
+          <t>Representative effective or total porosity of the reservoir interval, as specified by the source.</t>
         </is>
       </c>
       <c r="L141" s="17" t="n"/>
@@ -7545,7 +7545,7 @@
       </c>
       <c r="E142" s="17" t="inlineStr">
         <is>
-          <t>k.h from Log</t>
+          <t>Permeability</t>
         </is>
       </c>
       <c r="F142" s="17" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="G142" s="17" t="inlineStr">
         <is>
-          <t>md-ft</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H142" s="17" t="n"/>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="K142" s="17" t="inlineStr">
         <is>
-          <t>Permeability-thickness product estimated from petrophysical/log interpretation.</t>
+          <t>Representative formation permeability of the reservoir interval.</t>
         </is>
       </c>
       <c r="L142" s="17" t="n"/>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="E143" s="17" t="inlineStr">
         <is>
-          <t>Initial Total Skin from PTA</t>
+          <t>k.h from PTA</t>
         </is>
       </c>
       <c r="F143" s="17" t="inlineStr">
@@ -7602,17 +7602,21 @@
           <t>Number</t>
         </is>
       </c>
-      <c r="G143" s="17" t="n"/>
+      <c r="G143" s="17" t="inlineStr">
+        <is>
+          <t>md-ft</t>
+        </is>
+      </c>
       <c r="H143" s="17" t="n"/>
       <c r="I143" s="17" t="n"/>
       <c r="J143" s="17" t="inlineStr">
         <is>
-          <t>{"Whole number"}</t>
+          <t>{"Decimal": {"min": 0}}</t>
         </is>
       </c>
       <c r="K143" s="17" t="inlineStr">
         <is>
-          <t>Initial total skin factor derived from pressure transient analysis.</t>
+          <t>Permeability-thickness product derived from pressure transient analysis (PTA).</t>
         </is>
       </c>
       <c r="L143" s="17" t="n"/>
@@ -7639,25 +7643,29 @@
       </c>
       <c r="E144" s="17" t="inlineStr">
         <is>
-          <t>Fluid Type</t>
+          <t>k.h from Log</t>
         </is>
       </c>
       <c r="F144" s="17" t="inlineStr">
         <is>
-          <t>Dropdown Menu</t>
-        </is>
-      </c>
-      <c r="G144" s="17" t="n"/>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G144" s="17" t="inlineStr">
+        <is>
+          <t>md-ft</t>
+        </is>
+      </c>
       <c r="H144" s="17" t="n"/>
       <c r="I144" s="17" t="n"/>
       <c r="J144" s="17" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Oil", "Condensate", "Wet Gas", "Dry Gas"]}}</t>
+          <t>{"Decimal": {"min": 0}}</t>
         </is>
       </c>
       <c r="K144" s="17" t="inlineStr">
         <is>
-          <t>Primary reservoir/producing fluid type for the completion interval.</t>
+          <t>Permeability-thickness product estimated from petrophysical/log interpretation.</t>
         </is>
       </c>
       <c r="L144" s="17" t="n"/>
@@ -7684,7 +7692,7 @@
       </c>
       <c r="E145" s="17" t="inlineStr">
         <is>
-          <t>Oil Formation Volume Factor (Bo) at downhole conditions</t>
+          <t>Initial Total Skin from PTA</t>
         </is>
       </c>
       <c r="F145" s="17" t="inlineStr">
@@ -7697,12 +7705,12 @@
       <c r="I145" s="17" t="n"/>
       <c r="J145" s="17" t="inlineStr">
         <is>
-          <t>{"Decimal": {"min": 0}}</t>
+          <t>{"Whole number"}</t>
         </is>
       </c>
       <c r="K145" s="17" t="inlineStr">
         <is>
-          <t>Reservoir oil volume per unit stock-tank oil volume at the specified downhole pressure and temperature.</t>
+          <t>Initial total skin factor derived from pressure transient analysis.</t>
         </is>
       </c>
       <c r="L145" s="17" t="n"/>
@@ -7729,29 +7737,25 @@
       </c>
       <c r="E146" s="17" t="inlineStr">
         <is>
-          <t>Producing Fluid Viscosity</t>
+          <t>Fluid Type</t>
         </is>
       </c>
       <c r="F146" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="G146" s="17" t="inlineStr">
-        <is>
-          <t>cP</t>
-        </is>
-      </c>
+          <t>Dropdown Menu</t>
+        </is>
+      </c>
+      <c r="G146" s="17" t="n"/>
       <c r="H146" s="17" t="n"/>
       <c r="I146" s="17" t="n"/>
       <c r="J146" s="17" t="inlineStr">
         <is>
-          <t>{"Decimal": {"min": 0}}</t>
+          <t>{"List": {"options": ["Oil", "Condensate", "Wet Gas", "Dry Gas"]}}</t>
         </is>
       </c>
       <c r="K146" s="17" t="inlineStr">
         <is>
-          <t>Dynamic viscosity of the primary producing fluid at the specified reservoir/downhole conditions.</t>
+          <t>Primary reservoir/producing fluid type for the completion interval.</t>
         </is>
       </c>
       <c r="L146" s="17" t="n"/>
@@ -7778,7 +7782,7 @@
       </c>
       <c r="E147" s="17" t="inlineStr">
         <is>
-          <t>Oil Bubble Point (Pb)</t>
+          <t>Oil Formation Volume Factor (Bo) at downhole conditions</t>
         </is>
       </c>
       <c r="F147" s="17" t="inlineStr">
@@ -7786,11 +7790,7 @@
           <t>Number</t>
         </is>
       </c>
-      <c r="G147" s="17" t="inlineStr">
-        <is>
-          <t>psi</t>
-        </is>
-      </c>
+      <c r="G147" s="17" t="n"/>
       <c r="H147" s="17" t="n"/>
       <c r="I147" s="17" t="n"/>
       <c r="J147" s="17" t="inlineStr">
@@ -7800,7 +7800,7 @@
       </c>
       <c r="K147" s="17" t="inlineStr">
         <is>
-          <t>Pressure at which the first gas evolves from reservoir oil at the specified reservoir temperature.</t>
+          <t>Reservoir oil volume per unit stock-tank oil volume at the specified downhole pressure and temperature.</t>
         </is>
       </c>
       <c r="L147" s="17" t="n"/>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="E148" s="17" t="inlineStr">
         <is>
-          <t>Solution Gas Ratio (Rs)</t>
+          <t>Producing Fluid Viscosity</t>
         </is>
       </c>
       <c r="F148" s="17" t="inlineStr">
@@ -7837,7 +7837,7 @@
       </c>
       <c r="G148" s="17" t="inlineStr">
         <is>
-          <t>scf/stb</t>
+          <t>cP</t>
         </is>
       </c>
       <c r="H148" s="17" t="n"/>
@@ -7849,7 +7849,7 @@
       </c>
       <c r="K148" s="17" t="inlineStr">
         <is>
-          <t>Volume of gas dissolved in oil at the specified pressure and temperature, typically reported as scf/STB.</t>
+          <t>Dynamic viscosity of the primary producing fluid at the specified reservoir/downhole conditions.</t>
         </is>
       </c>
       <c r="L148" s="17" t="n"/>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="E149" s="17" t="inlineStr">
         <is>
-          <t>Frac gradient</t>
+          <t>Oil Bubble Point (Pb)</t>
         </is>
       </c>
       <c r="F149" s="17" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="G149" s="17" t="inlineStr">
         <is>
-          <t>ppg</t>
+          <t>psi</t>
         </is>
       </c>
       <c r="H149" s="17" t="n"/>
@@ -7898,11 +7898,109 @@
       </c>
       <c r="K149" s="17" t="inlineStr">
         <is>
-          <t>Formation fracture-pressure gradient at the applicable reservoir depth, typically expressed in psi/ft or equivalent units.</t>
+          <t>Pressure at which the first gas evolves from reservoir oil at the specified reservoir temperature.</t>
         </is>
       </c>
       <c r="L149" s="17" t="n"/>
       <c r="M149" s="1" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="24" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="17" t="inlineStr">
+        <is>
+          <t>Sand Body {id}</t>
+        </is>
+      </c>
+      <c r="C150" s="17" t="inlineStr">
+        <is>
+          <t>Reservoir Characterization</t>
+        </is>
+      </c>
+      <c r="D150" s="16" t="inlineStr">
+        <is>
+          <t>Reservoir Rock and Fluid Properties</t>
+        </is>
+      </c>
+      <c r="E150" s="17" t="inlineStr">
+        <is>
+          <t>Solution Gas Ratio (Rs)</t>
+        </is>
+      </c>
+      <c r="F150" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G150" s="17" t="inlineStr">
+        <is>
+          <t>scf/stb</t>
+        </is>
+      </c>
+      <c r="H150" s="17" t="n"/>
+      <c r="I150" s="17" t="n"/>
+      <c r="J150" s="17" t="inlineStr">
+        <is>
+          <t>{"Decimal": {"min": 0}}</t>
+        </is>
+      </c>
+      <c r="K150" s="17" t="inlineStr">
+        <is>
+          <t>Volume of gas dissolved in oil at the specified pressure and temperature, typically reported as scf/STB.</t>
+        </is>
+      </c>
+      <c r="L150" s="17" t="n"/>
+      <c r="M150" s="1" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="24" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="17" t="inlineStr">
+        <is>
+          <t>Sand Body {id}</t>
+        </is>
+      </c>
+      <c r="C151" s="17" t="inlineStr">
+        <is>
+          <t>Reservoir Characterization</t>
+        </is>
+      </c>
+      <c r="D151" s="16" t="inlineStr">
+        <is>
+          <t>Reservoir Rock and Fluid Properties</t>
+        </is>
+      </c>
+      <c r="E151" s="17" t="inlineStr">
+        <is>
+          <t>Frac gradient</t>
+        </is>
+      </c>
+      <c r="F151" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G151" s="17" t="inlineStr">
+        <is>
+          <t>ppg</t>
+        </is>
+      </c>
+      <c r="H151" s="17" t="n"/>
+      <c r="I151" s="17" t="n"/>
+      <c r="J151" s="17" t="inlineStr">
+        <is>
+          <t>{"Decimal": {"min": 0}}</t>
+        </is>
+      </c>
+      <c r="K151" s="17" t="inlineStr">
+        <is>
+          <t>Formation fracture-pressure gradient at the applicable reservoir depth, typically expressed in psi/ft or equivalent units.</t>
+        </is>
+      </c>
+      <c r="L151" s="17" t="n"/>
+      <c r="M151" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/MASTER.xlsx
+++ b/MASTER.xlsx
@@ -555,7 +555,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table22" displayName="Table22" ref="B1:L151" headerRowCount="1" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table22" displayName="Table22" ref="B1:L150" headerRowCount="1" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
   <autoFilter ref="B1:L151"/>
   <tableColumns count="11">
     <tableColumn id="4" name="Scope" dataDxfId="10"/>
@@ -875,7 +875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M151"/>
+  <dimension ref="A1:M150"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="30" defaultRowHeight="14.5"/>
   <cols>
     <col width="6.08984375" customWidth="1" style="1" min="1" max="1"/>
@@ -1214,7 +1214,7 @@
       <c r="H7" s="6" t="n"/>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>{"Oil Producer": {"Severity of sand production - Oil Well"}, "Gas Producer": {"Severity of sand production - Gas Well"}, "Gas Condensate Producer": {"Severity of sand production - Gas Well"}}</t>
+          <t>{'Oil Producer': {'Severity of sand production': True}, 'Gas Producer': {'Severity of sand production': True}, 'Gas Condensate Producer': {'Severity of sand production': True}}</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
@@ -1681,12 +1681,12 @@
         </is>
       </c>
       <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>{"Yes": {"Failure Details &amp; Performance Impact"}}</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>{'Yes': {'Time to first choke back': True, 'Time to well shut-in due to sand': True, 'Time to complete well failure': True, 'How is sand production known?': True, 'Sand failure mechanism': True, 'Did sanding start immediately after water breakthrough': True, 'Sand rate quantification': True, 'Well PI after choke-back': True, 'Total skin after choke-back': True, 'Non-Darcy skin after choke-back': True, 'Mechanical / Completion skin after choke-back': True, 'Lessons learned classification / RCFA outcomes': True, 'Oil Rate @ The First Choke Back': True, 'Oil Rate @ Shut-in': True, 'Gas Rate @ The First Choke Back': True, 'Gas Rate @ Shut-in': True, 'Water Rate @ The First Choke Back': True, 'Water Rate @ Shut-in': True}}</t>
+        </is>
+      </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
           <t>{"List": {"required": True, "options": ["Yes", "No"]}}</t>
@@ -1716,12 +1716,12 @@
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Failure Details &amp; Performance Impact</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Severity of sand production - Oil Well</t>
+          <t>Severity of sand production</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -1734,12 +1734,12 @@
       <c r="I18" s="6" t="n"/>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>{"List": {"required": True, "options": ["Minor (&lt;0.2 lb/1000 bbl)", "Moderate (0.2 to 2 lb/1000 bbl)", "Severe (2 to 10 lb/MMSCF)", "Catastrophic (&gt;10 lb/1000 bbl)"]}}</t>
+          <t>{'List': {'required': True, 'options_by': {'Well type': {'Oil Producer': ['Minor (&lt;0.2 lb/1000 bbl)', 'Moderate (0.2 to 2 lb/1000 bbl)', 'Severe (2 to 10 lb/1000 bbl)', 'Catastrophic (&gt;10 lb/1000 bbl)'], 'Gas Producer': ['Minor (&lt;0.01 lb/MMSCF)', 'Moderate (0.01 to 0.05 lb/MMSCF)', 'Severe (0.05 to 0.2 lb/MMSCF)', 'Catastrophic (&gt;0.2 lb/MMscf)'], 'Gas Condensate Producer': ['Minor (&lt;0.01 lb/MMSCF)', 'Moderate (0.01 to 0.05 lb/MMSCF)', 'Severe (0.05 to 0.2 lb/MMSCF)', 'Catastrophic (&gt;0.2 lb/MMscf)']}}}}</t>
         </is>
       </c>
       <c r="K18" s="8" t="inlineStr">
         <is>
-          <t>Quantitative severity of observed sand production based on rate</t>
+          <t>Severity of observed sand production. Thresholds follow the selected well type.</t>
         </is>
       </c>
       <c r="L18" s="6" t="n"/>
@@ -1761,30 +1761,34 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Failure Details &amp; Performance Impact</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Severity of sand production - Gas Well</t>
+          <t>Time to first choke back</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Dropdown Menu</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="n"/>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>days</t>
+        </is>
+      </c>
       <c r="H19" s="6" t="n"/>
       <c r="I19" s="6" t="n"/>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>{"List": {"required": True, "options": ["Minor (&lt;0.01 lb/MMSCF)", "Moderate (0.01 to 0.05 lb/MMSCF)", "Severe (0.05 to 0.2 lb/MMSCF)", "Catastrophic (&gt;0.2 lb/MMscf)"]}}</t>
-        </is>
-      </c>
-      <c r="K19" s="8" t="inlineStr">
-        <is>
-          <t>Quantitative severity of observed sand production based on rate</t>
+          <t>{"required": True, "Decimal": {"min": 0}}</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>Elapsed production time from first production/startup until the first choke reduction specifically caused by sand production.</t>
         </is>
       </c>
       <c r="L19" s="6" t="n"/>
@@ -1806,12 +1810,12 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>Failure Details &amp; Performance Impact</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Time to first choke back</t>
+          <t>Time to well shut-in due to sand</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -1831,9 +1835,9 @@
           <t>{"required": True, "Decimal": {"min": 0}}</t>
         </is>
       </c>
-      <c r="K20" s="6" t="inlineStr">
-        <is>
-          <t>Elapsed production time from first production/startup until the first choke reduction specifically caused by sand production.</t>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>Elapsed production time until the well was first shut in specifically because of sand production or its consequences.</t>
         </is>
       </c>
       <c r="L20" s="6" t="n"/>
@@ -1855,12 +1859,12 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Failure Details &amp; Performance Impact</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Time to well shut-in due to sand</t>
+          <t>Time to complete well failure</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -1880,9 +1884,9 @@
           <t>{"required": True, "Decimal": {"min": 0}}</t>
         </is>
       </c>
-      <c r="K21" s="8" t="inlineStr">
-        <is>
-          <t>Elapsed production time until the well was first shut in specifically because of sand production or its consequences.</t>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>Elapsed production time until sand-related failure resulted in loss of normal well functionality or production capability.</t>
         </is>
       </c>
       <c r="L21" s="6" t="n"/>
@@ -1904,34 +1908,30 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Failure Details &amp; Performance Impact</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Time to complete well failure</t>
+          <t>How is sand production known?</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>days</t>
-        </is>
-      </c>
+          <t>Dropdown Menu</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="n"/>
       <c r="H22" s="6" t="n"/>
       <c r="I22" s="6" t="n"/>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>{"required": True, "Decimal": {"min": 0}}</t>
+          <t>{"List": {"required": True, "options": ["Surface Solids Samples", "ASD Response", "Surface Equipment Erosion"]}}</t>
         </is>
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t>Elapsed production time until sand-related failure resulted in loss of normal well functionality or production capability.</t>
+          <t>Method or evidence used to confirm sand production, e.g., sand detector, surface sample, erosion, separator accumulation, or well intervention.</t>
         </is>
       </c>
       <c r="L22" s="6" t="n"/>
@@ -1953,12 +1953,12 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Failure Details &amp; Performance Impact</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>How is sand production known?</t>
+          <t>Sand Production &amp; Well Performance</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>Sand failure mechanism</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -1971,12 +1971,12 @@
       <c r="I23" s="6" t="n"/>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>{"List": {"required": True, "options": ["Surface Solids Samples", "ASD Response", "Surface Equipment Erosion"]}}</t>
+          <t>{"List": {"required": True, "options": ["Screen Plugging", "Water Breakthrough", "Flux (excessive perf fluid velocity)", "Incomplete Gravel Pack", "Compaction", "Excessive Drawdown", "Rapid Beanup", "Hard Shut-in", "Well Slugging", "Intervention Induced Damage", "Wrongly Sized Sand Control", "No Sand Control Installed", "Corrosion", "Geomechanical / Compaction", "Geomechanical / Other", "Annular Convergent Flow (for stand alone screens)", "Other", "Unknown"]}}</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>Method or evidence used to confirm sand production, e.g., sand detector, surface sample, erosion, separator accumulation, or well intervention.</t>
+          <t>Identified or inferred physical mechanism responsible for sand production or failure of the sand-control system.</t>
         </is>
       </c>
       <c r="L23" s="6" t="n"/>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>Failure Details &amp; Performance Impact</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Sand failure mechanism</t>
+          <t>Did sanding start immediately after water breakthrough</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -2011,20 +2011,16 @@
           <t>Dropdown Menu</t>
         </is>
       </c>
-      <c r="G24" s="6" t="n"/>
-      <c r="H24" s="6" t="n"/>
-      <c r="I24" s="6" t="n"/>
+      <c r="G24" s="8" t="n"/>
+      <c r="H24" s="8" t="n"/>
+      <c r="I24" s="8" t="n"/>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>{"List": {"required": True, "options": ["Screen Plugging", "Water Breakthrough", "Flux (excessive perf fluid velocity)", "Incomplete Gravel Pack", "Compaction", "Excessive Drawdown", "Rapid Beanup", "Hard Shut-in", "Well Slugging", "Intervention Induced Damage", "Wrongly Sized Sand Control", "No Sand Control Installed", "Corrosion", "Geomechanical / Compaction", "Geomechanical / Other", "Annular Convergent Flow (for stand alone screens)", "Other", "Unknown"]}}</t>
-        </is>
-      </c>
-      <c r="K24" s="6" t="inlineStr">
-        <is>
-          <t>Identified or inferred physical mechanism responsible for sand production or failure of the sand-control system.</t>
-        </is>
-      </c>
-      <c r="L24" s="6" t="n"/>
+          <t>{"List": {"required": False, "options": ["Yes", "No"]}}</t>
+        </is>
+      </c>
+      <c r="K24" s="8" t="n"/>
+      <c r="L24" s="8" t="n"/>
       <c r="M24" s="1" t="n"/>
     </row>
     <row r="25" ht="14" customHeight="1">
@@ -2043,12 +2039,12 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Failure Details &amp; Performance Impact</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>Did sanding start immediately after water breakthrough</t>
+          <t>Sand Production &amp; Well Performance</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>Sand rate quantification</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -2056,16 +2052,24 @@
           <t>Dropdown Menu</t>
         </is>
       </c>
-      <c r="G25" s="8" t="n"/>
-      <c r="H25" s="8" t="n"/>
-      <c r="I25" s="8" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>{"Measurable": {"Sand production rate at first choke back", "Sand production rate at well shut-in due to sand", "Sand production rate at complete well failure"}}</t>
+        </is>
+      </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>{"List": {"required": False, "options": ["Yes", "No"]}}</t>
-        </is>
-      </c>
-      <c r="K25" s="8" t="n"/>
-      <c r="L25" s="8" t="n"/>
+          <t>{"List": {"required": True, "options": ["Measurable", "Unable to quantify", "No sand"]}}</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>Reported sand production rate for the relevant operating condition or observation.</t>
+        </is>
+      </c>
+      <c r="L25" s="6" t="n"/>
       <c r="M25" s="1" t="n"/>
     </row>
     <row r="26" ht="14" customHeight="1">
@@ -2084,34 +2088,34 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Failure Details &amp; Performance Impact</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Sand rate quantification</t>
+          <t>Sand production rate at first choke back</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>Dropdown Menu</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="n"/>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>pptb or lb/mmscf</t>
+        </is>
+      </c>
       <c r="H26" s="6" t="n"/>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>{"Measurable": {"Sand production rate at first choke back", "Sand production rate at well shut-in due to sand", "Sand production rate at complete well failure"}}</t>
-        </is>
-      </c>
+      <c r="I26" s="6" t="n"/>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>{"List": {"required": True, "options": ["Measurable", "Unable to quantify", "No sand"]}}</t>
+          <t>{"Decimal": {"required": False, "min": 0}}</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>Reported sand production rate for the relevant operating condition or observation.</t>
+          <t>Measured or estimated sand production rate when the well was first choked back because of sand.</t>
         </is>
       </c>
       <c r="L26" s="6" t="n"/>
@@ -2133,12 +2137,12 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Failure Details &amp; Performance Impact</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Sand production rate at first choke back</t>
+          <t>Sand production rate at well shut-in due to sand</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -2160,7 +2164,7 @@
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>Measured or estimated sand production rate when the well was first choked back because of sand.</t>
+          <t>Measured or estimated sand production rate when sand caused the well to be shut in.</t>
         </is>
       </c>
       <c r="L27" s="6" t="n"/>
@@ -2182,12 +2186,12 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>Failure Details &amp; Performance Impact</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Sand production rate at well shut-in due to sand</t>
+          <t>Sand production rate at complete well failure</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -2209,7 +2213,7 @@
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>Measured or estimated sand production rate when sand caused the well to be shut in.</t>
+          <t>Measured or estimated sand production rate at the time of complete sand-related well failure.</t>
         </is>
       </c>
       <c r="L28" s="6" t="n"/>
@@ -2231,12 +2235,12 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Failure Details &amp; Performance Impact</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Sand production rate at complete well failure</t>
+          <t>Initial PI</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
@@ -2246,7 +2250,7 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>pptb or lb/mmscf</t>
+          <t>stb/d/psi or mmscf/d/psi</t>
         </is>
       </c>
       <c r="H29" s="6" t="n"/>
@@ -2258,7 +2262,7 @@
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>Measured or estimated sand production rate at the time of complete sand-related well failure.</t>
+          <t>Initial well productivity index measured or estimated before significant sand-related impairment.</t>
         </is>
       </c>
       <c r="L29" s="6" t="n"/>
@@ -2280,12 +2284,12 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Failure Details &amp; Performance Impact</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Initial PI</t>
+          <t>Initial total skin</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -2293,21 +2297,17 @@
           <t>Number</t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>stb/d/psi or mmscf/d/psi</t>
-        </is>
-      </c>
+      <c r="G30" s="6" t="n"/>
       <c r="H30" s="6" t="n"/>
       <c r="I30" s="6" t="n"/>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>{"Decimal": {"required": False, "min": 0}}</t>
+          <t>{"Decimal": {"required": False}}</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>Initial well productivity index measured or estimated before significant sand-related impairment.</t>
+          <t>Initial total well skin factor, including applicable mechanical, completion, damage, and flow effects.</t>
         </is>
       </c>
       <c r="L30" s="6" t="n"/>
@@ -2329,12 +2329,12 @@
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Failure Details &amp; Performance Impact</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>Initial total skin</t>
+          <t>Initial non-Darcy skin</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>Initial total well skin factor, including applicable mechanical, completion, damage, and flow effects.</t>
+          <t>Initial rate-dependent skin component associated with non-Darcy/turbulent flow effects.</t>
         </is>
       </c>
       <c r="L31" s="6" t="n"/>
@@ -2374,12 +2374,12 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>Failure Details &amp; Performance Impact</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Initial non-Darcy skin</t>
+          <t>Initial Mechanical / Completion skin</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>Initial rate-dependent skin component associated with non-Darcy/turbulent flow effects.</t>
+          <t>Initial skin contribution associated with well deviation or trajectory geometry.</t>
         </is>
       </c>
       <c r="L32" s="6" t="n"/>
@@ -2419,12 +2419,12 @@
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Failure Details &amp; Performance Impact</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Initial Mechanical / Completion skin</t>
+          <t>Well PI after choke-back</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
@@ -2432,17 +2432,21 @@
           <t>Number</t>
         </is>
       </c>
-      <c r="G33" s="6" t="n"/>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>stb/d/psi or mmscf/d/psi</t>
+        </is>
+      </c>
       <c r="H33" s="6" t="n"/>
       <c r="I33" s="6" t="n"/>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>{"Decimal": {"required": False}}</t>
+          <t>{"Decimal": {"required": False, "min": 0}}</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>Initial skin contribution associated with well deviation or trajectory geometry.</t>
+          <t>Productivity index measured or estimated after the sand-related choke-back.</t>
         </is>
       </c>
       <c r="L33" s="6" t="n"/>
@@ -2464,12 +2468,12 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Failure Details &amp; Performance Impact</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Well PI after choke-back</t>
+          <t>Total skin after choke-back</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
@@ -2477,21 +2481,17 @@
           <t>Number</t>
         </is>
       </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>stb/d/psi or mmscf/d/psi</t>
-        </is>
-      </c>
+      <c r="G34" s="6" t="n"/>
       <c r="H34" s="6" t="n"/>
       <c r="I34" s="6" t="n"/>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>{"Decimal": {"required": False, "min": 0}}</t>
+          <t>{"Decimal": {"required": False}}</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>Productivity index measured or estimated after the sand-related choke-back.</t>
+          <t>Total well skin factor measured or estimated after the sand-related choke-back.</t>
         </is>
       </c>
       <c r="L34" s="6" t="n"/>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Failure Details &amp; Performance Impact</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>Total skin after choke-back</t>
+          <t>Non-Darcy skin after choke-back</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>Total well skin factor measured or estimated after the sand-related choke-back.</t>
+          <t>Rate-dependent non-Darcy skin measured or estimated after the sand-related choke-back.</t>
         </is>
       </c>
       <c r="L35" s="6" t="n"/>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>Failure Details &amp; Performance Impact</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Non-Darcy skin after choke-back</t>
+          <t>Mechanical / Completion skin after choke-back</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t>Rate-dependent non-Darcy skin measured or estimated after the sand-related choke-back.</t>
+          <t>Well-deviation-related skin measured or estimated after the sand-related choke-back.</t>
         </is>
       </c>
       <c r="L36" s="6" t="n"/>
@@ -2603,17 +2603,17 @@
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Failure Details &amp; Performance Impact</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Mechanical / Completion skin after choke-back</t>
+          <t>Lessons learned classification / RCFA outcomes</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="G37" s="6" t="n"/>
@@ -2621,12 +2621,12 @@
       <c r="I37" s="6" t="n"/>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>{"Decimal": {"required": False}}</t>
+          <t>{"Text": {"required": False}}</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>Well-deviation-related skin measured or estimated after the sand-related choke-back.</t>
+          <t>Key findings, root causes, corrective actions, and lessons identified from post-failure review or root-cause failure analysis.</t>
         </is>
       </c>
       <c r="L37" s="6" t="n"/>
@@ -2646,19 +2646,19 @@
           <t>Well Specific</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>Failure Details &amp; Performance Impact</t>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Lessons learned classification / RCFA outcomes</t>
+          <t>Current well status</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Dropdown Menu</t>
         </is>
       </c>
       <c r="G38" s="6" t="n"/>
@@ -2666,12 +2666,12 @@
       <c r="I38" s="6" t="n"/>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>{"Text": {"required": False}}</t>
+          <t>{"List": {"required": False, "options": ["Flowing Unrestricted by Sand", "Flowing Restricted by Sand", "Shut-in Due to Sand", "Shut in due to reasons other than sand", "Not Producing"]}}</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
-          <t>Key findings, root causes, corrective actions, and lessons identified from post-failure review or root-cause failure analysis.</t>
+          <t>Most recently reported operational status of the well, e.g., producing, shut-in, suspended, abandoned, or failed.</t>
         </is>
       </c>
       <c r="L38" s="6" t="n"/>
@@ -2693,17 +2693,17 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Production Performance History</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Current well status</t>
+          <t>Well start-up date</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>Dropdown Menu</t>
+          <t>Short Date</t>
         </is>
       </c>
       <c r="G39" s="6" t="n"/>
@@ -2711,12 +2711,12 @@
       <c r="I39" s="6" t="n"/>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>{"List": {"required": False, "options": ["Flowing Unrestricted by Sand", "Flowing Restricted by Sand", "Shut-in Due to Sand", "Shut in due to reasons other than sand", "Not Producing"]}}</t>
+          <t>{"Short Date": {"required": False}}</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>Most recently reported operational status of the well, e.g., producing, shut-in, suspended, abandoned, or failed.</t>
+          <t>Date on which well startup/cleanup operations began following completion.</t>
         </is>
       </c>
       <c r="L39" s="6" t="n"/>
@@ -2738,12 +2738,12 @@
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Production Performance History</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Well start-up date</t>
+          <t>First production date</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="K40" s="6" t="inlineStr">
         <is>
-          <t>Date on which well startup/cleanup operations began following completion.</t>
+          <t>Date of first recorded hydrocarbon production from the completed well.</t>
         </is>
       </c>
       <c r="L40" s="6" t="n"/>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Production Performance History</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>First production date</t>
+          <t>Last production date</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>Date of first recorded hydrocarbon production from the completed well.</t>
+          <t>Most recent or final date on which production was recorded.</t>
         </is>
       </c>
       <c r="L41" s="6" t="n"/>
@@ -2828,30 +2828,34 @@
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Production Performance History</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Last production date</t>
+          <t>Oil Rate @ The First Choke Back</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>Short Date</t>
-        </is>
-      </c>
-      <c r="G42" s="6" t="n"/>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>stb/d</t>
+        </is>
+      </c>
       <c r="H42" s="6" t="n"/>
       <c r="I42" s="6" t="n"/>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>{"Short Date": {"required": False}}</t>
+          <t>{"Decimal": {"required": False, "min": 0}}</t>
         </is>
       </c>
       <c r="K42" s="6" t="inlineStr">
         <is>
-          <t>Most recent or final date on which production was recorded.</t>
+          <t>Oil production rate immediately before or at the first sand-related choke-back.</t>
         </is>
       </c>
       <c r="L42" s="6" t="n"/>
@@ -2873,12 +2877,12 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Production Performance History</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Oil Rate @ The First Choke Back</t>
+          <t>Oil Rate @ Shut-in</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -2900,7 +2904,7 @@
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>Oil production rate immediately before or at the first sand-related choke-back.</t>
+          <t>Oil production rate immediately before the sand-related well shut-in.</t>
         </is>
       </c>
       <c r="L43" s="6" t="n"/>
@@ -2922,12 +2926,12 @@
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Production Performance History</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Oil Rate @ Shut-in</t>
+          <t>Gas Rate @ The First Choke Back</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -2937,7 +2941,7 @@
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>stb/d</t>
+          <t>mmscf/d</t>
         </is>
       </c>
       <c r="H44" s="6" t="n"/>
@@ -2949,7 +2953,7 @@
       </c>
       <c r="K44" s="6" t="inlineStr">
         <is>
-          <t>Oil production rate immediately before the sand-related well shut-in.</t>
+          <t>Gas production rate immediately before or at the first sand-related choke-back.</t>
         </is>
       </c>
       <c r="L44" s="6" t="n"/>
@@ -2971,12 +2975,12 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Production Performance History</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Gas Rate @ The First Choke Back</t>
+          <t>Gas Rate @ Shut-in</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
@@ -2998,7 +3002,7 @@
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>Gas production rate immediately before or at the first sand-related choke-back.</t>
+          <t>Gas production rate immediately before the sand-related well shut-in.</t>
         </is>
       </c>
       <c r="L45" s="6" t="n"/>
@@ -3020,12 +3024,12 @@
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Production Performance History</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Gas Rate @ Shut-in</t>
+          <t>Water Rate @ The First Choke Back</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
@@ -3035,7 +3039,7 @@
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>mmscf/d</t>
+          <t>stb/d</t>
         </is>
       </c>
       <c r="H46" s="6" t="n"/>
@@ -3047,7 +3051,7 @@
       </c>
       <c r="K46" s="6" t="inlineStr">
         <is>
-          <t>Gas production rate immediately before the sand-related well shut-in.</t>
+          <t>Water production rate immediately before or at the first sand-related choke-back.</t>
         </is>
       </c>
       <c r="L46" s="6" t="n"/>
@@ -3069,12 +3073,12 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Production Performance History</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Water Rate @ The First Choke Back</t>
+          <t>Water Rate @ Shut-in</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
@@ -3096,7 +3100,7 @@
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>Water production rate immediately before or at the first sand-related choke-back.</t>
+          <t>Water production rate immediately before the sand-related well shut-in.</t>
         </is>
       </c>
       <c r="L47" s="6" t="n"/>
@@ -3118,12 +3122,12 @@
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Production Performance History</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Water Rate @ Shut-in</t>
+          <t>Peak oil rate</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
@@ -3140,12 +3144,12 @@
       <c r="I48" s="6" t="n"/>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>{"Decimal": {"required": False, "min": 0}}</t>
+          <t>{"Decimal": {"required": True, "min": 0}}</t>
         </is>
       </c>
       <c r="K48" s="6" t="inlineStr">
         <is>
-          <t>Water production rate immediately before the sand-related well shut-in.</t>
+          <t>Maximum recorded oil production rate during the evaluated well life.</t>
         </is>
       </c>
       <c r="L48" s="6" t="n"/>
@@ -3167,12 +3171,12 @@
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Production Performance History</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Peak oil rate</t>
+          <t>Peak gas rate</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
@@ -3182,7 +3186,7 @@
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>stb/d</t>
+          <t>mmscf/d</t>
         </is>
       </c>
       <c r="H49" s="6" t="n"/>
@@ -3194,7 +3198,7 @@
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>Maximum recorded oil production rate during the evaluated well life.</t>
+          <t>Maximum recorded gas production rate during the evaluated well life.</t>
         </is>
       </c>
       <c r="L49" s="6" t="n"/>
@@ -3216,12 +3220,12 @@
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Production Performance History</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Peak gas rate</t>
+          <t>Peak water rate</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
@@ -3231,7 +3235,7 @@
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>mmscf/d</t>
+          <t>stb/d</t>
         </is>
       </c>
       <c r="H50" s="6" t="n"/>
@@ -3243,7 +3247,7 @@
       </c>
       <c r="K50" s="6" t="inlineStr">
         <is>
-          <t>Maximum recorded gas production rate during the evaluated well life.</t>
+          <t>Maximum recorded water production rate during the evaluated well life.</t>
         </is>
       </c>
       <c r="L50" s="6" t="n"/>
@@ -3265,12 +3269,12 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>Production Performance History</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Peak water rate</t>
+          <t>Peak water cut</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
@@ -3280,7 +3284,7 @@
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>stb/d</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H51" s="6" t="n"/>
@@ -3292,7 +3296,7 @@
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>Maximum recorded water production rate during the evaluated well life.</t>
+          <t>Maximum recorded produced-water fraction of total liquid production.</t>
         </is>
       </c>
       <c r="L51" s="6" t="n"/>
@@ -3314,34 +3318,30 @@
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Production Performance History</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Peak water cut</t>
+          <t>Known sand face production chemistry issues</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="n"/>
       <c r="H52" s="6" t="n"/>
       <c r="I52" s="6" t="n"/>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>{"Decimal": {"required": True, "min": 0}}</t>
+          <t>{"Text": {"required": False}}</t>
         </is>
       </c>
       <c r="K52" s="6" t="inlineStr">
         <is>
-          <t>Maximum recorded produced-water fraction of total liquid production.</t>
+          <t>Known scale, precipitation, emulsion, fines, clay, asphaltene, or other chemical issues affecting the sandface/completion.</t>
         </is>
       </c>
       <c r="L52" s="6" t="n"/>
@@ -3363,30 +3363,34 @@
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>Production Performance History</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Known sand face production chemistry issues</t>
+          <t>Max drawdown over well life</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="n"/>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>psi</t>
+        </is>
+      </c>
       <c r="H53" s="6" t="n"/>
       <c r="I53" s="6" t="n"/>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>{"Text": {"required": False}}</t>
+          <t>{"Decimal": {"required": False, "min": 0}}</t>
         </is>
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>Known scale, precipitation, emulsion, fines, clay, asphaltene, or other chemical issues affecting the sandface/completion.</t>
+          <t>Maximum difference between reservoir pressure and flowing bottomhole pressure experienced during the well life.</t>
         </is>
       </c>
       <c r="L53" s="6" t="n"/>
@@ -3408,12 +3412,12 @@
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Production Performance History</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Max drawdown over well life</t>
+          <t>P50 drawdown over well life</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
@@ -3435,7 +3439,7 @@
       </c>
       <c r="K54" s="6" t="inlineStr">
         <is>
-          <t>Maximum difference between reservoir pressure and flowing bottomhole pressure experienced during the well life.</t>
+          <t>Median (50th percentile) pressure drawdown experienced during the evaluated well life.</t>
         </is>
       </c>
       <c r="L54" s="6" t="n"/>
@@ -3457,34 +3461,30 @@
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>Production Performance History</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>P50 drawdown over well life</t>
+          <t>Typical post-shut-in bean-up strategy</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>psi</t>
-        </is>
-      </c>
+          <t>Dropdown Menu</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="n"/>
       <c r="H55" s="6" t="n"/>
       <c r="I55" s="6" t="n"/>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>{"Decimal": {"required": False, "min": 0}}</t>
+          <t>{"List": {"required": False, "options": ["Gradual (≤ 0.01 in/hr average increase in choke diameter)", "Aggressive (&gt; 0.01 in/hr, or a single increase ≥ 0.05 in within 1 hr)", "Mixed (Both gradual and aggressive behavior occur during the evaluated period)", "Unknown (Insufficient choke-size/time data)", "Not applicable (No meaningful choke-management period exists)"]}}</t>
         </is>
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>Median (50th percentile) pressure drawdown experienced during the evaluated well life.</t>
+          <t>Typical rate and pattern of choke opening used when returning the well to production after a shut-in.</t>
         </is>
       </c>
       <c r="L55" s="6" t="n"/>
@@ -3506,12 +3506,12 @@
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Production Performance History</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>Typical post-shut-in bean-up strategy</t>
+          <t>Post shut-in oil/gas production rate response</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
@@ -3524,12 +3524,12 @@
       <c r="I56" s="6" t="n"/>
       <c r="J56" s="6" t="inlineStr">
         <is>
-          <t>{"List": {"required": False, "options": ["Gradual (≤ 0.01 in/hr average increase in choke diameter)", "Aggressive (&gt; 0.01 in/hr, or a single increase ≥ 0.05 in within 1 hr)", "Mixed (Both gradual and aggressive behavior occur during the evaluated period)", "Unknown (Insufficient choke-size/time data)", "Not applicable (No meaningful choke-management period exists)"]}}</t>
+          <t>{"List": {"required": False, "options": ["Same", "Increased", "Decreased", "Variable", "Unknown", "Not applicable"]}}</t>
         </is>
       </c>
       <c r="K56" s="6" t="inlineStr">
         <is>
-          <t>Typical rate and pattern of choke opening used when returning the well to production after a shut-in.</t>
+          <t>Observed hydrocarbon-rate behavior after restarting the well following a shut-in.</t>
         </is>
       </c>
       <c r="L56" s="6" t="n"/>
@@ -3551,12 +3551,12 @@
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>Production Performance History</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>Post shut-in oil/gas production rate response</t>
+          <t>Post-shut-in water-cut response</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>Observed hydrocarbon-rate behavior after restarting the well following a shut-in.</t>
+          <t>Observed change in water cut after restarting the well following a shut-in.</t>
         </is>
       </c>
       <c r="L57" s="6" t="n"/>
@@ -3596,12 +3596,12 @@
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Production Performance History</t>
+          <t>Sand Production &amp; Well Performance</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>Post-shut-in water-cut response</t>
+          <t>Post-shut-in sand response</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
@@ -3619,100 +3619,104 @@
       </c>
       <c r="K58" s="6" t="inlineStr">
         <is>
-          <t>Observed change in water cut after restarting the well following a shut-in.</t>
+          <t>Observed sand-production behavior after restarting the well following a shut-in.</t>
         </is>
       </c>
       <c r="L58" s="6" t="n"/>
       <c r="M58" s="1" t="n"/>
     </row>
     <row r="59" ht="14" customHeight="1">
-      <c r="A59" s="25" t="n">
+      <c r="A59" s="27" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="6" t="inlineStr">
+      <c r="B59" s="12" t="inlineStr">
         <is>
           <t>Well</t>
         </is>
       </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>Well Specific</t>
-        </is>
-      </c>
-      <c r="D59" s="8" t="inlineStr">
-        <is>
-          <t>Production Performance History</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>Post-shut-in sand response</t>
-        </is>
-      </c>
-      <c r="F59" s="6" t="inlineStr">
-        <is>
-          <t>Dropdown Menu</t>
-        </is>
-      </c>
-      <c r="G59" s="6" t="n"/>
-      <c r="H59" s="6" t="n"/>
-      <c r="I59" s="6" t="n"/>
-      <c r="J59" s="6" t="inlineStr">
-        <is>
-          <t>{"List": {"required": False, "options": ["Same", "Increased", "Decreased", "Variable", "Unknown", "Not applicable"]}}</t>
-        </is>
-      </c>
-      <c r="K59" s="6" t="inlineStr">
-        <is>
-          <t>Observed sand-production behavior after restarting the well following a shut-in.</t>
-        </is>
-      </c>
-      <c r="L59" s="6" t="n"/>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>Completion Intervals</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>Completion Intervals</t>
+        </is>
+      </c>
+      <c r="E59" s="12" t="inlineStr">
+        <is>
+          <t>Number of Completion Intervals</t>
+        </is>
+      </c>
+      <c r="F59" s="12" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G59" s="12" t="n"/>
+      <c r="H59" s="12" t="n"/>
+      <c r="I59" s="12" t="n"/>
+      <c r="J59" s="12" t="inlineStr">
+        <is>
+          <t>{"Whole number": {"min": 1, "max": 10}}</t>
+        </is>
+      </c>
+      <c r="K59" s="11" t="inlineStr">
+        <is>
+          <t>Number of distinct reservoir/completion intervals represented within the well.</t>
+        </is>
+      </c>
+      <c r="L59" s="11" t="n"/>
       <c r="M59" s="1" t="n"/>
     </row>
     <row r="60" ht="14" customHeight="1">
-      <c r="A60" s="27" t="n">
+      <c r="A60" s="26" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="12" t="inlineStr">
-        <is>
-          <t>Well</t>
-        </is>
-      </c>
-      <c r="C60" s="12" t="inlineStr">
-        <is>
-          <t>Completion Intervals</t>
-        </is>
-      </c>
-      <c r="D60" s="12" t="inlineStr">
-        <is>
-          <t>Completion Intervals</t>
-        </is>
-      </c>
-      <c r="E60" s="12" t="inlineStr">
-        <is>
-          <t>Number of Completion Intervals</t>
-        </is>
-      </c>
-      <c r="F60" s="12" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="G60" s="12" t="n"/>
-      <c r="H60" s="12" t="n"/>
-      <c r="I60" s="12" t="n"/>
-      <c r="J60" s="12" t="inlineStr">
-        <is>
-          <t>{"Whole number": {"min": 1, "max": 10}}</t>
-        </is>
-      </c>
-      <c r="K60" s="11" t="inlineStr">
-        <is>
-          <t>Number of distinct reservoir/completion intervals represented within the well.</t>
-        </is>
-      </c>
-      <c r="L60" s="11" t="n"/>
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t>Completion Interval {id}</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>Wellbore</t>
+        </is>
+      </c>
+      <c r="D60" s="13" t="inlineStr">
+        <is>
+          <t>Wellbore properties</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>Well Deviation</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>degrees</t>
+        </is>
+      </c>
+      <c r="H60" s="7" t="n"/>
+      <c r="I60" s="7" t="n"/>
+      <c r="J60" s="7" t="inlineStr">
+        <is>
+          <t>{"Decimal": {"min": 0, "max": 90}}</t>
+        </is>
+      </c>
+      <c r="K60" s="7" t="inlineStr">
+        <is>
+          <t>Angle of the wellbore from vertical at this completion interval (0 degrees is vertical; 90 degrees is horizontal).</t>
+        </is>
+      </c>
+      <c r="L60" s="7" t="n"/>
       <c r="M60" s="1" t="n"/>
     </row>
     <row r="61" ht="14" customHeight="1">
@@ -3726,39 +3730,43 @@
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>Wellbore</t>
-        </is>
-      </c>
-      <c r="D61" s="13" t="inlineStr">
-        <is>
-          <t>Wellbore properties</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>Well Deviation</t>
+          <t>Completion</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>Completion Details</t>
+        </is>
+      </c>
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t>Completion Type</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="G61" s="7" t="inlineStr">
-        <is>
-          <t>degrees</t>
-        </is>
-      </c>
-      <c r="H61" s="7" t="n"/>
-      <c r="I61" s="7" t="n"/>
+          <t>Dropdown Menu</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="n"/>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>{"Open Hole": {"Open Hole Details", "OH Drilling Details"}, "Cased Hole": {"Cased Hole Details"}}</t>
+        </is>
+      </c>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>{"Open Hole": {"OH Sand Control Selected Method", "Screen RIH Fluid Type in Open-Hole"}, "Cased Hole": {"CH Sand Control Selected Method", "Proppant / Unit Length", "Net Pressure Gain"}}</t>
+        </is>
+      </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>{"Decimal": {"min": 0, "max": 90}}</t>
-        </is>
-      </c>
-      <c r="K61" s="7" t="inlineStr">
-        <is>
-          <t>Angle of the wellbore from vertical at this completion interval (0 degrees is vertical; 90 degrees is horizontal).</t>
+          <t>{"List": {"options": ["Open Hole", "Cased Hole"]}}</t>
+        </is>
+      </c>
+      <c r="K61" s="9" t="inlineStr">
+        <is>
+          <t>Primary completion configuration used across the production interval</t>
         </is>
       </c>
       <c r="L61" s="7" t="n"/>
@@ -3783,35 +3791,27 @@
           <t>Completion Details</t>
         </is>
       </c>
-      <c r="E62" s="9" t="inlineStr">
-        <is>
-          <t>Completion Type</t>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>Sandface Completion Date</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>Dropdown Menu</t>
+          <t>Short Date</t>
         </is>
       </c>
       <c r="G62" s="7" t="n"/>
-      <c r="H62" s="7" t="inlineStr">
-        <is>
-          <t>{"Open Hole": {"Open Hole Details", "OH Drilling Details"}, "Cased Hole": {"Cased Hole Details"}}</t>
-        </is>
-      </c>
-      <c r="I62" s="7" t="inlineStr">
-        <is>
-          <t>{"Open Hole": {"OH Sand Control Selected Method", "Screen RIH Fluid Type in Open-Hole"}, "Cased Hole": {"CH Sand Control Selected Method", "Proppant / Unit Length", "Net Pressure Gain"}}</t>
-        </is>
-      </c>
+      <c r="H62" s="7" t="n"/>
+      <c r="I62" s="7" t="n"/>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Open Hole", "Cased Hole"]}}</t>
-        </is>
-      </c>
-      <c r="K62" s="9" t="inlineStr">
-        <is>
-          <t>Primary completion configuration used across the production interval</t>
+          <t>{"Short Date"}</t>
+        </is>
+      </c>
+      <c r="K62" s="7" t="inlineStr">
+        <is>
+          <t>Date the reservoir-facing/sandface completion was installed or completed.</t>
         </is>
       </c>
       <c r="L62" s="7" t="n"/>
@@ -3833,30 +3833,34 @@
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Completion Details</t>
+          <t>Open Hole Details</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>Sandface Completion Date</t>
+          <t>Casing Size above OH</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>Short Date</t>
-        </is>
-      </c>
-      <c r="G63" s="7" t="n"/>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>inch</t>
+        </is>
+      </c>
       <c r="H63" s="7" t="n"/>
       <c r="I63" s="7" t="n"/>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>{"Short Date"}</t>
+          <t>{"Decimal": {"min": 0}}</t>
         </is>
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>Date the reservoir-facing/sandface completion was installed or completed.</t>
+          <t>Nominal diameter of the final casing or liner string set immediately above the open-hole completion interval.</t>
         </is>
       </c>
       <c r="L63" s="7" t="n"/>
@@ -3883,7 +3887,7 @@
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>Casing Size above OH</t>
+          <t>Hole Size</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
@@ -3905,7 +3909,7 @@
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
-          <t>Nominal diameter of the final casing or liner string set immediately above the open-hole completion interval.</t>
+          <t>Nominal or measured open-hole diameter across the completed reservoir interval.</t>
         </is>
       </c>
       <c r="L64" s="7" t="n"/>
@@ -3932,7 +3936,7 @@
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>Hole Size</t>
+          <t>Gross Open Hole Length</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
@@ -3942,7 +3946,7 @@
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>inch</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="H65" s="7" t="n"/>
@@ -3952,9 +3956,9 @@
           <t>{"Decimal": {"min": 0}}</t>
         </is>
       </c>
-      <c r="K65" s="7" t="inlineStr">
-        <is>
-          <t>Nominal or measured open-hole diameter across the completed reservoir interval.</t>
+      <c r="K65" s="9" t="inlineStr">
+        <is>
+          <t>Total along-hole length of the open-hole completion interval, including non-pay sections.</t>
         </is>
       </c>
       <c r="L65" s="7" t="n"/>
@@ -3981,7 +3985,7 @@
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>Gross Open Hole Length</t>
+          <t>Net Pay Length</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
@@ -4001,9 +4005,9 @@
           <t>{"Decimal": {"min": 0}}</t>
         </is>
       </c>
-      <c r="K66" s="9" t="inlineStr">
-        <is>
-          <t>Total along-hole length of the open-hole completion interval, including non-pay sections.</t>
+      <c r="K66" s="7" t="inlineStr">
+        <is>
+          <t>Total reservoir interval considered productive/net pay within the completed section.</t>
         </is>
       </c>
       <c r="L66" s="7" t="n"/>
@@ -4030,29 +4034,25 @@
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>Net Pay Length</t>
+          <t>Filter cake breaker placement</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="G67" s="7" t="inlineStr">
-        <is>
-          <t>ft</t>
-        </is>
-      </c>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="n"/>
       <c r="H67" s="7" t="n"/>
       <c r="I67" s="7" t="n"/>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>{"Decimal": {"min": 0}}</t>
+          <t>{"List": {"options": ["Used", "Not used"]}}</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>Total reservoir interval considered productive/net pay within the completed section.</t>
+          <t>Specify whether the breaker treatment was placed to remove drilling-fluid filter cake from the open-hole interval.</t>
         </is>
       </c>
       <c r="L67" s="7" t="n"/>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>Filter cake breaker placement</t>
+          <t>Open Hole Packers deployed</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
@@ -4092,14 +4092,10 @@
       <c r="I68" s="7" t="n"/>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Used", "Not used"]}}</t>
-        </is>
-      </c>
-      <c r="K68" s="7" t="inlineStr">
-        <is>
-          <t>Specify whether the breaker treatment was placed to remove drilling-fluid filter cake from the open-hole interval.</t>
-        </is>
-      </c>
+          <t>{"List": {"options": ["Yes", "No"]}}</t>
+        </is>
+      </c>
+      <c r="K68" s="7" t="n"/>
       <c r="L68" s="7" t="n"/>
       <c r="M68" s="1" t="n"/>
     </row>
@@ -4119,17 +4115,17 @@
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Open Hole Details</t>
+          <t>OH Drilling Details</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>Open Hole Packers deployed</t>
+          <t>Drill Bit Size</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="G69" s="7" t="n"/>
@@ -4137,10 +4133,14 @@
       <c r="I69" s="7" t="n"/>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Yes", "No"]}}</t>
-        </is>
-      </c>
-      <c r="K69" s="7" t="n"/>
+          <t>{"Decimal": {"min": 0}}</t>
+        </is>
+      </c>
+      <c r="K69" s="7" t="inlineStr">
+        <is>
+          <t>Nominal drill-bit diameter used to drill the reservoir/production interval.</t>
+        </is>
+      </c>
       <c r="L69" s="7" t="n"/>
       <c r="M69" s="1" t="n"/>
     </row>
@@ -4158,19 +4158,19 @@
           <t>Completion</t>
         </is>
       </c>
-      <c r="D70" s="7" t="inlineStr">
+      <c r="D70" s="9" t="inlineStr">
         <is>
           <t>OH Drilling Details</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>Drill Bit Size</t>
+          <t>Reservoir Drilling Fluid Type</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Dropdown Menu</t>
         </is>
       </c>
       <c r="G70" s="7" t="n"/>
@@ -4178,12 +4178,12 @@
       <c r="I70" s="7" t="n"/>
       <c r="J70" s="7" t="inlineStr">
         <is>
-          <t>{"Decimal": {"min": 0}}</t>
+          <t>{"List": {"options": ["OBM", "WBM", "OBM Acid Soluble", "WBM Acid Soluble"]}}</t>
         </is>
       </c>
       <c r="K70" s="7" t="inlineStr">
         <is>
-          <t>Nominal drill-bit diameter used to drill the reservoir/production interval.</t>
+          <t>Type of drilling fluid used while drilling through the reservoir interval.</t>
         </is>
       </c>
       <c r="L70" s="7" t="n"/>
@@ -4210,25 +4210,29 @@
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>Reservoir Drilling Fluid Type</t>
+          <t>Reservoir Drilling Fluid Density</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>Dropdown Menu</t>
-        </is>
-      </c>
-      <c r="G71" s="7" t="n"/>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>ppg</t>
+        </is>
+      </c>
       <c r="H71" s="7" t="n"/>
       <c r="I71" s="7" t="n"/>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["OBM", "WBM", "OBM Acid Soluble", "WBM Acid Soluble"]}}</t>
+          <t>{"Decimal": {"min": 0}}</t>
         </is>
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>Type of drilling fluid used while drilling through the reservoir interval.</t>
+          <t>Density/mud weight of the drilling fluid used across the reservoir interval.</t>
         </is>
       </c>
       <c r="L71" s="7" t="n"/>
@@ -4255,29 +4259,25 @@
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>Reservoir Drilling Fluid Density</t>
+          <t>Weighting Agent</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="G72" s="7" t="inlineStr">
-        <is>
-          <t>ppg</t>
-        </is>
-      </c>
+          <t>Dropdown Menu</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="n"/>
       <c r="H72" s="7" t="n"/>
       <c r="I72" s="7" t="n"/>
       <c r="J72" s="7" t="inlineStr">
         <is>
-          <t>{"Decimal": {"min": 0}}</t>
+          <t>{"List": {"options": ["API Barite", "UFG Barite", "Calcium Carbonate", "Hematite", "Other", "None"]}}</t>
         </is>
       </c>
       <c r="K72" s="7" t="inlineStr">
         <is>
-          <t>Density/mud weight of the drilling fluid used across the reservoir interval.</t>
+          <t>Primary solid material used to increase drilling-fluid density, e.g., API barite, UFG barite, CaCO₃, or hematite.</t>
         </is>
       </c>
       <c r="L72" s="7" t="n"/>
@@ -4304,7 +4304,7 @@
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>Weighting Agent</t>
+          <t>Additional Bridging Agent</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
@@ -4317,12 +4317,12 @@
       <c r="I73" s="7" t="n"/>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["API Barite", "UFG Barite", "Calcium Carbonate", "Hematite", "Other", "None"]}}</t>
+          <t>{"List": {"options": ["CaCO3", "Other", "None"]}}</t>
         </is>
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>Primary solid material used to increase drilling-fluid density, e.g., API barite, UFG barite, CaCO₃, or hematite.</t>
+          <t>Additional particulate material used to bridge pore throats/fractures and control reservoir-fluid invasion.</t>
         </is>
       </c>
       <c r="L73" s="7" t="n"/>
@@ -4349,25 +4349,29 @@
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>Additional Bridging Agent</t>
+          <t>Weighting Agent Loading</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>Dropdown Menu</t>
-        </is>
-      </c>
-      <c r="G74" s="7" t="n"/>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>lb/bbl</t>
+        </is>
+      </c>
       <c r="H74" s="7" t="n"/>
       <c r="I74" s="7" t="n"/>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["CaCO3", "Other", "None"]}}</t>
+          <t>{"Decimal": {"min": 0}}</t>
         </is>
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>Additional particulate material used to bridge pore throats/fractures and control reservoir-fluid invasion.</t>
+          <t>Concentration of weighting agent added to the reservoir drilling fluid.</t>
         </is>
       </c>
       <c r="L74" s="7" t="n"/>
@@ -4394,7 +4398,7 @@
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>Weighting Agent Loading</t>
+          <t>Bridging Agent Loading</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
@@ -4416,7 +4420,7 @@
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>Concentration of weighting agent added to the reservoir drilling fluid.</t>
+          <t>Concentration of bridging agent added to the reservoir drilling fluid.</t>
         </is>
       </c>
       <c r="L75" s="7" t="n"/>
@@ -4443,29 +4447,25 @@
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>Bridging Agent Loading</t>
+          <t>Mud PSD D10/D25/D40/D50/D75/D90</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="G76" s="7" t="inlineStr">
-        <is>
-          <t>lb/bbl</t>
-        </is>
-      </c>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="n"/>
       <c r="H76" s="7" t="n"/>
       <c r="I76" s="7" t="n"/>
       <c r="J76" s="7" t="inlineStr">
         <is>
-          <t>{"Decimal": {"min": 0}}</t>
+          <t>{["Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}]}</t>
         </is>
       </c>
       <c r="K76" s="7" t="inlineStr">
         <is>
-          <t>Concentration of bridging agent added to the reservoir drilling fluid.</t>
+          <t>Particle-size distribution of solids/bridging material in the reservoir drilling fluid.</t>
         </is>
       </c>
       <c r="L76" s="7" t="n"/>
@@ -4492,25 +4492,29 @@
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>Mud PSD D10/D25/D40/D50/D75/D90</t>
+          <t>PST Test Volume</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="G77" s="7" t="n"/>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="H77" s="7" t="n"/>
       <c r="I77" s="7" t="n"/>
       <c r="J77" s="7" t="inlineStr">
         <is>
-          <t>{["Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}]}</t>
+          <t>{"Decimal": {"min": 0}}</t>
         </is>
       </c>
       <c r="K77" s="7" t="inlineStr">
         <is>
-          <t>Particle-size distribution of solids/bridging material in the reservoir drilling fluid.</t>
+          <t>Volume of wellbore fluid sample passed through the screen coupon to ensure no plugging</t>
         </is>
       </c>
       <c r="L77" s="7" t="n"/>
@@ -4530,14 +4534,14 @@
           <t>Completion</t>
         </is>
       </c>
-      <c r="D78" s="9" t="inlineStr">
-        <is>
-          <t>OH Drilling Details</t>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>Cased Hole Details</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>PST Test Volume</t>
+          <t>Casing Size</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
@@ -4547,7 +4551,7 @@
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>inch</t>
         </is>
       </c>
       <c r="H78" s="7" t="n"/>
@@ -4559,7 +4563,7 @@
       </c>
       <c r="K78" s="7" t="inlineStr">
         <is>
-          <t>Volume of wellbore fluid sample passed through the screen coupon to ensure no plugging</t>
+          <t>Nominal casing or liner diameter across the production interval.</t>
         </is>
       </c>
       <c r="L78" s="7" t="n"/>
@@ -4586,7 +4590,7 @@
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>Casing Size</t>
+          <t>Gross Perf Length</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
@@ -4596,7 +4600,7 @@
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>inch</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="H79" s="7" t="n"/>
@@ -4608,7 +4612,7 @@
       </c>
       <c r="K79" s="7" t="inlineStr">
         <is>
-          <t>Nominal casing or liner diameter across the production interval.</t>
+          <t>Total interval from the uppermost to lowermost perforation, including unperforated gaps.</t>
         </is>
       </c>
       <c r="L79" s="7" t="n"/>
@@ -4635,7 +4639,7 @@
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>Gross Perf Length</t>
+          <t>Net Perf Length</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
@@ -4657,7 +4661,7 @@
       </c>
       <c r="K80" s="7" t="inlineStr">
         <is>
-          <t>Total interval from the uppermost to lowermost perforation, including unperforated gaps.</t>
+          <t>Cumulative length actually perforated and open to formation flow.</t>
         </is>
       </c>
       <c r="L80" s="7" t="n"/>
@@ -4684,7 +4688,7 @@
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>Net Perf Length</t>
+          <t>Perforation Gun Size</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
@@ -4694,7 +4698,7 @@
       </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>inch</t>
         </is>
       </c>
       <c r="H81" s="7" t="n"/>
@@ -4706,7 +4710,7 @@
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
-          <t>Cumulative length actually perforated and open to formation flow.</t>
+          <t>Nominal outside diameter of the perforating gun used across the interval.</t>
         </is>
       </c>
       <c r="L81" s="7" t="n"/>
@@ -4733,7 +4737,7 @@
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>Perforation Gun Size</t>
+          <t>Perforation SPF</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
@@ -4743,7 +4747,7 @@
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>inch</t>
+          <t>shots/ft</t>
         </is>
       </c>
       <c r="H82" s="7" t="n"/>
@@ -4755,7 +4759,7 @@
       </c>
       <c r="K82" s="7" t="inlineStr">
         <is>
-          <t>Nominal outside diameter of the perforating gun used across the interval.</t>
+          <t>Perforation shot density expressed as shots per foot (SPF).</t>
         </is>
       </c>
       <c r="L82" s="7" t="n"/>
@@ -4782,29 +4786,25 @@
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>Perforation SPF</t>
+          <t>Perforation Charge Casing Material</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="G83" s="7" t="inlineStr">
-        <is>
-          <t>shots/ft</t>
-        </is>
-      </c>
+          <t>Dropdown Menu</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="n"/>
       <c r="H83" s="7" t="n"/>
       <c r="I83" s="7" t="n"/>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>{"Decimal": {"min": 0}}</t>
+          <t>{"List": {"options": ["Steel", "Low Debris Steel", "Zinc"]}}</t>
         </is>
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>Perforation shot density expressed as shots per foot (SPF).</t>
+          <t>Material of the shaped-charge case, e.g., steel, low-debris steel, or zinc.</t>
         </is>
       </c>
       <c r="L83" s="7" t="n"/>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>Perforation Charge Casing Material</t>
+          <t>Charge Type</t>
         </is>
       </c>
       <c r="F84" s="7" t="inlineStr">
@@ -4844,12 +4844,12 @@
       <c r="I84" s="7" t="n"/>
       <c r="J84" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Steel", "Low Debris Steel", "Zinc"]}}</t>
+          <t>{"List": {"options": ["BH", "DP"]}}</t>
         </is>
       </c>
       <c r="K84" s="7" t="inlineStr">
         <is>
-          <t>Material of the shaped-charge case, e.g., steel, low-debris steel, or zinc.</t>
+          <t>Type/design of shaped charge used, such as deep-penetrating or big-hole charge.</t>
         </is>
       </c>
       <c r="L84" s="7" t="n"/>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>Charge Type</t>
+          <t>Perforation Strategy</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
@@ -4889,12 +4889,12 @@
       <c r="I85" s="7" t="n"/>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["BH", "DP"]}}</t>
+          <t>{"List": {"options": ["OB", "UB", "OB &amp; Surge", "UB &amp; Surge"]}}</t>
         </is>
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>Type/design of shaped charge used, such as deep-penetrating or big-hole charge.</t>
+          <t>Overall perforating approach, including phasing, shot density, orientation, and pressure condition where available.</t>
         </is>
       </c>
       <c r="L85" s="7" t="n"/>
@@ -4921,25 +4921,29 @@
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>Perforation Strategy</t>
+          <t>OB / OB Magnitude</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>Dropdown Menu</t>
-        </is>
-      </c>
-      <c r="G86" s="7" t="n"/>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>psi</t>
+        </is>
+      </c>
       <c r="H86" s="7" t="n"/>
       <c r="I86" s="7" t="n"/>
       <c r="J86" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["OB", "UB", "OB &amp; Surge", "UB &amp; Surge"]}}</t>
+          <t>{"Decimal": {"min": 0}}</t>
         </is>
       </c>
       <c r="K86" s="7" t="inlineStr">
         <is>
-          <t>Overall perforating approach, including phasing, shot density, orientation, and pressure condition where available.</t>
+          <t>Perforating pressure condition and magnitude of overbalance relative to formation pressure at the time of perforation.</t>
         </is>
       </c>
       <c r="L86" s="7" t="n"/>
@@ -4961,34 +4965,38 @@
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Cased Hole Details</t>
+          <t>Sand Control Details</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>OB / OB Magnitude</t>
+          <t>OH Sand Control Selected Method</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="G87" s="7" t="inlineStr">
-        <is>
-          <t>psi</t>
-        </is>
-      </c>
-      <c r="H87" s="7" t="n"/>
-      <c r="I87" s="7" t="n"/>
+          <t>Dropdown Menu</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="n"/>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>{"SAS": {"Gravel Packing": False}, "Cased and Perforated": {"Liners and Screens": False, "Gravel Packing": False}}</t>
+        </is>
+      </c>
+      <c r="I87" s="7" t="inlineStr">
+        <is>
+          <t>{"OHGP": {"Placement Method", "Carrier Fluid Type - OHGP", "Pack Efficiency Source", "Pack Efficiency Percentage", "ICD / AICD", "Did screens get to Target Setting Depth", "Return Percentage", "If screens ran in mud, was mud removed once screens on bottom?"}, "SAS": {"Fluid Type Left in OH at end of Completion", "ICD / AICD", "Did screens get to Target Setting Depth", "If screens ran in mud, was mud removed once screens on bottom?", "Blank pipe run across non-pay sections instead of screens?"}, "CHFP": {"Carrier Fluid Type - CHFP", "Full Pack from Log"}, "CHGP": {"Carrier Fluid Type - CHGP", "Perf Packing", "Return Percentage", "Pack Efficiency Source", "Pack Efficiency Percentage"}}</t>
+        </is>
+      </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>{"Decimal": {"min": 0}}</t>
+          <t>{"List": {"options": ["OHGP", "SAS"]}}</t>
         </is>
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>Perforating pressure condition and magnitude of overbalance relative to formation pressure at the time of perforation.</t>
+          <t>Sand-control method installed in an open-hole interval, e.g., standalone screen or open-hole gravel pack.</t>
         </is>
       </c>
       <c r="L87" s="7" t="n"/>
@@ -5015,7 +5023,7 @@
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>OH Sand Control Selected Method</t>
+          <t>CH Sand Control Selected Method</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
@@ -5036,12 +5044,12 @@
       </c>
       <c r="J88" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["OHGP", "SAS"]}}</t>
+          <t>{"List": {"options": ["CHFP", "CHGP", "Cased and Perforated"]}}</t>
         </is>
       </c>
       <c r="K88" s="7" t="inlineStr">
         <is>
-          <t>Sand-control method installed in an open-hole interval, e.g., standalone screen or open-hole gravel pack.</t>
+          <t>Sand-control method installed in a cased/perforated interval, e.g., cased-hole gravel pack or frac pack.</t>
         </is>
       </c>
       <c r="L88" s="7" t="n"/>
@@ -5068,7 +5076,7 @@
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>CH Sand Control Selected Method</t>
+          <t>Sand Control Decision Justification</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
@@ -5077,24 +5085,16 @@
         </is>
       </c>
       <c r="G89" s="7" t="n"/>
-      <c r="H89" s="7" t="inlineStr">
-        <is>
-          <t>{"SAS": {"Gravel Packing": False}, "Cased and Perforated": {"Liners and Screens": False, "Gravel Packing": False}}</t>
-        </is>
-      </c>
-      <c r="I89" s="7" t="inlineStr">
-        <is>
-          <t>{"OHGP": {"Placement Method", "Carrier Fluid Type - OHGP", "Pack Efficiency Source", "Pack Efficiency Percentage", "ICD / AICD", "Did screens get to Target Setting Depth", "Return Percentage", "If screens ran in mud, was mud removed once screens on bottom?"}, "SAS": {"Fluid Type Left in OH at end of Completion", "ICD / AICD", "Did screens get to Target Setting Depth", "If screens ran in mud, was mud removed once screens on bottom?", "Blank pipe run across non-pay sections instead of screens?"}, "CHFP": {"Carrier Fluid Type - CHFP", "Full Pack from Log"}, "CHGP": {"Carrier Fluid Type - CHGP", "Perf Packing", "Return Percentage", "Pack Efficiency Source", "Pack Efficiency Percentage"}}</t>
-        </is>
-      </c>
+      <c r="H89" s="7" t="n"/>
+      <c r="I89" s="7" t="n"/>
       <c r="J89" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["CHFP", "CHGP", "Cased and Perforated"]}}</t>
+          <t>{"List": {"options": ["Uncertain Sand Risk / Conservative Design", "Offset Well Experience", "Core-Based Geomechanical Analysis", "Operational Constraint", "Regulatory Requirement", "Completion Type Standardization", "Unknown / Not Documented"]}}</t>
         </is>
       </c>
       <c r="K89" s="7" t="inlineStr">
         <is>
-          <t>Sand-control method installed in a cased/perforated interval, e.g., cased-hole gravel pack or frac pack.</t>
+          <t>Documented technical rationale for selecting the installed sand-control method.</t>
         </is>
       </c>
       <c r="L89" s="7" t="n"/>
@@ -5116,12 +5116,12 @@
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>Sand Control Details</t>
+          <t>Liners and Screens</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>Sand Control Decision Justification</t>
+          <t>Screen Type</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
@@ -5134,12 +5134,12 @@
       <c r="I90" s="7" t="n"/>
       <c r="J90" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Uncertain Sand Risk / Conservative Design", "Offset Well Experience", "Core-Based Geomechanical Analysis", "Operational Constraint", "Regulatory Requirement", "Completion Type Standardization", "Unknown / Not Documented"]}}</t>
+          <t>{"List": {"options": ["Plain Slotted Liners", "Wire-Wrapped Screens (WWS)", "Premium Mesh Screen", "Prepacked Screens", "Metal-Fiber / Wool Screen", "Ceramic Screen", "Other Erosion Resistant Screen", "Other"]}}</t>
         </is>
       </c>
       <c r="K90" s="7" t="inlineStr">
         <is>
-          <t>Documented technical rationale for selecting the installed sand-control method.</t>
+          <t>Type/design of sand-control screen installed across the production interval.</t>
         </is>
       </c>
       <c r="L90" s="7" t="n"/>
@@ -5166,12 +5166,12 @@
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>Screen Type</t>
+          <t>ICD / AICD</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>Dropdown Menu</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="G91" s="7" t="n"/>
@@ -5179,12 +5179,12 @@
       <c r="I91" s="7" t="n"/>
       <c r="J91" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Plain Slotted Liners", "Wire-Wrapped Screens (WWS)", "Premium Mesh Screen", "Prepacked Screens", "Metal-Fiber / Wool Screen", "Ceramic Screen", "Other Erosion Resistant Screen", "Other"]}}</t>
+          <t>{"List": {"options": ["Yes", "No"]}}</t>
         </is>
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
-          <t>Type/design of sand-control screen installed across the production interval.</t>
+          <t>Indicates whether an inflow control device (ICD) or autonomous inflow control device (AICD) is incorporated in the completion.</t>
         </is>
       </c>
       <c r="L91" s="7" t="n"/>
@@ -5211,25 +5211,29 @@
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>ICD / AICD</t>
+          <t>Screen Gauge</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>Boolean</t>
-        </is>
-      </c>
-      <c r="G92" s="7" t="n"/>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>gauge or micron</t>
+        </is>
+      </c>
       <c r="H92" s="7" t="n"/>
       <c r="I92" s="7" t="n"/>
       <c r="J92" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Yes", "No"]}}</t>
+          <t>{"Decimal": {"min": 0}}</t>
         </is>
       </c>
       <c r="K92" s="7" t="inlineStr">
         <is>
-          <t>Indicates whether an inflow control device (ICD) or autonomous inflow control device (AICD) is incorporated in the completion.</t>
+          <t>Nominal slot or screen-opening width. Primarily applicable to slotted liners and wire-wrapped screens.</t>
         </is>
       </c>
       <c r="L92" s="7" t="n"/>
@@ -5256,7 +5260,7 @@
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>Screen Gauge</t>
+          <t>Filter Media Size</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
@@ -5266,7 +5270,7 @@
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
-          <t>gauge or micron</t>
+          <t>micron</t>
         </is>
       </c>
       <c r="H93" s="7" t="n"/>
@@ -5278,7 +5282,7 @@
       </c>
       <c r="K93" s="7" t="inlineStr">
         <is>
-          <t>Nominal slot or screen-opening width. Primarily applicable to slotted liners and wire-wrapped screens.</t>
+          <t>Nominal pore or particle-retention rating of the screen’s filtering medium. Applicable to premium mesh, metal-fiber/wool, ceramic, and similar media-based screens.</t>
         </is>
       </c>
       <c r="L93" s="7" t="n"/>
@@ -5305,7 +5309,7 @@
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>Filter Media Size</t>
+          <t>Screen Base Pipe Size</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
@@ -5315,7 +5319,7 @@
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>micron</t>
+          <t>inch</t>
         </is>
       </c>
       <c r="H94" s="7" t="n"/>
@@ -5327,7 +5331,7 @@
       </c>
       <c r="K94" s="7" t="inlineStr">
         <is>
-          <t>Nominal pore or particle-retention rating of the screen’s filtering medium. Applicable to premium mesh, metal-fiber/wool, ceramic, and similar media-based screens.</t>
+          <t>Nominal outside diameter of the screen base pipe.</t>
         </is>
       </c>
       <c r="L94" s="7" t="n"/>
@@ -5354,29 +5358,25 @@
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>Screen Base Pipe Size</t>
+          <t>Fluid Type Left in OH at end of Completion</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
         <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="G95" s="7" t="inlineStr">
-        <is>
-          <t>inch</t>
-        </is>
-      </c>
+          <t>Dropdown Menu</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="n"/>
       <c r="H95" s="7" t="n"/>
       <c r="I95" s="7" t="n"/>
       <c r="J95" s="7" t="inlineStr">
         <is>
-          <t>{"Decimal": {"min": 0}}</t>
+          <t>{"List": {"options": ["Completion Brine", "Reservoir Drill-In Fluid", "Filter-Cake Breaker Fluid", "Produced Fluid / Hydrocarbon", "Mixed / Contaminated Fluid"]}}</t>
         </is>
       </c>
       <c r="K95" s="7" t="inlineStr">
         <is>
-          <t>Nominal outside diameter of the screen base pipe.</t>
+          <t>Fluid occupying the open-hole interval at the end of completion operations before cleanup/startup.</t>
         </is>
       </c>
       <c r="L95" s="7" t="n"/>
@@ -5386,7 +5386,7 @@
       <c r="A96" s="26" t="n">
         <v>95</v>
       </c>
-      <c r="B96" s="14" t="inlineStr">
+      <c r="B96" s="18" t="inlineStr">
         <is>
           <t>Completion Interval {id}</t>
         </is>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>Fluid Type Left in OH at end of Completion</t>
+          <t>Screen RIH Fluid Type in Casing</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
@@ -5412,16 +5412,16 @@
         </is>
       </c>
       <c r="G96" s="7" t="n"/>
-      <c r="H96" s="7" t="n"/>
-      <c r="I96" s="7" t="n"/>
+      <c r="H96" s="19" t="n"/>
+      <c r="I96" s="19" t="n"/>
       <c r="J96" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Completion Brine", "Reservoir Drill-In Fluid", "Filter-Cake Breaker Fluid", "Produced Fluid / Hydrocarbon", "Mixed / Contaminated Fluid"]}}</t>
+          <t>{"List": {"options": ["Brine", "OBM", "WBM", "Low/No Solids WBM", "Low/No Solids OBM"]}}</t>
         </is>
       </c>
       <c r="K96" s="7" t="inlineStr">
         <is>
-          <t>Fluid occupying the open-hole interval at the end of completion operations before cleanup/startup.</t>
+          <t>Fluid present in the casing while the screen assembly was run in hole (RIH).</t>
         </is>
       </c>
       <c r="L96" s="7" t="n"/>
@@ -5431,7 +5431,7 @@
       <c r="A97" s="26" t="n">
         <v>96</v>
       </c>
-      <c r="B97" s="18" t="inlineStr">
+      <c r="B97" s="14" t="inlineStr">
         <is>
           <t>Completion Interval {id}</t>
         </is>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>Screen RIH Fluid Type in Casing</t>
+          <t>Screen RIH Fluid Type in Open-Hole</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr">
@@ -5457,8 +5457,8 @@
         </is>
       </c>
       <c r="G97" s="7" t="n"/>
-      <c r="H97" s="19" t="n"/>
-      <c r="I97" s="19" t="n"/>
+      <c r="H97" s="7" t="n"/>
+      <c r="I97" s="7" t="n"/>
       <c r="J97" s="7" t="inlineStr">
         <is>
           <t>{"List": {"options": ["Brine", "OBM", "WBM", "Low/No Solids WBM", "Low/No Solids OBM"]}}</t>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="K97" s="7" t="inlineStr">
         <is>
-          <t>Fluid present in the casing while the screen assembly was run in hole (RIH).</t>
+          <t>Fluid present in the open-hole while the screen assembly was run in hole (RIH).</t>
         </is>
       </c>
       <c r="L97" s="7" t="n"/>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>Screen RIH Fluid Type in Open-Hole</t>
+          <t>If screens ran in mud, was mud removed once screens on bottom?</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>Dropdown Menu</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="G98" s="7" t="n"/>
@@ -5506,12 +5506,12 @@
       <c r="I98" s="7" t="n"/>
       <c r="J98" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Brine", "OBM", "WBM", "Low/No Solids WBM", "Low/No Solids OBM"]}}</t>
+          <t>{"List": {"options": ["Yes", "No"]}}</t>
         </is>
       </c>
       <c r="K98" s="7" t="inlineStr">
         <is>
-          <t>Fluid present in the open-hole while the screen assembly was run in hole (RIH).</t>
+          <t>Indicates whether drilling mud was displaced/removed after the screens reached final setting depth.</t>
         </is>
       </c>
       <c r="L98" s="7" t="n"/>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>If screens ran in mud, was mud removed once screens on bottom?</t>
+          <t>Did screens get to Target Setting Depth</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr">
@@ -5554,11 +5554,7 @@
           <t>{"List": {"options": ["Yes", "No"]}}</t>
         </is>
       </c>
-      <c r="K99" s="7" t="inlineStr">
-        <is>
-          <t>Indicates whether drilling mud was displaced/removed after the screens reached final setting depth.</t>
-        </is>
-      </c>
+      <c r="K99" s="7" t="n"/>
       <c r="L99" s="7" t="n"/>
       <c r="M99" s="1" t="n"/>
     </row>
@@ -5583,7 +5579,7 @@
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>Did screens get to Target Setting Depth</t>
+          <t>Blank pipe run across non-pay sections instead of screens?</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
@@ -5624,12 +5620,12 @@
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>Blank pipe run across non-pay sections instead of screens?</t>
+          <t>Screen Size Selection</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Dropdown Menu</t>
         </is>
       </c>
       <c r="G101" s="7" t="n"/>
@@ -5637,10 +5633,14 @@
       <c r="I101" s="7" t="n"/>
       <c r="J101" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Yes", "No"]}}</t>
-        </is>
-      </c>
-      <c r="K101" s="7" t="n"/>
+          <t>{"List": {"options": ["Screen retention test", "Rule of thumb", "Company standard"]}}</t>
+        </is>
+      </c>
+      <c r="K101" s="7" t="inlineStr">
+        <is>
+          <t>Basis used to select the screen size.</t>
+        </is>
+      </c>
       <c r="L101" s="7" t="n"/>
       <c r="M101" s="1" t="n"/>
     </row>
@@ -5660,12 +5660,12 @@
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>Liners and Screens</t>
+          <t>Gravel Packing</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>Screen Size Selection</t>
+          <t>Placement Method</t>
         </is>
       </c>
       <c r="F102" s="7" t="inlineStr">
@@ -5675,15 +5675,19 @@
       </c>
       <c r="G102" s="7" t="n"/>
       <c r="H102" s="7" t="n"/>
-      <c r="I102" s="7" t="n"/>
+      <c r="I102" s="7" t="inlineStr">
+        <is>
+          <t>{"Shunt": {"% Pack through Shunts", "Shunt Tubes"}, "Circ Pack": {"% Pack through Shunts": False, "Shunt Tubes": False}}</t>
+        </is>
+      </c>
       <c r="J102" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Screen retention test", "Rule of thumb", "Company standard"]}}</t>
+          <t>{"List": {"options": ["Shunt", "Circ Pack"]}}</t>
         </is>
       </c>
       <c r="K102" s="7" t="inlineStr">
         <is>
-          <t>Basis used to select the screen size.</t>
+          <t>Technique used to place gravel/proppant around the screen and across the production interval.</t>
         </is>
       </c>
       <c r="L102" s="7" t="n"/>
@@ -5710,31 +5714,27 @@
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>Placement Method</t>
+          <t>% Pack through Shunts</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>Dropdown Menu</t>
-        </is>
-      </c>
-      <c r="G103" s="7" t="n"/>
-      <c r="H103" s="7" t="n"/>
-      <c r="I103" s="7" t="inlineStr">
-        <is>
-          <t>{"Shunt": {"% Pack through Shunts", "Shunt Tubes"}, "Circ Pack": {"% Pack through Shunts": False, "Shunt Tubes": False}}</t>
-        </is>
-      </c>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H103" s="20" t="n"/>
+      <c r="I103" s="20" t="n"/>
       <c r="J103" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Shunt", "Circ Pack"]}}</t>
-        </is>
-      </c>
-      <c r="K103" s="7" t="inlineStr">
-        <is>
-          <t>Technique used to place gravel/proppant around the screen and across the production interval.</t>
-        </is>
-      </c>
+          <t>{"Decimal": {"min": 0}}</t>
+        </is>
+      </c>
+      <c r="K103" s="7" t="n"/>
       <c r="L103" s="7" t="n"/>
       <c r="M103" s="1" t="n"/>
     </row>
@@ -5759,24 +5759,20 @@
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>% Pack through Shunts</t>
+          <t>Shunt Tubes</t>
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="G104" s="7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H104" s="20" t="n"/>
-      <c r="I104" s="20" t="n"/>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="G104" s="7" t="n"/>
+      <c r="H104" s="7" t="n"/>
+      <c r="I104" s="7" t="n"/>
       <c r="J104" s="7" t="inlineStr">
         <is>
-          <t>{"Decimal": {"min": 0}}</t>
+          <t>{"List": {"options": ["Yes", "No"]}}</t>
         </is>
       </c>
       <c r="K104" s="7" t="n"/>
@@ -5804,12 +5800,12 @@
       </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
-          <t>Shunt Tubes</t>
+          <t>Proppant Type</t>
         </is>
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Dropdown Menu</t>
         </is>
       </c>
       <c r="G105" s="7" t="n"/>
@@ -5817,10 +5813,14 @@
       <c r="I105" s="7" t="n"/>
       <c r="J105" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Yes", "No"]}}</t>
-        </is>
-      </c>
-      <c r="K105" s="7" t="n"/>
+          <t>{"List": {"options": ["Natural Sand", "Ceramic Proppant"]}}</t>
+        </is>
+      </c>
+      <c r="K105" s="7" t="inlineStr">
+        <is>
+          <t>Material used as gravel-pack/proppant media, including material composition or commercial type where known.</t>
+        </is>
+      </c>
       <c r="L105" s="7" t="n"/>
       <c r="M105" s="1" t="n"/>
     </row>
@@ -5845,7 +5845,7 @@
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>Proppant Type</t>
+          <t>Proppant Size</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
@@ -5858,12 +5858,12 @@
       <c r="I106" s="7" t="n"/>
       <c r="J106" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Natural Sand", "Ceramic Proppant"]}}</t>
+          <t>{"List": {"options": ["16/20", "16/30", "20/40", "30/50", "40/60", "40/70", "35 Monomesh", "25 Monomesh", "40 Monomesh", "45 Monomesh"]}}</t>
         </is>
       </c>
       <c r="K106" s="7" t="inlineStr">
         <is>
-          <t>Material used as gravel-pack/proppant media, including material composition or commercial type where known.</t>
+          <t>Nominal gravel/proppant mesh-size range used in the sand-control treatment.</t>
         </is>
       </c>
       <c r="L106" s="7" t="n"/>
@@ -5890,25 +5890,29 @@
       </c>
       <c r="E107" s="7" t="inlineStr">
         <is>
-          <t>Proppant Size</t>
+          <t>Proppant / Unit Length</t>
         </is>
       </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>Dropdown Menu</t>
-        </is>
-      </c>
-      <c r="G107" s="7" t="n"/>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G107" s="7" t="inlineStr">
+        <is>
+          <t>lbs/ft</t>
+        </is>
+      </c>
       <c r="H107" s="7" t="n"/>
       <c r="I107" s="7" t="n"/>
       <c r="J107" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["16/20", "16/30", "20/40", "30/50", "40/60", "40/70", "35 Monomesh", "25 Monomesh", "40 Monomesh", "45 Monomesh"]}}</t>
+          <t>{"Decimal": {"min": 0}}</t>
         </is>
       </c>
       <c r="K107" s="7" t="inlineStr">
         <is>
-          <t>Nominal gravel/proppant mesh-size range used in the sand-control treatment.</t>
+          <t>Total quantity of gravel/proppant placed normalized by completed interval length.</t>
         </is>
       </c>
       <c r="L107" s="7" t="n"/>
@@ -5935,29 +5939,25 @@
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
-          <t>Proppant / Unit Length</t>
+          <t>Carrier Fluid Type - OHGP</t>
         </is>
       </c>
       <c r="F108" s="7" t="inlineStr">
         <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="G108" s="7" t="inlineStr">
-        <is>
-          <t>lbs/ft</t>
-        </is>
-      </c>
+          <t>Dropdown Menu</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="n"/>
       <c r="H108" s="7" t="n"/>
       <c r="I108" s="7" t="n"/>
       <c r="J108" s="7" t="inlineStr">
         <is>
-          <t>{"Decimal": {"min": 0}}</t>
+          <t>{"List": {"options": ["Brine", "Xanthan", "VES", "HEC", "Oil Based"]}}</t>
         </is>
       </c>
       <c r="K108" s="7" t="inlineStr">
         <is>
-          <t>Total quantity of gravel/proppant placed normalized by completed interval length.</t>
+          <t>Base fluid/system used to transport gravel or proppant during placement.</t>
         </is>
       </c>
       <c r="L108" s="7" t="n"/>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>Carrier Fluid Type - OHGP</t>
+          <t>Carrier Fluid Type - CHFP</t>
         </is>
       </c>
       <c r="F109" s="7" t="inlineStr">
@@ -5997,7 +5997,7 @@
       <c r="I109" s="7" t="n"/>
       <c r="J109" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Brine", "Xanthan", "VES", "HEC", "Oil Based"]}}</t>
+          <t>{"List": {"options": ["Xlink Gel", "VES", "HEC"]}}</t>
         </is>
       </c>
       <c r="K109" s="7" t="inlineStr">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t>Carrier Fluid Type - CHFP</t>
+          <t>Carrier Fluid Type - CHGP</t>
         </is>
       </c>
       <c r="F110" s="7" t="inlineStr">
@@ -6042,7 +6042,7 @@
       <c r="I110" s="7" t="n"/>
       <c r="J110" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Xlink Gel", "VES", "HEC"]}}</t>
+          <t>{"List": {"options": ["Brine", "Linear Gel", "HEC", "Xlinked Gel", "VES", "Xanthan"]}}</t>
         </is>
       </c>
       <c r="K110" s="7" t="inlineStr">
@@ -6074,25 +6074,29 @@
       </c>
       <c r="E111" s="7" t="inlineStr">
         <is>
-          <t>Carrier Fluid Type - CHGP</t>
+          <t>Carrier Fluid Density</t>
         </is>
       </c>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>Dropdown Menu</t>
-        </is>
-      </c>
-      <c r="G111" s="7" t="n"/>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G111" s="7" t="inlineStr">
+        <is>
+          <t>ppg</t>
+        </is>
+      </c>
       <c r="H111" s="7" t="n"/>
       <c r="I111" s="7" t="n"/>
       <c r="J111" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Brine", "Linear Gel", "HEC", "Xlinked Gel", "VES", "Xanthan"]}}</t>
+          <t>{"Decimal": {"min": 0}}</t>
         </is>
       </c>
       <c r="K111" s="7" t="inlineStr">
         <is>
-          <t>Base fluid/system used to transport gravel or proppant during placement.</t>
+          <t>Density of the carrier/slurry fluid used during gravel-pack placement.</t>
         </is>
       </c>
       <c r="L111" s="7" t="n"/>
@@ -6117,34 +6121,30 @@
           <t>Gravel Packing</t>
         </is>
       </c>
-      <c r="E112" s="7" t="inlineStr">
-        <is>
-          <t>Carrier Fluid Density</t>
-        </is>
-      </c>
-      <c r="F112" s="7" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="G112" s="7" t="inlineStr">
-        <is>
-          <t>ppg</t>
-        </is>
-      </c>
-      <c r="H112" s="7" t="n"/>
-      <c r="I112" s="7" t="n"/>
-      <c r="J112" s="7" t="inlineStr">
+      <c r="E112" s="13" t="inlineStr">
+        <is>
+          <t>Perf Packing</t>
+        </is>
+      </c>
+      <c r="F112" s="14" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G112" s="14" t="inlineStr">
+        <is>
+          <t>lbs/ft</t>
+        </is>
+      </c>
+      <c r="H112" s="20" t="n"/>
+      <c r="I112" s="20" t="n"/>
+      <c r="J112" s="14" t="inlineStr">
         <is>
           <t>{"Decimal": {"min": 0}}</t>
         </is>
       </c>
-      <c r="K112" s="7" t="inlineStr">
-        <is>
-          <t>Density of the carrier/slurry fluid used during gravel-pack placement.</t>
-        </is>
-      </c>
-      <c r="L112" s="7" t="n"/>
+      <c r="K112" s="14" t="n"/>
+      <c r="L112" s="14" t="n"/>
       <c r="M112" s="1" t="n"/>
     </row>
     <row r="113" ht="14" customHeight="1">
@@ -6166,30 +6166,34 @@
           <t>Gravel Packing</t>
         </is>
       </c>
-      <c r="E113" s="13" t="inlineStr">
-        <is>
-          <t>Perf Packing</t>
-        </is>
-      </c>
-      <c r="F113" s="14" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="G113" s="14" t="inlineStr">
-        <is>
-          <t>lbs/ft</t>
-        </is>
-      </c>
-      <c r="H113" s="20" t="n"/>
-      <c r="I113" s="20" t="n"/>
-      <c r="J113" s="14" t="inlineStr">
+      <c r="E113" s="7" t="inlineStr">
+        <is>
+          <t>Max Proppant Concentration</t>
+        </is>
+      </c>
+      <c r="F113" s="7" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G113" s="7" t="inlineStr">
+        <is>
+          <t>ppa</t>
+        </is>
+      </c>
+      <c r="H113" s="7" t="n"/>
+      <c r="I113" s="7" t="n"/>
+      <c r="J113" s="7" t="inlineStr">
         <is>
           <t>{"Decimal": {"min": 0}}</t>
         </is>
       </c>
-      <c r="K113" s="14" t="n"/>
-      <c r="L113" s="14" t="n"/>
+      <c r="K113" s="7" t="inlineStr">
+        <is>
+          <t>Maximum proppant concentration reached during the placement treatment.</t>
+        </is>
+      </c>
+      <c r="L113" s="7" t="n"/>
       <c r="M113" s="1" t="n"/>
     </row>
     <row r="114" ht="14" customHeight="1">
@@ -6213,7 +6217,7 @@
       </c>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>Max Proppant Concentration</t>
+          <t>Max Pump Rate</t>
         </is>
       </c>
       <c r="F114" s="7" t="inlineStr">
@@ -6223,7 +6227,7 @@
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>ppa</t>
+          <t>bpm</t>
         </is>
       </c>
       <c r="H114" s="7" t="n"/>
@@ -6235,7 +6239,7 @@
       </c>
       <c r="K114" s="7" t="inlineStr">
         <is>
-          <t>Maximum proppant concentration reached during the placement treatment.</t>
+          <t>Maximum pumping rate reached during gravel-pack placement.</t>
         </is>
       </c>
       <c r="L114" s="7" t="n"/>
@@ -6262,7 +6266,7 @@
       </c>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>Max Pump Rate</t>
+          <t>Net Pressure Gain</t>
         </is>
       </c>
       <c r="F115" s="7" t="inlineStr">
@@ -6272,7 +6276,7 @@
       </c>
       <c r="G115" s="7" t="inlineStr">
         <is>
-          <t>bpm</t>
+          <t>psi</t>
         </is>
       </c>
       <c r="H115" s="7" t="n"/>
@@ -6284,7 +6288,7 @@
       </c>
       <c r="K115" s="7" t="inlineStr">
         <is>
-          <t>Maximum pumping rate reached during gravel-pack placement.</t>
+          <t>Increase in net treatment pressure observed during gravel/proppant placement.</t>
         </is>
       </c>
       <c r="L115" s="7" t="n"/>
@@ -6311,7 +6315,7 @@
       </c>
       <c r="E116" s="7" t="inlineStr">
         <is>
-          <t>Net Pressure Gain</t>
+          <t>Return Percentage</t>
         </is>
       </c>
       <c r="F116" s="7" t="inlineStr">
@@ -6321,7 +6325,7 @@
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>psi</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H116" s="7" t="n"/>
@@ -6333,7 +6337,7 @@
       </c>
       <c r="K116" s="7" t="inlineStr">
         <is>
-          <t>Increase in net treatment pressure observed during gravel/proppant placement.</t>
+          <t>Percentage of pumped carrier fluid or slurry returns observed/recovered during the gravel-pack operation, as defined by the source.</t>
         </is>
       </c>
       <c r="L116" s="7" t="n"/>
@@ -6360,31 +6364,23 @@
       </c>
       <c r="E117" s="7" t="inlineStr">
         <is>
-          <t>Return Percentage</t>
+          <t>Full Pack from Log</t>
         </is>
       </c>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="G117" s="7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="G117" s="7" t="n"/>
       <c r="H117" s="7" t="n"/>
       <c r="I117" s="7" t="n"/>
       <c r="J117" s="7" t="inlineStr">
         <is>
-          <t>{"Decimal": {"min": 0}}</t>
-        </is>
-      </c>
-      <c r="K117" s="7" t="inlineStr">
-        <is>
-          <t>Percentage of pumped carrier fluid or slurry returns observed/recovered during the gravel-pack operation, as defined by the source.</t>
-        </is>
-      </c>
+          <t>{"List": {"options": ["Yes", "No"]}}</t>
+        </is>
+      </c>
+      <c r="K117" s="7" t="n"/>
       <c r="L117" s="7" t="n"/>
       <c r="M117" s="1" t="n"/>
     </row>
@@ -6409,23 +6405,31 @@
       </c>
       <c r="E118" s="7" t="inlineStr">
         <is>
-          <t>Full Pack from Log</t>
+          <t>Pack Efficiency Source</t>
         </is>
       </c>
       <c r="F118" s="7" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Dropdown Menu</t>
         </is>
       </c>
       <c r="G118" s="7" t="n"/>
       <c r="H118" s="7" t="n"/>
-      <c r="I118" s="7" t="n"/>
+      <c r="I118" s="7" t="inlineStr">
+        <is>
+          <t>{"None": {"Pack Efficiency Percentage": False}}</t>
+        </is>
+      </c>
       <c r="J118" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Yes", "No"]}}</t>
-        </is>
-      </c>
-      <c r="K118" s="7" t="n"/>
+          <t>{"List": {"options": ["Gravel Pack Log", "Gauge Analysis", "Volumetrics", "None"]}}</t>
+        </is>
+      </c>
+      <c r="K118" s="7" t="inlineStr">
+        <is>
+          <t>Method used to determine gravel-pack placement efficiency, e.g., evaluation log, volume balance, pumping data, or returns.</t>
+        </is>
+      </c>
       <c r="L118" s="7" t="n"/>
       <c r="M118" s="1" t="n"/>
     </row>
@@ -6450,29 +6454,29 @@
       </c>
       <c r="E119" s="7" t="inlineStr">
         <is>
-          <t>Pack Efficiency Source</t>
+          <t>Pack Efficiency Percentage</t>
         </is>
       </c>
       <c r="F119" s="7" t="inlineStr">
         <is>
-          <t>Dropdown Menu</t>
-        </is>
-      </c>
-      <c r="G119" s="7" t="n"/>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G119" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
       <c r="H119" s="7" t="n"/>
-      <c r="I119" s="7" t="inlineStr">
-        <is>
-          <t>{"None": {"Pack Efficiency Percentage": False}}</t>
-        </is>
-      </c>
+      <c r="I119" s="7" t="n"/>
       <c r="J119" s="7" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Gravel Pack Log", "Gauge Analysis", "Volumetrics", "None"]}}</t>
+          <t>{"Decimal": {"min": 0}}</t>
         </is>
       </c>
       <c r="K119" s="7" t="inlineStr">
         <is>
-          <t>Method used to determine gravel-pack placement efficiency, e.g., evaluation log, volume balance, pumping data, or returns.</t>
+          <t>Reported or calculated percentage of the target interval/annular volume successfully packed with gravel.</t>
         </is>
       </c>
       <c r="L119" s="7" t="n"/>
@@ -6499,122 +6503,118 @@
       </c>
       <c r="E120" s="7" t="inlineStr">
         <is>
-          <t>Pack Efficiency Percentage</t>
+          <t>Placement Issues</t>
         </is>
       </c>
       <c r="F120" s="7" t="inlineStr">
         <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="G120" s="7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="G120" s="7" t="n"/>
       <c r="H120" s="7" t="n"/>
       <c r="I120" s="7" t="n"/>
       <c r="J120" s="7" t="inlineStr">
         <is>
-          <t>{"Decimal": {"min": 0}}</t>
+          <t>{"List": {"options": ["Yes", "No"]}}</t>
         </is>
       </c>
       <c r="K120" s="7" t="inlineStr">
         <is>
-          <t>Reported or calculated percentage of the target interval/annular volume successfully packed with gravel.</t>
+          <t>Problems encountered during gravel placement, such as premature screenout, losses, bridging, incomplete packing, or poor returns.</t>
         </is>
       </c>
       <c r="L120" s="7" t="n"/>
       <c r="M120" s="1" t="n"/>
     </row>
     <row r="121" ht="14" customHeight="1">
-      <c r="A121" s="26" t="n">
+      <c r="A121" s="23" t="n">
         <v>120</v>
       </c>
-      <c r="B121" s="14" t="inlineStr">
+      <c r="B121" s="15" t="inlineStr">
         <is>
           <t>Completion Interval {id}</t>
         </is>
       </c>
-      <c r="C121" s="7" t="inlineStr">
-        <is>
-          <t>Completion</t>
-        </is>
-      </c>
-      <c r="D121" s="7" t="inlineStr">
-        <is>
-          <t>Gravel Packing</t>
-        </is>
-      </c>
-      <c r="E121" s="7" t="inlineStr">
-        <is>
-          <t>Placement Issues</t>
-        </is>
-      </c>
-      <c r="F121" s="7" t="inlineStr">
-        <is>
-          <t>Boolean</t>
-        </is>
-      </c>
-      <c r="G121" s="7" t="n"/>
-      <c r="H121" s="7" t="n"/>
-      <c r="I121" s="7" t="n"/>
-      <c r="J121" s="7" t="inlineStr">
-        <is>
-          <t>{"List": {"options": ["Yes", "No"]}}</t>
-        </is>
-      </c>
-      <c r="K121" s="7" t="inlineStr">
-        <is>
-          <t>Problems encountered during gravel placement, such as premature screenout, losses, bridging, incomplete packing, or poor returns.</t>
-        </is>
-      </c>
-      <c r="L121" s="7" t="n"/>
+      <c r="C121" s="15" t="inlineStr">
+        <is>
+          <t>Sand Bodies</t>
+        </is>
+      </c>
+      <c r="D121" s="15" t="inlineStr">
+        <is>
+          <t>Sand Bodies</t>
+        </is>
+      </c>
+      <c r="E121" s="15" t="inlineStr">
+        <is>
+          <t>Number of sand bodies</t>
+        </is>
+      </c>
+      <c r="F121" s="15" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G121" s="15" t="n"/>
+      <c r="H121" s="15" t="n"/>
+      <c r="I121" s="15" t="n"/>
+      <c r="J121" s="15" t="inlineStr">
+        <is>
+          <t>{"Whole number": {"min": 1, "max": 10}}</t>
+        </is>
+      </c>
+      <c r="K121" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Each completion interval can have several sand bodies. </t>
+        </is>
+      </c>
+      <c r="L121" s="15" t="n"/>
       <c r="M121" s="1" t="n"/>
     </row>
     <row r="122" ht="14" customHeight="1">
-      <c r="A122" s="23" t="n">
+      <c r="A122" s="24" t="n">
         <v>121</v>
       </c>
-      <c r="B122" s="15" t="inlineStr">
-        <is>
-          <t>Completion Interval {id}</t>
-        </is>
-      </c>
-      <c r="C122" s="15" t="inlineStr">
-        <is>
-          <t>Sand Bodies</t>
-        </is>
-      </c>
-      <c r="D122" s="15" t="inlineStr">
-        <is>
-          <t>Sand Bodies</t>
-        </is>
-      </c>
-      <c r="E122" s="15" t="inlineStr">
-        <is>
-          <t>Number of sand bodies</t>
-        </is>
-      </c>
-      <c r="F122" s="15" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="G122" s="15" t="n"/>
-      <c r="H122" s="15" t="n"/>
-      <c r="I122" s="15" t="n"/>
-      <c r="J122" s="15" t="inlineStr">
-        <is>
-          <t>{"Whole number": {"min": 1, "max": 10}}</t>
-        </is>
-      </c>
-      <c r="K122" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Each completion interval can have several sand bodies. </t>
-        </is>
-      </c>
-      <c r="L122" s="15" t="n"/>
+      <c r="B122" s="17" t="inlineStr">
+        <is>
+          <t>Sand Body {id}</t>
+        </is>
+      </c>
+      <c r="C122" s="16" t="inlineStr">
+        <is>
+          <t>Pre-production and cleanup</t>
+        </is>
+      </c>
+      <c r="D122" s="16" t="inlineStr">
+        <is>
+          <t>Pre-production and cleanup details</t>
+        </is>
+      </c>
+      <c r="E122" s="17" t="inlineStr">
+        <is>
+          <t>Remedial Acid Pumped as Productivity was Below Expectation</t>
+        </is>
+      </c>
+      <c r="F122" s="17" t="inlineStr">
+        <is>
+          <t>Dropdown Menu</t>
+        </is>
+      </c>
+      <c r="G122" s="17" t="n"/>
+      <c r="H122" s="17" t="n"/>
+      <c r="I122" s="17" t="n"/>
+      <c r="J122" s="17" t="inlineStr">
+        <is>
+          <t>{"List": {"options": ["Yes", "No", "Unknown", "Not Applicable"]}}</t>
+        </is>
+      </c>
+      <c r="K122" s="17" t="inlineStr">
+        <is>
+          <t>Indicates whether remedial acid treatment was performed because initial well productivity was below the expected level.</t>
+        </is>
+      </c>
+      <c r="L122" s="17" t="n"/>
       <c r="M122" s="1" t="n"/>
     </row>
     <row r="123" ht="14" customHeight="1">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="E123" s="17" t="inlineStr">
         <is>
-          <t>Remedial Acid Pumped as Productivity was Below Expectation</t>
+          <t>Remedial Acid Helped Productivity</t>
         </is>
       </c>
       <c r="F123" s="17" t="inlineStr">
@@ -6651,12 +6651,12 @@
       <c r="I123" s="17" t="n"/>
       <c r="J123" s="17" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Yes", "No", "Unknown", "Not Applicable"]}}</t>
+          <t>{"List": {"options": ["Yes", "No", "Partially", "Unknown", "Not Applicable"]}}</t>
         </is>
       </c>
       <c r="K123" s="17" t="inlineStr">
         <is>
-          <t>Indicates whether remedial acid treatment was performed because initial well productivity was below the expected level.</t>
+          <t>Indicates whether the remedial acid treatment produced a measurable or documented improvement in well productivity.</t>
         </is>
       </c>
       <c r="L123" s="17" t="n"/>
@@ -6683,7 +6683,7 @@
       </c>
       <c r="E124" s="17" t="inlineStr">
         <is>
-          <t>Remedial Acid Helped Productivity</t>
+          <t>Remedial Acid Type</t>
         </is>
       </c>
       <c r="F124" s="17" t="inlineStr">
@@ -6696,12 +6696,12 @@
       <c r="I124" s="17" t="n"/>
       <c r="J124" s="17" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Yes", "No", "Partially", "Unknown", "Not Applicable"]}}</t>
+          <t>{"List": {"options": ["Organic", "Inorganic", "Mud acid", "Blend", "Other", "Unknown", "Not applicable"]}}</t>
         </is>
       </c>
       <c r="K124" s="17" t="inlineStr">
         <is>
-          <t>Indicates whether the remedial acid treatment produced a measurable or documented improvement in well productivity.</t>
+          <t>Type or formulation of acid system used for the remedial treatment, e.g., HCl, mud acid, or organic acid.</t>
         </is>
       </c>
       <c r="L124" s="17" t="n"/>
@@ -6728,25 +6728,29 @@
       </c>
       <c r="E125" s="17" t="inlineStr">
         <is>
-          <t>Remedial Acid Type</t>
+          <t>Percentage of ideal PI or skin achieved</t>
         </is>
       </c>
       <c r="F125" s="17" t="inlineStr">
         <is>
-          <t>Dropdown Menu</t>
-        </is>
-      </c>
-      <c r="G125" s="17" t="n"/>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="G125" s="17" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
       <c r="H125" s="17" t="n"/>
       <c r="I125" s="17" t="n"/>
       <c r="J125" s="17" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Organic", "Inorganic", "Mud acid", "Blend", "Other", "Unknown", "Not applicable"]}}</t>
+          <t>{"Whole number"}</t>
         </is>
       </c>
       <c r="K125" s="17" t="inlineStr">
         <is>
-          <t>Type or formulation of acid system used for the remedial treatment, e.g., HCl, mud acid, or organic acid.</t>
+          <t>Well performance after cleanup expressed relative to the modeled/theoretical ideal PI or skin target.</t>
         </is>
       </c>
       <c r="L125" s="17" t="n"/>
@@ -6761,19 +6765,19 @@
           <t>Sand Body {id}</t>
         </is>
       </c>
-      <c r="C126" s="16" t="inlineStr">
-        <is>
-          <t>Pre-production and cleanup</t>
+      <c r="C126" s="17" t="inlineStr">
+        <is>
+          <t>Reservoir Characterization</t>
         </is>
       </c>
       <c r="D126" s="16" t="inlineStr">
         <is>
-          <t>Pre-production and cleanup details</t>
+          <t>Reservoir Rock and Fluid Properties</t>
         </is>
       </c>
       <c r="E126" s="17" t="inlineStr">
         <is>
-          <t>Percentage of ideal PI or skin achieved</t>
+          <t>Virgin Reservoir Pressure</t>
         </is>
       </c>
       <c r="F126" s="17" t="inlineStr">
@@ -6783,19 +6787,19 @@
       </c>
       <c r="G126" s="17" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>psi</t>
         </is>
       </c>
       <c r="H126" s="17" t="n"/>
       <c r="I126" s="17" t="n"/>
       <c r="J126" s="17" t="inlineStr">
         <is>
-          <t>{"Whole number"}</t>
+          <t>{"Decimal": {"min": 0}}</t>
         </is>
       </c>
       <c r="K126" s="17" t="inlineStr">
         <is>
-          <t>Well performance after cleanup expressed relative to the modeled/theoretical ideal PI or skin target.</t>
+          <t>Original reservoir pressure before depletion or production-induced pressure decline.</t>
         </is>
       </c>
       <c r="L126" s="17" t="n"/>
@@ -6822,7 +6826,7 @@
       </c>
       <c r="E127" s="17" t="inlineStr">
         <is>
-          <t>Virgin Reservoir Pressure</t>
+          <t>Reservoir Pressure at Time of Completion</t>
         </is>
       </c>
       <c r="F127" s="17" t="inlineStr">
@@ -6844,7 +6848,7 @@
       </c>
       <c r="K127" s="17" t="inlineStr">
         <is>
-          <t>Original reservoir pressure before depletion or production-induced pressure decline.</t>
+          <t>Estimated or measured reservoir pressure when the completion was installed.</t>
         </is>
       </c>
       <c r="L127" s="17" t="n"/>
@@ -6871,7 +6875,7 @@
       </c>
       <c r="E128" s="17" t="inlineStr">
         <is>
-          <t>Reservoir Pressure at Time of Completion</t>
+          <t>Reservoir pressure at first sand production</t>
         </is>
       </c>
       <c r="F128" s="17" t="inlineStr">
@@ -6893,7 +6897,7 @@
       </c>
       <c r="K128" s="17" t="inlineStr">
         <is>
-          <t>Estimated or measured reservoir pressure when the completion was installed.</t>
+          <t>Estimated or measured reservoir pressure when sand production was first observed.</t>
         </is>
       </c>
       <c r="L128" s="17" t="n"/>
@@ -6920,7 +6924,7 @@
       </c>
       <c r="E129" s="17" t="inlineStr">
         <is>
-          <t>Reservoir pressure at first sand production</t>
+          <t>Reservoir Temperature</t>
         </is>
       </c>
       <c r="F129" s="17" t="inlineStr">
@@ -6930,7 +6934,7 @@
       </c>
       <c r="G129" s="17" t="inlineStr">
         <is>
-          <t>psi</t>
+          <t>degF</t>
         </is>
       </c>
       <c r="H129" s="17" t="n"/>
@@ -6942,7 +6946,7 @@
       </c>
       <c r="K129" s="17" t="inlineStr">
         <is>
-          <t>Estimated or measured reservoir pressure when sand production was first observed.</t>
+          <t>Representative in-situ reservoir temperature for the completion interval.</t>
         </is>
       </c>
       <c r="L129" s="17" t="n"/>
@@ -6969,7 +6973,7 @@
       </c>
       <c r="E130" s="17" t="inlineStr">
         <is>
-          <t>Reservoir Temperature</t>
+          <t>Core Derived Min Rock UCS</t>
         </is>
       </c>
       <c r="F130" s="17" t="inlineStr">
@@ -6979,7 +6983,7 @@
       </c>
       <c r="G130" s="17" t="inlineStr">
         <is>
-          <t>degF</t>
+          <t>psi</t>
         </is>
       </c>
       <c r="H130" s="17" t="n"/>
@@ -6991,7 +6995,7 @@
       </c>
       <c r="K130" s="17" t="inlineStr">
         <is>
-          <t>Representative in-situ reservoir temperature for the completion interval.</t>
+          <t>Minimum laboratory-measured unconfined compressive strength (UCS) from representative core samples.</t>
         </is>
       </c>
       <c r="L130" s="17" t="n"/>
@@ -7018,7 +7022,7 @@
       </c>
       <c r="E131" s="17" t="inlineStr">
         <is>
-          <t>Core Derived Min Rock UCS</t>
+          <t>Core Derived P50 Rock UCS</t>
         </is>
       </c>
       <c r="F131" s="17" t="inlineStr">
@@ -7040,7 +7044,7 @@
       </c>
       <c r="K131" s="17" t="inlineStr">
         <is>
-          <t>Minimum laboratory-measured unconfined compressive strength (UCS) from representative core samples.</t>
+          <t>Median (50th percentile) laboratory-measured UCS of representative core samples.</t>
         </is>
       </c>
       <c r="L131" s="17" t="n"/>
@@ -7067,7 +7071,7 @@
       </c>
       <c r="E132" s="17" t="inlineStr">
         <is>
-          <t>Core Derived P50 Rock UCS</t>
+          <t>Shale Reactivity CEC</t>
         </is>
       </c>
       <c r="F132" s="17" t="inlineStr">
@@ -7075,11 +7079,7 @@
           <t>Number</t>
         </is>
       </c>
-      <c r="G132" s="17" t="inlineStr">
-        <is>
-          <t>psi</t>
-        </is>
-      </c>
+      <c r="G132" s="17" t="n"/>
       <c r="H132" s="17" t="n"/>
       <c r="I132" s="17" t="n"/>
       <c r="J132" s="17" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="K132" s="17" t="inlineStr">
         <is>
-          <t>Median (50th percentile) laboratory-measured UCS of representative core samples.</t>
+          <t>Cation exchange capacity (CEC) used as an indicator of clay/shale reactivity, typically reported in meq/100 g.</t>
         </is>
       </c>
       <c r="L132" s="17" t="n"/>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="E133" s="17" t="inlineStr">
         <is>
-          <t>Shale Reactivity CEC</t>
+          <t>Rock compressibility at initial reservoir pressure</t>
         </is>
       </c>
       <c r="F133" s="17" t="inlineStr">
@@ -7124,7 +7124,11 @@
           <t>Number</t>
         </is>
       </c>
-      <c r="G133" s="17" t="n"/>
+      <c r="G133" s="17" t="inlineStr">
+        <is>
+          <t>microsips</t>
+        </is>
+      </c>
       <c r="H133" s="17" t="n"/>
       <c r="I133" s="17" t="n"/>
       <c r="J133" s="17" t="inlineStr">
@@ -7134,7 +7138,7 @@
       </c>
       <c r="K133" s="17" t="inlineStr">
         <is>
-          <t>Cation exchange capacity (CEC) used as an indicator of clay/shale reactivity, typically reported in meq/100 g.</t>
+          <t>Rock/pore-volume compressibility evaluated at initial reservoir pressure.</t>
         </is>
       </c>
       <c r="L133" s="17" t="n"/>
@@ -7161,7 +7165,7 @@
       </c>
       <c r="E134" s="17" t="inlineStr">
         <is>
-          <t>Rock compressibility at initial reservoir pressure</t>
+          <t>Rock compressibility at first sand production</t>
         </is>
       </c>
       <c r="F134" s="17" t="inlineStr">
@@ -7183,7 +7187,7 @@
       </c>
       <c r="K134" s="17" t="inlineStr">
         <is>
-          <t>Rock/pore-volume compressibility evaluated at initial reservoir pressure.</t>
+          <t>Rock/pore-volume compressibility evaluated at reservoir pressure corresponding to first observed sand production.</t>
         </is>
       </c>
       <c r="L134" s="17" t="n"/>
@@ -7210,29 +7214,25 @@
       </c>
       <c r="E135" s="17" t="inlineStr">
         <is>
-          <t>Rock compressibility at first sand production</t>
+          <t>Source of sand sample</t>
         </is>
       </c>
       <c r="F135" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="G135" s="17" t="inlineStr">
-        <is>
-          <t>microsips</t>
-        </is>
-      </c>
+          <t>Dropdown Menu</t>
+        </is>
+      </c>
+      <c r="G135" s="17" t="n"/>
       <c r="H135" s="17" t="n"/>
       <c r="I135" s="17" t="n"/>
       <c r="J135" s="17" t="inlineStr">
         <is>
-          <t>{"Decimal": {"min": 0}}</t>
+          <t>{"List": {"options": ["cores", "bottom-hole sand sample", "surface sample", "analog well"]}}</t>
         </is>
       </c>
       <c r="K135" s="17" t="inlineStr">
         <is>
-          <t>Rock/pore-volume compressibility evaluated at reservoir pressure corresponding to first observed sand production.</t>
+          <t>Origin of the sample used for formation-sand characterization, e.g., core, produced sand, sidewall core, or cuttings.</t>
         </is>
       </c>
       <c r="L135" s="17" t="n"/>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="E136" s="17" t="inlineStr">
         <is>
-          <t>Source of sand sample</t>
+          <t>PSD Measurement Method</t>
         </is>
       </c>
       <c r="F136" s="17" t="inlineStr">
@@ -7272,12 +7272,12 @@
       <c r="I136" s="17" t="n"/>
       <c r="J136" s="17" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["cores", "bottom-hole sand sample", "surface sample", "analog well"]}}</t>
+          <t>{"List": {"options": ["LPSA", "Sieve"]}}</t>
         </is>
       </c>
       <c r="K136" s="17" t="inlineStr">
         <is>
-          <t>Origin of the sample used for formation-sand characterization, e.g., core, produced sand, sidewall core, or cuttings.</t>
+          <t>Laboratory or analytical technique used to determine formation-sand particle-size distribution.</t>
         </is>
       </c>
       <c r="L136" s="17" t="n"/>
@@ -7304,25 +7304,29 @@
       </c>
       <c r="E137" s="17" t="inlineStr">
         <is>
-          <t>PSD Measurement Method</t>
+          <t>PSD D10/D25/D40/D50/D75/D90</t>
         </is>
       </c>
       <c r="F137" s="17" t="inlineStr">
         <is>
-          <t>Dropdown Menu</t>
-        </is>
-      </c>
-      <c r="G137" s="17" t="n"/>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="G137" s="17" t="inlineStr">
+        <is>
+          <t>micron</t>
+        </is>
+      </c>
       <c r="H137" s="17" t="n"/>
       <c r="I137" s="17" t="n"/>
       <c r="J137" s="17" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["LPSA", "Sieve"]}}</t>
+          <t>{["Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}]}</t>
         </is>
       </c>
       <c r="K137" s="17" t="inlineStr">
         <is>
-          <t>Laboratory or analytical technique used to determine formation-sand particle-size distribution.</t>
+          <t>Particle diameters corresponding to specified cumulative percentiles of the formation-sand size distribution.</t>
         </is>
       </c>
       <c r="L137" s="17" t="n"/>
@@ -7349,29 +7353,29 @@
       </c>
       <c r="E138" s="17" t="inlineStr">
         <is>
-          <t>PSD D10/D25/D40/D50/D75/D90</t>
+          <t>Fines Content (Sub 44 microns)</t>
         </is>
       </c>
       <c r="F138" s="17" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="G138" s="17" t="inlineStr">
         <is>
-          <t>micron</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H138" s="17" t="n"/>
       <c r="I138" s="17" t="n"/>
       <c r="J138" s="17" t="inlineStr">
         <is>
-          <t>{["Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}, "Decimal": {"min": 0}]}</t>
+          <t>{"Decimal": {"min": 0}}</t>
         </is>
       </c>
       <c r="K138" s="17" t="inlineStr">
         <is>
-          <t>Particle diameters corresponding to specified cumulative percentiles of the formation-sand size distribution.</t>
+          <t>Fraction of formation particles below the defined fines-size threshold; record the threshold/method where available.</t>
         </is>
       </c>
       <c r="L138" s="17" t="n"/>
@@ -7398,7 +7402,7 @@
       </c>
       <c r="E139" s="17" t="inlineStr">
         <is>
-          <t>Fines Content (Sub 44 microns)</t>
+          <t>Initial PI</t>
         </is>
       </c>
       <c r="F139" s="17" t="inlineStr">
@@ -7408,7 +7412,7 @@
       </c>
       <c r="G139" s="17" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>stb/d/psi or mmscf/d/psi</t>
         </is>
       </c>
       <c r="H139" s="17" t="n"/>
@@ -7420,7 +7424,7 @@
       </c>
       <c r="K139" s="17" t="inlineStr">
         <is>
-          <t>Fraction of formation particles below the defined fines-size threshold; record the threshold/method where available.</t>
+          <t>Initial productivity index attributed to this completion/reservoir interval.</t>
         </is>
       </c>
       <c r="L139" s="17" t="n"/>
@@ -7447,7 +7451,7 @@
       </c>
       <c r="E140" s="17" t="inlineStr">
         <is>
-          <t>Initial PI</t>
+          <t>Porosity</t>
         </is>
       </c>
       <c r="F140" s="17" t="inlineStr">
@@ -7457,7 +7461,7 @@
       </c>
       <c r="G140" s="17" t="inlineStr">
         <is>
-          <t>stb/d/psi or mmscf/d/psi</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H140" s="17" t="n"/>
@@ -7469,7 +7473,7 @@
       </c>
       <c r="K140" s="17" t="inlineStr">
         <is>
-          <t>Initial productivity index attributed to this completion/reservoir interval.</t>
+          <t>Representative effective or total porosity of the reservoir interval, as specified by the source.</t>
         </is>
       </c>
       <c r="L140" s="17" t="n"/>
@@ -7496,7 +7500,7 @@
       </c>
       <c r="E141" s="17" t="inlineStr">
         <is>
-          <t>Porosity</t>
+          <t>Permeability</t>
         </is>
       </c>
       <c r="F141" s="17" t="inlineStr">
@@ -7506,7 +7510,7 @@
       </c>
       <c r="G141" s="17" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H141" s="17" t="n"/>
@@ -7518,7 +7522,7 @@
       </c>
       <c r="K141" s="17" t="inlineStr">
         <is>
-          <t>Representative effective or total porosity of the reservoir interval, as specified by the source.</t>
+          <t>Representative formation permeability of the reservoir interval.</t>
         </is>
       </c>
       <c r="L141" s="17" t="n"/>
@@ -7545,7 +7549,7 @@
       </c>
       <c r="E142" s="17" t="inlineStr">
         <is>
-          <t>Permeability</t>
+          <t>k.h from PTA</t>
         </is>
       </c>
       <c r="F142" s="17" t="inlineStr">
@@ -7555,7 +7559,7 @@
       </c>
       <c r="G142" s="17" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>md-ft</t>
         </is>
       </c>
       <c r="H142" s="17" t="n"/>
@@ -7567,7 +7571,7 @@
       </c>
       <c r="K142" s="17" t="inlineStr">
         <is>
-          <t>Representative formation permeability of the reservoir interval.</t>
+          <t>Permeability-thickness product derived from pressure transient analysis (PTA).</t>
         </is>
       </c>
       <c r="L142" s="17" t="n"/>
@@ -7594,7 +7598,7 @@
       </c>
       <c r="E143" s="17" t="inlineStr">
         <is>
-          <t>k.h from PTA</t>
+          <t>k.h from Log</t>
         </is>
       </c>
       <c r="F143" s="17" t="inlineStr">
@@ -7616,7 +7620,7 @@
       </c>
       <c r="K143" s="17" t="inlineStr">
         <is>
-          <t>Permeability-thickness product derived from pressure transient analysis (PTA).</t>
+          <t>Permeability-thickness product estimated from petrophysical/log interpretation.</t>
         </is>
       </c>
       <c r="L143" s="17" t="n"/>
@@ -7643,7 +7647,7 @@
       </c>
       <c r="E144" s="17" t="inlineStr">
         <is>
-          <t>k.h from Log</t>
+          <t>Initial Total Skin from PTA</t>
         </is>
       </c>
       <c r="F144" s="17" t="inlineStr">
@@ -7651,21 +7655,17 @@
           <t>Number</t>
         </is>
       </c>
-      <c r="G144" s="17" t="inlineStr">
-        <is>
-          <t>md-ft</t>
-        </is>
-      </c>
+      <c r="G144" s="17" t="n"/>
       <c r="H144" s="17" t="n"/>
       <c r="I144" s="17" t="n"/>
       <c r="J144" s="17" t="inlineStr">
         <is>
-          <t>{"Decimal": {"min": 0}}</t>
+          <t>{"Whole number"}</t>
         </is>
       </c>
       <c r="K144" s="17" t="inlineStr">
         <is>
-          <t>Permeability-thickness product estimated from petrophysical/log interpretation.</t>
+          <t>Initial total skin factor derived from pressure transient analysis.</t>
         </is>
       </c>
       <c r="L144" s="17" t="n"/>
@@ -7692,12 +7692,12 @@
       </c>
       <c r="E145" s="17" t="inlineStr">
         <is>
-          <t>Initial Total Skin from PTA</t>
+          <t>Fluid Type</t>
         </is>
       </c>
       <c r="F145" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Dropdown Menu</t>
         </is>
       </c>
       <c r="G145" s="17" t="n"/>
@@ -7705,12 +7705,12 @@
       <c r="I145" s="17" t="n"/>
       <c r="J145" s="17" t="inlineStr">
         <is>
-          <t>{"Whole number"}</t>
+          <t>{"List": {"options": ["Oil", "Condensate", "Wet Gas", "Dry Gas"]}}</t>
         </is>
       </c>
       <c r="K145" s="17" t="inlineStr">
         <is>
-          <t>Initial total skin factor derived from pressure transient analysis.</t>
+          <t>Primary reservoir/producing fluid type for the completion interval.</t>
         </is>
       </c>
       <c r="L145" s="17" t="n"/>
@@ -7737,12 +7737,12 @@
       </c>
       <c r="E146" s="17" t="inlineStr">
         <is>
-          <t>Fluid Type</t>
+          <t>Oil Formation Volume Factor (Bo) at downhole conditions</t>
         </is>
       </c>
       <c r="F146" s="17" t="inlineStr">
         <is>
-          <t>Dropdown Menu</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="G146" s="17" t="n"/>
@@ -7750,12 +7750,12 @@
       <c r="I146" s="17" t="n"/>
       <c r="J146" s="17" t="inlineStr">
         <is>
-          <t>{"List": {"options": ["Oil", "Condensate", "Wet Gas", "Dry Gas"]}}</t>
+          <t>{"Decimal": {"min": 0}}</t>
         </is>
       </c>
       <c r="K146" s="17" t="inlineStr">
         <is>
-          <t>Primary reservoir/producing fluid type for the completion interval.</t>
+          <t>Reservoir oil volume per unit stock-tank oil volume at the specified downhole pressure and temperature.</t>
         </is>
       </c>
       <c r="L146" s="17" t="n"/>
@@ -7782,7 +7782,7 @@
       </c>
       <c r="E147" s="17" t="inlineStr">
         <is>
-          <t>Oil Formation Volume Factor (Bo) at downhole conditions</t>
+          <t>Producing Fluid Viscosity</t>
         </is>
       </c>
       <c r="F147" s="17" t="inlineStr">
@@ -7790,7 +7790,11 @@
           <t>Number</t>
         </is>
       </c>
-      <c r="G147" s="17" t="n"/>
+      <c r="G147" s="17" t="inlineStr">
+        <is>
+          <t>cP</t>
+        </is>
+      </c>
       <c r="H147" s="17" t="n"/>
       <c r="I147" s="17" t="n"/>
       <c r="J147" s="17" t="inlineStr">
@@ -7800,7 +7804,7 @@
       </c>
       <c r="K147" s="17" t="inlineStr">
         <is>
-          <t>Reservoir oil volume per unit stock-tank oil volume at the specified downhole pressure and temperature.</t>
+          <t>Dynamic viscosity of the primary producing fluid at the specified reservoir/downhole conditions.</t>
         </is>
       </c>
       <c r="L147" s="17" t="n"/>
@@ -7827,7 +7831,7 @@
       </c>
       <c r="E148" s="17" t="inlineStr">
         <is>
-          <t>Producing Fluid Viscosity</t>
+          <t>Oil Bubble Point (Pb)</t>
         </is>
       </c>
       <c r="F148" s="17" t="inlineStr">
@@ -7837,7 +7841,7 @@
       </c>
       <c r="G148" s="17" t="inlineStr">
         <is>
-          <t>cP</t>
+          <t>psi</t>
         </is>
       </c>
       <c r="H148" s="17" t="n"/>
@@ -7849,7 +7853,7 @@
       </c>
       <c r="K148" s="17" t="inlineStr">
         <is>
-          <t>Dynamic viscosity of the primary producing fluid at the specified reservoir/downhole conditions.</t>
+          <t>Pressure at which the first gas evolves from reservoir oil at the specified reservoir temperature.</t>
         </is>
       </c>
       <c r="L148" s="17" t="n"/>
@@ -7876,7 +7880,7 @@
       </c>
       <c r="E149" s="17" t="inlineStr">
         <is>
-          <t>Oil Bubble Point (Pb)</t>
+          <t>Solution Gas Ratio (Rs)</t>
         </is>
       </c>
       <c r="F149" s="17" t="inlineStr">
@@ -7886,7 +7890,7 @@
       </c>
       <c r="G149" s="17" t="inlineStr">
         <is>
-          <t>psi</t>
+          <t>scf/stb</t>
         </is>
       </c>
       <c r="H149" s="17" t="n"/>
@@ -7898,7 +7902,7 @@
       </c>
       <c r="K149" s="17" t="inlineStr">
         <is>
-          <t>Pressure at which the first gas evolves from reservoir oil at the specified reservoir temperature.</t>
+          <t>Volume of gas dissolved in oil at the specified pressure and temperature, typically reported as scf/STB.</t>
         </is>
       </c>
       <c r="L149" s="17" t="n"/>
@@ -7925,7 +7929,7 @@
       </c>
       <c r="E150" s="17" t="inlineStr">
         <is>
-          <t>Solution Gas Ratio (Rs)</t>
+          <t>Frac gradient</t>
         </is>
       </c>
       <c r="F150" s="17" t="inlineStr">
@@ -7935,7 +7939,7 @@
       </c>
       <c r="G150" s="17" t="inlineStr">
         <is>
-          <t>scf/stb</t>
+          <t>ppg</t>
         </is>
       </c>
       <c r="H150" s="17" t="n"/>
@@ -7947,60 +7951,11 @@
       </c>
       <c r="K150" s="17" t="inlineStr">
         <is>
-          <t>Volume of gas dissolved in oil at the specified pressure and temperature, typically reported as scf/STB.</t>
+          <t>Formation fracture-pressure gradient at the applicable reservoir depth, typically expressed in psi/ft or equivalent units.</t>
         </is>
       </c>
       <c r="L150" s="17" t="n"/>
       <c r="M150" s="1" t="n"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="24" t="n">
-        <v>150</v>
-      </c>
-      <c r="B151" s="17" t="inlineStr">
-        <is>
-          <t>Sand Body {id}</t>
-        </is>
-      </c>
-      <c r="C151" s="17" t="inlineStr">
-        <is>
-          <t>Reservoir Characterization</t>
-        </is>
-      </c>
-      <c r="D151" s="16" t="inlineStr">
-        <is>
-          <t>Reservoir Rock and Fluid Properties</t>
-        </is>
-      </c>
-      <c r="E151" s="17" t="inlineStr">
-        <is>
-          <t>Frac gradient</t>
-        </is>
-      </c>
-      <c r="F151" s="17" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="G151" s="17" t="inlineStr">
-        <is>
-          <t>ppg</t>
-        </is>
-      </c>
-      <c r="H151" s="17" t="n"/>
-      <c r="I151" s="17" t="n"/>
-      <c r="J151" s="17" t="inlineStr">
-        <is>
-          <t>{"Decimal": {"min": 0}}</t>
-        </is>
-      </c>
-      <c r="K151" s="17" t="inlineStr">
-        <is>
-          <t>Formation fracture-pressure gradient at the applicable reservoir depth, typically expressed in psi/ft or equivalent units.</t>
-        </is>
-      </c>
-      <c r="L151" s="17" t="n"/>
-      <c r="M151" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
